--- a/artfynd/A 43282-2024 artfynd.xlsx
+++ b/artfynd/A 43282-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120287688</v>
+        <v>120289010</v>
       </c>
       <c r="B2" t="n">
-        <v>91863</v>
+        <v>91901</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -722,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615158</v>
+        <v>614953</v>
       </c>
       <c r="R2" t="n">
-        <v>6560470</v>
+        <v>6560281</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120289009</v>
+        <v>120289011</v>
       </c>
       <c r="B3" t="n">
-        <v>91863</v>
+        <v>91902</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,26 +810,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614895</v>
+        <v>614893</v>
       </c>
       <c r="R3" t="n">
-        <v>6560342</v>
+        <v>6560392</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120289011</v>
+        <v>120287703</v>
       </c>
       <c r="B4" t="n">
-        <v>91884</v>
+        <v>91881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,26 +929,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614893</v>
+        <v>614993</v>
       </c>
       <c r="R4" t="n">
-        <v>6560392</v>
+        <v>6560284</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120289010</v>
+        <v>120289009</v>
       </c>
       <c r="B5" t="n">
-        <v>91883</v>
+        <v>91881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,26 +1048,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614953</v>
+        <v>614895</v>
       </c>
       <c r="R5" t="n">
-        <v>6560281</v>
+        <v>6560342</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120287703</v>
+        <v>120287688</v>
       </c>
       <c r="B6" t="n">
-        <v>91863</v>
+        <v>91881</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1198,13 +1198,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>614993</v>
+        <v>615158</v>
       </c>
       <c r="R6" t="n">
-        <v>6560284</v>
+        <v>6560470</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 43282-2024 artfynd.xlsx
+++ b/artfynd/A 43282-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120289010</v>
+        <v>120287688</v>
       </c>
       <c r="B2" t="n">
-        <v>91901</v>
+        <v>91881</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -722,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614953</v>
+        <v>615158</v>
       </c>
       <c r="R2" t="n">
-        <v>6560281</v>
+        <v>6560470</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -913,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120287703</v>
+        <v>120289009</v>
       </c>
       <c r="B4" t="n">
         <v>91881</v>
@@ -948,7 +948,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614993</v>
+        <v>614895</v>
       </c>
       <c r="R4" t="n">
-        <v>6560284</v>
+        <v>6560342</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,7 +1032,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120289009</v>
+        <v>120287703</v>
       </c>
       <c r="B5" t="n">
         <v>91881</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614895</v>
+        <v>614993</v>
       </c>
       <c r="R5" t="n">
-        <v>6560342</v>
+        <v>6560284</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120287688</v>
+        <v>120289010</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>91901</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,26 +1167,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1198,13 +1198,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615158</v>
+        <v>614953</v>
       </c>
       <c r="R6" t="n">
-        <v>6560470</v>
+        <v>6560281</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 43282-2024 artfynd.xlsx
+++ b/artfynd/A 43282-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120287688</v>
+        <v>120289010</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>91901</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -722,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615158</v>
+        <v>614953</v>
       </c>
       <c r="R2" t="n">
-        <v>6560470</v>
+        <v>6560281</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120289011</v>
+        <v>120289009</v>
       </c>
       <c r="B3" t="n">
-        <v>91902</v>
+        <v>91881</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,26 +810,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614893</v>
+        <v>614895</v>
       </c>
       <c r="R3" t="n">
-        <v>6560392</v>
+        <v>6560342</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120289009</v>
+        <v>120287688</v>
       </c>
       <c r="B4" t="n">
         <v>91881</v>
@@ -948,7 +948,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614895</v>
+        <v>615158</v>
       </c>
       <c r="R4" t="n">
-        <v>6560342</v>
+        <v>6560470</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120287703</v>
+        <v>120289011</v>
       </c>
       <c r="B5" t="n">
-        <v>91881</v>
+        <v>91902</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,26 +1048,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614993</v>
+        <v>614893</v>
       </c>
       <c r="R5" t="n">
-        <v>6560284</v>
+        <v>6560392</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120289010</v>
+        <v>120287703</v>
       </c>
       <c r="B6" t="n">
-        <v>91901</v>
+        <v>91881</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,26 +1167,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>614953</v>
+        <v>614993</v>
       </c>
       <c r="R6" t="n">
-        <v>6560281</v>
+        <v>6560284</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 43282-2024 artfynd.xlsx
+++ b/artfynd/A 43282-2024 artfynd.xlsx
@@ -787,14 +787,14 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
+          <t>Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120289009</v>
+        <v>120287703</v>
       </c>
       <c r="B3" t="n">
         <v>91881</v>
@@ -829,7 +829,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614895</v>
+        <v>614993</v>
       </c>
       <c r="R3" t="n">
-        <v>6560342</v>
+        <v>6560284</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120287688</v>
+        <v>120289009</v>
       </c>
       <c r="B4" t="n">
         <v>91881</v>
@@ -948,7 +948,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615158</v>
+        <v>614895</v>
       </c>
       <c r="R4" t="n">
-        <v>6560470</v>
+        <v>6560342</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
+          <t>Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1144,14 +1144,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
+          <t>Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120287703</v>
+        <v>120287688</v>
       </c>
       <c r="B6" t="n">
         <v>91881</v>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1198,13 +1198,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>614993</v>
+        <v>615158</v>
       </c>
       <c r="R6" t="n">
-        <v>6560284</v>
+        <v>6560470</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 43282-2024 artfynd.xlsx
+++ b/artfynd/A 43282-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120289010</v>
+        <v>120287703</v>
       </c>
       <c r="B2" t="n">
-        <v>91901</v>
+        <v>91881</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614953</v>
+        <v>614993</v>
       </c>
       <c r="R2" t="n">
-        <v>6560281</v>
+        <v>6560284</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,17 +787,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120287703</v>
+        <v>120289010</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
+        <v>91901</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,26 +810,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614993</v>
+        <v>614953</v>
       </c>
       <c r="R3" t="n">
-        <v>6560284</v>
+        <v>6560281</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120289009</v>
+        <v>120289011</v>
       </c>
       <c r="B4" t="n">
-        <v>91881</v>
+        <v>91902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,26 +929,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614895</v>
+        <v>614893</v>
       </c>
       <c r="R4" t="n">
-        <v>6560342</v>
+        <v>6560392</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,17 +1025,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120289011</v>
+        <v>120287688</v>
       </c>
       <c r="B5" t="n">
-        <v>91902</v>
+        <v>91881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1079,13 +1079,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614893</v>
+        <v>615158</v>
       </c>
       <c r="R5" t="n">
-        <v>6560392</v>
+        <v>6560470</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,14 +1144,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120287688</v>
+        <v>120289009</v>
       </c>
       <c r="B6" t="n">
         <v>91881</v>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1198,13 +1198,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615158</v>
+        <v>614895</v>
       </c>
       <c r="R6" t="n">
-        <v>6560470</v>
+        <v>6560342</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 43282-2024 artfynd.xlsx
+++ b/artfynd/A 43282-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120287703</v>
+        <v>120289010</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>91901</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614993</v>
+        <v>614953</v>
       </c>
       <c r="R2" t="n">
-        <v>6560284</v>
+        <v>6560281</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120289010</v>
+        <v>120287703</v>
       </c>
       <c r="B3" t="n">
-        <v>91901</v>
+        <v>91881</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,26 +810,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614953</v>
+        <v>614993</v>
       </c>
       <c r="R3" t="n">
-        <v>6560281</v>
+        <v>6560284</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120289011</v>
+        <v>120287688</v>
       </c>
       <c r="B4" t="n">
-        <v>91902</v>
+        <v>91881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614893</v>
+        <v>615158</v>
       </c>
       <c r="R4" t="n">
-        <v>6560392</v>
+        <v>6560470</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120287688</v>
+        <v>120289011</v>
       </c>
       <c r="B5" t="n">
-        <v>91881</v>
+        <v>91902</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1079,13 +1079,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>615158</v>
+        <v>614893</v>
       </c>
       <c r="R5" t="n">
-        <v>6560470</v>
+        <v>6560392</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 43282-2024 artfynd.xlsx
+++ b/artfynd/A 43282-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120287703</v>
+        <v>120287688</v>
       </c>
       <c r="B3" t="n">
         <v>91881</v>
@@ -829,7 +829,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614993</v>
+        <v>615158</v>
       </c>
       <c r="R3" t="n">
-        <v>6560284</v>
+        <v>6560470</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120287688</v>
+        <v>120289011</v>
       </c>
       <c r="B4" t="n">
-        <v>91881</v>
+        <v>91902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615158</v>
+        <v>614893</v>
       </c>
       <c r="R4" t="n">
-        <v>6560470</v>
+        <v>6560392</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120289011</v>
+        <v>120287703</v>
       </c>
       <c r="B5" t="n">
-        <v>91902</v>
+        <v>91881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,26 +1048,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614893</v>
+        <v>614993</v>
       </c>
       <c r="R5" t="n">
-        <v>6560392</v>
+        <v>6560284</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 43282-2024 artfynd.xlsx
+++ b/artfynd/A 43282-2024 artfynd.xlsx
@@ -1959,10 +1959,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131738982</v>
+        <v>131737610</v>
       </c>
       <c r="B13" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>614776</v>
+        <v>614730</v>
       </c>
       <c r="R13" t="n">
-        <v>6560497</v>
+        <v>6560494</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131739018</v>
+        <v>131737744</v>
       </c>
       <c r="B14" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2071,34 +2071,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615028</v>
+        <v>614738</v>
       </c>
       <c r="R14" t="n">
-        <v>6560422</v>
+        <v>6560381</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,6 +2135,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,7 +2170,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131737744</v>
+        <v>131737716</v>
       </c>
       <c r="B15" t="n">
         <v>93154</v>
@@ -2191,19 +2200,19 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>614738</v>
+        <v>614917</v>
       </c>
       <c r="R15" t="n">
-        <v>6560381</v>
+        <v>6560491</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2240,7 +2249,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,7 +2280,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131737716</v>
+        <v>131737729</v>
       </c>
       <c r="B16" t="n">
         <v>93154</v>
@@ -2299,21 +2308,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>614917</v>
+        <v>614639</v>
       </c>
       <c r="R16" t="n">
-        <v>6560491</v>
+        <v>6560401</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,11 +2351,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2381,10 +2381,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131737729</v>
+        <v>131738982</v>
       </c>
       <c r="B17" t="n">
-        <v>93154</v>
+        <v>79879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2392,34 +2392,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>614639</v>
+        <v>614776</v>
       </c>
       <c r="R17" t="n">
-        <v>6560401</v>
+        <v>6560497</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2482,10 +2482,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131737610</v>
+        <v>131739018</v>
       </c>
       <c r="B18" t="n">
-        <v>93154</v>
+        <v>79879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2493,34 +2493,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>614730</v>
+        <v>615028</v>
       </c>
       <c r="R18" t="n">
-        <v>6560494</v>
+        <v>6560422</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3001,45 +3001,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131736022</v>
+        <v>131737603</v>
       </c>
       <c r="B23" t="n">
-        <v>92267</v>
+        <v>93154</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5420</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>614774</v>
+        <v>615176</v>
       </c>
       <c r="R23" t="n">
-        <v>6560503</v>
+        <v>6560478</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3066,12 +3066,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3212,7 +3212,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131737603</v>
+        <v>131737708</v>
       </c>
       <c r="B25" t="n">
         <v>93154</v>
@@ -3240,17 +3240,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615176</v>
+        <v>614945</v>
       </c>
       <c r="R25" t="n">
-        <v>6560478</v>
+        <v>6560420</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3277,12 +3281,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3313,7 +3322,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131737708</v>
+        <v>131737704</v>
       </c>
       <c r="B26" t="n">
         <v>93154</v>
@@ -3343,7 +3352,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3352,10 +3361,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>614945</v>
+        <v>615034</v>
       </c>
       <c r="R26" t="n">
-        <v>6560420</v>
+        <v>6560411</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3392,7 +3401,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3423,49 +3432,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131737704</v>
+        <v>131736022</v>
       </c>
       <c r="B27" t="n">
-        <v>93154</v>
+        <v>92267</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>615034</v>
+        <v>614774</v>
       </c>
       <c r="R27" t="n">
-        <v>6560411</v>
+        <v>6560503</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3498,11 +3503,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3533,10 +3533,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131740362</v>
+        <v>131737762</v>
       </c>
       <c r="B28" t="n">
-        <v>93145</v>
+        <v>93154</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3544,34 +3544,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>614974</v>
+        <v>614855</v>
       </c>
       <c r="R28" t="n">
-        <v>6560411</v>
+        <v>6560397</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3608,7 +3612,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3617,7 +3621,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3640,10 +3643,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131738985</v>
+        <v>131737779</v>
       </c>
       <c r="B29" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3651,34 +3654,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>614827</v>
+        <v>615173</v>
       </c>
       <c r="R29" t="n">
-        <v>6560518</v>
+        <v>6560476</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3705,12 +3712,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3741,10 +3753,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131739020</v>
+        <v>131737781</v>
       </c>
       <c r="B30" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3752,34 +3764,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>614839</v>
+        <v>615158</v>
       </c>
       <c r="R30" t="n">
-        <v>6560502</v>
+        <v>6560491</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3812,6 +3828,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3842,7 +3863,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131737762</v>
+        <v>131737746</v>
       </c>
       <c r="B31" t="n">
         <v>93154</v>
@@ -3877,14 +3898,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>614855</v>
+        <v>614777</v>
       </c>
       <c r="R31" t="n">
-        <v>6560397</v>
+        <v>6560432</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3952,7 +3973,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131737779</v>
+        <v>131737765</v>
       </c>
       <c r="B32" t="n">
         <v>93154</v>
@@ -3982,19 +4003,19 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615173</v>
+        <v>614814</v>
       </c>
       <c r="R32" t="n">
-        <v>6560476</v>
+        <v>6560371</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4031,7 +4052,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4062,10 +4083,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737781</v>
+        <v>131738985</v>
       </c>
       <c r="B33" t="n">
-        <v>93154</v>
+        <v>79879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4073,38 +4094,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>615158</v>
+        <v>614827</v>
       </c>
       <c r="R33" t="n">
-        <v>6560491</v>
+        <v>6560518</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4131,17 +4148,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4172,10 +4184,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131737746</v>
+        <v>131739020</v>
       </c>
       <c r="B34" t="n">
-        <v>93154</v>
+        <v>79879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,38 +4195,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>614777</v>
+        <v>614839</v>
       </c>
       <c r="R34" t="n">
-        <v>6560432</v>
+        <v>6560502</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4247,11 +4255,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4282,10 +4285,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131737750</v>
+        <v>131740362</v>
       </c>
       <c r="B35" t="n">
-        <v>93154</v>
+        <v>93145</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4293,38 +4296,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>614846</v>
+        <v>614974</v>
       </c>
       <c r="R35" t="n">
-        <v>6560435</v>
+        <v>6560411</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4361,7 +4360,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4370,6 +4369,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131737765</v>
+        <v>131737750</v>
       </c>
       <c r="B36" t="n">
         <v>93154</v>
@@ -4427,14 +4427,14 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>614814</v>
+        <v>614846</v>
       </c>
       <c r="R36" t="n">
-        <v>6560371</v>
+        <v>6560435</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4502,45 +4502,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131740334</v>
+        <v>131736787</v>
       </c>
       <c r="B37" t="n">
-        <v>93142</v>
+        <v>92200</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5448</v>
+        <v>2062</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>614945</v>
+        <v>614622</v>
       </c>
       <c r="R37" t="n">
-        <v>6560495</v>
+        <v>6560528</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4567,12 +4567,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4603,10 +4603,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131738986</v>
+        <v>131736576</v>
       </c>
       <c r="B38" t="n">
-        <v>79879</v>
+        <v>93132</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4614,34 +4614,38 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>614832</v>
+        <v>614640</v>
       </c>
       <c r="R38" t="n">
-        <v>6560556</v>
+        <v>6560409</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4668,12 +4672,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>9 st</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4704,7 +4713,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131739037</v>
+        <v>131738986</v>
       </c>
       <c r="B39" t="n">
         <v>79879</v>
@@ -4735,14 +4744,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>615086</v>
+        <v>614832</v>
       </c>
       <c r="R39" t="n">
-        <v>6560375</v>
+        <v>6560556</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4769,12 +4778,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4805,10 +4814,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131739024</v>
+        <v>131740334</v>
       </c>
       <c r="B40" t="n">
-        <v>79879</v>
+        <v>93142</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4816,21 +4825,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>5448</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4840,10 +4849,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>614774</v>
+        <v>614945</v>
       </c>
       <c r="R40" t="n">
-        <v>6560505</v>
+        <v>6560495</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5218,45 +5227,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131736787</v>
+        <v>131739037</v>
       </c>
       <c r="B44" t="n">
-        <v>92200</v>
+        <v>79879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2062</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>614622</v>
+        <v>615086</v>
       </c>
       <c r="R44" t="n">
-        <v>6560528</v>
+        <v>6560375</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5283,12 +5292,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5319,10 +5328,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131736576</v>
+        <v>131739024</v>
       </c>
       <c r="B45" t="n">
-        <v>93132</v>
+        <v>79879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5330,38 +5339,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>614640</v>
+        <v>614774</v>
       </c>
       <c r="R45" t="n">
-        <v>6560409</v>
+        <v>6560505</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5388,17 +5393,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>9 st</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6050,7 +6050,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131737728</v>
+        <v>131737608</v>
       </c>
       <c r="B52" t="n">
         <v>93154</v>
@@ -6078,21 +6078,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>614659</v>
+        <v>614654</v>
       </c>
       <c r="R52" t="n">
-        <v>6560444</v>
+        <v>6560489</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6119,17 +6115,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6160,7 +6151,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131737608</v>
+        <v>131737728</v>
       </c>
       <c r="B53" t="n">
         <v>93154</v>
@@ -6188,17 +6179,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>614654</v>
+        <v>614659</v>
       </c>
       <c r="R53" t="n">
-        <v>6560489</v>
+        <v>6560444</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6225,12 +6220,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6591,49 +6591,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131737712</v>
+        <v>131736812</v>
       </c>
       <c r="B57" t="n">
-        <v>93154</v>
+        <v>93128</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>614922</v>
+        <v>614856</v>
       </c>
       <c r="R57" t="n">
-        <v>6560461</v>
+        <v>6560514</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6660,17 +6656,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6811,45 +6802,49 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131736812</v>
+        <v>131737712</v>
       </c>
       <c r="B59" t="n">
-        <v>93128</v>
+        <v>93154</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>614856</v>
+        <v>614922</v>
       </c>
       <c r="R59" t="n">
-        <v>6560514</v>
+        <v>6560461</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6876,12 +6871,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6912,45 +6912,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131734255</v>
+        <v>131740397</v>
       </c>
       <c r="B60" t="n">
-        <v>97365</v>
+        <v>93145</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>990</v>
+        <v>5449</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Warnst.) R.M.Schust.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>614670</v>
+        <v>614907</v>
       </c>
       <c r="R60" t="n">
-        <v>6560435</v>
+        <v>6560338</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6977,12 +6977,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>5 st</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6991,6 +6996,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7013,45 +7019,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131740397</v>
+        <v>131734255</v>
       </c>
       <c r="B61" t="n">
-        <v>93145</v>
+        <v>97365</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5449</v>
+        <v>990</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Lophozia ascendens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Warnst.) R.M.Schust.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>614907</v>
+        <v>614670</v>
       </c>
       <c r="R61" t="n">
-        <v>6560338</v>
+        <v>6560435</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7078,17 +7084,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>5 st</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7097,7 +7098,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7120,32 +7120,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131739019</v>
+        <v>131736994</v>
       </c>
       <c r="B62" t="n">
-        <v>79879</v>
+        <v>91313</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>2051</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>615022</v>
+        <v>615157</v>
       </c>
       <c r="R62" t="n">
-        <v>6560428</v>
+        <v>6560412</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7185,12 +7185,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ramaria XXL</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7221,10 +7226,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131739038</v>
+        <v>131734662</v>
       </c>
       <c r="B63" t="n">
-        <v>79879</v>
+        <v>79017</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7232,34 +7237,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>614743</v>
+        <v>614665</v>
       </c>
       <c r="R63" t="n">
-        <v>6560468</v>
+        <v>6560415</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7286,12 +7291,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7652,10 +7657,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131734662</v>
+        <v>131739019</v>
       </c>
       <c r="B67" t="n">
-        <v>79017</v>
+        <v>79879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7663,34 +7668,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>614665</v>
+        <v>615022</v>
       </c>
       <c r="R67" t="n">
-        <v>6560415</v>
+        <v>6560428</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7717,12 +7722,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7753,45 +7758,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131736994</v>
+        <v>131739038</v>
       </c>
       <c r="B68" t="n">
-        <v>91313</v>
+        <v>79879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2051</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>615157</v>
+        <v>614743</v>
       </c>
       <c r="R68" t="n">
-        <v>6560412</v>
+        <v>6560468</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7818,17 +7823,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ramaria XXL</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7859,10 +7859,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131737261</v>
+        <v>131740391</v>
       </c>
       <c r="B69" t="n">
-        <v>93108</v>
+        <v>93145</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7870,38 +7870,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>614895</v>
+        <v>614945</v>
       </c>
       <c r="R69" t="n">
-        <v>6560392</v>
+        <v>6560479</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7938,7 +7934,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7947,6 +7943,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7969,45 +7966,49 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131737931</v>
+        <v>131740335</v>
       </c>
       <c r="B70" t="n">
-        <v>8453</v>
+        <v>93142</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>5448</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>614669</v>
+        <v>614815</v>
       </c>
       <c r="R70" t="n">
-        <v>6560513</v>
+        <v>6560508</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8034,12 +8035,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8070,10 +8076,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131736991</v>
+        <v>131740288</v>
       </c>
       <c r="B71" t="n">
-        <v>91313</v>
+        <v>93104</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8081,38 +8087,38 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2051</v>
+        <v>149</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>614736</v>
+        <v>614871</v>
       </c>
       <c r="R71" t="n">
-        <v>6560397</v>
+        <v>6560514</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8139,17 +8145,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>3 st</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8281,10 +8287,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131740391</v>
+        <v>131737261</v>
       </c>
       <c r="B73" t="n">
-        <v>93145</v>
+        <v>93108</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8292,34 +8298,38 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>614945</v>
+        <v>614895</v>
       </c>
       <c r="R73" t="n">
-        <v>6560479</v>
+        <v>6560392</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8356,7 +8366,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>2 st</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8365,7 +8375,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8388,49 +8397,49 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131740335</v>
+        <v>131736991</v>
       </c>
       <c r="B74" t="n">
-        <v>93142</v>
+        <v>91313</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5448</v>
+        <v>2051</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>614815</v>
+        <v>614736</v>
       </c>
       <c r="R74" t="n">
-        <v>6560508</v>
+        <v>6560397</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8457,17 +8466,17 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8498,49 +8507,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131740288</v>
+        <v>131737931</v>
       </c>
       <c r="B75" t="n">
-        <v>93104</v>
+        <v>8453</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>149</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>614871</v>
+        <v>614669</v>
       </c>
       <c r="R75" t="n">
-        <v>6560514</v>
+        <v>6560513</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8567,17 +8572,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8608,10 +8608,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131740369</v>
+        <v>131737723</v>
       </c>
       <c r="B76" t="n">
-        <v>93145</v>
+        <v>93154</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8619,34 +8619,38 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>615152</v>
+        <v>614756</v>
       </c>
       <c r="R76" t="n">
-        <v>6560500</v>
+        <v>6560527</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8683,7 +8687,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8692,7 +8696,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8715,10 +8718,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131740396</v>
+        <v>131737756</v>
       </c>
       <c r="B77" t="n">
-        <v>93145</v>
+        <v>93154</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8726,34 +8729,38 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>614785</v>
+        <v>614923</v>
       </c>
       <c r="R77" t="n">
-        <v>6560564</v>
+        <v>6560410</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8780,17 +8787,17 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8799,7 +8806,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8822,10 +8828,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131740337</v>
+        <v>131737725</v>
       </c>
       <c r="B78" t="n">
-        <v>93142</v>
+        <v>93154</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8833,38 +8839,38 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>614621</v>
+        <v>614660</v>
       </c>
       <c r="R78" t="n">
-        <v>6560438</v>
+        <v>6560511</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8901,7 +8907,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>15+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8932,10 +8938,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131738984</v>
+        <v>131737731</v>
       </c>
       <c r="B79" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8943,34 +8949,38 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>614801</v>
+        <v>614674</v>
       </c>
       <c r="R79" t="n">
-        <v>6560517</v>
+        <v>6560414</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8997,12 +9007,17 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9033,7 +9048,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131737723</v>
+        <v>131737730</v>
       </c>
       <c r="B80" t="n">
         <v>93154</v>
@@ -9063,19 +9078,19 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>614756</v>
+        <v>614656</v>
       </c>
       <c r="R80" t="n">
-        <v>6560527</v>
+        <v>6560418</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9112,7 +9127,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9143,7 +9158,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131737756</v>
+        <v>131737754</v>
       </c>
       <c r="B81" t="n">
         <v>93154</v>
@@ -9173,19 +9188,19 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>614923</v>
+        <v>614888</v>
       </c>
       <c r="R81" t="n">
-        <v>6560410</v>
+        <v>6560440</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9222,7 +9237,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9253,10 +9268,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131737725</v>
+        <v>131740369</v>
       </c>
       <c r="B82" t="n">
-        <v>93154</v>
+        <v>93145</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9264,23 +9279,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>3</t>
@@ -9288,14 +9299,14 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>614660</v>
+        <v>615152</v>
       </c>
       <c r="R82" t="n">
-        <v>6560511</v>
+        <v>6560500</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9341,6 +9352,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9363,10 +9375,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131737731</v>
+        <v>131740337</v>
       </c>
       <c r="B83" t="n">
-        <v>93154</v>
+        <v>93142</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9374,38 +9386,38 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>614674</v>
+        <v>614621</v>
       </c>
       <c r="R83" t="n">
-        <v>6560414</v>
+        <v>6560438</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9442,7 +9454,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15+</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9473,10 +9485,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131737730</v>
+        <v>131740396</v>
       </c>
       <c r="B84" t="n">
-        <v>93154</v>
+        <v>93145</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9484,38 +9496,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>614656</v>
+        <v>614785</v>
       </c>
       <c r="R84" t="n">
-        <v>6560418</v>
+        <v>6560564</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9542,17 +9550,17 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9561,6 +9569,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9583,49 +9592,49 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131737754</v>
+        <v>131736990</v>
       </c>
       <c r="B85" t="n">
-        <v>93154</v>
+        <v>91313</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5966</v>
+        <v>2051</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>614888</v>
+        <v>614738</v>
       </c>
       <c r="R85" t="n">
-        <v>6560440</v>
+        <v>6560408</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9652,17 +9661,17 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9693,49 +9702,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131736990</v>
+        <v>131738984</v>
       </c>
       <c r="B86" t="n">
-        <v>91313</v>
+        <v>79879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2051</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>614738</v>
+        <v>614801</v>
       </c>
       <c r="R86" t="n">
-        <v>6560408</v>
+        <v>6560517</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9762,17 +9767,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>3 st</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9910,10 +9910,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131740342</v>
+        <v>131740392</v>
       </c>
       <c r="B88" t="n">
-        <v>93142</v>
+        <v>93145</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9921,38 +9921,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5448</v>
+        <v>5449</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>614971</v>
+        <v>614832</v>
       </c>
       <c r="R88" t="n">
-        <v>6560251</v>
+        <v>6560458</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9979,17 +9975,17 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>12 st</t>
+          <t>10 st</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9998,6 +9994,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -10020,10 +10017,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131740392</v>
+        <v>131740342</v>
       </c>
       <c r="B89" t="n">
-        <v>93145</v>
+        <v>93142</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10031,34 +10028,38 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>614832</v>
+        <v>614971</v>
       </c>
       <c r="R89" t="n">
-        <v>6560458</v>
+        <v>6560251</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10085,17 +10086,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>10 st</t>
+          <t>12 st</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10104,7 +10105,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10334,10 +10334,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131739025</v>
+        <v>131737265</v>
       </c>
       <c r="B92" t="n">
-        <v>79879</v>
+        <v>93108</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10345,34 +10345,38 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>614887</v>
+        <v>615132</v>
       </c>
       <c r="R92" t="n">
-        <v>6560423</v>
+        <v>6560489</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10399,12 +10403,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10646,10 +10655,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131737265</v>
+        <v>131737732</v>
       </c>
       <c r="B95" t="n">
-        <v>93108</v>
+        <v>93154</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10657,38 +10666,38 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>615132</v>
+        <v>614684</v>
       </c>
       <c r="R95" t="n">
-        <v>6560489</v>
+        <v>6560422</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10715,17 +10724,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10756,7 +10765,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131737732</v>
+        <v>131737718</v>
       </c>
       <c r="B96" t="n">
         <v>93154</v>
@@ -10791,14 +10800,14 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>614684</v>
+        <v>614844</v>
       </c>
       <c r="R96" t="n">
-        <v>6560422</v>
+        <v>6560496</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10866,7 +10875,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131737718</v>
+        <v>131737745</v>
       </c>
       <c r="B97" t="n">
         <v>93154</v>
@@ -10896,19 +10905,19 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>48</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>614844</v>
+        <v>614779</v>
       </c>
       <c r="R97" t="n">
-        <v>6560496</v>
+        <v>6560385</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10945,7 +10954,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10976,10 +10985,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131737745</v>
+        <v>131739025</v>
       </c>
       <c r="B98" t="n">
-        <v>93154</v>
+        <v>79879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10987,38 +10996,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>614779</v>
+        <v>614887</v>
       </c>
       <c r="R98" t="n">
-        <v>6560385</v>
+        <v>6560423</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11051,11 +11056,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>48</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11086,45 +11086,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131739042</v>
+        <v>131736992</v>
       </c>
       <c r="B99" t="n">
-        <v>79879</v>
+        <v>91313</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>2051</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>614859</v>
+        <v>614848</v>
       </c>
       <c r="R99" t="n">
-        <v>6560517</v>
+        <v>6560378</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11151,12 +11151,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11187,10 +11187,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131739016</v>
+        <v>131740395</v>
       </c>
       <c r="B100" t="n">
-        <v>79879</v>
+        <v>93145</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11198,34 +11198,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>615035</v>
+        <v>614715</v>
       </c>
       <c r="R100" t="n">
-        <v>6560425</v>
+        <v>6560514</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11252,12 +11252,17 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>6 st</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11266,6 +11271,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11288,10 +11294,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131739017</v>
+        <v>131740398</v>
       </c>
       <c r="B101" t="n">
-        <v>79879</v>
+        <v>93145</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11299,34 +11305,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>615032</v>
+        <v>614907</v>
       </c>
       <c r="R101" t="n">
-        <v>6560425</v>
+        <v>6560326</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11353,12 +11359,17 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11367,6 +11378,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11389,10 +11401,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131740398</v>
+        <v>131737722</v>
       </c>
       <c r="B102" t="n">
-        <v>93145</v>
+        <v>93154</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11400,34 +11412,38 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>614907</v>
+        <v>614773</v>
       </c>
       <c r="R102" t="n">
-        <v>6560326</v>
+        <v>6560515</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11454,17 +11470,17 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>1o</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11473,7 +11489,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11496,10 +11511,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131740395</v>
+        <v>131737757</v>
       </c>
       <c r="B103" t="n">
-        <v>93145</v>
+        <v>93154</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11507,34 +11522,38 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>614715</v>
+        <v>614887</v>
       </c>
       <c r="R103" t="n">
-        <v>6560514</v>
+        <v>6560362</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11561,17 +11580,17 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>6 st</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11580,7 +11599,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11603,7 +11621,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131737722</v>
+        <v>131737776</v>
       </c>
       <c r="B104" t="n">
         <v>93154</v>
@@ -11633,19 +11651,19 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nord, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>614773</v>
+        <v>615009</v>
       </c>
       <c r="R104" t="n">
-        <v>6560515</v>
+        <v>6560307</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11682,7 +11700,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>1o</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11713,10 +11731,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131737757</v>
+        <v>131739042</v>
       </c>
       <c r="B105" t="n">
-        <v>93154</v>
+        <v>79879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11724,38 +11742,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>614887</v>
+        <v>614859</v>
       </c>
       <c r="R105" t="n">
-        <v>6560362</v>
+        <v>6560517</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11782,17 +11796,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11823,10 +11832,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131737776</v>
+        <v>131739016</v>
       </c>
       <c r="B106" t="n">
-        <v>93154</v>
+        <v>79879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11834,38 +11843,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nystugan Nord, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>615009</v>
+        <v>615035</v>
       </c>
       <c r="R106" t="n">
-        <v>6560307</v>
+        <v>6560425</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11898,11 +11903,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11933,45 +11933,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131736992</v>
+        <v>131739017</v>
       </c>
       <c r="B107" t="n">
-        <v>91313</v>
+        <v>79879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2051</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>614848</v>
+        <v>615032</v>
       </c>
       <c r="R107" t="n">
-        <v>6560378</v>
+        <v>6560425</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12034,10 +12034,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131737715</v>
+        <v>131732521</v>
       </c>
       <c r="B108" t="n">
-        <v>93154</v>
+        <v>78926</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12045,38 +12045,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>614932</v>
+        <v>614661</v>
       </c>
       <c r="R108" t="n">
-        <v>6560487</v>
+        <v>6560444</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12109,11 +12105,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12144,7 +12135,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131737780</v>
+        <v>131737715</v>
       </c>
       <c r="B109" t="n">
         <v>93154</v>
@@ -12174,19 +12165,19 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>615164</v>
+        <v>614932</v>
       </c>
       <c r="R109" t="n">
-        <v>6560465</v>
+        <v>6560487</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12223,7 +12214,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12254,45 +12245,49 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131736993</v>
+        <v>131737780</v>
       </c>
       <c r="B110" t="n">
-        <v>91313</v>
+        <v>93154</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2051</v>
+        <v>5966</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>614719</v>
+        <v>615164</v>
       </c>
       <c r="R110" t="n">
-        <v>6560440</v>
+        <v>6560465</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12319,12 +12314,17 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12355,10 +12355,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131739021</v>
+        <v>131740080</v>
       </c>
       <c r="B111" t="n">
-        <v>79879</v>
+        <v>91849</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12366,34 +12366,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>614820</v>
+        <v>615060</v>
       </c>
       <c r="R111" t="n">
-        <v>6560501</v>
+        <v>6560430</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12420,12 +12420,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12456,45 +12456,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131740080</v>
+        <v>131736993</v>
       </c>
       <c r="B112" t="n">
-        <v>91849</v>
+        <v>91313</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5442</v>
+        <v>2051</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>615060</v>
+        <v>614719</v>
       </c>
       <c r="R112" t="n">
-        <v>6560430</v>
+        <v>6560440</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12521,12 +12521,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12557,10 +12557,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131732521</v>
+        <v>131739021</v>
       </c>
       <c r="B113" t="n">
-        <v>78926</v>
+        <v>79879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12568,34 +12568,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>614661</v>
+        <v>614820</v>
       </c>
       <c r="R113" t="n">
-        <v>6560444</v>
+        <v>6560501</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12658,10 +12658,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131739022</v>
+        <v>131737739</v>
       </c>
       <c r="B114" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12669,34 +12669,38 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>614790</v>
+        <v>614717</v>
       </c>
       <c r="R114" t="n">
-        <v>6560493</v>
+        <v>6560453</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12729,6 +12733,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12759,45 +12768,49 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131733366</v>
+        <v>131737752</v>
       </c>
       <c r="B115" t="n">
-        <v>92486</v>
+        <v>93154</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>615138</v>
+        <v>614875</v>
       </c>
       <c r="R115" t="n">
-        <v>6560392</v>
+        <v>6560431</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12830,6 +12843,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>29</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12860,7 +12878,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131737739</v>
+        <v>131737766</v>
       </c>
       <c r="B116" t="n">
         <v>93154</v>
@@ -12890,19 +12908,19 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>614717</v>
+        <v>614826</v>
       </c>
       <c r="R116" t="n">
-        <v>6560453</v>
+        <v>6560351</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12939,7 +12957,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12970,7 +12988,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131737752</v>
+        <v>131737710</v>
       </c>
       <c r="B117" t="n">
         <v>93154</v>
@@ -13000,19 +13018,19 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>614875</v>
+        <v>614961</v>
       </c>
       <c r="R117" t="n">
-        <v>6560431</v>
+        <v>6560414</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13049,7 +13067,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13080,49 +13098,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131737766</v>
+        <v>131733366</v>
       </c>
       <c r="B118" t="n">
-        <v>93154</v>
+        <v>92486</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>614826</v>
+        <v>615138</v>
       </c>
       <c r="R118" t="n">
-        <v>6560351</v>
+        <v>6560392</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13155,11 +13169,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13190,10 +13199,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131737710</v>
+        <v>131739022</v>
       </c>
       <c r="B119" t="n">
-        <v>93154</v>
+        <v>79879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13201,38 +13210,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>614961</v>
+        <v>614790</v>
       </c>
       <c r="R119" t="n">
-        <v>6560414</v>
+        <v>6560493</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13265,11 +13270,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13401,45 +13401,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131739040</v>
+        <v>131733367</v>
       </c>
       <c r="B121" t="n">
-        <v>79879</v>
+        <v>92486</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>6031</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>614705</v>
+        <v>614939</v>
       </c>
       <c r="R121" t="n">
-        <v>6560468</v>
+        <v>6560438</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13466,12 +13466,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13502,45 +13502,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131737605</v>
+        <v>131733476</v>
       </c>
       <c r="B122" t="n">
-        <v>93154</v>
+        <v>8442</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5966</v>
+        <v>106554</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>614921</v>
+        <v>614831</v>
       </c>
       <c r="R122" t="n">
-        <v>6560349</v>
+        <v>6560599</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13567,12 +13567,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13603,10 +13603,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131737753</v>
+        <v>131733306</v>
       </c>
       <c r="B123" t="n">
-        <v>93154</v>
+        <v>93110</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13614,26 +13614,26 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -13642,10 +13642,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>614883</v>
+        <v>614689</v>
       </c>
       <c r="R123" t="n">
-        <v>6560422</v>
+        <v>6560516</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13672,17 +13672,17 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1 St</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13713,7 +13713,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131737719</v>
+        <v>131737605</v>
       </c>
       <c r="B124" t="n">
         <v>93154</v>
@@ -13741,21 +13741,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>614817</v>
+        <v>614921</v>
       </c>
       <c r="R124" t="n">
-        <v>6560509</v>
+        <v>6560349</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13782,17 +13778,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13823,7 +13814,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131737768</v>
+        <v>131737753</v>
       </c>
       <c r="B125" t="n">
         <v>93154</v>
@@ -13853,19 +13844,19 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>614843</v>
+        <v>614883</v>
       </c>
       <c r="R125" t="n">
-        <v>6560322</v>
+        <v>6560422</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13902,7 +13893,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13933,7 +13924,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131737778</v>
+        <v>131737719</v>
       </c>
       <c r="B126" t="n">
         <v>93154</v>
@@ -13963,19 +13954,19 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>615115</v>
+        <v>614817</v>
       </c>
       <c r="R126" t="n">
-        <v>6560377</v>
+        <v>6560509</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14012,7 +14003,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14043,7 +14034,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131737741</v>
+        <v>131737768</v>
       </c>
       <c r="B127" t="n">
         <v>93154</v>
@@ -14073,19 +14064,19 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>614754</v>
+        <v>614843</v>
       </c>
       <c r="R127" t="n">
-        <v>6560449</v>
+        <v>6560322</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14122,7 +14113,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14153,7 +14144,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131737751</v>
+        <v>131737778</v>
       </c>
       <c r="B128" t="n">
         <v>93154</v>
@@ -14183,19 +14174,19 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>614860</v>
+        <v>615115</v>
       </c>
       <c r="R128" t="n">
-        <v>6560430</v>
+        <v>6560377</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14232,7 +14223,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14263,7 +14254,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131737604</v>
+        <v>131737741</v>
       </c>
       <c r="B129" t="n">
         <v>93154</v>
@@ -14291,17 +14282,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>615114</v>
+        <v>614754</v>
       </c>
       <c r="R129" t="n">
-        <v>6560473</v>
+        <v>6560449</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14328,12 +14323,17 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14364,10 +14364,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131740367</v>
+        <v>131737751</v>
       </c>
       <c r="B130" t="n">
-        <v>93145</v>
+        <v>93154</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14375,22 +14375,26 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -14399,10 +14403,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>614742</v>
+        <v>614860</v>
       </c>
       <c r="R130" t="n">
-        <v>6560443</v>
+        <v>6560430</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14439,7 +14443,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14448,7 +14452,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -14578,45 +14581,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131733367</v>
+        <v>131740367</v>
       </c>
       <c r="B132" t="n">
-        <v>92486</v>
+        <v>93145</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6031</v>
+        <v>5449</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>614939</v>
+        <v>614742</v>
       </c>
       <c r="R132" t="n">
-        <v>6560438</v>
+        <v>6560443</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14651,12 +14654,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14679,10 +14688,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131733476</v>
+        <v>131732765</v>
       </c>
       <c r="B133" t="n">
-        <v>8442</v>
+        <v>93116</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14690,21 +14699,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106554</v>
+        <v>4364</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14714,10 +14723,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>614831</v>
+        <v>614878</v>
       </c>
       <c r="R133" t="n">
-        <v>6560599</v>
+        <v>6560511</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14750,6 +14759,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Förekommer spritt rikligt</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14780,10 +14794,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131733306</v>
+        <v>131737604</v>
       </c>
       <c r="B134" t="n">
-        <v>93110</v>
+        <v>93154</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14791,38 +14805,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>614689</v>
+        <v>615114</v>
       </c>
       <c r="R134" t="n">
-        <v>6560516</v>
+        <v>6560473</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14849,17 +14859,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>1 St</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14890,32 +14895,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131732765</v>
+        <v>131739040</v>
       </c>
       <c r="B135" t="n">
-        <v>93116</v>
+        <v>79879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14925,10 +14930,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>614878</v>
+        <v>614705</v>
       </c>
       <c r="R135" t="n">
-        <v>6560511</v>
+        <v>6560468</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14955,17 +14960,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Förekommer spritt rikligt</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15106,10 +15106,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>131737743</v>
+        <v>131739551</v>
       </c>
       <c r="B137" t="n">
-        <v>93154</v>
+        <v>91828</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15117,38 +15117,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>614731</v>
+        <v>614622</v>
       </c>
       <c r="R137" t="n">
-        <v>6560390</v>
+        <v>6560528</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15175,17 +15171,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15216,45 +15207,49 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>131737932</v>
+        <v>131737743</v>
       </c>
       <c r="B138" t="n">
-        <v>8453</v>
+        <v>93154</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>615059</v>
+        <v>614731</v>
       </c>
       <c r="R138" t="n">
-        <v>6560324</v>
+        <v>6560390</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15281,17 +15276,17 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>Förekommer spritt på tallågor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15322,49 +15317,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>131737707</v>
+        <v>131737932</v>
       </c>
       <c r="B139" t="n">
-        <v>93154</v>
+        <v>8453</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>614934</v>
+        <v>615059</v>
       </c>
       <c r="R139" t="n">
-        <v>6560422</v>
+        <v>6560324</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15391,17 +15382,17 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Förekommer spritt på tallågor</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15432,7 +15423,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>131737748</v>
+        <v>131737707</v>
       </c>
       <c r="B140" t="n">
         <v>93154</v>
@@ -15462,19 +15453,19 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>614792</v>
+        <v>614934</v>
       </c>
       <c r="R140" t="n">
-        <v>6560431</v>
+        <v>6560422</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15511,7 +15502,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15542,10 +15533,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>131740394</v>
+        <v>131737748</v>
       </c>
       <c r="B141" t="n">
-        <v>93145</v>
+        <v>93154</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15553,22 +15544,26 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -15577,10 +15572,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>614731</v>
+        <v>614792</v>
       </c>
       <c r="R141" t="n">
-        <v>6560512</v>
+        <v>6560431</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15607,17 +15602,17 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>1 st</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15626,7 +15621,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15649,45 +15643,49 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>131740304</v>
+        <v>131740243</v>
       </c>
       <c r="B142" t="n">
-        <v>91321</v>
+        <v>92760</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>256703</v>
+        <v>4745</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>615108</v>
+        <v>614829</v>
       </c>
       <c r="R142" t="n">
-        <v>6560375</v>
+        <v>6560371</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15714,12 +15712,17 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15750,10 +15753,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>131740243</v>
+        <v>131740394</v>
       </c>
       <c r="B143" t="n">
-        <v>92760</v>
+        <v>93145</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15761,23 +15764,19 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4745</v>
+        <v>5449</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Fr.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
           <t>1</t>
@@ -15785,14 +15784,14 @@
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>614829</v>
+        <v>614731</v>
       </c>
       <c r="R143" t="n">
-        <v>6560371</v>
+        <v>6560512</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15819,17 +15818,17 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 st</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15838,6 +15837,7 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -15860,45 +15860,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>131740402</v>
+        <v>131740304</v>
       </c>
       <c r="B144" t="n">
-        <v>93145</v>
+        <v>91321</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5449</v>
+        <v>256703</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>615135</v>
+        <v>615108</v>
       </c>
       <c r="R144" t="n">
-        <v>6560485</v>
+        <v>6560375</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15933,18 +15933,12 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Ca 25st</t>
-        </is>
-      </c>
       <c r="AD144" t="b">
         <v>0</v>
       </c>
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -15967,10 +15961,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>131739551</v>
+        <v>131740402</v>
       </c>
       <c r="B145" t="n">
-        <v>91828</v>
+        <v>93145</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15978,34 +15972,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1202</v>
+        <v>5449</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>614622</v>
+        <v>615135</v>
       </c>
       <c r="R145" t="n">
-        <v>6560528</v>
+        <v>6560485</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16032,12 +16026,17 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Ca 25st</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16046,6 +16045,7 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -16068,10 +16068,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>131737264</v>
+        <v>131740400</v>
       </c>
       <c r="B146" t="n">
-        <v>93108</v>
+        <v>93145</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16079,38 +16079,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>615062</v>
+        <v>614952</v>
       </c>
       <c r="R146" t="n">
-        <v>6560402</v>
+        <v>6560279</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16147,7 +16143,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16156,6 +16152,7 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -16508,10 +16505,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>131737266</v>
+        <v>131732523</v>
       </c>
       <c r="B150" t="n">
-        <v>93108</v>
+        <v>78926</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16519,38 +16516,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>615141</v>
+        <v>614818</v>
       </c>
       <c r="R150" t="n">
-        <v>6560479</v>
+        <v>6560356</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16577,17 +16570,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>2 st</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16618,7 +16606,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>131737262</v>
+        <v>131737264</v>
       </c>
       <c r="B151" t="n">
         <v>93108</v>
@@ -16648,19 +16636,19 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>614741</v>
+        <v>615062</v>
       </c>
       <c r="R151" t="n">
-        <v>6560504</v>
+        <v>6560402</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16697,7 +16685,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>1 st</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16728,10 +16716,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>131740400</v>
+        <v>131737266</v>
       </c>
       <c r="B152" t="n">
-        <v>93145</v>
+        <v>93108</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16739,19 +16727,23 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr"/>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I152" t="inlineStr">
         <is>
           <t>2</t>
@@ -16759,14 +16751,14 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>614952</v>
+        <v>615141</v>
       </c>
       <c r="R152" t="n">
-        <v>6560279</v>
+        <v>6560479</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16812,7 +16804,6 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -16835,10 +16826,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>131732523</v>
+        <v>131737262</v>
       </c>
       <c r="B153" t="n">
-        <v>78926</v>
+        <v>93108</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16846,34 +16837,38 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>614818</v>
+        <v>614741</v>
       </c>
       <c r="R153" t="n">
-        <v>6560356</v>
+        <v>6560504</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16900,12 +16895,17 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>1 st</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16936,10 +16936,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>131737777</v>
+        <v>131740364</v>
       </c>
       <c r="B154" t="n">
-        <v>93154</v>
+        <v>93145</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16947,38 +16947,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>615134</v>
+        <v>614841</v>
       </c>
       <c r="R154" t="n">
-        <v>6560409</v>
+        <v>6560503</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17015,7 +17011,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17024,6 +17020,7 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -17046,49 +17043,45 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>131737772</v>
+        <v>131732764</v>
       </c>
       <c r="B155" t="n">
-        <v>93154</v>
+        <v>93116</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>614898</v>
+        <v>614871</v>
       </c>
       <c r="R155" t="n">
-        <v>6560304</v>
+        <v>6560446</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17115,17 +17108,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17156,7 +17144,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>131737606</v>
+        <v>131737777</v>
       </c>
       <c r="B156" t="n">
         <v>93154</v>
@@ -17184,17 +17172,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>614656</v>
+        <v>615134</v>
       </c>
       <c r="R156" t="n">
-        <v>6560442</v>
+        <v>6560409</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17221,12 +17213,17 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17257,7 +17254,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>131737709</v>
+        <v>131737772</v>
       </c>
       <c r="B157" t="n">
         <v>93154</v>
@@ -17287,19 +17284,19 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>614958</v>
+        <v>614898</v>
       </c>
       <c r="R157" t="n">
-        <v>6560433</v>
+        <v>6560304</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17336,7 +17333,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17367,7 +17364,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>131737759</v>
+        <v>131737709</v>
       </c>
       <c r="B158" t="n">
         <v>93154</v>
@@ -17397,19 +17394,19 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>614874</v>
+        <v>614958</v>
       </c>
       <c r="R158" t="n">
-        <v>6560379</v>
+        <v>6560433</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17446,7 +17443,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17477,7 +17474,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>131737761</v>
+        <v>131737759</v>
       </c>
       <c r="B159" t="n">
         <v>93154</v>
@@ -17507,7 +17504,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -17516,10 +17513,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>614870</v>
+        <v>614874</v>
       </c>
       <c r="R159" t="n">
-        <v>6560397</v>
+        <v>6560379</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17556,7 +17553,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17587,7 +17584,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>131737755</v>
+        <v>131737761</v>
       </c>
       <c r="B160" t="n">
         <v>93154</v>
@@ -17617,19 +17614,19 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>614894</v>
+        <v>614870</v>
       </c>
       <c r="R160" t="n">
-        <v>6560431</v>
+        <v>6560397</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17666,7 +17663,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17697,7 +17694,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>131737611</v>
+        <v>131737606</v>
       </c>
       <c r="B161" t="n">
         <v>93154</v>
@@ -17728,14 +17725,14 @@
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>614822</v>
+        <v>614656</v>
       </c>
       <c r="R161" t="n">
-        <v>6560500</v>
+        <v>6560442</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17798,7 +17795,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>131737763</v>
+        <v>131737611</v>
       </c>
       <c r="B162" t="n">
         <v>93154</v>
@@ -17826,21 +17823,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>614847</v>
+        <v>614822</v>
       </c>
       <c r="R162" t="n">
-        <v>6560380</v>
+        <v>6560500</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17867,17 +17860,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17908,10 +17896,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>131740364</v>
+        <v>131737755</v>
       </c>
       <c r="B163" t="n">
-        <v>93145</v>
+        <v>93154</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17919,22 +17907,26 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -17943,10 +17935,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>614841</v>
+        <v>614894</v>
       </c>
       <c r="R163" t="n">
-        <v>6560503</v>
+        <v>6560431</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17983,7 +17975,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17992,7 +17984,6 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -18015,45 +18006,49 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>131732764</v>
+        <v>131737763</v>
       </c>
       <c r="B164" t="n">
-        <v>93116</v>
+        <v>93154</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>614871</v>
+        <v>614847</v>
       </c>
       <c r="R164" t="n">
-        <v>6560446</v>
+        <v>6560380</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18080,12 +18075,17 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18116,49 +18116,45 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>131740287</v>
+        <v>131737609</v>
       </c>
       <c r="B165" t="n">
-        <v>93104</v>
+        <v>93154</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>149</v>
+        <v>5966</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>614868</v>
+        <v>614698</v>
       </c>
       <c r="R165" t="n">
-        <v>6560512</v>
+        <v>6560522</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18185,17 +18181,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18333,45 +18324,49 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>131738710</v>
+        <v>131740287</v>
       </c>
       <c r="B167" t="n">
-        <v>97274</v>
+        <v>93104</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>53</v>
+        <v>149</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
+          <t>(Peck) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>614670</v>
+        <v>614868</v>
       </c>
       <c r="R167" t="n">
-        <v>6560435</v>
+        <v>6560512</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18398,12 +18393,17 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18755,10 +18755,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>131737609</v>
+        <v>131738710</v>
       </c>
       <c r="B171" t="n">
-        <v>93154</v>
+        <v>97274</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18766,34 +18766,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>614698</v>
+        <v>614670</v>
       </c>
       <c r="R171" t="n">
-        <v>6560522</v>
+        <v>6560435</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18820,12 +18820,12 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19070,10 +19070,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>131737740</v>
+        <v>131734664</v>
       </c>
       <c r="B174" t="n">
-        <v>93154</v>
+        <v>79017</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19081,38 +19081,34 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>614746</v>
+        <v>615034</v>
       </c>
       <c r="R174" t="n">
-        <v>6560453</v>
+        <v>6560418</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19145,11 +19141,6 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19180,10 +19171,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>131737742</v>
+        <v>131734663</v>
       </c>
       <c r="B175" t="n">
-        <v>93154</v>
+        <v>79017</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19191,38 +19182,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>614738</v>
+        <v>614679</v>
       </c>
       <c r="R175" t="n">
-        <v>6560442</v>
+        <v>6560422</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19249,17 +19236,12 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19290,7 +19272,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>131737721</v>
+        <v>131737740</v>
       </c>
       <c r="B176" t="n">
         <v>93154</v>
@@ -19320,7 +19302,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -19329,10 +19311,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>614776</v>
+        <v>614746</v>
       </c>
       <c r="R176" t="n">
-        <v>6560488</v>
+        <v>6560453</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19369,7 +19351,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19400,7 +19382,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>131737775</v>
+        <v>131737742</v>
       </c>
       <c r="B177" t="n">
         <v>93154</v>
@@ -19430,19 +19412,19 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Nystugan Nord, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>614989</v>
+        <v>614738</v>
       </c>
       <c r="R177" t="n">
-        <v>6560288</v>
+        <v>6560442</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19479,7 +19461,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19510,7 +19492,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>131737738</v>
+        <v>131737721</v>
       </c>
       <c r="B178" t="n">
         <v>93154</v>
@@ -19540,7 +19522,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -19549,10 +19531,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>614711</v>
+        <v>614776</v>
       </c>
       <c r="R178" t="n">
-        <v>6560481</v>
+        <v>6560488</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19589,7 +19571,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19620,10 +19602,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>131735737</v>
+        <v>131737775</v>
       </c>
       <c r="B179" t="n">
-        <v>92618</v>
+        <v>93154</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19631,38 +19613,38 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>366</v>
+        <v>5966</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nystugan Nord, Srm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>615093</v>
+        <v>614989</v>
       </c>
       <c r="R179" t="n">
-        <v>6560461</v>
+        <v>6560288</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19689,17 +19671,17 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19730,10 +19712,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>131734664</v>
+        <v>131737738</v>
       </c>
       <c r="B180" t="n">
-        <v>79017</v>
+        <v>93154</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19741,34 +19723,38 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>615034</v>
+        <v>614711</v>
       </c>
       <c r="R180" t="n">
-        <v>6560418</v>
+        <v>6560481</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19801,6 +19787,11 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19831,10 +19822,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>131734663</v>
+        <v>131735737</v>
       </c>
       <c r="B181" t="n">
-        <v>79017</v>
+        <v>92618</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19842,34 +19833,38 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6446</v>
+        <v>366</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>614679</v>
+        <v>615093</v>
       </c>
       <c r="R181" t="n">
-        <v>6560422</v>
+        <v>6560461</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19896,12 +19891,17 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD181" t="b">

--- a/artfynd/A 43282-2024 artfynd.xlsx
+++ b/artfynd/A 43282-2024 artfynd.xlsx
@@ -2583,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131737607</v>
+        <v>131740240</v>
       </c>
       <c r="B19" t="n">
-        <v>93158</v>
+        <v>92764</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,34 +2594,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>614643</v>
+        <v>615041</v>
       </c>
       <c r="R19" t="n">
-        <v>6560479</v>
+        <v>6560443</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2684,32 +2684,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131740240</v>
+        <v>131732769</v>
       </c>
       <c r="B20" t="n">
-        <v>92764</v>
+        <v>93120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2719,10 +2719,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615041</v>
+        <v>615104</v>
       </c>
       <c r="R20" t="n">
-        <v>6560443</v>
+        <v>6560485</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2749,12 +2749,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Återkommer spritt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2785,45 +2790,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131732769</v>
+        <v>131737607</v>
       </c>
       <c r="B21" t="n">
-        <v>93120</v>
+        <v>93158</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615104</v>
+        <v>614643</v>
       </c>
       <c r="R21" t="n">
-        <v>6560485</v>
+        <v>6560479</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2850,17 +2855,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Återkommer spritt</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4603,10 +4603,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131740334</v>
+        <v>131738986</v>
       </c>
       <c r="B38" t="n">
-        <v>93146</v>
+        <v>79883</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4614,21 +4614,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5448</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4638,10 +4638,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>614945</v>
+        <v>614832</v>
       </c>
       <c r="R38" t="n">
-        <v>6560495</v>
+        <v>6560556</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4704,10 +4704,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131737764</v>
+        <v>131739037</v>
       </c>
       <c r="B39" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4715,38 +4715,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>614836</v>
+        <v>615086</v>
       </c>
       <c r="R39" t="n">
-        <v>6560376</v>
+        <v>6560375</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4773,17 +4769,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>9</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4814,10 +4805,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131737733</v>
+        <v>131739024</v>
       </c>
       <c r="B40" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4825,34 +4816,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>614695</v>
+        <v>614774</v>
       </c>
       <c r="R40" t="n">
-        <v>6560413</v>
+        <v>6560505</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4915,10 +4906,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131737713</v>
+        <v>131740334</v>
       </c>
       <c r="B41" t="n">
-        <v>93158</v>
+        <v>93146</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4926,21 +4917,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4950,10 +4941,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>614935</v>
+        <v>614945</v>
       </c>
       <c r="R41" t="n">
-        <v>6560472</v>
+        <v>6560495</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5016,45 +5007,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131736787</v>
+        <v>131737764</v>
       </c>
       <c r="B42" t="n">
-        <v>92204</v>
+        <v>93158</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2062</v>
+        <v>5966</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>614622</v>
+        <v>614836</v>
       </c>
       <c r="R42" t="n">
-        <v>6560528</v>
+        <v>6560376</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5081,12 +5076,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5117,10 +5117,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131736576</v>
+        <v>131737733</v>
       </c>
       <c r="B43" t="n">
-        <v>93136</v>
+        <v>93158</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5128,38 +5128,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>614640</v>
+        <v>614695</v>
       </c>
       <c r="R43" t="n">
-        <v>6560409</v>
+        <v>6560413</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5186,17 +5182,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>9 st</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5227,10 +5218,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131738986</v>
+        <v>131737713</v>
       </c>
       <c r="B44" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5238,21 +5229,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5262,10 +5253,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>614832</v>
+        <v>614935</v>
       </c>
       <c r="R44" t="n">
-        <v>6560556</v>
+        <v>6560472</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5292,12 +5283,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5328,45 +5319,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131739037</v>
+        <v>131736787</v>
       </c>
       <c r="B45" t="n">
-        <v>79883</v>
+        <v>92204</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>2062</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>615086</v>
+        <v>614622</v>
       </c>
       <c r="R45" t="n">
-        <v>6560375</v>
+        <v>6560528</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5393,12 +5384,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5429,10 +5420,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131739024</v>
+        <v>131736576</v>
       </c>
       <c r="B46" t="n">
-        <v>79883</v>
+        <v>93136</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5440,34 +5431,38 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>614774</v>
+        <v>614640</v>
       </c>
       <c r="R46" t="n">
-        <v>6560505</v>
+        <v>6560409</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5494,12 +5489,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>9 st</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6481,45 +6481,49 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131736812</v>
+        <v>131735736</v>
       </c>
       <c r="B56" t="n">
-        <v>93132</v>
+        <v>92622</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4366</v>
+        <v>366</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>614856</v>
+        <v>614666</v>
       </c>
       <c r="R56" t="n">
-        <v>6560514</v>
+        <v>6560445</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6546,12 +6550,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6582,10 +6591,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131740242</v>
+        <v>131737712</v>
       </c>
       <c r="B57" t="n">
-        <v>92764</v>
+        <v>93158</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6593,38 +6602,38 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>614849</v>
+        <v>614922</v>
       </c>
       <c r="R57" t="n">
-        <v>6560382</v>
+        <v>6560461</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6661,7 +6670,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6692,49 +6701,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131737712</v>
+        <v>131736812</v>
       </c>
       <c r="B58" t="n">
-        <v>93158</v>
+        <v>93132</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>614922</v>
+        <v>614856</v>
       </c>
       <c r="R58" t="n">
-        <v>6560461</v>
+        <v>6560514</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6761,17 +6766,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6802,10 +6802,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131735736</v>
+        <v>131740242</v>
       </c>
       <c r="B59" t="n">
-        <v>92622</v>
+        <v>92764</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6813,38 +6813,38 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>366</v>
+        <v>4745</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>614666</v>
+        <v>614849</v>
       </c>
       <c r="R59" t="n">
-        <v>6560445</v>
+        <v>6560382</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6871,17 +6871,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>3 st</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6912,49 +6912,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131737714</v>
+        <v>131734255</v>
       </c>
       <c r="B60" t="n">
-        <v>93158</v>
+        <v>97369</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>990</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Warnst.) R.M.Schust.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>614933</v>
+        <v>614670</v>
       </c>
       <c r="R60" t="n">
-        <v>6560495</v>
+        <v>6560435</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6981,17 +6977,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>60+</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7022,45 +7013,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131740397</v>
+        <v>131736994</v>
       </c>
       <c r="B61" t="n">
-        <v>93149</v>
+        <v>91317</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5449</v>
+        <v>2051</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Ramaria boreimaxima</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>614907</v>
+        <v>615157</v>
       </c>
       <c r="R61" t="n">
-        <v>6560338</v>
+        <v>6560412</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7097,7 +7088,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>5 st</t>
+          <t>Ramaria XXL</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7106,7 +7097,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7129,10 +7119,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131737749</v>
+        <v>131739019</v>
       </c>
       <c r="B62" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7140,38 +7130,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>614849</v>
+        <v>615022</v>
       </c>
       <c r="R62" t="n">
-        <v>6560446</v>
+        <v>6560428</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7204,11 +7190,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7239,10 +7220,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131737717</v>
+        <v>131739038</v>
       </c>
       <c r="B63" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7250,38 +7231,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>614838</v>
+        <v>614743</v>
       </c>
       <c r="R63" t="n">
-        <v>6560512</v>
+        <v>6560468</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7308,17 +7285,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7349,45 +7321,49 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131736994</v>
+        <v>131737714</v>
       </c>
       <c r="B64" t="n">
-        <v>91317</v>
+        <v>93158</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2051</v>
+        <v>5966</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>615157</v>
+        <v>614933</v>
       </c>
       <c r="R64" t="n">
-        <v>6560412</v>
+        <v>6560495</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7414,17 +7390,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ramaria XXL</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7455,45 +7431,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131734255</v>
+        <v>131740397</v>
       </c>
       <c r="B65" t="n">
-        <v>97369</v>
+        <v>93149</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>990</v>
+        <v>5449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Warnst.) R.M.Schust.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>614670</v>
+        <v>614907</v>
       </c>
       <c r="R65" t="n">
-        <v>6560435</v>
+        <v>6560338</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7520,12 +7496,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>5 st</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7534,6 +7515,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7556,10 +7538,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131739019</v>
+        <v>131737749</v>
       </c>
       <c r="B66" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7567,34 +7549,38 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>615022</v>
+        <v>614849</v>
       </c>
       <c r="R66" t="n">
-        <v>6560428</v>
+        <v>6560446</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7627,6 +7613,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7657,10 +7648,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131739038</v>
+        <v>131737717</v>
       </c>
       <c r="B67" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7668,34 +7659,38 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>614743</v>
+        <v>614838</v>
       </c>
       <c r="R67" t="n">
-        <v>6560468</v>
+        <v>6560512</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7722,12 +7717,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -11086,45 +11086,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131740398</v>
+        <v>131736992</v>
       </c>
       <c r="B99" t="n">
-        <v>93149</v>
+        <v>91317</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5449</v>
+        <v>2051</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Ramaria boreimaxima</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>614907</v>
+        <v>614848</v>
       </c>
       <c r="R99" t="n">
-        <v>6560326</v>
+        <v>6560378</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11151,17 +11151,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>4 st</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11170,7 +11165,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11193,10 +11187,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131739016</v>
+        <v>131740398</v>
       </c>
       <c r="B100" t="n">
-        <v>79883</v>
+        <v>93149</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11204,34 +11198,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>615035</v>
+        <v>614907</v>
       </c>
       <c r="R100" t="n">
-        <v>6560425</v>
+        <v>6560326</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11258,12 +11252,17 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11272,6 +11271,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11294,10 +11294,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131739017</v>
+        <v>131740395</v>
       </c>
       <c r="B101" t="n">
-        <v>79883</v>
+        <v>93149</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11305,34 +11305,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>615032</v>
+        <v>614715</v>
       </c>
       <c r="R101" t="n">
-        <v>6560425</v>
+        <v>6560514</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11359,12 +11359,17 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>6 st</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11373,6 +11378,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11395,45 +11401,49 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131736992</v>
+        <v>131737757</v>
       </c>
       <c r="B102" t="n">
-        <v>91317</v>
+        <v>93158</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2051</v>
+        <v>5966</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>614848</v>
+        <v>614887</v>
       </c>
       <c r="R102" t="n">
-        <v>6560378</v>
+        <v>6560362</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11460,12 +11470,17 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11496,10 +11511,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131740395</v>
+        <v>131737722</v>
       </c>
       <c r="B103" t="n">
-        <v>93149</v>
+        <v>93158</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11507,22 +11522,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11531,10 +11550,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>614715</v>
+        <v>614773</v>
       </c>
       <c r="R103" t="n">
-        <v>6560514</v>
+        <v>6560515</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11561,17 +11580,17 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>6 st</t>
+          <t>1o</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11580,7 +11599,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11603,7 +11621,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131737757</v>
+        <v>131737776</v>
       </c>
       <c r="B104" t="n">
         <v>93158</v>
@@ -11633,19 +11651,19 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nord, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>614887</v>
+        <v>615009</v>
       </c>
       <c r="R104" t="n">
-        <v>6560362</v>
+        <v>6560307</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11682,7 +11700,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11713,10 +11731,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131737722</v>
+        <v>131739042</v>
       </c>
       <c r="B105" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11724,38 +11742,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>614773</v>
+        <v>614859</v>
       </c>
       <c r="R105" t="n">
-        <v>6560515</v>
+        <v>6560517</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11782,17 +11796,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>1o</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11823,7 +11832,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131739042</v>
+        <v>131739016</v>
       </c>
       <c r="B106" t="n">
         <v>79883</v>
@@ -11854,14 +11863,14 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>614859</v>
+        <v>615035</v>
       </c>
       <c r="R106" t="n">
-        <v>6560517</v>
+        <v>6560425</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11888,12 +11897,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11924,10 +11933,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131737776</v>
+        <v>131739017</v>
       </c>
       <c r="B107" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11935,38 +11944,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nystugan Nord, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>615009</v>
+        <v>615032</v>
       </c>
       <c r="R107" t="n">
-        <v>6560307</v>
+        <v>6560425</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11999,11 +12004,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12658,10 +12658,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131737739</v>
+        <v>131736464</v>
       </c>
       <c r="B114" t="n">
-        <v>93158</v>
+        <v>57899</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12669,38 +12669,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nord, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>614717</v>
+        <v>614934</v>
       </c>
       <c r="R114" t="n">
-        <v>6560453</v>
+        <v>6560353</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12727,17 +12723,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12768,10 +12759,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131739022</v>
+        <v>131737766</v>
       </c>
       <c r="B115" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12779,34 +12770,38 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>614790</v>
+        <v>614826</v>
       </c>
       <c r="R115" t="n">
-        <v>6560493</v>
+        <v>6560351</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12839,6 +12834,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12869,45 +12869,49 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131733366</v>
+        <v>131737710</v>
       </c>
       <c r="B116" t="n">
-        <v>92490</v>
+        <v>93158</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>615138</v>
+        <v>614961</v>
       </c>
       <c r="R116" t="n">
-        <v>6560392</v>
+        <v>6560414</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12940,6 +12944,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12970,7 +12979,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131737766</v>
+        <v>131737739</v>
       </c>
       <c r="B117" t="n">
         <v>93158</v>
@@ -13000,19 +13009,19 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>614826</v>
+        <v>614717</v>
       </c>
       <c r="R117" t="n">
-        <v>6560351</v>
+        <v>6560453</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13049,7 +13058,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13080,7 +13089,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131737710</v>
+        <v>131737752</v>
       </c>
       <c r="B118" t="n">
         <v>93158</v>
@@ -13110,19 +13119,19 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>614961</v>
+        <v>614875</v>
       </c>
       <c r="R118" t="n">
-        <v>6560414</v>
+        <v>6560431</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13159,7 +13168,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13190,45 +13199,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131736464</v>
+        <v>131733366</v>
       </c>
       <c r="B119" t="n">
-        <v>57899</v>
+        <v>92490</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>6031</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Nystugan Nord, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>614934</v>
+        <v>615138</v>
       </c>
       <c r="R119" t="n">
-        <v>6560353</v>
+        <v>6560392</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13255,12 +13264,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13291,10 +13300,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131737752</v>
+        <v>131739022</v>
       </c>
       <c r="B120" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13302,38 +13311,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>614875</v>
+        <v>614790</v>
       </c>
       <c r="R120" t="n">
-        <v>6560431</v>
+        <v>6560493</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13366,11 +13371,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14996,10 +14996,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131733304</v>
+        <v>131739551</v>
       </c>
       <c r="B136" t="n">
-        <v>93114</v>
+        <v>91832</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15007,38 +15007,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4362</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>614759</v>
+        <v>614622</v>
       </c>
       <c r="R136" t="n">
-        <v>6560440</v>
+        <v>6560528</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15065,17 +15061,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>8 st</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15106,10 +15097,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>131740243</v>
+        <v>131737748</v>
       </c>
       <c r="B137" t="n">
-        <v>92764</v>
+        <v>93158</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15117,38 +15108,38 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>614829</v>
+        <v>614792</v>
       </c>
       <c r="R137" t="n">
-        <v>6560371</v>
+        <v>6560431</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15185,7 +15176,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15216,45 +15207,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>131740304</v>
+        <v>131740394</v>
       </c>
       <c r="B138" t="n">
-        <v>91325</v>
+        <v>93149</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>256703</v>
+        <v>5449</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>615108</v>
+        <v>614731</v>
       </c>
       <c r="R138" t="n">
-        <v>6560375</v>
+        <v>6560512</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15289,12 +15280,18 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>1 st</t>
+        </is>
+      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -15317,10 +15314,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>131739551</v>
+        <v>131737743</v>
       </c>
       <c r="B139" t="n">
-        <v>91832</v>
+        <v>93158</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15328,34 +15325,38 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>614622</v>
+        <v>614731</v>
       </c>
       <c r="R139" t="n">
-        <v>6560528</v>
+        <v>6560390</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15382,12 +15383,17 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15418,10 +15424,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>131737748</v>
+        <v>131740402</v>
       </c>
       <c r="B140" t="n">
-        <v>93158</v>
+        <v>93149</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15429,38 +15435,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>614792</v>
+        <v>615135</v>
       </c>
       <c r="R140" t="n">
-        <v>6560431</v>
+        <v>6560485</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15487,17 +15489,17 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>Ca 25st</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15506,6 +15508,7 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15528,10 +15531,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>131740394</v>
+        <v>131737707</v>
       </c>
       <c r="B141" t="n">
-        <v>93149</v>
+        <v>93158</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15539,34 +15542,38 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>614731</v>
+        <v>614934</v>
       </c>
       <c r="R141" t="n">
-        <v>6560512</v>
+        <v>6560422</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15593,17 +15600,17 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>1 st</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15612,7 +15619,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15635,49 +15641,45 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>131737743</v>
+        <v>131737932</v>
       </c>
       <c r="B142" t="n">
-        <v>93158</v>
+        <v>8454</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>614731</v>
+        <v>615059</v>
       </c>
       <c r="R142" t="n">
-        <v>6560390</v>
+        <v>6560324</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15704,17 +15706,17 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Förekommer spritt på tallågor</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15745,10 +15747,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>131740402</v>
+        <v>131733304</v>
       </c>
       <c r="B143" t="n">
-        <v>93149</v>
+        <v>93114</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15756,34 +15758,38 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr"/>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>615135</v>
+        <v>614759</v>
       </c>
       <c r="R143" t="n">
-        <v>6560485</v>
+        <v>6560440</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15820,7 +15826,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ca 25st</t>
+          <t>8 st</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15829,7 +15835,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -15852,10 +15857,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>131737707</v>
+        <v>131740243</v>
       </c>
       <c r="B144" t="n">
-        <v>93158</v>
+        <v>92764</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15863,38 +15868,38 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>614934</v>
+        <v>614829</v>
       </c>
       <c r="R144" t="n">
-        <v>6560422</v>
+        <v>6560371</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15931,7 +15936,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15962,10 +15967,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>131737932</v>
+        <v>131740304</v>
       </c>
       <c r="B145" t="n">
-        <v>8454</v>
+        <v>91325</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15973,21 +15978,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>106545</v>
+        <v>256703</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15997,10 +16002,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>615059</v>
+        <v>615108</v>
       </c>
       <c r="R145" t="n">
-        <v>6560324</v>
+        <v>6560375</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16033,11 +16038,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Förekommer spritt på tallågor</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16068,10 +16068,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>131732523</v>
+        <v>131740400</v>
       </c>
       <c r="B146" t="n">
-        <v>78930</v>
+        <v>93149</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16079,34 +16079,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>353</v>
+        <v>5449</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>614818</v>
+        <v>614952</v>
       </c>
       <c r="R146" t="n">
-        <v>6560356</v>
+        <v>6560279</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16133,12 +16133,17 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16147,6 +16152,7 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -16169,10 +16175,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>131737264</v>
+        <v>131737726</v>
       </c>
       <c r="B147" t="n">
-        <v>93112</v>
+        <v>93158</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16180,38 +16186,38 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>615062</v>
+        <v>614639</v>
       </c>
       <c r="R147" t="n">
-        <v>6560402</v>
+        <v>6560514</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16238,17 +16244,17 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16279,10 +16285,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>131737266</v>
+        <v>131737727</v>
       </c>
       <c r="B148" t="n">
-        <v>93112</v>
+        <v>93158</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16290,38 +16296,38 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>615141</v>
+        <v>614657</v>
       </c>
       <c r="R148" t="n">
-        <v>6560479</v>
+        <v>6560454</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16348,17 +16354,17 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>2 st</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16389,10 +16395,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>131737262</v>
+        <v>131737706</v>
       </c>
       <c r="B149" t="n">
-        <v>93112</v>
+        <v>93158</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16400,38 +16406,38 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>614741</v>
+        <v>615019</v>
       </c>
       <c r="R149" t="n">
-        <v>6560504</v>
+        <v>6560434</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16458,17 +16464,17 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>1 st</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16499,10 +16505,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>131740400</v>
+        <v>131732523</v>
       </c>
       <c r="B150" t="n">
-        <v>93149</v>
+        <v>78930</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16510,34 +16516,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5449</v>
+        <v>353</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>614952</v>
+        <v>614818</v>
       </c>
       <c r="R150" t="n">
-        <v>6560279</v>
+        <v>6560356</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16564,17 +16570,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>2 st</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16583,7 +16584,6 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16606,10 +16606,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>131737726</v>
+        <v>131737264</v>
       </c>
       <c r="B151" t="n">
-        <v>93158</v>
+        <v>93112</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16617,38 +16617,38 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>614639</v>
+        <v>615062</v>
       </c>
       <c r="R151" t="n">
-        <v>6560514</v>
+        <v>6560402</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16675,17 +16675,17 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16716,10 +16716,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>131737727</v>
+        <v>131737266</v>
       </c>
       <c r="B152" t="n">
-        <v>93158</v>
+        <v>93112</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16727,38 +16727,38 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>614657</v>
+        <v>615141</v>
       </c>
       <c r="R152" t="n">
-        <v>6560454</v>
+        <v>6560479</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16785,17 +16785,17 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16826,10 +16826,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>131737706</v>
+        <v>131737262</v>
       </c>
       <c r="B153" t="n">
-        <v>93158</v>
+        <v>93112</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16837,38 +16837,38 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>615019</v>
+        <v>614741</v>
       </c>
       <c r="R153" t="n">
-        <v>6560434</v>
+        <v>6560504</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16895,17 +16895,17 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1 st</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18856,10 +18856,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>131735737</v>
+        <v>131737721</v>
       </c>
       <c r="B172" t="n">
-        <v>92622</v>
+        <v>93158</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18867,21 +18867,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>366</v>
+        <v>5966</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -18891,14 +18891,14 @@
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>615093</v>
+        <v>614776</v>
       </c>
       <c r="R172" t="n">
-        <v>6560461</v>
+        <v>6560488</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18925,17 +18925,17 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18966,10 +18966,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>131732524</v>
+        <v>131740359</v>
       </c>
       <c r="B173" t="n">
-        <v>78930</v>
+        <v>93149</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18977,34 +18977,34 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>353</v>
+        <v>5449</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>614915</v>
+        <v>614877</v>
       </c>
       <c r="R173" t="n">
-        <v>6560407</v>
+        <v>6560513</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19031,12 +19031,17 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19045,6 +19050,7 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
+      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
@@ -19067,7 +19073,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>131737721</v>
+        <v>131737742</v>
       </c>
       <c r="B174" t="n">
         <v>93158</v>
@@ -19097,7 +19103,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
@@ -19106,10 +19112,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>614776</v>
+        <v>614738</v>
       </c>
       <c r="R174" t="n">
-        <v>6560488</v>
+        <v>6560442</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19146,7 +19152,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19177,7 +19183,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>131740359</v>
+        <v>131740399</v>
       </c>
       <c r="B175" t="n">
         <v>93149</v>
@@ -19203,19 +19209,19 @@
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>614877</v>
+        <v>614904</v>
       </c>
       <c r="R175" t="n">
-        <v>6560513</v>
+        <v>6560330</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19242,17 +19248,17 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5 st</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19284,7 +19290,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>131737742</v>
+        <v>131737775</v>
       </c>
       <c r="B176" t="n">
         <v>93158</v>
@@ -19314,19 +19320,19 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nord, Srm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>614738</v>
+        <v>614989</v>
       </c>
       <c r="R176" t="n">
-        <v>6560442</v>
+        <v>6560288</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19363,7 +19369,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19394,10 +19400,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>131740399</v>
+        <v>131737738</v>
       </c>
       <c r="B177" t="n">
-        <v>93149</v>
+        <v>93158</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19405,34 +19411,38 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>614904</v>
+        <v>614711</v>
       </c>
       <c r="R177" t="n">
-        <v>6560330</v>
+        <v>6560481</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19459,17 +19469,17 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>5 st</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19478,7 +19488,6 @@
       <c r="AE177" t="b">
         <v>0</v>
       </c>
-      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
@@ -19501,7 +19510,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>131737775</v>
+        <v>131737740</v>
       </c>
       <c r="B178" t="n">
         <v>93158</v>
@@ -19531,19 +19540,19 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Nystugan Nord, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>614989</v>
+        <v>614746</v>
       </c>
       <c r="R178" t="n">
-        <v>6560288</v>
+        <v>6560453</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19580,7 +19589,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19611,10 +19620,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>131737738</v>
+        <v>131734664</v>
       </c>
       <c r="B179" t="n">
-        <v>93158</v>
+        <v>79021</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19622,38 +19631,34 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>614711</v>
+        <v>615034</v>
       </c>
       <c r="R179" t="n">
-        <v>6560481</v>
+        <v>6560418</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19686,11 +19691,6 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19721,10 +19721,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>131737740</v>
+        <v>131734663</v>
       </c>
       <c r="B180" t="n">
-        <v>93158</v>
+        <v>79021</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19732,38 +19732,34 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>614746</v>
+        <v>614679</v>
       </c>
       <c r="R180" t="n">
-        <v>6560453</v>
+        <v>6560422</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19790,17 +19786,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19831,10 +19822,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>131734664</v>
+        <v>131735737</v>
       </c>
       <c r="B181" t="n">
-        <v>79021</v>
+        <v>92622</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19842,34 +19833,38 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6446</v>
+        <v>366</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>615034</v>
+        <v>615093</v>
       </c>
       <c r="R181" t="n">
-        <v>6560418</v>
+        <v>6560461</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19896,12 +19891,17 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19932,10 +19932,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>131734663</v>
+        <v>131732524</v>
       </c>
       <c r="B182" t="n">
-        <v>79021</v>
+        <v>78930</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19943,34 +19943,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>614679</v>
+        <v>614915</v>
       </c>
       <c r="R182" t="n">
-        <v>6560422</v>
+        <v>6560407</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19997,12 +19997,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD182" t="b">

--- a/artfynd/A 43282-2024 artfynd.xlsx
+++ b/artfynd/A 43282-2024 artfynd.xlsx
@@ -2583,45 +2583,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131732769</v>
+        <v>131737607</v>
       </c>
       <c r="B19" t="n">
-        <v>93126</v>
+        <v>93164</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615104</v>
+        <v>614643</v>
       </c>
       <c r="R19" t="n">
-        <v>6560485</v>
+        <v>6560479</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2648,17 +2648,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Återkommer spritt</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2689,10 +2684,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131737607</v>
+        <v>131740240</v>
       </c>
       <c r="B20" t="n">
-        <v>93164</v>
+        <v>92770</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2700,34 +2695,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>614643</v>
+        <v>615041</v>
       </c>
       <c r="R20" t="n">
-        <v>6560479</v>
+        <v>6560443</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,32 +2785,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131740240</v>
+        <v>131732769</v>
       </c>
       <c r="B21" t="n">
-        <v>92770</v>
+        <v>93126</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2825,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615041</v>
+        <v>615104</v>
       </c>
       <c r="R21" t="n">
-        <v>6560443</v>
+        <v>6560485</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2855,12 +2850,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Återkommer spritt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3533,10 +3533,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131737762</v>
+        <v>131738985</v>
       </c>
       <c r="B28" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3544,38 +3544,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>614855</v>
+        <v>614827</v>
       </c>
       <c r="R28" t="n">
-        <v>6560397</v>
+        <v>6560518</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3602,17 +3598,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3643,10 +3634,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131737779</v>
+        <v>131739020</v>
       </c>
       <c r="B29" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3654,38 +3645,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>615173</v>
+        <v>614839</v>
       </c>
       <c r="R29" t="n">
-        <v>6560476</v>
+        <v>6560502</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3718,11 +3705,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3753,10 +3735,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131737781</v>
+        <v>131740362</v>
       </c>
       <c r="B30" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3764,23 +3746,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>1</t>
@@ -3792,10 +3770,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615158</v>
+        <v>614974</v>
       </c>
       <c r="R30" t="n">
-        <v>6560491</v>
+        <v>6560411</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3841,6 +3819,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3863,7 +3842,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131737746</v>
+        <v>131737762</v>
       </c>
       <c r="B31" t="n">
         <v>93164</v>
@@ -3898,14 +3877,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>614777</v>
+        <v>614855</v>
       </c>
       <c r="R31" t="n">
-        <v>6560432</v>
+        <v>6560397</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3973,7 +3952,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131737750</v>
+        <v>131737779</v>
       </c>
       <c r="B32" t="n">
         <v>93164</v>
@@ -4003,19 +3982,19 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>614846</v>
+        <v>615173</v>
       </c>
       <c r="R32" t="n">
-        <v>6560435</v>
+        <v>6560476</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4052,7 +4031,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4083,7 +4062,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737765</v>
+        <v>131737781</v>
       </c>
       <c r="B33" t="n">
         <v>93164</v>
@@ -4113,19 +4092,19 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>614814</v>
+        <v>615158</v>
       </c>
       <c r="R33" t="n">
-        <v>6560371</v>
+        <v>6560491</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4162,7 +4141,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4193,10 +4172,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131738985</v>
+        <v>131737746</v>
       </c>
       <c r="B34" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4204,34 +4183,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>614827</v>
+        <v>614777</v>
       </c>
       <c r="R34" t="n">
-        <v>6560518</v>
+        <v>6560432</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4258,12 +4241,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4294,10 +4282,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131739020</v>
+        <v>131737750</v>
       </c>
       <c r="B35" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4305,34 +4293,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>614839</v>
+        <v>614846</v>
       </c>
       <c r="R35" t="n">
-        <v>6560502</v>
+        <v>6560435</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4365,6 +4357,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4395,10 +4392,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131740362</v>
+        <v>131737765</v>
       </c>
       <c r="B36" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4406,34 +4403,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>614974</v>
+        <v>614814</v>
       </c>
       <c r="R36" t="n">
-        <v>6560411</v>
+        <v>6560371</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4470,7 +4471,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4479,7 +4480,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -6912,45 +6912,49 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131736994</v>
+        <v>131737749</v>
       </c>
       <c r="B60" t="n">
-        <v>91323</v>
+        <v>93164</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2051</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>615157</v>
+        <v>614849</v>
       </c>
       <c r="R60" t="n">
-        <v>6560412</v>
+        <v>6560446</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6977,17 +6981,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ramaria XXL</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7018,7 +7022,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131737749</v>
+        <v>131737714</v>
       </c>
       <c r="B61" t="n">
         <v>93164</v>
@@ -7048,7 +7052,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7057,10 +7061,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>614849</v>
+        <v>614933</v>
       </c>
       <c r="R61" t="n">
-        <v>6560446</v>
+        <v>6560495</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7097,7 +7101,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7128,10 +7132,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131737714</v>
+        <v>131739038</v>
       </c>
       <c r="B62" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7139,38 +7143,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>614933</v>
+        <v>614743</v>
       </c>
       <c r="R62" t="n">
-        <v>6560495</v>
+        <v>6560468</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7197,17 +7197,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>60+</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7238,32 +7233,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131739019</v>
+        <v>131736994</v>
       </c>
       <c r="B63" t="n">
-        <v>79885</v>
+        <v>91323</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>2051</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7273,10 +7268,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>615022</v>
+        <v>615157</v>
       </c>
       <c r="R63" t="n">
-        <v>6560428</v>
+        <v>6560412</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7303,12 +7298,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ramaria XXL</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7339,45 +7339,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131739038</v>
+        <v>131734255</v>
       </c>
       <c r="B64" t="n">
-        <v>79885</v>
+        <v>97375</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>990</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>614743</v>
+        <v>614670</v>
       </c>
       <c r="R64" t="n">
-        <v>6560468</v>
+        <v>6560435</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7440,10 +7440,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131734662</v>
+        <v>131737717</v>
       </c>
       <c r="B65" t="n">
-        <v>79023</v>
+        <v>93164</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7451,34 +7451,38 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>614665</v>
+        <v>614838</v>
       </c>
       <c r="R65" t="n">
-        <v>6560415</v>
+        <v>6560512</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7505,12 +7509,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7541,45 +7550,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131734255</v>
+        <v>131740397</v>
       </c>
       <c r="B66" t="n">
-        <v>97375</v>
+        <v>93155</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>990</v>
+        <v>5449</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Warnst.) R.M.Schust.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>614670</v>
+        <v>614907</v>
       </c>
       <c r="R66" t="n">
-        <v>6560435</v>
+        <v>6560338</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7606,12 +7615,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>5 st</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7620,6 +7634,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7642,10 +7657,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131737717</v>
+        <v>131739019</v>
       </c>
       <c r="B67" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7653,38 +7668,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>614838</v>
+        <v>615022</v>
       </c>
       <c r="R67" t="n">
-        <v>6560512</v>
+        <v>6560428</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7717,11 +7728,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7752,10 +7758,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131740397</v>
+        <v>131734662</v>
       </c>
       <c r="B68" t="n">
-        <v>93155</v>
+        <v>79023</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7763,34 +7769,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>614907</v>
+        <v>614665</v>
       </c>
       <c r="R68" t="n">
-        <v>6560338</v>
+        <v>6560415</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7817,17 +7823,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>5 st</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7836,7 +7837,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -9803,49 +9803,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131737732</v>
+        <v>131733475</v>
       </c>
       <c r="B87" t="n">
-        <v>93164</v>
+        <v>8443</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5966</v>
+        <v>106554</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>614684</v>
+        <v>614840</v>
       </c>
       <c r="R87" t="n">
-        <v>6560422</v>
+        <v>6560403</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9872,17 +9868,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9913,10 +9904,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131740366</v>
+        <v>131737724</v>
       </c>
       <c r="B88" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9924,22 +9915,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9948,10 +9943,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>614682</v>
+        <v>614765</v>
       </c>
       <c r="R88" t="n">
-        <v>6560491</v>
+        <v>6560506</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9988,7 +9983,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9997,7 +9992,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -10020,10 +10014,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131740392</v>
+        <v>131737718</v>
       </c>
       <c r="B89" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10031,22 +10025,26 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10055,10 +10053,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>614832</v>
+        <v>614844</v>
       </c>
       <c r="R89" t="n">
-        <v>6560458</v>
+        <v>6560496</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10085,17 +10083,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>10 st</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10104,7 +10102,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10127,10 +10124,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131740342</v>
+        <v>131737745</v>
       </c>
       <c r="B90" t="n">
-        <v>93152</v>
+        <v>93164</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10138,38 +10135,38 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>48</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>614971</v>
+        <v>614779</v>
       </c>
       <c r="R90" t="n">
-        <v>6560251</v>
+        <v>6560385</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10196,17 +10193,17 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>12 st</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10237,10 +10234,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131737265</v>
+        <v>131739025</v>
       </c>
       <c r="B91" t="n">
-        <v>93118</v>
+        <v>79885</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10248,38 +10245,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>615132</v>
+        <v>614887</v>
       </c>
       <c r="R91" t="n">
-        <v>6560489</v>
+        <v>6560423</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10306,17 +10299,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>4 st</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10347,45 +10335,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131732767</v>
+        <v>131737045</v>
       </c>
       <c r="B92" t="n">
-        <v>93126</v>
+        <v>92137</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>615105</v>
+        <v>614622</v>
       </c>
       <c r="R92" t="n">
-        <v>6560378</v>
+        <v>6560529</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10418,11 +10406,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Spritt i området</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10453,7 +10436,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131737724</v>
+        <v>131737732</v>
       </c>
       <c r="B93" t="n">
         <v>93164</v>
@@ -10488,14 +10471,14 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>614765</v>
+        <v>614684</v>
       </c>
       <c r="R93" t="n">
-        <v>6560506</v>
+        <v>6560422</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10563,10 +10546,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131737718</v>
+        <v>131740366</v>
       </c>
       <c r="B94" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10574,26 +10557,22 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -10602,10 +10581,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>614844</v>
+        <v>614682</v>
       </c>
       <c r="R94" t="n">
-        <v>6560496</v>
+        <v>6560491</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10642,7 +10621,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10651,6 +10630,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10673,10 +10653,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131737745</v>
+        <v>131740392</v>
       </c>
       <c r="B95" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10684,38 +10664,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>614779</v>
+        <v>614832</v>
       </c>
       <c r="R95" t="n">
-        <v>6560385</v>
+        <v>6560458</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10742,17 +10718,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>10 st</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10761,6 +10737,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10783,10 +10760,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131739025</v>
+        <v>131740342</v>
       </c>
       <c r="B96" t="n">
-        <v>79885</v>
+        <v>93152</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10794,34 +10771,38 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>5448</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>614887</v>
+        <v>614971</v>
       </c>
       <c r="R96" t="n">
-        <v>6560423</v>
+        <v>6560251</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10848,12 +10829,17 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>12 st</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10884,45 +10870,49 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131733475</v>
+        <v>131737265</v>
       </c>
       <c r="B97" t="n">
-        <v>8443</v>
+        <v>93118</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106554</v>
+        <v>4361</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>614840</v>
+        <v>615132</v>
       </c>
       <c r="R97" t="n">
-        <v>6560403</v>
+        <v>6560489</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10949,12 +10939,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10985,45 +10980,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131737045</v>
+        <v>131732767</v>
       </c>
       <c r="B98" t="n">
-        <v>92137</v>
+        <v>93126</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>614622</v>
+        <v>615105</v>
       </c>
       <c r="R98" t="n">
-        <v>6560529</v>
+        <v>6560378</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11056,6 +11051,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Spritt i området</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12135,10 +12135,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131732521</v>
+        <v>131737715</v>
       </c>
       <c r="B109" t="n">
-        <v>78932</v>
+        <v>93164</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12146,34 +12146,38 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>614661</v>
+        <v>614932</v>
       </c>
       <c r="R109" t="n">
-        <v>6560444</v>
+        <v>6560487</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12206,6 +12210,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12236,10 +12245,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131740080</v>
+        <v>131737780</v>
       </c>
       <c r="B110" t="n">
-        <v>91859</v>
+        <v>93164</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12247,34 +12256,38 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>615060</v>
+        <v>615164</v>
       </c>
       <c r="R110" t="n">
-        <v>6560430</v>
+        <v>6560465</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12301,12 +12314,17 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12337,10 +12355,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131737715</v>
+        <v>131732521</v>
       </c>
       <c r="B111" t="n">
-        <v>93164</v>
+        <v>78932</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12348,38 +12366,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>614932</v>
+        <v>614661</v>
       </c>
       <c r="R111" t="n">
-        <v>6560487</v>
+        <v>6560444</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12412,11 +12426,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12447,10 +12456,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131737780</v>
+        <v>131740080</v>
       </c>
       <c r="B112" t="n">
-        <v>93164</v>
+        <v>91859</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12458,38 +12467,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>615164</v>
+        <v>615060</v>
       </c>
       <c r="R112" t="n">
-        <v>6560465</v>
+        <v>6560430</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12516,17 +12521,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13401,10 +13401,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131739040</v>
+        <v>131737605</v>
       </c>
       <c r="B121" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13412,34 +13412,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>614705</v>
+        <v>614921</v>
       </c>
       <c r="R121" t="n">
-        <v>6560468</v>
+        <v>6560349</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13466,12 +13466,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13502,45 +13502,49 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131733476</v>
+        <v>131737753</v>
       </c>
       <c r="B122" t="n">
-        <v>8443</v>
+        <v>93164</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106554</v>
+        <v>5966</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>614831</v>
+        <v>614883</v>
       </c>
       <c r="R122" t="n">
-        <v>6560599</v>
+        <v>6560422</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13567,12 +13571,17 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13603,45 +13612,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131740365</v>
+        <v>131733367</v>
       </c>
       <c r="B123" t="n">
-        <v>93155</v>
+        <v>92496</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5449</v>
+        <v>6031</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>614741</v>
+        <v>614939</v>
       </c>
       <c r="R123" t="n">
-        <v>6560508</v>
+        <v>6560438</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13676,18 +13685,12 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13710,10 +13713,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131740367</v>
+        <v>131737719</v>
       </c>
       <c r="B124" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13721,22 +13724,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -13745,10 +13752,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>614742</v>
+        <v>614817</v>
       </c>
       <c r="R124" t="n">
-        <v>6560443</v>
+        <v>6560509</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13785,7 +13792,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13794,7 +13801,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13817,7 +13823,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131737741</v>
+        <v>131737768</v>
       </c>
       <c r="B125" t="n">
         <v>93164</v>
@@ -13847,19 +13853,19 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>614754</v>
+        <v>614843</v>
       </c>
       <c r="R125" t="n">
-        <v>6560449</v>
+        <v>6560322</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13896,7 +13902,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13927,10 +13933,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131733306</v>
+        <v>131737778</v>
       </c>
       <c r="B126" t="n">
-        <v>93120</v>
+        <v>93164</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13938,38 +13944,38 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>614689</v>
+        <v>615115</v>
       </c>
       <c r="R126" t="n">
-        <v>6560516</v>
+        <v>6560377</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13996,17 +14002,17 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>1 St</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14037,45 +14043,49 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131732765</v>
+        <v>131737751</v>
       </c>
       <c r="B127" t="n">
-        <v>93126</v>
+        <v>93164</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>614878</v>
+        <v>614860</v>
       </c>
       <c r="R127" t="n">
-        <v>6560511</v>
+        <v>6560430</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14102,17 +14112,17 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Förekommer spritt rikligt</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14143,7 +14153,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131737605</v>
+        <v>131737604</v>
       </c>
       <c r="B128" t="n">
         <v>93164</v>
@@ -14174,14 +14184,14 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>614921</v>
+        <v>615114</v>
       </c>
       <c r="R128" t="n">
-        <v>6560349</v>
+        <v>6560473</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14244,10 +14254,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131737753</v>
+        <v>131739040</v>
       </c>
       <c r="B129" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14255,38 +14265,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>614883</v>
+        <v>614705</v>
       </c>
       <c r="R129" t="n">
-        <v>6560422</v>
+        <v>6560468</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14313,17 +14319,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14354,10 +14355,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131733367</v>
+        <v>131733476</v>
       </c>
       <c r="B130" t="n">
-        <v>92496</v>
+        <v>8443</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14365,34 +14366,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6031</v>
+        <v>106554</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>614939</v>
+        <v>614831</v>
       </c>
       <c r="R130" t="n">
-        <v>6560438</v>
+        <v>6560599</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14419,12 +14420,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14455,10 +14456,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131737719</v>
+        <v>131740365</v>
       </c>
       <c r="B131" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14466,26 +14467,22 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -14494,10 +14491,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>614817</v>
+        <v>614741</v>
       </c>
       <c r="R131" t="n">
-        <v>6560509</v>
+        <v>6560508</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14534,7 +14531,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14543,6 +14540,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14565,10 +14563,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131737768</v>
+        <v>131740367</v>
       </c>
       <c r="B132" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14576,38 +14574,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>614843</v>
+        <v>614742</v>
       </c>
       <c r="R132" t="n">
-        <v>6560322</v>
+        <v>6560443</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14644,7 +14638,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14653,6 +14647,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14675,7 +14670,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131737778</v>
+        <v>131737741</v>
       </c>
       <c r="B133" t="n">
         <v>93164</v>
@@ -14705,19 +14700,19 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>615115</v>
+        <v>614754</v>
       </c>
       <c r="R133" t="n">
-        <v>6560377</v>
+        <v>6560449</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14754,7 +14749,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14785,10 +14780,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131737751</v>
+        <v>131733306</v>
       </c>
       <c r="B134" t="n">
-        <v>93164</v>
+        <v>93120</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14796,26 +14791,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -14824,10 +14819,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>614860</v>
+        <v>614689</v>
       </c>
       <c r="R134" t="n">
-        <v>6560430</v>
+        <v>6560516</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14854,17 +14849,17 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1 St</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14895,45 +14890,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131737604</v>
+        <v>131732765</v>
       </c>
       <c r="B135" t="n">
-        <v>93164</v>
+        <v>93126</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>615114</v>
+        <v>614878</v>
       </c>
       <c r="R135" t="n">
-        <v>6560473</v>
+        <v>6560511</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14960,12 +14955,17 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Förekommer spritt rikligt</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14996,45 +14996,49 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131737932</v>
+        <v>131733304</v>
       </c>
       <c r="B136" t="n">
-        <v>8454</v>
+        <v>93120</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>106545</v>
+        <v>4362</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>615059</v>
+        <v>614759</v>
       </c>
       <c r="R136" t="n">
-        <v>6560324</v>
+        <v>6560440</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15071,7 +15075,7 @@
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Förekommer spritt på tallågor</t>
+          <t>8 st</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15102,45 +15106,49 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>131740304</v>
+        <v>131737743</v>
       </c>
       <c r="B137" t="n">
-        <v>91331</v>
+        <v>93164</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>256703</v>
+        <v>5966</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>615108</v>
+        <v>614731</v>
       </c>
       <c r="R137" t="n">
-        <v>6560375</v>
+        <v>6560390</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15167,12 +15175,17 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15203,7 +15216,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>131737743</v>
+        <v>131737707</v>
       </c>
       <c r="B138" t="n">
         <v>93164</v>
@@ -15233,19 +15246,19 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>614731</v>
+        <v>614934</v>
       </c>
       <c r="R138" t="n">
-        <v>6560390</v>
+        <v>6560422</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15282,7 +15295,7 @@
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15313,7 +15326,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>131737707</v>
+        <v>131737748</v>
       </c>
       <c r="B139" t="n">
         <v>93164</v>
@@ -15343,19 +15356,19 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>614934</v>
+        <v>614792</v>
       </c>
       <c r="R139" t="n">
-        <v>6560422</v>
+        <v>6560431</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15392,7 +15405,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15423,10 +15436,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>131737748</v>
+        <v>131740394</v>
       </c>
       <c r="B140" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15434,26 +15447,22 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -15462,10 +15471,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>614792</v>
+        <v>614731</v>
       </c>
       <c r="R140" t="n">
-        <v>6560431</v>
+        <v>6560512</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15492,17 +15501,17 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1 st</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15511,6 +15520,7 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15533,10 +15543,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>131739551</v>
+        <v>131740402</v>
       </c>
       <c r="B141" t="n">
-        <v>91838</v>
+        <v>93155</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15544,34 +15554,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1202</v>
+        <v>5449</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>614622</v>
+        <v>615135</v>
       </c>
       <c r="R141" t="n">
-        <v>6560528</v>
+        <v>6560485</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15598,12 +15608,17 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Ca 25st</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15612,6 +15627,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15634,10 +15650,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>131740394</v>
+        <v>131739551</v>
       </c>
       <c r="B142" t="n">
-        <v>93155</v>
+        <v>91838</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15645,34 +15661,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5449</v>
+        <v>1202</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>614731</v>
+        <v>614622</v>
       </c>
       <c r="R142" t="n">
-        <v>6560512</v>
+        <v>6560528</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15699,17 +15715,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>1 st</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15718,7 +15729,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15741,10 +15751,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>131740402</v>
+        <v>131740243</v>
       </c>
       <c r="B143" t="n">
-        <v>93155</v>
+        <v>92770</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15752,34 +15762,38 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5449</v>
+        <v>4745</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr"/>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>615135</v>
+        <v>614829</v>
       </c>
       <c r="R143" t="n">
-        <v>6560485</v>
+        <v>6560371</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15806,17 +15820,17 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ca 25st</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15825,7 +15839,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -15848,49 +15861,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>131733304</v>
+        <v>131737932</v>
       </c>
       <c r="B144" t="n">
-        <v>93120</v>
+        <v>8454</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4362</v>
+        <v>106545</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>614759</v>
+        <v>615059</v>
       </c>
       <c r="R144" t="n">
-        <v>6560440</v>
+        <v>6560324</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15927,7 +15936,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>8 st</t>
+          <t>Förekommer spritt på tallågor</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15958,49 +15967,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>131740243</v>
+        <v>131740304</v>
       </c>
       <c r="B145" t="n">
-        <v>92770</v>
+        <v>91331</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4745</v>
+        <v>256703</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>614829</v>
+        <v>615108</v>
       </c>
       <c r="R145" t="n">
-        <v>6560371</v>
+        <v>6560375</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16027,17 +16032,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18856,10 +18856,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>131737721</v>
+        <v>131735737</v>
       </c>
       <c r="B172" t="n">
-        <v>93164</v>
+        <v>92628</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18867,21 +18867,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5966</v>
+        <v>366</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -18891,14 +18891,14 @@
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>614776</v>
+        <v>615093</v>
       </c>
       <c r="R172" t="n">
-        <v>6560488</v>
+        <v>6560461</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18925,17 +18925,17 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18966,10 +18966,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>131737775</v>
+        <v>131732524</v>
       </c>
       <c r="B173" t="n">
-        <v>93164</v>
+        <v>78932</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18977,38 +18977,34 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Nystugan Nord, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>614989</v>
+        <v>614915</v>
       </c>
       <c r="R173" t="n">
-        <v>6560288</v>
+        <v>6560407</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19035,17 +19031,12 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>14</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19278,10 +19269,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>131735737</v>
+        <v>131740359</v>
       </c>
       <c r="B176" t="n">
-        <v>92628</v>
+        <v>93155</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19289,38 +19280,34 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>366</v>
+        <v>5449</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>615093</v>
+        <v>614877</v>
       </c>
       <c r="R176" t="n">
-        <v>6560461</v>
+        <v>6560513</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19347,17 +19334,17 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19366,6 +19353,7 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -19388,10 +19376,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>131732524</v>
+        <v>131737740</v>
       </c>
       <c r="B177" t="n">
-        <v>78932</v>
+        <v>93164</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19399,34 +19387,38 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>614915</v>
+        <v>614746</v>
       </c>
       <c r="R177" t="n">
-        <v>6560407</v>
+        <v>6560453</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19453,12 +19445,17 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19489,10 +19486,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>131740359</v>
+        <v>131737742</v>
       </c>
       <c r="B178" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19500,22 +19497,26 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -19524,10 +19525,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>614877</v>
+        <v>614738</v>
       </c>
       <c r="R178" t="n">
-        <v>6560513</v>
+        <v>6560442</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19554,17 +19555,17 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19573,7 +19574,6 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
-      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -19596,7 +19596,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>131737740</v>
+        <v>131737738</v>
       </c>
       <c r="B179" t="n">
         <v>93164</v>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -19635,10 +19635,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>614746</v>
+        <v>614711</v>
       </c>
       <c r="R179" t="n">
-        <v>6560453</v>
+        <v>6560481</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19706,10 +19706,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>131737742</v>
+        <v>131740399</v>
       </c>
       <c r="B180" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19717,23 +19717,19 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
           <t>5</t>
@@ -19741,14 +19737,14 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>614738</v>
+        <v>614904</v>
       </c>
       <c r="R180" t="n">
-        <v>6560442</v>
+        <v>6560330</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19775,17 +19771,17 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 st</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19794,6 +19790,7 @@
       <c r="AE180" t="b">
         <v>0</v>
       </c>
+      <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
       </c>
@@ -19816,7 +19813,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>131737738</v>
+        <v>131737721</v>
       </c>
       <c r="B181" t="n">
         <v>93164</v>
@@ -19846,7 +19843,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -19855,10 +19852,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>614711</v>
+        <v>614776</v>
       </c>
       <c r="R181" t="n">
-        <v>6560481</v>
+        <v>6560488</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19895,7 +19892,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19926,10 +19923,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>131740399</v>
+        <v>131737775</v>
       </c>
       <c r="B182" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19937,34 +19934,38 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nystugan Nord, Srm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>614904</v>
+        <v>614989</v>
       </c>
       <c r="R182" t="n">
-        <v>6560330</v>
+        <v>6560288</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19991,17 +19992,17 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>5 st</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20010,7 +20011,6 @@
       <c r="AE182" t="b">
         <v>0</v>
       </c>
-      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43282-2024 artfynd.xlsx
+++ b/artfynd/A 43282-2024 artfynd.xlsx
@@ -3533,10 +3533,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131738985</v>
+        <v>131740362</v>
       </c>
       <c r="B28" t="n">
-        <v>79885</v>
+        <v>93155</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3544,34 +3544,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>614827</v>
+        <v>614974</v>
       </c>
       <c r="R28" t="n">
-        <v>6560518</v>
+        <v>6560411</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3598,12 +3598,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3612,6 +3617,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3634,10 +3640,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131739020</v>
+        <v>131737762</v>
       </c>
       <c r="B29" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3645,34 +3651,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>614839</v>
+        <v>614855</v>
       </c>
       <c r="R29" t="n">
-        <v>6560502</v>
+        <v>6560397</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3705,6 +3715,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3735,10 +3750,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131740362</v>
+        <v>131737779</v>
       </c>
       <c r="B30" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3746,22 +3761,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3770,10 +3789,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>614974</v>
+        <v>615173</v>
       </c>
       <c r="R30" t="n">
-        <v>6560411</v>
+        <v>6560476</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3810,7 +3829,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3819,7 +3838,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3842,7 +3860,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131737762</v>
+        <v>131737781</v>
       </c>
       <c r="B31" t="n">
         <v>93164</v>
@@ -3872,19 +3890,19 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>614855</v>
+        <v>615158</v>
       </c>
       <c r="R31" t="n">
-        <v>6560397</v>
+        <v>6560491</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3921,7 +3939,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3952,7 +3970,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131737779</v>
+        <v>131737746</v>
       </c>
       <c r="B32" t="n">
         <v>93164</v>
@@ -3982,19 +4000,19 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615173</v>
+        <v>614777</v>
       </c>
       <c r="R32" t="n">
-        <v>6560476</v>
+        <v>6560432</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4031,7 +4049,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4062,7 +4080,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737781</v>
+        <v>131737750</v>
       </c>
       <c r="B33" t="n">
         <v>93164</v>
@@ -4092,19 +4110,19 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>615158</v>
+        <v>614846</v>
       </c>
       <c r="R33" t="n">
-        <v>6560491</v>
+        <v>6560435</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4141,7 +4159,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4172,7 +4190,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131737746</v>
+        <v>131737765</v>
       </c>
       <c r="B34" t="n">
         <v>93164</v>
@@ -4202,19 +4220,19 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>614777</v>
+        <v>614814</v>
       </c>
       <c r="R34" t="n">
-        <v>6560432</v>
+        <v>6560371</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4251,7 +4269,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4282,10 +4300,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131737750</v>
+        <v>131738985</v>
       </c>
       <c r="B35" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4293,38 +4311,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>614846</v>
+        <v>614827</v>
       </c>
       <c r="R35" t="n">
-        <v>6560435</v>
+        <v>6560518</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4351,17 +4365,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4392,10 +4401,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131737765</v>
+        <v>131739020</v>
       </c>
       <c r="B36" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4403,38 +4412,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>614814</v>
+        <v>614839</v>
       </c>
       <c r="R36" t="n">
-        <v>6560371</v>
+        <v>6560502</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4467,11 +4472,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4713,10 +4713,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131738986</v>
+        <v>131737733</v>
       </c>
       <c r="B39" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4724,34 +4724,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>614832</v>
+        <v>614695</v>
       </c>
       <c r="R39" t="n">
-        <v>6560556</v>
+        <v>6560413</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4778,12 +4778,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4814,10 +4814,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131739037</v>
+        <v>131737764</v>
       </c>
       <c r="B40" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4825,34 +4825,38 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>615086</v>
+        <v>614836</v>
       </c>
       <c r="R40" t="n">
-        <v>6560375</v>
+        <v>6560376</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4879,12 +4883,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4915,10 +4924,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131739024</v>
+        <v>131737713</v>
       </c>
       <c r="B41" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4926,21 +4935,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4950,10 +4959,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>614774</v>
+        <v>614935</v>
       </c>
       <c r="R41" t="n">
-        <v>6560505</v>
+        <v>6560472</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5016,10 +5025,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131736037</v>
+        <v>131738986</v>
       </c>
       <c r="B42" t="n">
-        <v>92076</v>
+        <v>79885</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5027,34 +5036,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1101</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>614602</v>
+        <v>614832</v>
       </c>
       <c r="R42" t="n">
-        <v>6560488</v>
+        <v>6560556</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5081,12 +5090,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5117,10 +5126,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131740334</v>
+        <v>131739037</v>
       </c>
       <c r="B43" t="n">
-        <v>93152</v>
+        <v>79885</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5128,34 +5137,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5448</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>614945</v>
+        <v>615086</v>
       </c>
       <c r="R43" t="n">
-        <v>6560495</v>
+        <v>6560375</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5182,12 +5191,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5218,10 +5227,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131737733</v>
+        <v>131739024</v>
       </c>
       <c r="B44" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5229,34 +5238,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>614695</v>
+        <v>614774</v>
       </c>
       <c r="R44" t="n">
-        <v>6560413</v>
+        <v>6560505</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5319,10 +5328,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131737764</v>
+        <v>131736037</v>
       </c>
       <c r="B45" t="n">
-        <v>93164</v>
+        <v>92076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5330,38 +5339,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>1101</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>614836</v>
+        <v>614602</v>
       </c>
       <c r="R45" t="n">
-        <v>6560376</v>
+        <v>6560488</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5394,11 +5399,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5429,10 +5429,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131737713</v>
+        <v>131740334</v>
       </c>
       <c r="B46" t="n">
-        <v>93164</v>
+        <v>93152</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5440,21 +5440,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5464,10 +5464,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>614935</v>
+        <v>614945</v>
       </c>
       <c r="R46" t="n">
-        <v>6560472</v>
+        <v>6560495</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5530,10 +5530,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131739023</v>
+        <v>131740368</v>
       </c>
       <c r="B47" t="n">
-        <v>79885</v>
+        <v>93155</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5541,34 +5541,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>614757</v>
+        <v>614772</v>
       </c>
       <c r="R47" t="n">
-        <v>6560461</v>
+        <v>6560415</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5603,12 +5603,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5631,10 +5637,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131740368</v>
+        <v>131740341</v>
       </c>
       <c r="B48" t="n">
-        <v>93155</v>
+        <v>93152</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5642,34 +5648,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>614772</v>
+        <v>614963</v>
       </c>
       <c r="R48" t="n">
-        <v>6560415</v>
+        <v>6560256</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5696,17 +5706,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8 st</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5715,7 +5725,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5738,10 +5747,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131740341</v>
+        <v>131737728</v>
       </c>
       <c r="B49" t="n">
-        <v>93152</v>
+        <v>93164</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5749,38 +5758,38 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>614963</v>
+        <v>614659</v>
       </c>
       <c r="R49" t="n">
-        <v>6560256</v>
+        <v>6560444</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5807,17 +5816,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>8 st</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5848,7 +5857,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737728</v>
+        <v>131737734</v>
       </c>
       <c r="B50" t="n">
         <v>93164</v>
@@ -5878,19 +5887,19 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>614659</v>
+        <v>614708</v>
       </c>
       <c r="R50" t="n">
-        <v>6560444</v>
+        <v>6560403</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5927,7 +5936,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5958,10 +5967,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737734</v>
+        <v>131739023</v>
       </c>
       <c r="B51" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5969,38 +5978,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>614708</v>
+        <v>614757</v>
       </c>
       <c r="R51" t="n">
-        <v>6560403</v>
+        <v>6560461</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6033,11 +6038,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6481,10 +6481,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131737712</v>
+        <v>131740242</v>
       </c>
       <c r="B56" t="n">
-        <v>93164</v>
+        <v>92770</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6492,38 +6492,38 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>614922</v>
+        <v>614849</v>
       </c>
       <c r="R56" t="n">
-        <v>6560461</v>
+        <v>6560382</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6591,49 +6591,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131740242</v>
+        <v>131736812</v>
       </c>
       <c r="B57" t="n">
-        <v>92770</v>
+        <v>93138</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>614849</v>
+        <v>614856</v>
       </c>
       <c r="R57" t="n">
-        <v>6560382</v>
+        <v>6560514</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6660,17 +6656,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6701,45 +6692,49 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131736812</v>
+        <v>131735736</v>
       </c>
       <c r="B58" t="n">
-        <v>93138</v>
+        <v>92628</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4366</v>
+        <v>366</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>614856</v>
+        <v>614666</v>
       </c>
       <c r="R58" t="n">
-        <v>6560514</v>
+        <v>6560445</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6766,12 +6761,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6802,10 +6802,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131735736</v>
+        <v>131737712</v>
       </c>
       <c r="B59" t="n">
-        <v>92628</v>
+        <v>93164</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6813,38 +6813,38 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>366</v>
+        <v>5966</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>614666</v>
+        <v>614922</v>
       </c>
       <c r="R59" t="n">
-        <v>6560445</v>
+        <v>6560461</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6871,17 +6871,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>3 st</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7969,37 +7969,33 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131740288</v>
+        <v>131740391</v>
       </c>
       <c r="B70" t="n">
-        <v>93114</v>
+        <v>93155</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>149</v>
+        <v>5449</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8008,10 +8004,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>614871</v>
+        <v>614945</v>
       </c>
       <c r="R70" t="n">
-        <v>6560514</v>
+        <v>6560479</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8038,17 +8034,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8057,6 +8053,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8079,10 +8076,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131740391</v>
+        <v>131740335</v>
       </c>
       <c r="B71" t="n">
-        <v>93155</v>
+        <v>93152</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8090,22 +8087,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8114,10 +8115,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>614945</v>
+        <v>614815</v>
       </c>
       <c r="R71" t="n">
-        <v>6560479</v>
+        <v>6560508</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8144,17 +8145,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>2 st</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8163,7 +8164,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8186,37 +8186,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131740335</v>
+        <v>131740288</v>
       </c>
       <c r="B72" t="n">
-        <v>93152</v>
+        <v>93114</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5448</v>
+        <v>149</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8225,10 +8225,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>614815</v>
+        <v>614871</v>
       </c>
       <c r="R72" t="n">
-        <v>6560508</v>
+        <v>6560514</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8296,45 +8296,49 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131737931</v>
+        <v>131737261</v>
       </c>
       <c r="B73" t="n">
-        <v>8454</v>
+        <v>93118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>4361</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>614669</v>
+        <v>614895</v>
       </c>
       <c r="R73" t="n">
-        <v>6560513</v>
+        <v>6560392</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8361,12 +8365,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8397,49 +8406,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131737261</v>
+        <v>131739788</v>
       </c>
       <c r="B74" t="n">
-        <v>93118</v>
+        <v>92561</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4361</v>
+        <v>3298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>614895</v>
+        <v>615070</v>
       </c>
       <c r="R74" t="n">
-        <v>6560392</v>
+        <v>6560325</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8466,17 +8471,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>4 st</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8507,10 +8507,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131739788</v>
+        <v>131737931</v>
       </c>
       <c r="B75" t="n">
-        <v>92561</v>
+        <v>8454</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8518,34 +8518,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3298</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>615070</v>
+        <v>614669</v>
       </c>
       <c r="R75" t="n">
-        <v>6560325</v>
+        <v>6560513</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9803,45 +9803,49 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131733475</v>
+        <v>131737732</v>
       </c>
       <c r="B87" t="n">
-        <v>8443</v>
+        <v>93164</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106554</v>
+        <v>5966</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>614840</v>
+        <v>614684</v>
       </c>
       <c r="R87" t="n">
-        <v>6560403</v>
+        <v>6560422</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9868,12 +9872,17 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9904,10 +9913,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131737724</v>
+        <v>131740366</v>
       </c>
       <c r="B88" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9915,26 +9924,22 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9943,10 +9948,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>614765</v>
+        <v>614682</v>
       </c>
       <c r="R88" t="n">
-        <v>6560506</v>
+        <v>6560491</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9983,7 +9988,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9992,6 +9997,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -10014,10 +10020,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131737718</v>
+        <v>131740392</v>
       </c>
       <c r="B89" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10025,26 +10031,22 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10053,10 +10055,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>614844</v>
+        <v>614832</v>
       </c>
       <c r="R89" t="n">
-        <v>6560496</v>
+        <v>6560458</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10083,17 +10085,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10 st</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10102,6 +10104,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10124,10 +10127,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131737745</v>
+        <v>131740342</v>
       </c>
       <c r="B90" t="n">
-        <v>93164</v>
+        <v>93152</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10135,38 +10138,38 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>614779</v>
+        <v>614971</v>
       </c>
       <c r="R90" t="n">
-        <v>6560385</v>
+        <v>6560251</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10193,17 +10196,17 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>12 st</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10234,10 +10237,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131739025</v>
+        <v>131737265</v>
       </c>
       <c r="B91" t="n">
-        <v>79885</v>
+        <v>93118</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10245,34 +10248,38 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>614887</v>
+        <v>615132</v>
       </c>
       <c r="R91" t="n">
-        <v>6560423</v>
+        <v>6560489</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10299,12 +10306,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10335,45 +10347,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131737045</v>
+        <v>131732767</v>
       </c>
       <c r="B92" t="n">
-        <v>92137</v>
+        <v>93126</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>614622</v>
+        <v>615105</v>
       </c>
       <c r="R92" t="n">
-        <v>6560529</v>
+        <v>6560378</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10406,6 +10418,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Spritt i området</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10436,7 +10453,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131737732</v>
+        <v>131737724</v>
       </c>
       <c r="B93" t="n">
         <v>93164</v>
@@ -10471,14 +10488,14 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>614684</v>
+        <v>614765</v>
       </c>
       <c r="R93" t="n">
-        <v>6560422</v>
+        <v>6560506</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10546,10 +10563,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131740366</v>
+        <v>131737718</v>
       </c>
       <c r="B94" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10557,22 +10574,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -10581,10 +10602,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>614682</v>
+        <v>614844</v>
       </c>
       <c r="R94" t="n">
-        <v>6560491</v>
+        <v>6560496</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10621,7 +10642,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10630,7 +10651,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10653,10 +10673,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131740392</v>
+        <v>131737745</v>
       </c>
       <c r="B95" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10664,34 +10684,38 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>48</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>614832</v>
+        <v>614779</v>
       </c>
       <c r="R95" t="n">
-        <v>6560458</v>
+        <v>6560385</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10718,17 +10742,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>10 st</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10737,7 +10761,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10760,10 +10783,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131740342</v>
+        <v>131739025</v>
       </c>
       <c r="B96" t="n">
-        <v>93152</v>
+        <v>79885</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10771,38 +10794,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5448</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>614971</v>
+        <v>614887</v>
       </c>
       <c r="R96" t="n">
-        <v>6560251</v>
+        <v>6560423</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10829,17 +10848,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>12 st</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10870,49 +10884,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131737265</v>
+        <v>131733475</v>
       </c>
       <c r="B97" t="n">
-        <v>93118</v>
+        <v>8443</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4361</v>
+        <v>106554</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>615132</v>
+        <v>614840</v>
       </c>
       <c r="R97" t="n">
-        <v>6560489</v>
+        <v>6560403</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10939,17 +10949,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>4 st</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10980,45 +10985,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131732767</v>
+        <v>131737045</v>
       </c>
       <c r="B98" t="n">
-        <v>93126</v>
+        <v>92137</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>615105</v>
+        <v>614622</v>
       </c>
       <c r="R98" t="n">
-        <v>6560378</v>
+        <v>6560529</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11051,11 +11056,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Spritt i området</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11086,49 +11086,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131737722</v>
+        <v>131736992</v>
       </c>
       <c r="B99" t="n">
-        <v>93164</v>
+        <v>91323</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5966</v>
+        <v>2051</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>614773</v>
+        <v>614848</v>
       </c>
       <c r="R99" t="n">
-        <v>6560515</v>
+        <v>6560378</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11155,17 +11151,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>1o</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11196,10 +11187,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131740395</v>
+        <v>131737722</v>
       </c>
       <c r="B100" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11207,22 +11198,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11231,10 +11226,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>614715</v>
+        <v>614773</v>
       </c>
       <c r="R100" t="n">
-        <v>6560514</v>
+        <v>6560515</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11261,17 +11256,17 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>6 st</t>
+          <t>1o</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11280,7 +11275,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11303,7 +11297,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131740398</v>
+        <v>131740395</v>
       </c>
       <c r="B101" t="n">
         <v>93155</v>
@@ -11329,19 +11323,19 @@
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>614907</v>
+        <v>614715</v>
       </c>
       <c r="R101" t="n">
-        <v>6560326</v>
+        <v>6560514</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11378,7 +11372,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>6 st</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11410,10 +11404,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131737757</v>
+        <v>131740398</v>
       </c>
       <c r="B102" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11421,38 +11415,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>614887</v>
+        <v>614907</v>
       </c>
       <c r="R102" t="n">
-        <v>6560362</v>
+        <v>6560326</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11479,17 +11469,17 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11498,6 +11488,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11520,7 +11511,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737776</v>
+        <v>131737757</v>
       </c>
       <c r="B103" t="n">
         <v>93164</v>
@@ -11550,19 +11541,19 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Nystugan Nord, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>615009</v>
+        <v>614887</v>
       </c>
       <c r="R103" t="n">
-        <v>6560307</v>
+        <v>6560362</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11599,7 +11590,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11630,10 +11621,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131739042</v>
+        <v>131737776</v>
       </c>
       <c r="B104" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11641,34 +11632,38 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nord, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>614859</v>
+        <v>615009</v>
       </c>
       <c r="R104" t="n">
-        <v>6560517</v>
+        <v>6560307</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11695,12 +11690,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11832,45 +11832,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131736992</v>
+        <v>131739017</v>
       </c>
       <c r="B106" t="n">
-        <v>91323</v>
+        <v>79885</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2051</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>614848</v>
+        <v>615032</v>
       </c>
       <c r="R106" t="n">
-        <v>6560378</v>
+        <v>6560425</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11933,7 +11933,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131739017</v>
+        <v>131739042</v>
       </c>
       <c r="B107" t="n">
         <v>79885</v>
@@ -11964,14 +11964,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>615032</v>
+        <v>614859</v>
       </c>
       <c r="R107" t="n">
-        <v>6560425</v>
+        <v>6560517</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12135,10 +12135,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131737715</v>
+        <v>131732521</v>
       </c>
       <c r="B109" t="n">
-        <v>93164</v>
+        <v>78932</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12146,38 +12146,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>614932</v>
+        <v>614661</v>
       </c>
       <c r="R109" t="n">
-        <v>6560487</v>
+        <v>6560444</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12210,11 +12206,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12245,10 +12236,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131737780</v>
+        <v>131740080</v>
       </c>
       <c r="B110" t="n">
-        <v>93164</v>
+        <v>91859</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12256,38 +12247,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>615164</v>
+        <v>615060</v>
       </c>
       <c r="R110" t="n">
-        <v>6560465</v>
+        <v>6560430</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12314,17 +12301,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12355,10 +12337,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131732521</v>
+        <v>131737715</v>
       </c>
       <c r="B111" t="n">
-        <v>78932</v>
+        <v>93164</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12366,34 +12348,38 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>614661</v>
+        <v>614932</v>
       </c>
       <c r="R111" t="n">
-        <v>6560444</v>
+        <v>6560487</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12426,6 +12412,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12456,10 +12447,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131740080</v>
+        <v>131737780</v>
       </c>
       <c r="B112" t="n">
-        <v>91859</v>
+        <v>93164</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12467,34 +12458,38 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>615060</v>
+        <v>615164</v>
       </c>
       <c r="R112" t="n">
-        <v>6560430</v>
+        <v>6560465</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12521,12 +12516,17 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -18856,10 +18856,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>131735737</v>
+        <v>131737721</v>
       </c>
       <c r="B172" t="n">
-        <v>92628</v>
+        <v>93164</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18867,21 +18867,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>366</v>
+        <v>5966</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -18891,14 +18891,14 @@
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>615093</v>
+        <v>614776</v>
       </c>
       <c r="R172" t="n">
-        <v>6560461</v>
+        <v>6560488</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18925,17 +18925,17 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18966,10 +18966,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>131732524</v>
+        <v>131737775</v>
       </c>
       <c r="B173" t="n">
-        <v>78932</v>
+        <v>93164</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18977,34 +18977,38 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nystugan Nord, Srm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>614915</v>
+        <v>614989</v>
       </c>
       <c r="R173" t="n">
-        <v>6560407</v>
+        <v>6560288</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19031,12 +19035,17 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>14</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19269,10 +19278,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>131740359</v>
+        <v>131735737</v>
       </c>
       <c r="B176" t="n">
-        <v>93155</v>
+        <v>92628</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19280,34 +19289,38 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>5449</v>
+        <v>366</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr"/>
+          <t>Artomyces pyxidatus</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>614877</v>
+        <v>615093</v>
       </c>
       <c r="R176" t="n">
-        <v>6560513</v>
+        <v>6560461</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19334,17 +19347,17 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19353,7 +19366,6 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
-      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -19376,10 +19388,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>131737740</v>
+        <v>131732524</v>
       </c>
       <c r="B177" t="n">
-        <v>93164</v>
+        <v>78932</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19387,38 +19399,34 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>614746</v>
+        <v>614915</v>
       </c>
       <c r="R177" t="n">
-        <v>6560453</v>
+        <v>6560407</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19445,17 +19453,12 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19486,10 +19489,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>131737742</v>
+        <v>131740359</v>
       </c>
       <c r="B178" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19497,26 +19500,22 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -19525,10 +19524,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>614738</v>
+        <v>614877</v>
       </c>
       <c r="R178" t="n">
-        <v>6560442</v>
+        <v>6560513</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19555,17 +19554,17 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19574,6 +19573,7 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -19596,7 +19596,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>131737738</v>
+        <v>131737740</v>
       </c>
       <c r="B179" t="n">
         <v>93164</v>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -19635,10 +19635,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>614711</v>
+        <v>614746</v>
       </c>
       <c r="R179" t="n">
-        <v>6560481</v>
+        <v>6560453</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19706,10 +19706,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>131740399</v>
+        <v>131737742</v>
       </c>
       <c r="B180" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19717,19 +19717,23 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I180" t="inlineStr">
         <is>
           <t>5</t>
@@ -19737,14 +19741,14 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>614904</v>
+        <v>614738</v>
       </c>
       <c r="R180" t="n">
-        <v>6560330</v>
+        <v>6560442</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19771,17 +19775,17 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>5 st</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19790,7 +19794,6 @@
       <c r="AE180" t="b">
         <v>0</v>
       </c>
-      <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
       </c>
@@ -19813,7 +19816,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>131737721</v>
+        <v>131737738</v>
       </c>
       <c r="B181" t="n">
         <v>93164</v>
@@ -19843,7 +19846,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -19852,10 +19855,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>614776</v>
+        <v>614711</v>
       </c>
       <c r="R181" t="n">
-        <v>6560488</v>
+        <v>6560481</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19892,7 +19895,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19923,10 +19926,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>131737775</v>
+        <v>131740399</v>
       </c>
       <c r="B182" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19934,38 +19937,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Nystugan Nord, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>614989</v>
+        <v>614904</v>
       </c>
       <c r="R182" t="n">
-        <v>6560288</v>
+        <v>6560330</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19992,17 +19991,17 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5 st</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20011,6 +20010,7 @@
       <c r="AE182" t="b">
         <v>0</v>
       </c>
+      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43282-2024 artfynd.xlsx
+++ b/artfynd/A 43282-2024 artfynd.xlsx
@@ -2583,45 +2583,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131737607</v>
+        <v>131732769</v>
       </c>
       <c r="B19" t="n">
-        <v>93164</v>
+        <v>93126</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>614643</v>
+        <v>615104</v>
       </c>
       <c r="R19" t="n">
-        <v>6560479</v>
+        <v>6560485</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2648,12 +2648,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Återkommer spritt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,45 +2790,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131732769</v>
+        <v>131737607</v>
       </c>
       <c r="B21" t="n">
-        <v>93126</v>
+        <v>93164</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615104</v>
+        <v>614643</v>
       </c>
       <c r="R21" t="n">
-        <v>6560485</v>
+        <v>6560479</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2850,17 +2855,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Återkommer spritt</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -6481,10 +6481,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131740242</v>
+        <v>131737712</v>
       </c>
       <c r="B56" t="n">
-        <v>92770</v>
+        <v>93164</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6492,38 +6492,38 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>614849</v>
+        <v>614922</v>
       </c>
       <c r="R56" t="n">
-        <v>6560382</v>
+        <v>6560461</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6591,45 +6591,49 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131736812</v>
+        <v>131740242</v>
       </c>
       <c r="B57" t="n">
-        <v>93138</v>
+        <v>92770</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4366</v>
+        <v>4745</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>614856</v>
+        <v>614849</v>
       </c>
       <c r="R57" t="n">
-        <v>6560514</v>
+        <v>6560382</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6656,12 +6660,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6692,49 +6701,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131735736</v>
+        <v>131736812</v>
       </c>
       <c r="B58" t="n">
-        <v>92628</v>
+        <v>93138</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>366</v>
+        <v>4366</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>614666</v>
+        <v>614856</v>
       </c>
       <c r="R58" t="n">
-        <v>6560445</v>
+        <v>6560514</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6761,17 +6766,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>3 st</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6802,10 +6802,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131737712</v>
+        <v>131735736</v>
       </c>
       <c r="B59" t="n">
-        <v>93164</v>
+        <v>92628</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6813,38 +6813,38 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5966</v>
+        <v>366</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>614922</v>
+        <v>614666</v>
       </c>
       <c r="R59" t="n">
-        <v>6560461</v>
+        <v>6560445</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6871,17 +6871,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6912,49 +6912,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131737749</v>
+        <v>131736994</v>
       </c>
       <c r="B60" t="n">
-        <v>93164</v>
+        <v>91323</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>2051</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>614849</v>
+        <v>615157</v>
       </c>
       <c r="R60" t="n">
-        <v>6560446</v>
+        <v>6560412</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6981,17 +6977,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Ramaria XXL</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7022,7 +7018,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131737714</v>
+        <v>131737749</v>
       </c>
       <c r="B61" t="n">
         <v>93164</v>
@@ -7052,7 +7048,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7061,10 +7057,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>614933</v>
+        <v>614849</v>
       </c>
       <c r="R61" t="n">
-        <v>6560495</v>
+        <v>6560446</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7101,7 +7097,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7132,10 +7128,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131739038</v>
+        <v>131737714</v>
       </c>
       <c r="B62" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7143,34 +7139,38 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>614743</v>
+        <v>614933</v>
       </c>
       <c r="R62" t="n">
-        <v>6560468</v>
+        <v>6560495</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7197,12 +7197,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>60+</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7233,32 +7238,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131736994</v>
+        <v>131739019</v>
       </c>
       <c r="B63" t="n">
-        <v>91323</v>
+        <v>79885</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2051</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7268,10 +7273,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>615157</v>
+        <v>615022</v>
       </c>
       <c r="R63" t="n">
-        <v>6560412</v>
+        <v>6560428</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7298,17 +7303,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ramaria XXL</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7339,45 +7339,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131734255</v>
+        <v>131739038</v>
       </c>
       <c r="B64" t="n">
-        <v>97375</v>
+        <v>79885</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>990</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>614670</v>
+        <v>614743</v>
       </c>
       <c r="R64" t="n">
-        <v>6560435</v>
+        <v>6560468</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7440,10 +7440,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131737717</v>
+        <v>131734662</v>
       </c>
       <c r="B65" t="n">
-        <v>93164</v>
+        <v>79023</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7451,38 +7451,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>614838</v>
+        <v>614665</v>
       </c>
       <c r="R65" t="n">
-        <v>6560512</v>
+        <v>6560415</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7509,17 +7505,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7550,45 +7541,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131740397</v>
+        <v>131734255</v>
       </c>
       <c r="B66" t="n">
-        <v>93155</v>
+        <v>97375</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5449</v>
+        <v>990</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Lophozia ascendens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Warnst.) R.M.Schust.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>614907</v>
+        <v>614670</v>
       </c>
       <c r="R66" t="n">
-        <v>6560338</v>
+        <v>6560435</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7615,17 +7606,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>5 st</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7634,7 +7620,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7657,10 +7642,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131739019</v>
+        <v>131737717</v>
       </c>
       <c r="B67" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7668,34 +7653,38 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>615022</v>
+        <v>614838</v>
       </c>
       <c r="R67" t="n">
-        <v>6560428</v>
+        <v>6560512</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7728,6 +7717,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7758,10 +7752,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131734662</v>
+        <v>131740397</v>
       </c>
       <c r="B68" t="n">
-        <v>79023</v>
+        <v>93155</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7769,34 +7763,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>614665</v>
+        <v>614907</v>
       </c>
       <c r="R68" t="n">
-        <v>6560415</v>
+        <v>6560338</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7823,12 +7817,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>5 st</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7837,6 +7836,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7969,33 +7969,37 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131740391</v>
+        <v>131740288</v>
       </c>
       <c r="B70" t="n">
-        <v>93155</v>
+        <v>93114</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5449</v>
+        <v>149</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>Boletopsis grisea</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Peck) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8004,10 +8008,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>614945</v>
+        <v>614871</v>
       </c>
       <c r="R70" t="n">
-        <v>6560479</v>
+        <v>6560514</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8034,17 +8038,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>2 st</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8053,7 +8057,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8076,10 +8079,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131740335</v>
+        <v>131740391</v>
       </c>
       <c r="B71" t="n">
-        <v>93152</v>
+        <v>93155</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8087,26 +8090,22 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5448</v>
+        <v>5449</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8115,10 +8114,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>614815</v>
+        <v>614945</v>
       </c>
       <c r="R71" t="n">
-        <v>6560508</v>
+        <v>6560479</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8145,17 +8144,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8164,6 +8163,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8186,37 +8186,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131740288</v>
+        <v>131740335</v>
       </c>
       <c r="B72" t="n">
-        <v>93114</v>
+        <v>93152</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>149</v>
+        <v>5448</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8225,10 +8225,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>614871</v>
+        <v>614815</v>
       </c>
       <c r="R72" t="n">
-        <v>6560514</v>
+        <v>6560508</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8296,49 +8296,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131737261</v>
+        <v>131737931</v>
       </c>
       <c r="B73" t="n">
-        <v>93118</v>
+        <v>8454</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4361</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>614895</v>
+        <v>614669</v>
       </c>
       <c r="R73" t="n">
-        <v>6560392</v>
+        <v>6560513</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8365,17 +8361,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>4 st</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8406,45 +8397,49 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131739788</v>
+        <v>131737261</v>
       </c>
       <c r="B74" t="n">
-        <v>92561</v>
+        <v>93118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3298</v>
+        <v>4361</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>615070</v>
+        <v>614895</v>
       </c>
       <c r="R74" t="n">
-        <v>6560325</v>
+        <v>6560392</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8471,12 +8466,17 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8507,10 +8507,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131737931</v>
+        <v>131739788</v>
       </c>
       <c r="B75" t="n">
-        <v>8454</v>
+        <v>92561</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8518,34 +8518,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>3298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>614669</v>
+        <v>615070</v>
       </c>
       <c r="R75" t="n">
-        <v>6560513</v>
+        <v>6560325</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9803,49 +9803,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131737732</v>
+        <v>131733475</v>
       </c>
       <c r="B87" t="n">
-        <v>93164</v>
+        <v>8443</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5966</v>
+        <v>106554</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>614684</v>
+        <v>614840</v>
       </c>
       <c r="R87" t="n">
-        <v>6560422</v>
+        <v>6560403</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9872,17 +9868,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9913,10 +9904,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131740366</v>
+        <v>131737724</v>
       </c>
       <c r="B88" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9924,22 +9915,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9948,10 +9943,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>614682</v>
+        <v>614765</v>
       </c>
       <c r="R88" t="n">
-        <v>6560491</v>
+        <v>6560506</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9988,7 +9983,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9997,7 +9992,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -10020,10 +10014,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131740392</v>
+        <v>131737718</v>
       </c>
       <c r="B89" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10031,22 +10025,26 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10055,10 +10053,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>614832</v>
+        <v>614844</v>
       </c>
       <c r="R89" t="n">
-        <v>6560458</v>
+        <v>6560496</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10085,17 +10083,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>10 st</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10104,7 +10102,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10127,10 +10124,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131740342</v>
+        <v>131737745</v>
       </c>
       <c r="B90" t="n">
-        <v>93152</v>
+        <v>93164</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10138,38 +10135,38 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>48</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>614971</v>
+        <v>614779</v>
       </c>
       <c r="R90" t="n">
-        <v>6560251</v>
+        <v>6560385</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10196,17 +10193,17 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>12 st</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10237,10 +10234,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131737265</v>
+        <v>131739025</v>
       </c>
       <c r="B91" t="n">
-        <v>93118</v>
+        <v>79885</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10248,38 +10245,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>615132</v>
+        <v>614887</v>
       </c>
       <c r="R91" t="n">
-        <v>6560489</v>
+        <v>6560423</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10306,17 +10299,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>4 st</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10347,45 +10335,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131732767</v>
+        <v>131737045</v>
       </c>
       <c r="B92" t="n">
-        <v>93126</v>
+        <v>92137</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>615105</v>
+        <v>614622</v>
       </c>
       <c r="R92" t="n">
-        <v>6560378</v>
+        <v>6560529</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10418,11 +10406,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Spritt i området</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10453,7 +10436,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131737724</v>
+        <v>131737732</v>
       </c>
       <c r="B93" t="n">
         <v>93164</v>
@@ -10488,14 +10471,14 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>614765</v>
+        <v>614684</v>
       </c>
       <c r="R93" t="n">
-        <v>6560506</v>
+        <v>6560422</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10563,10 +10546,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131737718</v>
+        <v>131740366</v>
       </c>
       <c r="B94" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10574,26 +10557,22 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -10602,10 +10581,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>614844</v>
+        <v>614682</v>
       </c>
       <c r="R94" t="n">
-        <v>6560496</v>
+        <v>6560491</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10642,7 +10621,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10651,6 +10630,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10673,10 +10653,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131737745</v>
+        <v>131740392</v>
       </c>
       <c r="B95" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10684,38 +10664,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>614779</v>
+        <v>614832</v>
       </c>
       <c r="R95" t="n">
-        <v>6560385</v>
+        <v>6560458</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10742,17 +10718,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>10 st</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10761,6 +10737,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10783,10 +10760,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131739025</v>
+        <v>131740342</v>
       </c>
       <c r="B96" t="n">
-        <v>79885</v>
+        <v>93152</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10794,34 +10771,38 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>5448</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>614887</v>
+        <v>614971</v>
       </c>
       <c r="R96" t="n">
-        <v>6560423</v>
+        <v>6560251</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10848,12 +10829,17 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>12 st</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10884,45 +10870,49 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131733475</v>
+        <v>131737265</v>
       </c>
       <c r="B97" t="n">
-        <v>8443</v>
+        <v>93118</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106554</v>
+        <v>4361</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>614840</v>
+        <v>615132</v>
       </c>
       <c r="R97" t="n">
-        <v>6560403</v>
+        <v>6560489</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10949,12 +10939,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10985,45 +10980,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131737045</v>
+        <v>131732767</v>
       </c>
       <c r="B98" t="n">
-        <v>92137</v>
+        <v>93126</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>614622</v>
+        <v>615105</v>
       </c>
       <c r="R98" t="n">
-        <v>6560529</v>
+        <v>6560378</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11056,6 +11051,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Spritt i området</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11086,45 +11086,49 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131736992</v>
+        <v>131737722</v>
       </c>
       <c r="B99" t="n">
-        <v>91323</v>
+        <v>93164</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2051</v>
+        <v>5966</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>614848</v>
+        <v>614773</v>
       </c>
       <c r="R99" t="n">
-        <v>6560378</v>
+        <v>6560515</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11151,12 +11155,17 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>1o</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11187,10 +11196,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131737722</v>
+        <v>131740395</v>
       </c>
       <c r="B100" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11198,26 +11207,22 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11226,10 +11231,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>614773</v>
+        <v>614715</v>
       </c>
       <c r="R100" t="n">
-        <v>6560515</v>
+        <v>6560514</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11256,17 +11261,17 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>1o</t>
+          <t>6 st</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11275,6 +11280,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11297,7 +11303,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131740395</v>
+        <v>131740398</v>
       </c>
       <c r="B101" t="n">
         <v>93155</v>
@@ -11323,19 +11329,19 @@
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>614715</v>
+        <v>614907</v>
       </c>
       <c r="R101" t="n">
-        <v>6560514</v>
+        <v>6560326</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11372,7 +11378,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>6 st</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11404,10 +11410,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131740398</v>
+        <v>131737757</v>
       </c>
       <c r="B102" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11415,34 +11421,38 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>614907</v>
+        <v>614887</v>
       </c>
       <c r="R102" t="n">
-        <v>6560326</v>
+        <v>6560362</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11469,17 +11479,17 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11488,7 +11498,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11511,7 +11520,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737757</v>
+        <v>131737776</v>
       </c>
       <c r="B103" t="n">
         <v>93164</v>
@@ -11541,19 +11550,19 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nord, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>614887</v>
+        <v>615009</v>
       </c>
       <c r="R103" t="n">
-        <v>6560362</v>
+        <v>6560307</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11590,7 +11599,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11621,10 +11630,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131737776</v>
+        <v>131739042</v>
       </c>
       <c r="B104" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11632,38 +11641,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nystugan Nord, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>615009</v>
+        <v>614859</v>
       </c>
       <c r="R104" t="n">
-        <v>6560307</v>
+        <v>6560517</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11690,17 +11695,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11832,45 +11832,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131739017</v>
+        <v>131736992</v>
       </c>
       <c r="B106" t="n">
-        <v>79885</v>
+        <v>91323</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>2051</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>615032</v>
+        <v>614848</v>
       </c>
       <c r="R106" t="n">
-        <v>6560425</v>
+        <v>6560378</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11933,7 +11933,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131739042</v>
+        <v>131739017</v>
       </c>
       <c r="B107" t="n">
         <v>79885</v>
@@ -11964,14 +11964,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>614859</v>
+        <v>615032</v>
       </c>
       <c r="R107" t="n">
-        <v>6560517</v>
+        <v>6560425</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13401,10 +13401,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131737605</v>
+        <v>131739040</v>
       </c>
       <c r="B121" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13412,34 +13412,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>614921</v>
+        <v>614705</v>
       </c>
       <c r="R121" t="n">
-        <v>6560349</v>
+        <v>6560468</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13466,12 +13466,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13502,49 +13502,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131737753</v>
+        <v>131733476</v>
       </c>
       <c r="B122" t="n">
-        <v>93164</v>
+        <v>8443</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5966</v>
+        <v>106554</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>614883</v>
+        <v>614831</v>
       </c>
       <c r="R122" t="n">
-        <v>6560422</v>
+        <v>6560599</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13571,17 +13567,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13612,45 +13603,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131733367</v>
+        <v>131740365</v>
       </c>
       <c r="B123" t="n">
-        <v>92496</v>
+        <v>93155</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6031</v>
+        <v>5449</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>614939</v>
+        <v>614741</v>
       </c>
       <c r="R123" t="n">
-        <v>6560438</v>
+        <v>6560508</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13685,12 +13676,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13713,10 +13710,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131737719</v>
+        <v>131740367</v>
       </c>
       <c r="B124" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13724,26 +13721,22 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -13752,10 +13745,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>614817</v>
+        <v>614742</v>
       </c>
       <c r="R124" t="n">
-        <v>6560509</v>
+        <v>6560443</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13792,7 +13785,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13801,6 +13794,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13823,7 +13817,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131737768</v>
+        <v>131737741</v>
       </c>
       <c r="B125" t="n">
         <v>93164</v>
@@ -13853,19 +13847,19 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>614843</v>
+        <v>614754</v>
       </c>
       <c r="R125" t="n">
-        <v>6560322</v>
+        <v>6560449</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13902,7 +13896,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13933,10 +13927,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131737778</v>
+        <v>131733306</v>
       </c>
       <c r="B126" t="n">
-        <v>93164</v>
+        <v>93120</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13944,38 +13938,38 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>615115</v>
+        <v>614689</v>
       </c>
       <c r="R126" t="n">
-        <v>6560377</v>
+        <v>6560516</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14002,17 +13996,17 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>1 St</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14043,49 +14037,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131737751</v>
+        <v>131732765</v>
       </c>
       <c r="B127" t="n">
-        <v>93164</v>
+        <v>93126</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>614860</v>
+        <v>614878</v>
       </c>
       <c r="R127" t="n">
-        <v>6560430</v>
+        <v>6560511</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14112,17 +14102,17 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>Förekommer spritt rikligt</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14153,7 +14143,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131737604</v>
+        <v>131737605</v>
       </c>
       <c r="B128" t="n">
         <v>93164</v>
@@ -14184,14 +14174,14 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>615114</v>
+        <v>614921</v>
       </c>
       <c r="R128" t="n">
-        <v>6560473</v>
+        <v>6560349</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14254,10 +14244,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131739040</v>
+        <v>131737753</v>
       </c>
       <c r="B129" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14265,34 +14255,38 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>614705</v>
+        <v>614883</v>
       </c>
       <c r="R129" t="n">
-        <v>6560468</v>
+        <v>6560422</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14319,12 +14313,17 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14355,10 +14354,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131733476</v>
+        <v>131733367</v>
       </c>
       <c r="B130" t="n">
-        <v>8443</v>
+        <v>92496</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14366,34 +14365,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106554</v>
+        <v>6031</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>614831</v>
+        <v>614939</v>
       </c>
       <c r="R130" t="n">
-        <v>6560599</v>
+        <v>6560438</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14420,12 +14419,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14456,10 +14455,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131740365</v>
+        <v>131737719</v>
       </c>
       <c r="B131" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14467,22 +14466,26 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -14491,10 +14494,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>614741</v>
+        <v>614817</v>
       </c>
       <c r="R131" t="n">
-        <v>6560508</v>
+        <v>6560509</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14531,7 +14534,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14540,7 +14543,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14563,10 +14565,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131740367</v>
+        <v>131737768</v>
       </c>
       <c r="B132" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14574,34 +14576,38 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>614742</v>
+        <v>614843</v>
       </c>
       <c r="R132" t="n">
-        <v>6560443</v>
+        <v>6560322</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14638,7 +14644,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14647,7 +14653,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14670,7 +14675,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131737741</v>
+        <v>131737778</v>
       </c>
       <c r="B133" t="n">
         <v>93164</v>
@@ -14700,19 +14705,19 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>614754</v>
+        <v>615115</v>
       </c>
       <c r="R133" t="n">
-        <v>6560449</v>
+        <v>6560377</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14749,7 +14754,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14780,10 +14785,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131733306</v>
+        <v>131737751</v>
       </c>
       <c r="B134" t="n">
-        <v>93120</v>
+        <v>93164</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14791,26 +14796,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -14819,10 +14824,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>614689</v>
+        <v>614860</v>
       </c>
       <c r="R134" t="n">
-        <v>6560516</v>
+        <v>6560430</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14849,17 +14854,17 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>1 St</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14890,45 +14895,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131732765</v>
+        <v>131737604</v>
       </c>
       <c r="B135" t="n">
-        <v>93126</v>
+        <v>93164</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>614878</v>
+        <v>615114</v>
       </c>
       <c r="R135" t="n">
-        <v>6560511</v>
+        <v>6560473</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14955,17 +14960,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Förekommer spritt rikligt</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14996,10 +14996,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131733304</v>
+        <v>131740394</v>
       </c>
       <c r="B136" t="n">
-        <v>93120</v>
+        <v>93155</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15007,26 +15007,22 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -15035,10 +15031,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>614759</v>
+        <v>614731</v>
       </c>
       <c r="R136" t="n">
-        <v>6560440</v>
+        <v>6560512</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15075,7 +15071,7 @@
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>8 st</t>
+          <t>1 st</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15084,6 +15080,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -15106,10 +15103,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>131737743</v>
+        <v>131740402</v>
       </c>
       <c r="B137" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15117,38 +15114,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>614731</v>
+        <v>615135</v>
       </c>
       <c r="R137" t="n">
-        <v>6560390</v>
+        <v>6560485</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15175,17 +15168,17 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Ca 25st</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15194,6 +15187,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -15216,10 +15210,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>131737707</v>
+        <v>131733304</v>
       </c>
       <c r="B138" t="n">
-        <v>93164</v>
+        <v>93120</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15227,38 +15221,38 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>614934</v>
+        <v>614759</v>
       </c>
       <c r="R138" t="n">
-        <v>6560422</v>
+        <v>6560440</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15285,17 +15279,17 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8 st</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15326,10 +15320,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>131737748</v>
+        <v>131740243</v>
       </c>
       <c r="B139" t="n">
-        <v>93164</v>
+        <v>92770</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15337,38 +15331,38 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>614792</v>
+        <v>614829</v>
       </c>
       <c r="R139" t="n">
-        <v>6560431</v>
+        <v>6560371</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15405,7 +15399,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15436,10 +15430,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>131740394</v>
+        <v>131737743</v>
       </c>
       <c r="B140" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15447,34 +15441,38 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q140" t="n">
         <v>614731</v>
       </c>
       <c r="R140" t="n">
-        <v>6560512</v>
+        <v>6560390</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15501,17 +15499,17 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>1 st</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15520,7 +15518,6 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15543,10 +15540,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>131740402</v>
+        <v>131737707</v>
       </c>
       <c r="B141" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15554,22 +15551,26 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -15578,10 +15579,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>615135</v>
+        <v>614934</v>
       </c>
       <c r="R141" t="n">
-        <v>6560485</v>
+        <v>6560422</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15608,17 +15609,17 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Ca 25st</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15627,7 +15628,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15650,10 +15650,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>131739551</v>
+        <v>131737748</v>
       </c>
       <c r="B142" t="n">
-        <v>91838</v>
+        <v>93164</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15661,34 +15661,38 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>614622</v>
+        <v>614792</v>
       </c>
       <c r="R142" t="n">
-        <v>6560528</v>
+        <v>6560431</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15715,12 +15719,17 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15751,10 +15760,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>131740243</v>
+        <v>131739551</v>
       </c>
       <c r="B143" t="n">
-        <v>92770</v>
+        <v>91838</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15762,38 +15771,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4745</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>614829</v>
+        <v>614622</v>
       </c>
       <c r="R143" t="n">
-        <v>6560371</v>
+        <v>6560528</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15820,17 +15825,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD143" t="b">

--- a/artfynd/A 43282-2024 artfynd.xlsx
+++ b/artfynd/A 43282-2024 artfynd.xlsx
@@ -2583,45 +2583,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131732769</v>
+        <v>131737607</v>
       </c>
       <c r="B19" t="n">
-        <v>93126</v>
+        <v>93164</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615104</v>
+        <v>614643</v>
       </c>
       <c r="R19" t="n">
-        <v>6560485</v>
+        <v>6560479</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2648,17 +2648,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Återkommer spritt</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2790,45 +2785,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131737607</v>
+        <v>131732769</v>
       </c>
       <c r="B21" t="n">
-        <v>93164</v>
+        <v>93126</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>614643</v>
+        <v>615104</v>
       </c>
       <c r="R21" t="n">
-        <v>6560479</v>
+        <v>6560485</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2855,12 +2850,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Återkommer spritt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2891,7 +2891,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131737603</v>
+        <v>131737737</v>
       </c>
       <c r="B22" t="n">
         <v>93164</v>
@@ -2919,17 +2919,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>615176</v>
+        <v>614697</v>
       </c>
       <c r="R22" t="n">
-        <v>6560478</v>
+        <v>6560445</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2956,12 +2960,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2992,7 +3001,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131737708</v>
+        <v>131737603</v>
       </c>
       <c r="B23" t="n">
         <v>93164</v>
@@ -3020,21 +3029,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>614945</v>
+        <v>615176</v>
       </c>
       <c r="R23" t="n">
-        <v>6560420</v>
+        <v>6560478</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3061,17 +3066,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3102,7 +3102,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131737704</v>
+        <v>131737708</v>
       </c>
       <c r="B24" t="n">
         <v>93164</v>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615034</v>
+        <v>614945</v>
       </c>
       <c r="R24" t="n">
-        <v>6560411</v>
+        <v>6560420</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3212,10 +3212,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131740241</v>
+        <v>131737704</v>
       </c>
       <c r="B25" t="n">
-        <v>92770</v>
+        <v>93164</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3223,26 +3223,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>614922</v>
+        <v>615034</v>
       </c>
       <c r="R25" t="n">
-        <v>6560422</v>
+        <v>6560411</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3322,45 +3322,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131736022</v>
+        <v>131740241</v>
       </c>
       <c r="B26" t="n">
-        <v>92277</v>
+        <v>92770</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5420</v>
+        <v>4745</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>614774</v>
+        <v>614922</v>
       </c>
       <c r="R26" t="n">
-        <v>6560503</v>
+        <v>6560422</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3393,6 +3397,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3423,49 +3432,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131737737</v>
+        <v>131736022</v>
       </c>
       <c r="B27" t="n">
-        <v>93164</v>
+        <v>92277</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>614697</v>
+        <v>614774</v>
       </c>
       <c r="R27" t="n">
-        <v>6560445</v>
+        <v>6560503</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3498,11 +3503,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -6912,45 +6912,49 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131736994</v>
+        <v>131737749</v>
       </c>
       <c r="B60" t="n">
-        <v>91323</v>
+        <v>93164</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2051</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>615157</v>
+        <v>614849</v>
       </c>
       <c r="R60" t="n">
-        <v>6560412</v>
+        <v>6560446</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6977,17 +6981,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ramaria XXL</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7018,7 +7022,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131737749</v>
+        <v>131737714</v>
       </c>
       <c r="B61" t="n">
         <v>93164</v>
@@ -7048,7 +7052,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7057,10 +7061,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>614849</v>
+        <v>614933</v>
       </c>
       <c r="R61" t="n">
-        <v>6560446</v>
+        <v>6560495</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7097,7 +7101,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7128,10 +7132,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131737714</v>
+        <v>131739038</v>
       </c>
       <c r="B62" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7139,38 +7143,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>614933</v>
+        <v>614743</v>
       </c>
       <c r="R62" t="n">
-        <v>6560495</v>
+        <v>6560468</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7197,17 +7197,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>60+</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7238,32 +7233,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131739019</v>
+        <v>131736994</v>
       </c>
       <c r="B63" t="n">
-        <v>79885</v>
+        <v>91323</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>2051</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7273,10 +7268,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>615022</v>
+        <v>615157</v>
       </c>
       <c r="R63" t="n">
-        <v>6560428</v>
+        <v>6560412</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7303,12 +7298,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ramaria XXL</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7339,45 +7339,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131739038</v>
+        <v>131734255</v>
       </c>
       <c r="B64" t="n">
-        <v>79885</v>
+        <v>97375</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>990</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>614743</v>
+        <v>614670</v>
       </c>
       <c r="R64" t="n">
-        <v>6560468</v>
+        <v>6560435</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7440,10 +7440,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131734662</v>
+        <v>131737717</v>
       </c>
       <c r="B65" t="n">
-        <v>79023</v>
+        <v>93164</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7451,34 +7451,38 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>614665</v>
+        <v>614838</v>
       </c>
       <c r="R65" t="n">
-        <v>6560415</v>
+        <v>6560512</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7505,12 +7509,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7541,45 +7550,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131734255</v>
+        <v>131740397</v>
       </c>
       <c r="B66" t="n">
-        <v>97375</v>
+        <v>93155</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>990</v>
+        <v>5449</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Warnst.) R.M.Schust.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>614670</v>
+        <v>614907</v>
       </c>
       <c r="R66" t="n">
-        <v>6560435</v>
+        <v>6560338</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7606,12 +7615,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>5 st</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7620,6 +7634,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7642,10 +7657,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131737717</v>
+        <v>131739019</v>
       </c>
       <c r="B67" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7653,38 +7668,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>614838</v>
+        <v>615022</v>
       </c>
       <c r="R67" t="n">
-        <v>6560512</v>
+        <v>6560428</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7717,11 +7728,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7752,10 +7758,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131740397</v>
+        <v>131734662</v>
       </c>
       <c r="B68" t="n">
-        <v>93155</v>
+        <v>79023</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7763,34 +7769,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>614907</v>
+        <v>614665</v>
       </c>
       <c r="R68" t="n">
-        <v>6560338</v>
+        <v>6560415</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7817,17 +7823,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>5 st</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7836,7 +7837,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -9803,45 +9803,49 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131733475</v>
+        <v>131737732</v>
       </c>
       <c r="B87" t="n">
-        <v>8443</v>
+        <v>93164</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106554</v>
+        <v>5966</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>614840</v>
+        <v>614684</v>
       </c>
       <c r="R87" t="n">
-        <v>6560403</v>
+        <v>6560422</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9868,12 +9872,17 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9904,10 +9913,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131737724</v>
+        <v>131740366</v>
       </c>
       <c r="B88" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9915,26 +9924,22 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9943,10 +9948,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>614765</v>
+        <v>614682</v>
       </c>
       <c r="R88" t="n">
-        <v>6560506</v>
+        <v>6560491</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9983,7 +9988,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9992,6 +9997,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -10014,10 +10020,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131737718</v>
+        <v>131740392</v>
       </c>
       <c r="B89" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10025,26 +10031,22 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10053,10 +10055,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>614844</v>
+        <v>614832</v>
       </c>
       <c r="R89" t="n">
-        <v>6560496</v>
+        <v>6560458</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10083,17 +10085,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10 st</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10102,6 +10104,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10124,10 +10127,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131737745</v>
+        <v>131740342</v>
       </c>
       <c r="B90" t="n">
-        <v>93164</v>
+        <v>93152</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10135,38 +10138,38 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>614779</v>
+        <v>614971</v>
       </c>
       <c r="R90" t="n">
-        <v>6560385</v>
+        <v>6560251</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10193,17 +10196,17 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>12 st</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10234,10 +10237,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131739025</v>
+        <v>131737265</v>
       </c>
       <c r="B91" t="n">
-        <v>79885</v>
+        <v>93118</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10245,34 +10248,38 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>614887</v>
+        <v>615132</v>
       </c>
       <c r="R91" t="n">
-        <v>6560423</v>
+        <v>6560489</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10299,12 +10306,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10335,45 +10347,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131737045</v>
+        <v>131732767</v>
       </c>
       <c r="B92" t="n">
-        <v>92137</v>
+        <v>93126</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>614622</v>
+        <v>615105</v>
       </c>
       <c r="R92" t="n">
-        <v>6560529</v>
+        <v>6560378</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10406,6 +10418,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Spritt i området</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10436,7 +10453,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131737732</v>
+        <v>131737724</v>
       </c>
       <c r="B93" t="n">
         <v>93164</v>
@@ -10471,14 +10488,14 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>614684</v>
+        <v>614765</v>
       </c>
       <c r="R93" t="n">
-        <v>6560422</v>
+        <v>6560506</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10546,10 +10563,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131740366</v>
+        <v>131737718</v>
       </c>
       <c r="B94" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10557,22 +10574,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -10581,10 +10602,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>614682</v>
+        <v>614844</v>
       </c>
       <c r="R94" t="n">
-        <v>6560491</v>
+        <v>6560496</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10621,7 +10642,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10630,7 +10651,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10653,10 +10673,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131740392</v>
+        <v>131737745</v>
       </c>
       <c r="B95" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10664,34 +10684,38 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>48</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>614832</v>
+        <v>614779</v>
       </c>
       <c r="R95" t="n">
-        <v>6560458</v>
+        <v>6560385</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10718,17 +10742,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>10 st</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10737,7 +10761,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10760,10 +10783,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131740342</v>
+        <v>131739025</v>
       </c>
       <c r="B96" t="n">
-        <v>93152</v>
+        <v>79885</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10771,38 +10794,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5448</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>614971</v>
+        <v>614887</v>
       </c>
       <c r="R96" t="n">
-        <v>6560251</v>
+        <v>6560423</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10829,17 +10848,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>12 st</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10870,49 +10884,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131737265</v>
+        <v>131733475</v>
       </c>
       <c r="B97" t="n">
-        <v>93118</v>
+        <v>8443</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4361</v>
+        <v>106554</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>615132</v>
+        <v>614840</v>
       </c>
       <c r="R97" t="n">
-        <v>6560489</v>
+        <v>6560403</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10939,17 +10949,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>4 st</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10980,45 +10985,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131732767</v>
+        <v>131737045</v>
       </c>
       <c r="B98" t="n">
-        <v>93126</v>
+        <v>92137</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>615105</v>
+        <v>614622</v>
       </c>
       <c r="R98" t="n">
-        <v>6560378</v>
+        <v>6560529</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11051,11 +11056,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Spritt i området</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11086,49 +11086,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131737722</v>
+        <v>131736992</v>
       </c>
       <c r="B99" t="n">
-        <v>93164</v>
+        <v>91323</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5966</v>
+        <v>2051</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>614773</v>
+        <v>614848</v>
       </c>
       <c r="R99" t="n">
-        <v>6560515</v>
+        <v>6560378</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11155,17 +11151,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>1o</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11196,10 +11187,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131740395</v>
+        <v>131737722</v>
       </c>
       <c r="B100" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11207,22 +11198,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11231,10 +11226,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>614715</v>
+        <v>614773</v>
       </c>
       <c r="R100" t="n">
-        <v>6560514</v>
+        <v>6560515</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11261,17 +11256,17 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>6 st</t>
+          <t>1o</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11280,7 +11275,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11303,7 +11297,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131740398</v>
+        <v>131740395</v>
       </c>
       <c r="B101" t="n">
         <v>93155</v>
@@ -11329,19 +11323,19 @@
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>614907</v>
+        <v>614715</v>
       </c>
       <c r="R101" t="n">
-        <v>6560326</v>
+        <v>6560514</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11378,7 +11372,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>6 st</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11410,10 +11404,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131737757</v>
+        <v>131740398</v>
       </c>
       <c r="B102" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11421,38 +11415,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>614887</v>
+        <v>614907</v>
       </c>
       <c r="R102" t="n">
-        <v>6560362</v>
+        <v>6560326</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11479,17 +11469,17 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11498,6 +11488,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11520,7 +11511,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737776</v>
+        <v>131737757</v>
       </c>
       <c r="B103" t="n">
         <v>93164</v>
@@ -11550,19 +11541,19 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Nystugan Nord, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>615009</v>
+        <v>614887</v>
       </c>
       <c r="R103" t="n">
-        <v>6560307</v>
+        <v>6560362</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11599,7 +11590,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11630,10 +11621,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131739042</v>
+        <v>131737776</v>
       </c>
       <c r="B104" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11641,34 +11632,38 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nord, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>614859</v>
+        <v>615009</v>
       </c>
       <c r="R104" t="n">
-        <v>6560517</v>
+        <v>6560307</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11695,12 +11690,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11832,45 +11832,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131736992</v>
+        <v>131739017</v>
       </c>
       <c r="B106" t="n">
-        <v>91323</v>
+        <v>79885</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2051</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>614848</v>
+        <v>615032</v>
       </c>
       <c r="R106" t="n">
-        <v>6560378</v>
+        <v>6560425</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11933,7 +11933,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131739017</v>
+        <v>131739042</v>
       </c>
       <c r="B107" t="n">
         <v>79885</v>
@@ -11964,14 +11964,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>615032</v>
+        <v>614859</v>
       </c>
       <c r="R107" t="n">
-        <v>6560425</v>
+        <v>6560517</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13401,10 +13401,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131739040</v>
+        <v>131737605</v>
       </c>
       <c r="B121" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13412,34 +13412,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>614705</v>
+        <v>614921</v>
       </c>
       <c r="R121" t="n">
-        <v>6560468</v>
+        <v>6560349</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13466,12 +13466,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13502,45 +13502,49 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131733476</v>
+        <v>131737753</v>
       </c>
       <c r="B122" t="n">
-        <v>8443</v>
+        <v>93164</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106554</v>
+        <v>5966</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>614831</v>
+        <v>614883</v>
       </c>
       <c r="R122" t="n">
-        <v>6560599</v>
+        <v>6560422</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13567,12 +13571,17 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13603,45 +13612,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131740365</v>
+        <v>131733367</v>
       </c>
       <c r="B123" t="n">
-        <v>93155</v>
+        <v>92496</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5449</v>
+        <v>6031</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>614741</v>
+        <v>614939</v>
       </c>
       <c r="R123" t="n">
-        <v>6560508</v>
+        <v>6560438</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13676,18 +13685,12 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13710,10 +13713,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131740367</v>
+        <v>131737719</v>
       </c>
       <c r="B124" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13721,22 +13724,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -13745,10 +13752,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>614742</v>
+        <v>614817</v>
       </c>
       <c r="R124" t="n">
-        <v>6560443</v>
+        <v>6560509</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13785,7 +13792,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13794,7 +13801,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13817,7 +13823,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131737741</v>
+        <v>131737768</v>
       </c>
       <c r="B125" t="n">
         <v>93164</v>
@@ -13847,19 +13853,19 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>614754</v>
+        <v>614843</v>
       </c>
       <c r="R125" t="n">
-        <v>6560449</v>
+        <v>6560322</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13896,7 +13902,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13927,10 +13933,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131733306</v>
+        <v>131737778</v>
       </c>
       <c r="B126" t="n">
-        <v>93120</v>
+        <v>93164</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13938,38 +13944,38 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>614689</v>
+        <v>615115</v>
       </c>
       <c r="R126" t="n">
-        <v>6560516</v>
+        <v>6560377</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13996,17 +14002,17 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>1 St</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14037,45 +14043,49 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131732765</v>
+        <v>131737751</v>
       </c>
       <c r="B127" t="n">
-        <v>93126</v>
+        <v>93164</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>614878</v>
+        <v>614860</v>
       </c>
       <c r="R127" t="n">
-        <v>6560511</v>
+        <v>6560430</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14102,17 +14112,17 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Förekommer spritt rikligt</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14143,7 +14153,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131737605</v>
+        <v>131737604</v>
       </c>
       <c r="B128" t="n">
         <v>93164</v>
@@ -14174,14 +14184,14 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>614921</v>
+        <v>615114</v>
       </c>
       <c r="R128" t="n">
-        <v>6560349</v>
+        <v>6560473</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14244,10 +14254,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131737753</v>
+        <v>131739040</v>
       </c>
       <c r="B129" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14255,38 +14265,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>614883</v>
+        <v>614705</v>
       </c>
       <c r="R129" t="n">
-        <v>6560422</v>
+        <v>6560468</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14313,17 +14319,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14354,10 +14355,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131733367</v>
+        <v>131733476</v>
       </c>
       <c r="B130" t="n">
-        <v>92496</v>
+        <v>8443</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14365,34 +14366,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6031</v>
+        <v>106554</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>614939</v>
+        <v>614831</v>
       </c>
       <c r="R130" t="n">
-        <v>6560438</v>
+        <v>6560599</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14419,12 +14420,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14455,10 +14456,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131737719</v>
+        <v>131740365</v>
       </c>
       <c r="B131" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14466,26 +14467,22 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -14494,10 +14491,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>614817</v>
+        <v>614741</v>
       </c>
       <c r="R131" t="n">
-        <v>6560509</v>
+        <v>6560508</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14534,7 +14531,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14543,6 +14540,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14565,10 +14563,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131737768</v>
+        <v>131740367</v>
       </c>
       <c r="B132" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14576,38 +14574,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>614843</v>
+        <v>614742</v>
       </c>
       <c r="R132" t="n">
-        <v>6560322</v>
+        <v>6560443</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14644,7 +14638,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14653,6 +14647,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14675,7 +14670,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131737778</v>
+        <v>131737741</v>
       </c>
       <c r="B133" t="n">
         <v>93164</v>
@@ -14705,19 +14700,19 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>615115</v>
+        <v>614754</v>
       </c>
       <c r="R133" t="n">
-        <v>6560377</v>
+        <v>6560449</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14754,7 +14749,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14785,10 +14780,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131737751</v>
+        <v>131733306</v>
       </c>
       <c r="B134" t="n">
-        <v>93164</v>
+        <v>93120</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14796,26 +14791,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -14824,10 +14819,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>614860</v>
+        <v>614689</v>
       </c>
       <c r="R134" t="n">
-        <v>6560430</v>
+        <v>6560516</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14854,17 +14849,17 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1 St</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14895,45 +14890,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131737604</v>
+        <v>131732765</v>
       </c>
       <c r="B135" t="n">
-        <v>93164</v>
+        <v>93126</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>615114</v>
+        <v>614878</v>
       </c>
       <c r="R135" t="n">
-        <v>6560473</v>
+        <v>6560511</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14960,12 +14955,17 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Förekommer spritt rikligt</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14996,10 +14996,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131740394</v>
+        <v>131733304</v>
       </c>
       <c r="B136" t="n">
-        <v>93155</v>
+        <v>93120</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15007,22 +15007,26 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr"/>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -15031,10 +15035,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>614731</v>
+        <v>614759</v>
       </c>
       <c r="R136" t="n">
-        <v>6560512</v>
+        <v>6560440</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15071,7 +15075,7 @@
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>1 st</t>
+          <t>8 st</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15080,7 +15084,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -15103,10 +15106,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>131740402</v>
+        <v>131737743</v>
       </c>
       <c r="B137" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15114,34 +15117,38 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>615135</v>
+        <v>614731</v>
       </c>
       <c r="R137" t="n">
-        <v>6560485</v>
+        <v>6560390</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15168,17 +15175,17 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Ca 25st</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15187,7 +15194,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -15210,10 +15216,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>131733304</v>
+        <v>131737707</v>
       </c>
       <c r="B138" t="n">
-        <v>93120</v>
+        <v>93164</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15221,38 +15227,38 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>614759</v>
+        <v>614934</v>
       </c>
       <c r="R138" t="n">
-        <v>6560440</v>
+        <v>6560422</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15279,17 +15285,17 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>8 st</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15320,10 +15326,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>131740243</v>
+        <v>131737748</v>
       </c>
       <c r="B139" t="n">
-        <v>92770</v>
+        <v>93164</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15331,38 +15337,38 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>614829</v>
+        <v>614792</v>
       </c>
       <c r="R139" t="n">
-        <v>6560371</v>
+        <v>6560431</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15399,7 +15405,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15430,10 +15436,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>131737743</v>
+        <v>131740394</v>
       </c>
       <c r="B140" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15441,38 +15447,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q140" t="n">
         <v>614731</v>
       </c>
       <c r="R140" t="n">
-        <v>6560390</v>
+        <v>6560512</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15499,17 +15501,17 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 st</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15518,6 +15520,7 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15540,10 +15543,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>131737707</v>
+        <v>131740402</v>
       </c>
       <c r="B141" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15551,26 +15554,22 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -15579,10 +15578,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>614934</v>
+        <v>615135</v>
       </c>
       <c r="R141" t="n">
-        <v>6560422</v>
+        <v>6560485</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15609,17 +15608,17 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Ca 25st</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15628,6 +15627,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15650,10 +15650,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>131737748</v>
+        <v>131739551</v>
       </c>
       <c r="B142" t="n">
-        <v>93164</v>
+        <v>91838</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15661,38 +15661,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>614792</v>
+        <v>614622</v>
       </c>
       <c r="R142" t="n">
-        <v>6560431</v>
+        <v>6560528</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15719,17 +15715,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>13</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15760,10 +15751,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>131739551</v>
+        <v>131740243</v>
       </c>
       <c r="B143" t="n">
-        <v>91838</v>
+        <v>92770</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15771,34 +15762,38 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1202</v>
+        <v>4745</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>614622</v>
+        <v>614829</v>
       </c>
       <c r="R143" t="n">
-        <v>6560528</v>
+        <v>6560371</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15825,12 +15820,17 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD143" t="b">

--- a/artfynd/A 43282-2024 artfynd.xlsx
+++ b/artfynd/A 43282-2024 artfynd.xlsx
@@ -2583,45 +2583,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131737607</v>
+        <v>131732769</v>
       </c>
       <c r="B19" t="n">
-        <v>93164</v>
+        <v>93126</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>614643</v>
+        <v>615104</v>
       </c>
       <c r="R19" t="n">
-        <v>6560479</v>
+        <v>6560485</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2648,12 +2648,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Återkommer spritt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,45 +2790,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131732769</v>
+        <v>131737607</v>
       </c>
       <c r="B21" t="n">
-        <v>93126</v>
+        <v>93164</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615104</v>
+        <v>614643</v>
       </c>
       <c r="R21" t="n">
-        <v>6560485</v>
+        <v>6560479</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2850,17 +2855,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Återkommer spritt</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -5530,10 +5530,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131740368</v>
+        <v>131739023</v>
       </c>
       <c r="B47" t="n">
-        <v>93155</v>
+        <v>79885</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5541,34 +5541,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>614772</v>
+        <v>614757</v>
       </c>
       <c r="R47" t="n">
-        <v>6560415</v>
+        <v>6560461</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5603,18 +5603,12 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5637,10 +5631,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131740341</v>
+        <v>131740368</v>
       </c>
       <c r="B48" t="n">
-        <v>93152</v>
+        <v>93155</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5648,38 +5642,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5448</v>
+        <v>5449</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>614963</v>
+        <v>614772</v>
       </c>
       <c r="R48" t="n">
-        <v>6560256</v>
+        <v>6560415</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5706,17 +5696,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>8 st</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5725,6 +5715,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5747,10 +5738,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131737728</v>
+        <v>131740341</v>
       </c>
       <c r="B49" t="n">
-        <v>93164</v>
+        <v>93152</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5758,38 +5749,38 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>614659</v>
+        <v>614963</v>
       </c>
       <c r="R49" t="n">
-        <v>6560444</v>
+        <v>6560256</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5816,17 +5807,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8 st</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5857,7 +5848,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737734</v>
+        <v>131737728</v>
       </c>
       <c r="B50" t="n">
         <v>93164</v>
@@ -5887,19 +5878,19 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>614708</v>
+        <v>614659</v>
       </c>
       <c r="R50" t="n">
-        <v>6560403</v>
+        <v>6560444</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5936,7 +5927,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5967,10 +5958,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131739023</v>
+        <v>131737734</v>
       </c>
       <c r="B51" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5978,34 +5969,38 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>614757</v>
+        <v>614708</v>
       </c>
       <c r="R51" t="n">
-        <v>6560461</v>
+        <v>6560403</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6038,6 +6033,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6481,10 +6481,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131737712</v>
+        <v>131740242</v>
       </c>
       <c r="B56" t="n">
-        <v>93164</v>
+        <v>92770</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6492,38 +6492,38 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>614922</v>
+        <v>614849</v>
       </c>
       <c r="R56" t="n">
-        <v>6560461</v>
+        <v>6560382</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6591,49 +6591,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131740242</v>
+        <v>131736812</v>
       </c>
       <c r="B57" t="n">
-        <v>92770</v>
+        <v>93138</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>614849</v>
+        <v>614856</v>
       </c>
       <c r="R57" t="n">
-        <v>6560382</v>
+        <v>6560514</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6660,17 +6656,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6701,45 +6692,49 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131736812</v>
+        <v>131735736</v>
       </c>
       <c r="B58" t="n">
-        <v>93138</v>
+        <v>92628</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4366</v>
+        <v>366</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>614856</v>
+        <v>614666</v>
       </c>
       <c r="R58" t="n">
-        <v>6560514</v>
+        <v>6560445</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6766,12 +6761,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6802,10 +6802,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131735736</v>
+        <v>131737712</v>
       </c>
       <c r="B59" t="n">
-        <v>92628</v>
+        <v>93164</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6813,38 +6813,38 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>366</v>
+        <v>5966</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>614666</v>
+        <v>614922</v>
       </c>
       <c r="R59" t="n">
-        <v>6560445</v>
+        <v>6560461</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6871,17 +6871,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>3 st</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7969,37 +7969,33 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131740288</v>
+        <v>131740391</v>
       </c>
       <c r="B70" t="n">
-        <v>93114</v>
+        <v>93155</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>149</v>
+        <v>5449</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8008,10 +8004,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>614871</v>
+        <v>614945</v>
       </c>
       <c r="R70" t="n">
-        <v>6560514</v>
+        <v>6560479</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8038,17 +8034,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8057,6 +8053,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8079,10 +8076,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131740391</v>
+        <v>131740335</v>
       </c>
       <c r="B71" t="n">
-        <v>93155</v>
+        <v>93152</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8090,22 +8087,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8114,10 +8115,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>614945</v>
+        <v>614815</v>
       </c>
       <c r="R71" t="n">
-        <v>6560479</v>
+        <v>6560508</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8144,17 +8145,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>2 st</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8163,7 +8164,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8186,37 +8186,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131740335</v>
+        <v>131740288</v>
       </c>
       <c r="B72" t="n">
-        <v>93152</v>
+        <v>93114</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5448</v>
+        <v>149</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8225,10 +8225,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>614815</v>
+        <v>614871</v>
       </c>
       <c r="R72" t="n">
-        <v>6560508</v>
+        <v>6560514</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8296,45 +8296,49 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131737931</v>
+        <v>131737261</v>
       </c>
       <c r="B73" t="n">
-        <v>8454</v>
+        <v>93118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>4361</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>614669</v>
+        <v>614895</v>
       </c>
       <c r="R73" t="n">
-        <v>6560513</v>
+        <v>6560392</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8361,12 +8365,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8397,49 +8406,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131737261</v>
+        <v>131739788</v>
       </c>
       <c r="B74" t="n">
-        <v>93118</v>
+        <v>92561</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4361</v>
+        <v>3298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>614895</v>
+        <v>615070</v>
       </c>
       <c r="R74" t="n">
-        <v>6560392</v>
+        <v>6560325</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8466,17 +8471,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>4 st</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8507,10 +8507,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131739788</v>
+        <v>131737931</v>
       </c>
       <c r="B75" t="n">
-        <v>92561</v>
+        <v>8454</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8518,34 +8518,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3298</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>615070</v>
+        <v>614669</v>
       </c>
       <c r="R75" t="n">
-        <v>6560325</v>
+        <v>6560513</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -11086,45 +11086,49 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131736992</v>
+        <v>131737722</v>
       </c>
       <c r="B99" t="n">
-        <v>91323</v>
+        <v>93164</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2051</v>
+        <v>5966</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>614848</v>
+        <v>614773</v>
       </c>
       <c r="R99" t="n">
-        <v>6560378</v>
+        <v>6560515</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11151,12 +11155,17 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>1o</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11187,10 +11196,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131737722</v>
+        <v>131740395</v>
       </c>
       <c r="B100" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11198,26 +11207,22 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11226,10 +11231,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>614773</v>
+        <v>614715</v>
       </c>
       <c r="R100" t="n">
-        <v>6560515</v>
+        <v>6560514</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11256,17 +11261,17 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>1o</t>
+          <t>6 st</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11275,6 +11280,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11297,7 +11303,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131740395</v>
+        <v>131740398</v>
       </c>
       <c r="B101" t="n">
         <v>93155</v>
@@ -11323,19 +11329,19 @@
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>614715</v>
+        <v>614907</v>
       </c>
       <c r="R101" t="n">
-        <v>6560514</v>
+        <v>6560326</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11372,7 +11378,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>6 st</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11404,10 +11410,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131740398</v>
+        <v>131737757</v>
       </c>
       <c r="B102" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11415,34 +11421,38 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>614907</v>
+        <v>614887</v>
       </c>
       <c r="R102" t="n">
-        <v>6560326</v>
+        <v>6560362</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11469,17 +11479,17 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11488,7 +11498,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11511,7 +11520,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737757</v>
+        <v>131737776</v>
       </c>
       <c r="B103" t="n">
         <v>93164</v>
@@ -11541,19 +11550,19 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nord, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>614887</v>
+        <v>615009</v>
       </c>
       <c r="R103" t="n">
-        <v>6560362</v>
+        <v>6560307</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11590,7 +11599,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11621,10 +11630,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131737776</v>
+        <v>131739042</v>
       </c>
       <c r="B104" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11632,38 +11641,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nystugan Nord, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>615009</v>
+        <v>614859</v>
       </c>
       <c r="R104" t="n">
-        <v>6560307</v>
+        <v>6560517</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11690,17 +11695,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11832,45 +11832,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131739017</v>
+        <v>131736992</v>
       </c>
       <c r="B106" t="n">
-        <v>79885</v>
+        <v>91323</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>2051</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>615032</v>
+        <v>614848</v>
       </c>
       <c r="R106" t="n">
-        <v>6560425</v>
+        <v>6560378</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11933,7 +11933,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131739042</v>
+        <v>131739017</v>
       </c>
       <c r="B107" t="n">
         <v>79885</v>
@@ -11964,14 +11964,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>614859</v>
+        <v>615032</v>
       </c>
       <c r="R107" t="n">
-        <v>6560517</v>
+        <v>6560425</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13401,10 +13401,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131737605</v>
+        <v>131739040</v>
       </c>
       <c r="B121" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13412,34 +13412,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>614921</v>
+        <v>614705</v>
       </c>
       <c r="R121" t="n">
-        <v>6560349</v>
+        <v>6560468</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13466,12 +13466,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13502,49 +13502,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131737753</v>
+        <v>131733476</v>
       </c>
       <c r="B122" t="n">
-        <v>93164</v>
+        <v>8443</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5966</v>
+        <v>106554</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>614883</v>
+        <v>614831</v>
       </c>
       <c r="R122" t="n">
-        <v>6560422</v>
+        <v>6560599</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13571,17 +13567,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13612,45 +13603,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131733367</v>
+        <v>131740365</v>
       </c>
       <c r="B123" t="n">
-        <v>92496</v>
+        <v>93155</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6031</v>
+        <v>5449</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>614939</v>
+        <v>614741</v>
       </c>
       <c r="R123" t="n">
-        <v>6560438</v>
+        <v>6560508</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13685,12 +13676,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13713,10 +13710,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131737719</v>
+        <v>131740367</v>
       </c>
       <c r="B124" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13724,26 +13721,22 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -13752,10 +13745,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>614817</v>
+        <v>614742</v>
       </c>
       <c r="R124" t="n">
-        <v>6560509</v>
+        <v>6560443</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13792,7 +13785,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13801,6 +13794,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13823,7 +13817,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131737768</v>
+        <v>131737741</v>
       </c>
       <c r="B125" t="n">
         <v>93164</v>
@@ -13853,19 +13847,19 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>614843</v>
+        <v>614754</v>
       </c>
       <c r="R125" t="n">
-        <v>6560322</v>
+        <v>6560449</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13902,7 +13896,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13933,10 +13927,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131737778</v>
+        <v>131733306</v>
       </c>
       <c r="B126" t="n">
-        <v>93164</v>
+        <v>93120</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13944,38 +13938,38 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>615115</v>
+        <v>614689</v>
       </c>
       <c r="R126" t="n">
-        <v>6560377</v>
+        <v>6560516</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14002,17 +13996,17 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>1 St</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14043,49 +14037,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131737751</v>
+        <v>131732765</v>
       </c>
       <c r="B127" t="n">
-        <v>93164</v>
+        <v>93126</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>614860</v>
+        <v>614878</v>
       </c>
       <c r="R127" t="n">
-        <v>6560430</v>
+        <v>6560511</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14112,17 +14102,17 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>Förekommer spritt rikligt</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14153,7 +14143,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131737604</v>
+        <v>131737605</v>
       </c>
       <c r="B128" t="n">
         <v>93164</v>
@@ -14184,14 +14174,14 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>615114</v>
+        <v>614921</v>
       </c>
       <c r="R128" t="n">
-        <v>6560473</v>
+        <v>6560349</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14254,10 +14244,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131739040</v>
+        <v>131737753</v>
       </c>
       <c r="B129" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14265,34 +14255,38 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>614705</v>
+        <v>614883</v>
       </c>
       <c r="R129" t="n">
-        <v>6560468</v>
+        <v>6560422</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14319,12 +14313,17 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14355,10 +14354,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131733476</v>
+        <v>131733367</v>
       </c>
       <c r="B130" t="n">
-        <v>8443</v>
+        <v>92496</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14366,34 +14365,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106554</v>
+        <v>6031</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>614831</v>
+        <v>614939</v>
       </c>
       <c r="R130" t="n">
-        <v>6560599</v>
+        <v>6560438</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14420,12 +14419,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14456,10 +14455,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131740365</v>
+        <v>131737719</v>
       </c>
       <c r="B131" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14467,22 +14466,26 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -14491,10 +14494,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>614741</v>
+        <v>614817</v>
       </c>
       <c r="R131" t="n">
-        <v>6560508</v>
+        <v>6560509</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14531,7 +14534,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14540,7 +14543,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14563,10 +14565,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131740367</v>
+        <v>131737768</v>
       </c>
       <c r="B132" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14574,34 +14576,38 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>614742</v>
+        <v>614843</v>
       </c>
       <c r="R132" t="n">
-        <v>6560443</v>
+        <v>6560322</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14638,7 +14644,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14647,7 +14653,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14670,7 +14675,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131737741</v>
+        <v>131737778</v>
       </c>
       <c r="B133" t="n">
         <v>93164</v>
@@ -14700,19 +14705,19 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>614754</v>
+        <v>615115</v>
       </c>
       <c r="R133" t="n">
-        <v>6560449</v>
+        <v>6560377</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14749,7 +14754,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14780,10 +14785,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131733306</v>
+        <v>131737751</v>
       </c>
       <c r="B134" t="n">
-        <v>93120</v>
+        <v>93164</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14791,26 +14796,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -14819,10 +14824,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>614689</v>
+        <v>614860</v>
       </c>
       <c r="R134" t="n">
-        <v>6560516</v>
+        <v>6560430</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14849,17 +14854,17 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>1 St</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14890,45 +14895,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131732765</v>
+        <v>131737604</v>
       </c>
       <c r="B135" t="n">
-        <v>93126</v>
+        <v>93164</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>614878</v>
+        <v>615114</v>
       </c>
       <c r="R135" t="n">
-        <v>6560511</v>
+        <v>6560473</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14955,17 +14960,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Förekommer spritt rikligt</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14996,10 +14996,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131733304</v>
+        <v>131740394</v>
       </c>
       <c r="B136" t="n">
-        <v>93120</v>
+        <v>93155</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15007,26 +15007,22 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -15035,10 +15031,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>614759</v>
+        <v>614731</v>
       </c>
       <c r="R136" t="n">
-        <v>6560440</v>
+        <v>6560512</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15075,7 +15071,7 @@
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>8 st</t>
+          <t>1 st</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15084,6 +15080,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -15106,10 +15103,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>131737743</v>
+        <v>131740402</v>
       </c>
       <c r="B137" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15117,38 +15114,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>614731</v>
+        <v>615135</v>
       </c>
       <c r="R137" t="n">
-        <v>6560390</v>
+        <v>6560485</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15175,17 +15168,17 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Ca 25st</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15194,6 +15187,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -15216,10 +15210,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>131737707</v>
+        <v>131733304</v>
       </c>
       <c r="B138" t="n">
-        <v>93164</v>
+        <v>93120</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15227,38 +15221,38 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>614934</v>
+        <v>614759</v>
       </c>
       <c r="R138" t="n">
-        <v>6560422</v>
+        <v>6560440</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15285,17 +15279,17 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8 st</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15326,10 +15320,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>131737748</v>
+        <v>131740243</v>
       </c>
       <c r="B139" t="n">
-        <v>93164</v>
+        <v>92770</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15337,38 +15331,38 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>614792</v>
+        <v>614829</v>
       </c>
       <c r="R139" t="n">
-        <v>6560431</v>
+        <v>6560371</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15405,7 +15399,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15436,10 +15430,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>131740394</v>
+        <v>131737743</v>
       </c>
       <c r="B140" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15447,34 +15441,38 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q140" t="n">
         <v>614731</v>
       </c>
       <c r="R140" t="n">
-        <v>6560512</v>
+        <v>6560390</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15501,17 +15499,17 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>1 st</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15520,7 +15518,6 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15543,10 +15540,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>131740402</v>
+        <v>131737707</v>
       </c>
       <c r="B141" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15554,22 +15551,26 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -15578,10 +15579,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>615135</v>
+        <v>614934</v>
       </c>
       <c r="R141" t="n">
-        <v>6560485</v>
+        <v>6560422</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15608,17 +15609,17 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Ca 25st</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15627,7 +15628,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15650,10 +15650,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>131739551</v>
+        <v>131737748</v>
       </c>
       <c r="B142" t="n">
-        <v>91838</v>
+        <v>93164</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15661,34 +15661,38 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>614622</v>
+        <v>614792</v>
       </c>
       <c r="R142" t="n">
-        <v>6560528</v>
+        <v>6560431</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15715,12 +15719,17 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15751,10 +15760,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>131740243</v>
+        <v>131739551</v>
       </c>
       <c r="B143" t="n">
-        <v>92770</v>
+        <v>91838</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15762,38 +15771,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4745</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>614829</v>
+        <v>614622</v>
       </c>
       <c r="R143" t="n">
-        <v>6560371</v>
+        <v>6560528</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15820,17 +15825,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD143" t="b">

--- a/artfynd/A 43282-2024 artfynd.xlsx
+++ b/artfynd/A 43282-2024 artfynd.xlsx
@@ -2891,7 +2891,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131737737</v>
+        <v>131737603</v>
       </c>
       <c r="B22" t="n">
         <v>93164</v>
@@ -2919,21 +2919,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>614697</v>
+        <v>615176</v>
       </c>
       <c r="R22" t="n">
-        <v>6560445</v>
+        <v>6560478</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2960,17 +2956,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3001,7 +2992,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131737603</v>
+        <v>131737708</v>
       </c>
       <c r="B23" t="n">
         <v>93164</v>
@@ -3029,17 +3020,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615176</v>
+        <v>614945</v>
       </c>
       <c r="R23" t="n">
-        <v>6560478</v>
+        <v>6560420</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3066,12 +3061,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3102,7 +3102,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131737708</v>
+        <v>131737704</v>
       </c>
       <c r="B24" t="n">
         <v>93164</v>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>614945</v>
+        <v>615034</v>
       </c>
       <c r="R24" t="n">
-        <v>6560420</v>
+        <v>6560411</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3212,10 +3212,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131737704</v>
+        <v>131740241</v>
       </c>
       <c r="B25" t="n">
-        <v>93164</v>
+        <v>92770</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3223,26 +3223,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615034</v>
+        <v>614922</v>
       </c>
       <c r="R25" t="n">
-        <v>6560411</v>
+        <v>6560422</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3322,49 +3322,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131740241</v>
+        <v>131736022</v>
       </c>
       <c r="B26" t="n">
-        <v>92770</v>
+        <v>92277</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4745</v>
+        <v>5420</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>614922</v>
+        <v>614774</v>
       </c>
       <c r="R26" t="n">
-        <v>6560422</v>
+        <v>6560503</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3397,11 +3393,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3432,45 +3423,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131736022</v>
+        <v>131737737</v>
       </c>
       <c r="B27" t="n">
-        <v>92277</v>
+        <v>93164</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5420</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>614774</v>
+        <v>614697</v>
       </c>
       <c r="R27" t="n">
-        <v>6560503</v>
+        <v>6560445</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3503,6 +3498,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -5530,10 +5530,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131739023</v>
+        <v>131740368</v>
       </c>
       <c r="B47" t="n">
-        <v>79885</v>
+        <v>93155</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5541,34 +5541,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>614757</v>
+        <v>614772</v>
       </c>
       <c r="R47" t="n">
-        <v>6560461</v>
+        <v>6560415</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5603,12 +5603,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5631,10 +5637,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131740368</v>
+        <v>131740341</v>
       </c>
       <c r="B48" t="n">
-        <v>93155</v>
+        <v>93152</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5642,34 +5648,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>614772</v>
+        <v>614963</v>
       </c>
       <c r="R48" t="n">
-        <v>6560415</v>
+        <v>6560256</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5696,17 +5706,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8 st</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5715,7 +5725,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5738,10 +5747,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131740341</v>
+        <v>131737728</v>
       </c>
       <c r="B49" t="n">
-        <v>93152</v>
+        <v>93164</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5749,38 +5758,38 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>614963</v>
+        <v>614659</v>
       </c>
       <c r="R49" t="n">
-        <v>6560256</v>
+        <v>6560444</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5807,17 +5816,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>8 st</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5848,7 +5857,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737728</v>
+        <v>131737734</v>
       </c>
       <c r="B50" t="n">
         <v>93164</v>
@@ -5878,19 +5887,19 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>614659</v>
+        <v>614708</v>
       </c>
       <c r="R50" t="n">
-        <v>6560444</v>
+        <v>6560403</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5927,7 +5936,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5958,10 +5967,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737734</v>
+        <v>131739023</v>
       </c>
       <c r="B51" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5969,38 +5978,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>614708</v>
+        <v>614757</v>
       </c>
       <c r="R51" t="n">
-        <v>6560403</v>
+        <v>6560461</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6033,11 +6038,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6481,10 +6481,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131740242</v>
+        <v>131737712</v>
       </c>
       <c r="B56" t="n">
-        <v>92770</v>
+        <v>93164</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6492,38 +6492,38 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>614849</v>
+        <v>614922</v>
       </c>
       <c r="R56" t="n">
-        <v>6560382</v>
+        <v>6560461</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6591,45 +6591,49 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131736812</v>
+        <v>131740242</v>
       </c>
       <c r="B57" t="n">
-        <v>93138</v>
+        <v>92770</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4366</v>
+        <v>4745</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>614856</v>
+        <v>614849</v>
       </c>
       <c r="R57" t="n">
-        <v>6560514</v>
+        <v>6560382</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6656,12 +6660,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6692,49 +6701,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131735736</v>
+        <v>131736812</v>
       </c>
       <c r="B58" t="n">
-        <v>92628</v>
+        <v>93138</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>366</v>
+        <v>4366</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>614666</v>
+        <v>614856</v>
       </c>
       <c r="R58" t="n">
-        <v>6560445</v>
+        <v>6560514</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6761,17 +6766,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>3 st</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6802,10 +6802,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131737712</v>
+        <v>131735736</v>
       </c>
       <c r="B59" t="n">
-        <v>93164</v>
+        <v>92628</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6813,38 +6813,38 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5966</v>
+        <v>366</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>614922</v>
+        <v>614666</v>
       </c>
       <c r="R59" t="n">
-        <v>6560461</v>
+        <v>6560445</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6871,17 +6871,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7969,33 +7969,37 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131740391</v>
+        <v>131740288</v>
       </c>
       <c r="B70" t="n">
-        <v>93155</v>
+        <v>93114</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5449</v>
+        <v>149</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>Boletopsis grisea</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Peck) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8004,10 +8008,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>614945</v>
+        <v>614871</v>
       </c>
       <c r="R70" t="n">
-        <v>6560479</v>
+        <v>6560514</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8034,17 +8038,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>2 st</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8053,7 +8057,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8076,10 +8079,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131740335</v>
+        <v>131740391</v>
       </c>
       <c r="B71" t="n">
-        <v>93152</v>
+        <v>93155</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8087,26 +8090,22 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5448</v>
+        <v>5449</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8115,10 +8114,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>614815</v>
+        <v>614945</v>
       </c>
       <c r="R71" t="n">
-        <v>6560508</v>
+        <v>6560479</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8145,17 +8144,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8164,6 +8163,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8186,37 +8186,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131740288</v>
+        <v>131740335</v>
       </c>
       <c r="B72" t="n">
-        <v>93114</v>
+        <v>93152</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>149</v>
+        <v>5448</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8225,10 +8225,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>614871</v>
+        <v>614815</v>
       </c>
       <c r="R72" t="n">
-        <v>6560514</v>
+        <v>6560508</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8296,49 +8296,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131737261</v>
+        <v>131737931</v>
       </c>
       <c r="B73" t="n">
-        <v>93118</v>
+        <v>8454</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4361</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>614895</v>
+        <v>614669</v>
       </c>
       <c r="R73" t="n">
-        <v>6560392</v>
+        <v>6560513</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8365,17 +8361,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>4 st</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8406,45 +8397,49 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131739788</v>
+        <v>131737261</v>
       </c>
       <c r="B74" t="n">
-        <v>92561</v>
+        <v>93118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3298</v>
+        <v>4361</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>615070</v>
+        <v>614895</v>
       </c>
       <c r="R74" t="n">
-        <v>6560325</v>
+        <v>6560392</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8471,12 +8466,17 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8507,10 +8507,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131737931</v>
+        <v>131739788</v>
       </c>
       <c r="B75" t="n">
-        <v>8454</v>
+        <v>92561</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8518,34 +8518,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>3298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>614669</v>
+        <v>615070</v>
       </c>
       <c r="R75" t="n">
-        <v>6560513</v>
+        <v>6560325</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -11086,49 +11086,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131737722</v>
+        <v>131736992</v>
       </c>
       <c r="B99" t="n">
-        <v>93164</v>
+        <v>91323</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5966</v>
+        <v>2051</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>614773</v>
+        <v>614848</v>
       </c>
       <c r="R99" t="n">
-        <v>6560515</v>
+        <v>6560378</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11155,17 +11151,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>1o</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11196,10 +11187,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131740395</v>
+        <v>131737722</v>
       </c>
       <c r="B100" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11207,22 +11198,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11231,10 +11226,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>614715</v>
+        <v>614773</v>
       </c>
       <c r="R100" t="n">
-        <v>6560514</v>
+        <v>6560515</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11261,17 +11256,17 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>6 st</t>
+          <t>1o</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11280,7 +11275,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11303,7 +11297,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131740398</v>
+        <v>131740395</v>
       </c>
       <c r="B101" t="n">
         <v>93155</v>
@@ -11329,19 +11323,19 @@
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>614907</v>
+        <v>614715</v>
       </c>
       <c r="R101" t="n">
-        <v>6560326</v>
+        <v>6560514</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11378,7 +11372,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>6 st</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11410,10 +11404,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131737757</v>
+        <v>131740398</v>
       </c>
       <c r="B102" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11421,38 +11415,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>614887</v>
+        <v>614907</v>
       </c>
       <c r="R102" t="n">
-        <v>6560362</v>
+        <v>6560326</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11479,17 +11469,17 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11498,6 +11488,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11520,7 +11511,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737776</v>
+        <v>131737757</v>
       </c>
       <c r="B103" t="n">
         <v>93164</v>
@@ -11550,19 +11541,19 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Nystugan Nord, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>615009</v>
+        <v>614887</v>
       </c>
       <c r="R103" t="n">
-        <v>6560307</v>
+        <v>6560362</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11599,7 +11590,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11630,10 +11621,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131739042</v>
+        <v>131737776</v>
       </c>
       <c r="B104" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11641,34 +11632,38 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nord, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>614859</v>
+        <v>615009</v>
       </c>
       <c r="R104" t="n">
-        <v>6560517</v>
+        <v>6560307</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11695,12 +11690,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11832,45 +11832,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131736992</v>
+        <v>131739017</v>
       </c>
       <c r="B106" t="n">
-        <v>91323</v>
+        <v>79885</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2051</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>614848</v>
+        <v>615032</v>
       </c>
       <c r="R106" t="n">
-        <v>6560378</v>
+        <v>6560425</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11933,7 +11933,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131739017</v>
+        <v>131739042</v>
       </c>
       <c r="B107" t="n">
         <v>79885</v>
@@ -11964,14 +11964,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>615032</v>
+        <v>614859</v>
       </c>
       <c r="R107" t="n">
-        <v>6560425</v>
+        <v>6560517</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12135,10 +12135,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131732521</v>
+        <v>131737715</v>
       </c>
       <c r="B109" t="n">
-        <v>78932</v>
+        <v>93164</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12146,34 +12146,38 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>614661</v>
+        <v>614932</v>
       </c>
       <c r="R109" t="n">
-        <v>6560444</v>
+        <v>6560487</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12206,6 +12210,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12236,10 +12245,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131740080</v>
+        <v>131737780</v>
       </c>
       <c r="B110" t="n">
-        <v>91859</v>
+        <v>93164</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12247,34 +12256,38 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>615060</v>
+        <v>615164</v>
       </c>
       <c r="R110" t="n">
-        <v>6560430</v>
+        <v>6560465</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12301,12 +12314,17 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12337,10 +12355,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131737715</v>
+        <v>131732521</v>
       </c>
       <c r="B111" t="n">
-        <v>93164</v>
+        <v>78932</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12348,38 +12366,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>614932</v>
+        <v>614661</v>
       </c>
       <c r="R111" t="n">
-        <v>6560487</v>
+        <v>6560444</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12412,11 +12426,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12447,10 +12456,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131737780</v>
+        <v>131740080</v>
       </c>
       <c r="B112" t="n">
-        <v>93164</v>
+        <v>91859</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12458,38 +12467,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>615164</v>
+        <v>615060</v>
       </c>
       <c r="R112" t="n">
-        <v>6560465</v>
+        <v>6560430</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12516,17 +12521,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13401,10 +13401,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131739040</v>
+        <v>131737605</v>
       </c>
       <c r="B121" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13412,34 +13412,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>614705</v>
+        <v>614921</v>
       </c>
       <c r="R121" t="n">
-        <v>6560468</v>
+        <v>6560349</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13466,12 +13466,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13502,45 +13502,49 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131733476</v>
+        <v>131737753</v>
       </c>
       <c r="B122" t="n">
-        <v>8443</v>
+        <v>93164</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106554</v>
+        <v>5966</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>614831</v>
+        <v>614883</v>
       </c>
       <c r="R122" t="n">
-        <v>6560599</v>
+        <v>6560422</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13567,12 +13571,17 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13603,45 +13612,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131740365</v>
+        <v>131733367</v>
       </c>
       <c r="B123" t="n">
-        <v>93155</v>
+        <v>92496</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5449</v>
+        <v>6031</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>614741</v>
+        <v>614939</v>
       </c>
       <c r="R123" t="n">
-        <v>6560508</v>
+        <v>6560438</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13676,18 +13685,12 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13710,10 +13713,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131740367</v>
+        <v>131737719</v>
       </c>
       <c r="B124" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13721,22 +13724,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -13745,10 +13752,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>614742</v>
+        <v>614817</v>
       </c>
       <c r="R124" t="n">
-        <v>6560443</v>
+        <v>6560509</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13785,7 +13792,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13794,7 +13801,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13817,7 +13823,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131737741</v>
+        <v>131737768</v>
       </c>
       <c r="B125" t="n">
         <v>93164</v>
@@ -13847,19 +13853,19 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>614754</v>
+        <v>614843</v>
       </c>
       <c r="R125" t="n">
-        <v>6560449</v>
+        <v>6560322</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13896,7 +13902,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13927,10 +13933,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131733306</v>
+        <v>131737778</v>
       </c>
       <c r="B126" t="n">
-        <v>93120</v>
+        <v>93164</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13938,38 +13944,38 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>614689</v>
+        <v>615115</v>
       </c>
       <c r="R126" t="n">
-        <v>6560516</v>
+        <v>6560377</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13996,17 +14002,17 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>1 St</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14037,45 +14043,49 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131732765</v>
+        <v>131737751</v>
       </c>
       <c r="B127" t="n">
-        <v>93126</v>
+        <v>93164</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>614878</v>
+        <v>614860</v>
       </c>
       <c r="R127" t="n">
-        <v>6560511</v>
+        <v>6560430</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14102,17 +14112,17 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Förekommer spritt rikligt</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14143,7 +14153,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131737605</v>
+        <v>131737604</v>
       </c>
       <c r="B128" t="n">
         <v>93164</v>
@@ -14174,14 +14184,14 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>614921</v>
+        <v>615114</v>
       </c>
       <c r="R128" t="n">
-        <v>6560349</v>
+        <v>6560473</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14244,10 +14254,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131737753</v>
+        <v>131739040</v>
       </c>
       <c r="B129" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14255,38 +14265,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>614883</v>
+        <v>614705</v>
       </c>
       <c r="R129" t="n">
-        <v>6560422</v>
+        <v>6560468</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14313,17 +14319,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14354,10 +14355,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131733367</v>
+        <v>131733476</v>
       </c>
       <c r="B130" t="n">
-        <v>92496</v>
+        <v>8443</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14365,34 +14366,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6031</v>
+        <v>106554</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>614939</v>
+        <v>614831</v>
       </c>
       <c r="R130" t="n">
-        <v>6560438</v>
+        <v>6560599</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14419,12 +14420,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14455,10 +14456,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131737719</v>
+        <v>131740365</v>
       </c>
       <c r="B131" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14466,26 +14467,22 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -14494,10 +14491,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>614817</v>
+        <v>614741</v>
       </c>
       <c r="R131" t="n">
-        <v>6560509</v>
+        <v>6560508</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14534,7 +14531,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14543,6 +14540,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14565,10 +14563,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131737768</v>
+        <v>131740367</v>
       </c>
       <c r="B132" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14576,38 +14574,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>614843</v>
+        <v>614742</v>
       </c>
       <c r="R132" t="n">
-        <v>6560322</v>
+        <v>6560443</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14644,7 +14638,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14653,6 +14647,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14675,7 +14670,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131737778</v>
+        <v>131737741</v>
       </c>
       <c r="B133" t="n">
         <v>93164</v>
@@ -14705,19 +14700,19 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>615115</v>
+        <v>614754</v>
       </c>
       <c r="R133" t="n">
-        <v>6560377</v>
+        <v>6560449</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14754,7 +14749,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14785,10 +14780,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131737751</v>
+        <v>131733306</v>
       </c>
       <c r="B134" t="n">
-        <v>93164</v>
+        <v>93120</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14796,26 +14791,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -14824,10 +14819,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>614860</v>
+        <v>614689</v>
       </c>
       <c r="R134" t="n">
-        <v>6560430</v>
+        <v>6560516</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14854,17 +14849,17 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1 St</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14895,45 +14890,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131737604</v>
+        <v>131732765</v>
       </c>
       <c r="B135" t="n">
-        <v>93164</v>
+        <v>93126</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>615114</v>
+        <v>614878</v>
       </c>
       <c r="R135" t="n">
-        <v>6560473</v>
+        <v>6560511</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14960,12 +14955,17 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Förekommer spritt rikligt</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -18856,10 +18856,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>131737721</v>
+        <v>131735737</v>
       </c>
       <c r="B172" t="n">
-        <v>93164</v>
+        <v>92628</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18867,21 +18867,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5966</v>
+        <v>366</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -18891,14 +18891,14 @@
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>614776</v>
+        <v>615093</v>
       </c>
       <c r="R172" t="n">
-        <v>6560488</v>
+        <v>6560461</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18925,17 +18925,17 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18966,10 +18966,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>131737775</v>
+        <v>131732524</v>
       </c>
       <c r="B173" t="n">
-        <v>93164</v>
+        <v>78932</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18977,38 +18977,34 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Nystugan Nord, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>614989</v>
+        <v>614915</v>
       </c>
       <c r="R173" t="n">
-        <v>6560288</v>
+        <v>6560407</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19035,17 +19031,12 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>14</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19278,10 +19269,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>131735737</v>
+        <v>131740359</v>
       </c>
       <c r="B176" t="n">
-        <v>92628</v>
+        <v>93155</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19289,38 +19280,34 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>366</v>
+        <v>5449</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>615093</v>
+        <v>614877</v>
       </c>
       <c r="R176" t="n">
-        <v>6560461</v>
+        <v>6560513</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19347,17 +19334,17 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19366,6 +19353,7 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -19388,10 +19376,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>131732524</v>
+        <v>131737740</v>
       </c>
       <c r="B177" t="n">
-        <v>78932</v>
+        <v>93164</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19399,34 +19387,38 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>614915</v>
+        <v>614746</v>
       </c>
       <c r="R177" t="n">
-        <v>6560407</v>
+        <v>6560453</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19453,12 +19445,17 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19489,10 +19486,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>131740359</v>
+        <v>131737742</v>
       </c>
       <c r="B178" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19500,22 +19497,26 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -19524,10 +19525,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>614877</v>
+        <v>614738</v>
       </c>
       <c r="R178" t="n">
-        <v>6560513</v>
+        <v>6560442</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19554,17 +19555,17 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19573,7 +19574,6 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
-      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -19596,7 +19596,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>131737740</v>
+        <v>131737738</v>
       </c>
       <c r="B179" t="n">
         <v>93164</v>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -19635,10 +19635,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>614746</v>
+        <v>614711</v>
       </c>
       <c r="R179" t="n">
-        <v>6560453</v>
+        <v>6560481</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19706,10 +19706,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>131737742</v>
+        <v>131740399</v>
       </c>
       <c r="B180" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19717,23 +19717,19 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
           <t>5</t>
@@ -19741,14 +19737,14 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>614738</v>
+        <v>614904</v>
       </c>
       <c r="R180" t="n">
-        <v>6560442</v>
+        <v>6560330</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19775,17 +19771,17 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 st</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19794,6 +19790,7 @@
       <c r="AE180" t="b">
         <v>0</v>
       </c>
+      <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
       </c>
@@ -19816,7 +19813,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>131737738</v>
+        <v>131737721</v>
       </c>
       <c r="B181" t="n">
         <v>93164</v>
@@ -19846,7 +19843,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -19855,10 +19852,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>614711</v>
+        <v>614776</v>
       </c>
       <c r="R181" t="n">
-        <v>6560481</v>
+        <v>6560488</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19895,7 +19892,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19926,10 +19923,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>131740399</v>
+        <v>131737775</v>
       </c>
       <c r="B182" t="n">
-        <v>93155</v>
+        <v>93164</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19937,34 +19934,38 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nystugan Nord, Srm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>614904</v>
+        <v>614989</v>
       </c>
       <c r="R182" t="n">
-        <v>6560330</v>
+        <v>6560288</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19991,17 +19992,17 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>5 st</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20010,7 +20011,6 @@
       <c r="AE182" t="b">
         <v>0</v>
       </c>
-      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43282-2024 artfynd.xlsx
+++ b/artfynd/A 43282-2024 artfynd.xlsx
@@ -1748,7 +1748,7 @@
         <v>131737744</v>
       </c>
       <c r="B11" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>131737716</v>
       </c>
       <c r="B12" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>131740401</v>
       </c>
       <c r="B13" t="n">
-        <v>93158</v>
+        <v>93163</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>131737729</v>
       </c>
       <c r="B14" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>131740363</v>
       </c>
       <c r="B15" t="n">
-        <v>93158</v>
+        <v>93163</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>131737610</v>
       </c>
       <c r="B16" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>131738982</v>
       </c>
       <c r="B17" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>131739018</v>
       </c>
       <c r="B18" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131740240</v>
+        <v>131737607</v>
       </c>
       <c r="B19" t="n">
-        <v>92773</v>
+        <v>93172</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,34 +2594,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615041</v>
+        <v>614643</v>
       </c>
       <c r="R19" t="n">
-        <v>6560443</v>
+        <v>6560479</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2684,32 +2684,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131732769</v>
+        <v>131740240</v>
       </c>
       <c r="B20" t="n">
-        <v>93129</v>
+        <v>92778</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2719,10 +2719,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615104</v>
+        <v>615041</v>
       </c>
       <c r="R20" t="n">
-        <v>6560485</v>
+        <v>6560443</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2749,17 +2749,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Återkommer spritt</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,45 +2785,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131737607</v>
+        <v>131732769</v>
       </c>
       <c r="B21" t="n">
-        <v>93167</v>
+        <v>93134</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>614643</v>
+        <v>615104</v>
       </c>
       <c r="R21" t="n">
-        <v>6560479</v>
+        <v>6560485</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2855,12 +2850,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Återkommer spritt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2891,45 +2891,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131736022</v>
+        <v>131737737</v>
       </c>
       <c r="B22" t="n">
-        <v>92280</v>
+        <v>93172</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5420</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>614774</v>
+        <v>614697</v>
       </c>
       <c r="R22" t="n">
-        <v>6560503</v>
+        <v>6560445</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2962,6 +2966,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2992,10 +3001,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131740241</v>
+        <v>131737603</v>
       </c>
       <c r="B23" t="n">
-        <v>92773</v>
+        <v>93172</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3003,38 +3012,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>614922</v>
+        <v>615176</v>
       </c>
       <c r="R23" t="n">
-        <v>6560422</v>
+        <v>6560478</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3061,17 +3066,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3102,10 +3102,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131737737</v>
+        <v>131737708</v>
       </c>
       <c r="B24" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3132,19 +3132,19 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>614697</v>
+        <v>614945</v>
       </c>
       <c r="R24" t="n">
-        <v>6560445</v>
+        <v>6560420</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3212,10 +3212,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131737603</v>
+        <v>131737704</v>
       </c>
       <c r="B25" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,17 +3240,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615176</v>
+        <v>615034</v>
       </c>
       <c r="R25" t="n">
-        <v>6560478</v>
+        <v>6560411</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3277,12 +3281,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3313,49 +3322,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131737708</v>
+        <v>131736022</v>
       </c>
       <c r="B26" t="n">
-        <v>93167</v>
+        <v>92285</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>614945</v>
+        <v>614774</v>
       </c>
       <c r="R26" t="n">
-        <v>6560420</v>
+        <v>6560503</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3388,11 +3393,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3423,10 +3423,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131737704</v>
+        <v>131740241</v>
       </c>
       <c r="B27" t="n">
-        <v>93167</v>
+        <v>92778</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3434,26 +3434,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>615034</v>
+        <v>614922</v>
       </c>
       <c r="R27" t="n">
-        <v>6560411</v>
+        <v>6560422</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3533,10 +3533,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131738985</v>
+        <v>131737762</v>
       </c>
       <c r="B28" t="n">
-        <v>79888</v>
+        <v>93172</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3544,34 +3544,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>614827</v>
+        <v>614855</v>
       </c>
       <c r="R28" t="n">
-        <v>6560518</v>
+        <v>6560397</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3598,12 +3602,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3634,10 +3643,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131739020</v>
+        <v>131737779</v>
       </c>
       <c r="B29" t="n">
-        <v>79888</v>
+        <v>93172</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3645,34 +3654,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>614839</v>
+        <v>615173</v>
       </c>
       <c r="R29" t="n">
-        <v>6560502</v>
+        <v>6560476</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3705,6 +3718,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3735,10 +3753,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131737762</v>
+        <v>131737781</v>
       </c>
       <c r="B30" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3765,19 +3783,19 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>614855</v>
+        <v>615158</v>
       </c>
       <c r="R30" t="n">
-        <v>6560397</v>
+        <v>6560491</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3814,7 +3832,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3845,10 +3863,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131737779</v>
+        <v>131737746</v>
       </c>
       <c r="B31" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3875,19 +3893,19 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615173</v>
+        <v>614777</v>
       </c>
       <c r="R31" t="n">
-        <v>6560476</v>
+        <v>6560432</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3924,7 +3942,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3955,10 +3973,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131737781</v>
+        <v>131740362</v>
       </c>
       <c r="B32" t="n">
-        <v>93167</v>
+        <v>93163</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3966,23 +3984,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>1</t>
@@ -3994,10 +4008,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615158</v>
+        <v>614974</v>
       </c>
       <c r="R32" t="n">
-        <v>6560491</v>
+        <v>6560411</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4043,6 +4057,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4065,10 +4080,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737746</v>
+        <v>131737750</v>
       </c>
       <c r="B33" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4095,7 +4110,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4104,10 +4119,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>614777</v>
+        <v>614846</v>
       </c>
       <c r="R33" t="n">
-        <v>6560432</v>
+        <v>6560435</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4144,7 +4159,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4175,10 +4190,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131740362</v>
+        <v>131737765</v>
       </c>
       <c r="B34" t="n">
-        <v>93158</v>
+        <v>93172</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4186,34 +4201,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>614974</v>
+        <v>614814</v>
       </c>
       <c r="R34" t="n">
-        <v>6560411</v>
+        <v>6560371</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4250,7 +4269,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4259,7 +4278,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4282,10 +4300,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131737750</v>
+        <v>131738985</v>
       </c>
       <c r="B35" t="n">
-        <v>93167</v>
+        <v>79893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4293,38 +4311,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>614846</v>
+        <v>614827</v>
       </c>
       <c r="R35" t="n">
-        <v>6560435</v>
+        <v>6560518</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4351,17 +4365,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4392,10 +4401,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131737765</v>
+        <v>131739020</v>
       </c>
       <c r="B36" t="n">
-        <v>93167</v>
+        <v>79893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4403,38 +4412,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>614814</v>
+        <v>614839</v>
       </c>
       <c r="R36" t="n">
-        <v>6560371</v>
+        <v>6560502</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4467,11 +4472,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4505,7 +4505,7 @@
         <v>131736037</v>
       </c>
       <c r="B37" t="n">
-        <v>92079</v>
+        <v>92084</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>131736787</v>
       </c>
       <c r="B38" t="n">
-        <v>92213</v>
+        <v>92218</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>131736576</v>
       </c>
       <c r="B39" t="n">
-        <v>93145</v>
+        <v>93150</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4814,10 +4814,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131738986</v>
+        <v>131740334</v>
       </c>
       <c r="B40" t="n">
-        <v>79888</v>
+        <v>93160</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4825,21 +4825,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>5448</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4849,10 +4849,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>614832</v>
+        <v>614945</v>
       </c>
       <c r="R40" t="n">
-        <v>6560556</v>
+        <v>6560495</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4879,12 +4879,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4915,10 +4915,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131739037</v>
+        <v>131737733</v>
       </c>
       <c r="B41" t="n">
-        <v>79888</v>
+        <v>93172</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4926,34 +4926,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>615086</v>
+        <v>614695</v>
       </c>
       <c r="R41" t="n">
-        <v>6560375</v>
+        <v>6560413</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4980,12 +4980,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5016,10 +5016,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131739024</v>
+        <v>131737764</v>
       </c>
       <c r="B42" t="n">
-        <v>79888</v>
+        <v>93172</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5027,34 +5027,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>614774</v>
+        <v>614836</v>
       </c>
       <c r="R42" t="n">
-        <v>6560505</v>
+        <v>6560376</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5087,6 +5091,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5117,10 +5126,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131740334</v>
+        <v>131737713</v>
       </c>
       <c r="B43" t="n">
-        <v>93155</v>
+        <v>93172</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5128,21 +5137,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5152,10 +5161,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>614945</v>
+        <v>614935</v>
       </c>
       <c r="R43" t="n">
-        <v>6560495</v>
+        <v>6560472</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5218,10 +5227,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131737733</v>
+        <v>131738986</v>
       </c>
       <c r="B44" t="n">
-        <v>93167</v>
+        <v>79893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5229,34 +5238,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>614695</v>
+        <v>614832</v>
       </c>
       <c r="R44" t="n">
-        <v>6560413</v>
+        <v>6560556</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5283,12 +5292,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5319,10 +5328,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131737764</v>
+        <v>131739037</v>
       </c>
       <c r="B45" t="n">
-        <v>93167</v>
+        <v>79893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5330,38 +5339,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>614836</v>
+        <v>615086</v>
       </c>
       <c r="R45" t="n">
-        <v>6560376</v>
+        <v>6560375</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5388,17 +5393,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>9</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5429,10 +5429,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131737713</v>
+        <v>131739024</v>
       </c>
       <c r="B46" t="n">
-        <v>93167</v>
+        <v>79893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5440,21 +5440,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5464,10 +5464,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>614935</v>
+        <v>614774</v>
       </c>
       <c r="R46" t="n">
-        <v>6560472</v>
+        <v>6560505</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5533,7 +5533,7 @@
         <v>131739023</v>
       </c>
       <c r="B47" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>131740368</v>
       </c>
       <c r="B48" t="n">
-        <v>93158</v>
+        <v>93163</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>131740341</v>
       </c>
       <c r="B49" t="n">
-        <v>93155</v>
+        <v>93160</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>131737612</v>
       </c>
       <c r="B50" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>131737613</v>
       </c>
       <c r="B51" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>131737728</v>
       </c>
       <c r="B52" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>131737608</v>
       </c>
       <c r="B53" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>131737734</v>
       </c>
       <c r="B54" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>131737760</v>
       </c>
       <c r="B55" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>131735736</v>
       </c>
       <c r="B56" t="n">
-        <v>92631</v>
+        <v>92636</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>131736812</v>
       </c>
       <c r="B57" t="n">
-        <v>93141</v>
+        <v>93146</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6692,10 +6692,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131737712</v>
+        <v>131740242</v>
       </c>
       <c r="B58" t="n">
-        <v>93167</v>
+        <v>92778</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6703,38 +6703,38 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>614922</v>
+        <v>614849</v>
       </c>
       <c r="R58" t="n">
-        <v>6560461</v>
+        <v>6560382</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6802,10 +6802,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131740242</v>
+        <v>131737712</v>
       </c>
       <c r="B59" t="n">
-        <v>92773</v>
+        <v>93172</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6813,38 +6813,38 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>614849</v>
+        <v>614922</v>
       </c>
       <c r="R59" t="n">
-        <v>6560382</v>
+        <v>6560461</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6912,10 +6912,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131736994</v>
+        <v>131734255</v>
       </c>
       <c r="B60" t="n">
-        <v>91326</v>
+        <v>97383</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6923,34 +6923,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2051</v>
+        <v>990</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>615157</v>
+        <v>614670</v>
       </c>
       <c r="R60" t="n">
-        <v>6560412</v>
+        <v>6560435</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6977,17 +6977,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ramaria XXL</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7018,10 +7013,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131734255</v>
+        <v>131736994</v>
       </c>
       <c r="B61" t="n">
-        <v>97378</v>
+        <v>91331</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7029,34 +7024,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>990</v>
+        <v>2051</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>614670</v>
+        <v>615157</v>
       </c>
       <c r="R61" t="n">
-        <v>6560435</v>
+        <v>6560412</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7083,12 +7078,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ramaria XXL</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7119,10 +7119,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131734662</v>
+        <v>131737717</v>
       </c>
       <c r="B62" t="n">
-        <v>79026</v>
+        <v>93172</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7130,34 +7130,38 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>614665</v>
+        <v>614838</v>
       </c>
       <c r="R62" t="n">
-        <v>6560415</v>
+        <v>6560512</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7184,12 +7188,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7220,10 +7229,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131739019</v>
+        <v>131740397</v>
       </c>
       <c r="B63" t="n">
-        <v>79888</v>
+        <v>93163</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7231,34 +7240,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>615022</v>
+        <v>614907</v>
       </c>
       <c r="R63" t="n">
-        <v>6560428</v>
+        <v>6560338</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7285,12 +7294,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>5 st</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7299,6 +7313,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7321,10 +7336,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131739038</v>
+        <v>131737749</v>
       </c>
       <c r="B64" t="n">
-        <v>79888</v>
+        <v>93172</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7332,34 +7347,38 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>614743</v>
+        <v>614849</v>
       </c>
       <c r="R64" t="n">
-        <v>6560468</v>
+        <v>6560446</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7386,12 +7405,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7422,10 +7446,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131737717</v>
+        <v>131737714</v>
       </c>
       <c r="B65" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7452,7 +7476,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7461,10 +7485,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>614838</v>
+        <v>614933</v>
       </c>
       <c r="R65" t="n">
-        <v>6560512</v>
+        <v>6560495</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7501,7 +7525,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7532,10 +7556,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131740397</v>
+        <v>131739019</v>
       </c>
       <c r="B66" t="n">
-        <v>93158</v>
+        <v>79893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7543,34 +7567,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>614907</v>
+        <v>615022</v>
       </c>
       <c r="R66" t="n">
-        <v>6560338</v>
+        <v>6560428</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7597,17 +7621,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>5 st</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7616,7 +7635,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7639,10 +7657,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131737749</v>
+        <v>131739038</v>
       </c>
       <c r="B67" t="n">
-        <v>93167</v>
+        <v>79893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7650,38 +7668,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>614849</v>
+        <v>614743</v>
       </c>
       <c r="R67" t="n">
-        <v>6560446</v>
+        <v>6560468</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7708,17 +7722,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>9</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7749,10 +7758,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131737714</v>
+        <v>131734662</v>
       </c>
       <c r="B68" t="n">
-        <v>93167</v>
+        <v>79031</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7760,38 +7769,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>614933</v>
+        <v>614665</v>
       </c>
       <c r="R68" t="n">
-        <v>6560495</v>
+        <v>6560415</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7818,17 +7823,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>60+</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7859,49 +7859,49 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131737261</v>
+        <v>131740288</v>
       </c>
       <c r="B69" t="n">
-        <v>93121</v>
+        <v>93122</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4361</v>
+        <v>149</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>614895</v>
+        <v>614871</v>
       </c>
       <c r="R69" t="n">
-        <v>6560392</v>
+        <v>6560514</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7928,17 +7928,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7969,45 +7969,49 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131739788</v>
+        <v>131736991</v>
       </c>
       <c r="B70" t="n">
-        <v>92564</v>
+        <v>91331</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3298</v>
+        <v>2051</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>615070</v>
+        <v>614736</v>
       </c>
       <c r="R70" t="n">
-        <v>6560325</v>
+        <v>6560397</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8034,12 +8038,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8070,49 +8079,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131736991</v>
+        <v>131740391</v>
       </c>
       <c r="B71" t="n">
-        <v>91326</v>
+        <v>93163</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2051</v>
+        <v>5449</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>614736</v>
+        <v>614945</v>
       </c>
       <c r="R71" t="n">
-        <v>6560397</v>
+        <v>6560479</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8149,7 +8154,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>3 st</t>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8158,6 +8163,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8180,37 +8186,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131740288</v>
+        <v>131740335</v>
       </c>
       <c r="B72" t="n">
-        <v>93117</v>
+        <v>93160</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>149</v>
+        <v>5448</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8219,10 +8225,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>614871</v>
+        <v>614815</v>
       </c>
       <c r="R72" t="n">
-        <v>6560514</v>
+        <v>6560508</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8259,7 +8265,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8290,10 +8296,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131740391</v>
+        <v>131737261</v>
       </c>
       <c r="B73" t="n">
-        <v>93158</v>
+        <v>93126</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8301,34 +8307,38 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>614945</v>
+        <v>614895</v>
       </c>
       <c r="R73" t="n">
-        <v>6560479</v>
+        <v>6560392</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8365,7 +8375,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>2 st</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8374,7 +8384,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8397,49 +8406,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131740335</v>
+        <v>131739788</v>
       </c>
       <c r="B74" t="n">
-        <v>93155</v>
+        <v>92569</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5448</v>
+        <v>3298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>614815</v>
+        <v>615070</v>
       </c>
       <c r="R74" t="n">
-        <v>6560508</v>
+        <v>6560325</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8466,17 +8471,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8611,7 +8611,7 @@
         <v>131736990</v>
       </c>
       <c r="B76" t="n">
-        <v>91326</v>
+        <v>91331</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8718,10 +8718,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131738984</v>
+        <v>131740369</v>
       </c>
       <c r="B77" t="n">
-        <v>79888</v>
+        <v>93163</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8729,34 +8729,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>614801</v>
+        <v>615152</v>
       </c>
       <c r="R77" t="n">
-        <v>6560517</v>
+        <v>6560500</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8783,12 +8783,17 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8797,6 +8802,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8819,10 +8825,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131740369</v>
+        <v>131737723</v>
       </c>
       <c r="B78" t="n">
-        <v>93158</v>
+        <v>93172</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8830,34 +8836,38 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>615152</v>
+        <v>614756</v>
       </c>
       <c r="R78" t="n">
-        <v>6560500</v>
+        <v>6560527</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8894,7 +8904,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8903,7 +8913,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8926,10 +8935,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131737723</v>
+        <v>131737756</v>
       </c>
       <c r="B79" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8956,19 +8965,19 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>614756</v>
+        <v>614923</v>
       </c>
       <c r="R79" t="n">
-        <v>6560527</v>
+        <v>6560410</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9005,7 +9014,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9036,10 +9045,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131737756</v>
+        <v>131737725</v>
       </c>
       <c r="B80" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9066,19 +9075,19 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>614923</v>
+        <v>614660</v>
       </c>
       <c r="R80" t="n">
-        <v>6560410</v>
+        <v>6560511</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9115,7 +9124,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9146,10 +9155,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131737725</v>
+        <v>131740337</v>
       </c>
       <c r="B81" t="n">
-        <v>93167</v>
+        <v>93160</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9157,38 +9166,38 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>614660</v>
+        <v>614621</v>
       </c>
       <c r="R81" t="n">
-        <v>6560511</v>
+        <v>6560438</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9225,7 +9234,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15+</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9256,10 +9265,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131740337</v>
+        <v>131737731</v>
       </c>
       <c r="B82" t="n">
-        <v>93155</v>
+        <v>93172</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9267,38 +9276,38 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>614621</v>
+        <v>614674</v>
       </c>
       <c r="R82" t="n">
-        <v>6560438</v>
+        <v>6560414</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9335,7 +9344,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>15+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9366,10 +9375,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131737731</v>
+        <v>131740396</v>
       </c>
       <c r="B83" t="n">
-        <v>93167</v>
+        <v>93163</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9377,23 +9386,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>4</t>
@@ -9401,14 +9406,14 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>614674</v>
+        <v>614785</v>
       </c>
       <c r="R83" t="n">
-        <v>6560414</v>
+        <v>6560564</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9435,17 +9440,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9454,6 +9459,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9476,10 +9482,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131740396</v>
+        <v>131737730</v>
       </c>
       <c r="B84" t="n">
-        <v>93158</v>
+        <v>93172</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9487,34 +9493,38 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>614785</v>
+        <v>614656</v>
       </c>
       <c r="R84" t="n">
-        <v>6560564</v>
+        <v>6560418</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9541,17 +9551,17 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9560,7 +9570,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9583,10 +9592,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131737730</v>
+        <v>131737754</v>
       </c>
       <c r="B85" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9613,19 +9622,19 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>614656</v>
+        <v>614888</v>
       </c>
       <c r="R85" t="n">
-        <v>6560418</v>
+        <v>6560440</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9662,7 +9671,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9693,10 +9702,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131737754</v>
+        <v>131738984</v>
       </c>
       <c r="B86" t="n">
-        <v>93167</v>
+        <v>79893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9704,38 +9713,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>614888</v>
+        <v>614801</v>
       </c>
       <c r="R86" t="n">
-        <v>6560440</v>
+        <v>6560517</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9762,17 +9767,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9806,7 +9806,7 @@
         <v>131737265</v>
       </c>
       <c r="B87" t="n">
-        <v>93121</v>
+        <v>93126</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9913,10 +9913,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131737045</v>
+        <v>131737724</v>
       </c>
       <c r="B88" t="n">
-        <v>92140</v>
+        <v>93172</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9924,34 +9924,38 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>658</v>
+        <v>5966</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>614622</v>
+        <v>614765</v>
       </c>
       <c r="R88" t="n">
-        <v>6560529</v>
+        <v>6560506</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9978,12 +9982,17 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10014,10 +10023,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131739025</v>
+        <v>131737732</v>
       </c>
       <c r="B89" t="n">
-        <v>79888</v>
+        <v>93172</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10025,34 +10034,38 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>614887</v>
+        <v>614684</v>
       </c>
       <c r="R89" t="n">
-        <v>6560423</v>
+        <v>6560422</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10085,6 +10098,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10115,45 +10133,49 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131732767</v>
+        <v>131737718</v>
       </c>
       <c r="B90" t="n">
-        <v>93129</v>
+        <v>93172</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>615105</v>
+        <v>614844</v>
       </c>
       <c r="R90" t="n">
-        <v>6560378</v>
+        <v>6560496</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10180,17 +10202,17 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Spritt i området</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10221,10 +10243,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131737724</v>
+        <v>131740366</v>
       </c>
       <c r="B91" t="n">
-        <v>93167</v>
+        <v>93163</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10232,26 +10254,22 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -10260,10 +10278,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>614765</v>
+        <v>614682</v>
       </c>
       <c r="R91" t="n">
-        <v>6560506</v>
+        <v>6560491</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10300,7 +10318,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10309,6 +10327,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10331,10 +10350,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131737732</v>
+        <v>131737745</v>
       </c>
       <c r="B92" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10361,19 +10380,19 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>48</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>614684</v>
+        <v>614779</v>
       </c>
       <c r="R92" t="n">
-        <v>6560422</v>
+        <v>6560385</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10410,7 +10429,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10441,10 +10460,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131737718</v>
+        <v>131740392</v>
       </c>
       <c r="B93" t="n">
-        <v>93167</v>
+        <v>93163</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10452,26 +10471,22 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10480,10 +10495,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>614844</v>
+        <v>614832</v>
       </c>
       <c r="R93" t="n">
-        <v>6560496</v>
+        <v>6560458</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10510,17 +10525,17 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10 st</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10529,6 +10544,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10551,10 +10567,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131740366</v>
+        <v>131740342</v>
       </c>
       <c r="B94" t="n">
-        <v>93158</v>
+        <v>93160</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10562,34 +10578,38 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>614682</v>
+        <v>614971</v>
       </c>
       <c r="R94" t="n">
-        <v>6560491</v>
+        <v>6560251</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10616,17 +10636,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12 st</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10635,7 +10655,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10658,49 +10677,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131737745</v>
+        <v>131733475</v>
       </c>
       <c r="B95" t="n">
-        <v>93167</v>
+        <v>8444</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5966</v>
+        <v>106554</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>614779</v>
+        <v>614840</v>
       </c>
       <c r="R95" t="n">
-        <v>6560385</v>
+        <v>6560403</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10727,17 +10742,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>48</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10768,10 +10778,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131740392</v>
+        <v>131737045</v>
       </c>
       <c r="B96" t="n">
-        <v>93158</v>
+        <v>92145</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10779,34 +10789,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5449</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>614832</v>
+        <v>614622</v>
       </c>
       <c r="R96" t="n">
-        <v>6560458</v>
+        <v>6560529</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10833,17 +10843,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>10 st</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10852,7 +10857,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10875,10 +10879,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131740342</v>
+        <v>131739025</v>
       </c>
       <c r="B97" t="n">
-        <v>93155</v>
+        <v>79893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10886,38 +10890,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5448</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>614971</v>
+        <v>614887</v>
       </c>
       <c r="R97" t="n">
-        <v>6560251</v>
+        <v>6560423</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10944,17 +10944,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>12 st</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10985,10 +10980,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131733475</v>
+        <v>131732767</v>
       </c>
       <c r="B98" t="n">
-        <v>8444</v>
+        <v>93134</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10996,34 +10991,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106554</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>614840</v>
+        <v>615105</v>
       </c>
       <c r="R98" t="n">
-        <v>6560403</v>
+        <v>6560378</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11050,12 +11045,17 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Spritt i området</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11089,7 +11089,7 @@
         <v>131737722</v>
       </c>
       <c r="B99" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>131740395</v>
       </c>
       <c r="B100" t="n">
-        <v>93158</v>
+        <v>93163</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>131740398</v>
       </c>
       <c r="B101" t="n">
-        <v>93158</v>
+        <v>93163</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>131737757</v>
       </c>
       <c r="B102" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>131737776</v>
       </c>
       <c r="B103" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11630,45 +11630,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131736992</v>
+        <v>131739042</v>
       </c>
       <c r="B104" t="n">
-        <v>91326</v>
+        <v>79893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2051</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>614848</v>
+        <v>614859</v>
       </c>
       <c r="R104" t="n">
-        <v>6560378</v>
+        <v>6560517</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11695,12 +11695,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11731,10 +11731,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131739042</v>
+        <v>131739016</v>
       </c>
       <c r="B105" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11762,14 +11762,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>614859</v>
+        <v>615035</v>
       </c>
       <c r="R105" t="n">
-        <v>6560517</v>
+        <v>6560425</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11796,12 +11796,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11832,10 +11832,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131739016</v>
+        <v>131739017</v>
       </c>
       <c r="B106" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>615035</v>
+        <v>615032</v>
       </c>
       <c r="R106" t="n">
         <v>6560425</v>
@@ -11933,45 +11933,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131739017</v>
+        <v>131736992</v>
       </c>
       <c r="B107" t="n">
-        <v>79888</v>
+        <v>91331</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>2051</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>615032</v>
+        <v>614848</v>
       </c>
       <c r="R107" t="n">
-        <v>6560425</v>
+        <v>6560378</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12034,32 +12034,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131736993</v>
+        <v>131739021</v>
       </c>
       <c r="B108" t="n">
-        <v>91326</v>
+        <v>79893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2051</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12069,10 +12069,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>614719</v>
+        <v>614820</v>
       </c>
       <c r="R108" t="n">
-        <v>6560440</v>
+        <v>6560501</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12099,12 +12099,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12135,10 +12135,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131739021</v>
+        <v>131732521</v>
       </c>
       <c r="B109" t="n">
-        <v>79888</v>
+        <v>78940</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12146,34 +12146,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>614820</v>
+        <v>614661</v>
       </c>
       <c r="R109" t="n">
-        <v>6560501</v>
+        <v>6560444</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12236,45 +12236,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131740080</v>
+        <v>131736993</v>
       </c>
       <c r="B110" t="n">
-        <v>91862</v>
+        <v>91331</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5442</v>
+        <v>2051</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>615060</v>
+        <v>614719</v>
       </c>
       <c r="R110" t="n">
-        <v>6560430</v>
+        <v>6560440</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12301,12 +12301,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12340,7 +12340,7 @@
         <v>131737715</v>
       </c>
       <c r="B111" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>131737780</v>
       </c>
       <c r="B112" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12557,10 +12557,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131732521</v>
+        <v>131740080</v>
       </c>
       <c r="B113" t="n">
-        <v>78935</v>
+        <v>91867</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12568,34 +12568,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>614661</v>
+        <v>615060</v>
       </c>
       <c r="R113" t="n">
-        <v>6560444</v>
+        <v>6560430</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12622,12 +12622,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12658,10 +12658,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131739022</v>
+        <v>131736464</v>
       </c>
       <c r="B114" t="n">
-        <v>79888</v>
+        <v>57909</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12669,34 +12669,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nord, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>614790</v>
+        <v>614934</v>
       </c>
       <c r="R114" t="n">
-        <v>6560493</v>
+        <v>6560353</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12723,12 +12723,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12759,10 +12759,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131737739</v>
+        <v>131739022</v>
       </c>
       <c r="B115" t="n">
-        <v>93167</v>
+        <v>79893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12770,38 +12770,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>614717</v>
+        <v>614790</v>
       </c>
       <c r="R115" t="n">
-        <v>6560453</v>
+        <v>6560493</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12834,11 +12830,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12869,10 +12860,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131737752</v>
+        <v>131737739</v>
       </c>
       <c r="B116" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12899,7 +12890,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -12908,10 +12899,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>614875</v>
+        <v>614717</v>
       </c>
       <c r="R116" t="n">
-        <v>6560431</v>
+        <v>6560453</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12948,7 +12939,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12979,10 +12970,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131737766</v>
+        <v>131737752</v>
       </c>
       <c r="B117" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13009,19 +13000,19 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>614826</v>
+        <v>614875</v>
       </c>
       <c r="R117" t="n">
-        <v>6560351</v>
+        <v>6560431</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13058,7 +13049,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13089,45 +13080,49 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131733366</v>
+        <v>131737766</v>
       </c>
       <c r="B118" t="n">
-        <v>92499</v>
+        <v>93172</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>615138</v>
+        <v>614826</v>
       </c>
       <c r="R118" t="n">
-        <v>6560392</v>
+        <v>6560351</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13160,6 +13155,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13190,49 +13190,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131737710</v>
+        <v>131733366</v>
       </c>
       <c r="B119" t="n">
-        <v>93167</v>
+        <v>92504</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>614961</v>
+        <v>615138</v>
       </c>
       <c r="R119" t="n">
-        <v>6560414</v>
+        <v>6560392</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13265,11 +13261,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13300,10 +13291,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131736464</v>
+        <v>131737710</v>
       </c>
       <c r="B120" t="n">
-        <v>57904</v>
+        <v>93172</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13311,34 +13302,38 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Nystugan Nord, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>614934</v>
+        <v>614961</v>
       </c>
       <c r="R120" t="n">
-        <v>6560353</v>
+        <v>6560414</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13365,12 +13360,17 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13401,10 +13401,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131739040</v>
+        <v>131733306</v>
       </c>
       <c r="B121" t="n">
-        <v>79888</v>
+        <v>93128</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13412,34 +13412,38 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>614705</v>
+        <v>614689</v>
       </c>
       <c r="R121" t="n">
-        <v>6560468</v>
+        <v>6560516</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13466,12 +13470,17 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>1 St</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13502,45 +13511,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131732765</v>
+        <v>131740365</v>
       </c>
       <c r="B122" t="n">
-        <v>93129</v>
+        <v>93163</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>614878</v>
+        <v>614741</v>
       </c>
       <c r="R122" t="n">
-        <v>6560511</v>
+        <v>6560508</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13567,17 +13576,17 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Förekommer spritt rikligt</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13586,6 +13595,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13608,10 +13618,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131740365</v>
+        <v>131737605</v>
       </c>
       <c r="B123" t="n">
-        <v>93158</v>
+        <v>93172</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13619,34 +13629,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>614741</v>
+        <v>614921</v>
       </c>
       <c r="R123" t="n">
-        <v>6560508</v>
+        <v>6560349</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13673,17 +13683,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13692,7 +13697,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13715,10 +13719,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131737605</v>
+        <v>131737753</v>
       </c>
       <c r="B124" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13743,17 +13747,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>614921</v>
+        <v>614883</v>
       </c>
       <c r="R124" t="n">
-        <v>6560349</v>
+        <v>6560422</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13780,12 +13788,17 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13816,49 +13829,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131737753</v>
+        <v>131733367</v>
       </c>
       <c r="B125" t="n">
-        <v>93167</v>
+        <v>92504</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>614883</v>
+        <v>614939</v>
       </c>
       <c r="R125" t="n">
-        <v>6560422</v>
+        <v>6560438</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13891,11 +13900,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13926,45 +13930,49 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131733367</v>
+        <v>131737719</v>
       </c>
       <c r="B126" t="n">
-        <v>92499</v>
+        <v>93172</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>614939</v>
+        <v>614817</v>
       </c>
       <c r="R126" t="n">
-        <v>6560438</v>
+        <v>6560509</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13997,6 +14005,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14027,10 +14040,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131737719</v>
+        <v>131737768</v>
       </c>
       <c r="B127" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14057,19 +14070,19 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>614817</v>
+        <v>614843</v>
       </c>
       <c r="R127" t="n">
-        <v>6560509</v>
+        <v>6560322</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14106,7 +14119,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14137,10 +14150,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131737768</v>
+        <v>131740367</v>
       </c>
       <c r="B128" t="n">
-        <v>93167</v>
+        <v>93163</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14148,38 +14161,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>614843</v>
+        <v>614742</v>
       </c>
       <c r="R128" t="n">
-        <v>6560322</v>
+        <v>6560443</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14216,7 +14225,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14225,6 +14234,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -14247,10 +14257,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131740367</v>
+        <v>131737778</v>
       </c>
       <c r="B129" t="n">
-        <v>93158</v>
+        <v>93172</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14258,34 +14268,38 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>614742</v>
+        <v>615115</v>
       </c>
       <c r="R129" t="n">
-        <v>6560443</v>
+        <v>6560377</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14322,7 +14336,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14331,7 +14345,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -14354,10 +14367,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131737778</v>
+        <v>131737741</v>
       </c>
       <c r="B130" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14384,19 +14397,19 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>615115</v>
+        <v>614754</v>
       </c>
       <c r="R130" t="n">
-        <v>6560377</v>
+        <v>6560449</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14433,7 +14446,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14464,10 +14477,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131737741</v>
+        <v>131737751</v>
       </c>
       <c r="B131" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14494,7 +14507,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -14503,10 +14516,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>614754</v>
+        <v>614860</v>
       </c>
       <c r="R131" t="n">
-        <v>6560449</v>
+        <v>6560430</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14543,7 +14556,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14574,10 +14587,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131737751</v>
+        <v>131737604</v>
       </c>
       <c r="B132" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14602,21 +14615,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>614860</v>
+        <v>615114</v>
       </c>
       <c r="R132" t="n">
-        <v>6560430</v>
+        <v>6560473</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14643,17 +14652,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14684,10 +14688,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131733306</v>
+        <v>131739040</v>
       </c>
       <c r="B133" t="n">
-        <v>93123</v>
+        <v>79893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14695,38 +14699,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>614689</v>
+        <v>614705</v>
       </c>
       <c r="R133" t="n">
-        <v>6560516</v>
+        <v>6560468</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14753,17 +14753,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>1 St</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14794,45 +14789,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131737604</v>
+        <v>131732765</v>
       </c>
       <c r="B134" t="n">
-        <v>93167</v>
+        <v>93134</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>615114</v>
+        <v>614878</v>
       </c>
       <c r="R134" t="n">
-        <v>6560473</v>
+        <v>6560511</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14859,12 +14854,17 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Förekommer spritt rikligt</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14996,10 +14996,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131740243</v>
+        <v>131739551</v>
       </c>
       <c r="B136" t="n">
-        <v>92773</v>
+        <v>91846</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15007,38 +15007,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4745</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>614829</v>
+        <v>614622</v>
       </c>
       <c r="R136" t="n">
-        <v>6560371</v>
+        <v>6560528</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15065,17 +15061,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15109,7 +15100,7 @@
         <v>131733304</v>
       </c>
       <c r="B137" t="n">
-        <v>93123</v>
+        <v>93128</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15216,10 +15207,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>131739551</v>
+        <v>131737743</v>
       </c>
       <c r="B138" t="n">
-        <v>91841</v>
+        <v>93172</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15227,34 +15218,38 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>614622</v>
+        <v>614731</v>
       </c>
       <c r="R138" t="n">
-        <v>6560528</v>
+        <v>6560390</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15281,12 +15276,17 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15317,10 +15317,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>131737743</v>
+        <v>131740394</v>
       </c>
       <c r="B139" t="n">
-        <v>93167</v>
+        <v>93163</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15328,38 +15328,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q139" t="n">
         <v>614731</v>
       </c>
       <c r="R139" t="n">
-        <v>6560390</v>
+        <v>6560512</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15386,17 +15382,17 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 st</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15405,6 +15401,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -15427,10 +15424,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>131740394</v>
+        <v>131737707</v>
       </c>
       <c r="B140" t="n">
-        <v>93158</v>
+        <v>93172</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15438,34 +15435,38 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>614731</v>
+        <v>614934</v>
       </c>
       <c r="R140" t="n">
-        <v>6560512</v>
+        <v>6560422</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15492,17 +15493,17 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>1 st</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15511,7 +15512,6 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15534,10 +15534,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>131737707</v>
+        <v>131737748</v>
       </c>
       <c r="B141" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15564,19 +15564,19 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>614934</v>
+        <v>614792</v>
       </c>
       <c r="R141" t="n">
-        <v>6560422</v>
+        <v>6560431</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15613,7 +15613,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15644,10 +15644,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>131737748</v>
+        <v>131740402</v>
       </c>
       <c r="B142" t="n">
-        <v>93167</v>
+        <v>93163</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15655,38 +15655,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>614792</v>
+        <v>615135</v>
       </c>
       <c r="R142" t="n">
-        <v>6560431</v>
+        <v>6560485</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15713,17 +15709,17 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>Ca 25st</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15732,6 +15728,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15754,10 +15751,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>131740402</v>
+        <v>131740243</v>
       </c>
       <c r="B143" t="n">
-        <v>93158</v>
+        <v>92778</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15765,34 +15762,38 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5449</v>
+        <v>4745</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr"/>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>615135</v>
+        <v>614829</v>
       </c>
       <c r="R143" t="n">
-        <v>6560485</v>
+        <v>6560371</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15819,17 +15820,17 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ca 25st</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15838,7 +15839,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -15970,7 +15970,7 @@
         <v>131740304</v>
       </c>
       <c r="B145" t="n">
-        <v>91334</v>
+        <v>91339</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16068,10 +16068,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>131737264</v>
+        <v>131732523</v>
       </c>
       <c r="B146" t="n">
-        <v>93121</v>
+        <v>78940</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16079,38 +16079,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>615062</v>
+        <v>614818</v>
       </c>
       <c r="R146" t="n">
-        <v>6560402</v>
+        <v>6560356</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16137,17 +16133,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>4 st</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16178,10 +16169,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>131737266</v>
+        <v>131737264</v>
       </c>
       <c r="B147" t="n">
-        <v>93121</v>
+        <v>93126</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16208,7 +16199,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -16217,10 +16208,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>615141</v>
+        <v>615062</v>
       </c>
       <c r="R147" t="n">
-        <v>6560479</v>
+        <v>6560402</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16257,7 +16248,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>2 st</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16288,10 +16279,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>131737262</v>
+        <v>131737266</v>
       </c>
       <c r="B148" t="n">
-        <v>93121</v>
+        <v>93126</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16318,19 +16309,19 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>614741</v>
+        <v>615141</v>
       </c>
       <c r="R148" t="n">
-        <v>6560504</v>
+        <v>6560479</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16367,7 +16358,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>1 st</t>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16398,10 +16389,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>131732523</v>
+        <v>131737262</v>
       </c>
       <c r="B149" t="n">
-        <v>78935</v>
+        <v>93126</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16409,34 +16400,38 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>614818</v>
+        <v>614741</v>
       </c>
       <c r="R149" t="n">
-        <v>6560356</v>
+        <v>6560504</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16463,12 +16458,17 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>1 st</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16502,7 +16502,7 @@
         <v>131737727</v>
       </c>
       <c r="B150" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         <v>131737726</v>
       </c>
       <c r="B151" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         <v>131737706</v>
       </c>
       <c r="B152" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>131740400</v>
       </c>
       <c r="B153" t="n">
-        <v>93158</v>
+        <v>93163</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>131740364</v>
       </c>
       <c r="B154" t="n">
-        <v>93158</v>
+        <v>93163</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>131737777</v>
       </c>
       <c r="B155" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>131737772</v>
       </c>
       <c r="B156" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>131737606</v>
       </c>
       <c r="B157" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>131737709</v>
       </c>
       <c r="B158" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>131737759</v>
       </c>
       <c r="B159" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>131737761</v>
       </c>
       <c r="B160" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>131737755</v>
       </c>
       <c r="B161" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>131737611</v>
       </c>
       <c r="B162" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>131737763</v>
       </c>
       <c r="B163" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>131732764</v>
       </c>
       <c r="B164" t="n">
-        <v>93129</v>
+        <v>93134</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
         <v>131738710</v>
       </c>
       <c r="B165" t="n">
-        <v>97287</v>
+        <v>97292</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>131740287</v>
       </c>
       <c r="B166" t="n">
-        <v>93117</v>
+        <v>93122</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>131737767</v>
       </c>
       <c r="B167" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>131737720</v>
       </c>
       <c r="B168" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18541,7 +18541,7 @@
         <v>131740393</v>
       </c>
       <c r="B169" t="n">
-        <v>93158</v>
+        <v>93163</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>131737735</v>
       </c>
       <c r="B170" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>131737609</v>
       </c>
       <c r="B171" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18856,10 +18856,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>131734664</v>
+        <v>131740359</v>
       </c>
       <c r="B172" t="n">
-        <v>79026</v>
+        <v>93163</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18867,34 +18867,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>615034</v>
+        <v>614877</v>
       </c>
       <c r="R172" t="n">
-        <v>6560418</v>
+        <v>6560513</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18921,12 +18921,17 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18935,6 +18940,7 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -18957,10 +18963,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>131734663</v>
+        <v>131737740</v>
       </c>
       <c r="B173" t="n">
-        <v>79026</v>
+        <v>93172</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18968,34 +18974,38 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>614679</v>
+        <v>614746</v>
       </c>
       <c r="R173" t="n">
-        <v>6560422</v>
+        <v>6560453</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19022,12 +19032,17 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19058,10 +19073,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>131735737</v>
+        <v>131737742</v>
       </c>
       <c r="B174" t="n">
-        <v>92631</v>
+        <v>93172</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19069,38 +19084,38 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>366</v>
+        <v>5966</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>615093</v>
+        <v>614738</v>
       </c>
       <c r="R174" t="n">
-        <v>6560461</v>
+        <v>6560442</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19127,17 +19142,17 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19168,10 +19183,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>131732524</v>
+        <v>131737721</v>
       </c>
       <c r="B175" t="n">
-        <v>78935</v>
+        <v>93172</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19179,34 +19194,38 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>614915</v>
+        <v>614776</v>
       </c>
       <c r="R175" t="n">
-        <v>6560407</v>
+        <v>6560488</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19233,12 +19252,17 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19269,10 +19293,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>131740359</v>
+        <v>131737775</v>
       </c>
       <c r="B176" t="n">
-        <v>93158</v>
+        <v>93172</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19280,34 +19304,38 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nord, Srm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>614877</v>
+        <v>614989</v>
       </c>
       <c r="R176" t="n">
-        <v>6560513</v>
+        <v>6560288</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19334,17 +19362,17 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19353,7 +19381,6 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
-      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -19376,10 +19403,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>131737740</v>
+        <v>131737738</v>
       </c>
       <c r="B177" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19406,7 +19433,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -19415,10 +19442,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>614746</v>
+        <v>614711</v>
       </c>
       <c r="R177" t="n">
-        <v>6560453</v>
+        <v>6560481</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19455,7 +19482,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19486,10 +19513,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>131737742</v>
+        <v>131740399</v>
       </c>
       <c r="B178" t="n">
-        <v>93167</v>
+        <v>93163</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19497,23 +19524,19 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
           <t>5</t>
@@ -19521,14 +19544,14 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>614738</v>
+        <v>614904</v>
       </c>
       <c r="R178" t="n">
-        <v>6560442</v>
+        <v>6560330</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19555,17 +19578,17 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 st</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19574,6 +19597,7 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -19596,10 +19620,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>131737721</v>
+        <v>131735737</v>
       </c>
       <c r="B179" t="n">
-        <v>93167</v>
+        <v>92636</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19607,21 +19631,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5966</v>
+        <v>366</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -19631,14 +19655,14 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>614776</v>
+        <v>615093</v>
       </c>
       <c r="R179" t="n">
-        <v>6560488</v>
+        <v>6560461</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19665,17 +19689,17 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19706,10 +19730,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>131737775</v>
+        <v>131732524</v>
       </c>
       <c r="B180" t="n">
-        <v>93167</v>
+        <v>78940</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19717,38 +19741,34 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Nystugan Nord, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>614989</v>
+        <v>614915</v>
       </c>
       <c r="R180" t="n">
-        <v>6560288</v>
+        <v>6560407</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19775,17 +19795,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>14</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19816,10 +19831,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>131737738</v>
+        <v>131734664</v>
       </c>
       <c r="B181" t="n">
-        <v>93167</v>
+        <v>79031</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19827,38 +19842,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>614711</v>
+        <v>615034</v>
       </c>
       <c r="R181" t="n">
-        <v>6560481</v>
+        <v>6560418</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19891,11 +19902,6 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19926,10 +19932,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>131740399</v>
+        <v>131734663</v>
       </c>
       <c r="B182" t="n">
-        <v>93158</v>
+        <v>79031</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19937,34 +19943,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>614904</v>
+        <v>614679</v>
       </c>
       <c r="R182" t="n">
-        <v>6560330</v>
+        <v>6560422</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19991,17 +19997,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>5 st</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20010,7 +20011,6 @@
       <c r="AE182" t="b">
         <v>0</v>
       </c>
-      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43282-2024 artfynd.xlsx
+++ b/artfynd/A 43282-2024 artfynd.xlsx
@@ -2583,45 +2583,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131737607</v>
+        <v>131732769</v>
       </c>
       <c r="B19" t="n">
-        <v>93172</v>
+        <v>93134</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>614643</v>
+        <v>615104</v>
       </c>
       <c r="R19" t="n">
-        <v>6560479</v>
+        <v>6560485</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2648,12 +2648,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Återkommer spritt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2684,10 +2689,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131740240</v>
+        <v>131737607</v>
       </c>
       <c r="B20" t="n">
-        <v>92778</v>
+        <v>93172</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,34 +2700,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615041</v>
+        <v>614643</v>
       </c>
       <c r="R20" t="n">
-        <v>6560443</v>
+        <v>6560479</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2785,32 +2790,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131732769</v>
+        <v>131740240</v>
       </c>
       <c r="B21" t="n">
-        <v>93134</v>
+        <v>92778</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2825,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615104</v>
+        <v>615041</v>
       </c>
       <c r="R21" t="n">
-        <v>6560485</v>
+        <v>6560443</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2850,17 +2855,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Återkommer spritt</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3533,10 +3533,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131737762</v>
+        <v>131738985</v>
       </c>
       <c r="B28" t="n">
-        <v>93172</v>
+        <v>79893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3544,38 +3544,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>614855</v>
+        <v>614827</v>
       </c>
       <c r="R28" t="n">
-        <v>6560397</v>
+        <v>6560518</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3602,17 +3598,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3643,10 +3634,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131737779</v>
+        <v>131739020</v>
       </c>
       <c r="B29" t="n">
-        <v>93172</v>
+        <v>79893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3654,38 +3645,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>615173</v>
+        <v>614839</v>
       </c>
       <c r="R29" t="n">
-        <v>6560476</v>
+        <v>6560502</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3718,11 +3705,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3753,7 +3735,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131737781</v>
+        <v>131737762</v>
       </c>
       <c r="B30" t="n">
         <v>93172</v>
@@ -3783,19 +3765,19 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615158</v>
+        <v>614855</v>
       </c>
       <c r="R30" t="n">
-        <v>6560491</v>
+        <v>6560397</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3832,7 +3814,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3863,7 +3845,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131737746</v>
+        <v>131737779</v>
       </c>
       <c r="B31" t="n">
         <v>93172</v>
@@ -3893,19 +3875,19 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>614777</v>
+        <v>615173</v>
       </c>
       <c r="R31" t="n">
-        <v>6560432</v>
+        <v>6560476</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3942,7 +3924,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3973,10 +3955,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131740362</v>
+        <v>131737781</v>
       </c>
       <c r="B32" t="n">
-        <v>93163</v>
+        <v>93172</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3984,19 +3966,23 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>1</t>
@@ -4008,10 +3994,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>614974</v>
+        <v>615158</v>
       </c>
       <c r="R32" t="n">
-        <v>6560411</v>
+        <v>6560491</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4057,7 +4043,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4080,7 +4065,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737750</v>
+        <v>131737746</v>
       </c>
       <c r="B33" t="n">
         <v>93172</v>
@@ -4110,7 +4095,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4119,10 +4104,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>614846</v>
+        <v>614777</v>
       </c>
       <c r="R33" t="n">
-        <v>6560435</v>
+        <v>6560432</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4159,7 +4144,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4190,10 +4175,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131737765</v>
+        <v>131740362</v>
       </c>
       <c r="B34" t="n">
-        <v>93172</v>
+        <v>93163</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4201,38 +4186,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>614814</v>
+        <v>614974</v>
       </c>
       <c r="R34" t="n">
-        <v>6560371</v>
+        <v>6560411</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4269,7 +4250,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4278,6 +4259,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4300,10 +4282,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131738985</v>
+        <v>131737750</v>
       </c>
       <c r="B35" t="n">
-        <v>79893</v>
+        <v>93172</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4311,34 +4293,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>614827</v>
+        <v>614846</v>
       </c>
       <c r="R35" t="n">
-        <v>6560518</v>
+        <v>6560435</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4365,12 +4351,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4401,10 +4392,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131739020</v>
+        <v>131737765</v>
       </c>
       <c r="B36" t="n">
-        <v>79893</v>
+        <v>93172</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4412,34 +4403,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>614839</v>
+        <v>614814</v>
       </c>
       <c r="R36" t="n">
-        <v>6560502</v>
+        <v>6560371</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4472,6 +4467,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4502,10 +4502,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131736037</v>
+        <v>131738986</v>
       </c>
       <c r="B37" t="n">
-        <v>92084</v>
+        <v>79893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4513,34 +4513,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1101</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>614602</v>
+        <v>614832</v>
       </c>
       <c r="R37" t="n">
-        <v>6560488</v>
+        <v>6560556</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4567,12 +4567,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4603,45 +4603,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131736787</v>
+        <v>131739037</v>
       </c>
       <c r="B38" t="n">
-        <v>92218</v>
+        <v>79893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2062</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>614622</v>
+        <v>615086</v>
       </c>
       <c r="R38" t="n">
-        <v>6560528</v>
+        <v>6560375</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4704,10 +4704,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131736576</v>
+        <v>131739024</v>
       </c>
       <c r="B39" t="n">
-        <v>93150</v>
+        <v>79893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4715,38 +4715,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>614640</v>
+        <v>614774</v>
       </c>
       <c r="R39" t="n">
-        <v>6560409</v>
+        <v>6560505</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4773,17 +4769,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>9 st</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4814,10 +4805,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131740334</v>
+        <v>131736037</v>
       </c>
       <c r="B40" t="n">
-        <v>93160</v>
+        <v>92084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4825,34 +4816,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5448</v>
+        <v>1101</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>614945</v>
+        <v>614602</v>
       </c>
       <c r="R40" t="n">
-        <v>6560495</v>
+        <v>6560488</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4915,45 +4906,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131737733</v>
+        <v>131736787</v>
       </c>
       <c r="B41" t="n">
-        <v>93172</v>
+        <v>92218</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>2062</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>614695</v>
+        <v>614622</v>
       </c>
       <c r="R41" t="n">
-        <v>6560413</v>
+        <v>6560528</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4980,12 +4971,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5016,10 +5007,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131737764</v>
+        <v>131736576</v>
       </c>
       <c r="B42" t="n">
-        <v>93172</v>
+        <v>93150</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5027,21 +5018,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5051,14 +5042,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>614836</v>
+        <v>614640</v>
       </c>
       <c r="R42" t="n">
-        <v>6560376</v>
+        <v>6560409</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5085,17 +5076,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9 st</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5126,10 +5117,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131737713</v>
+        <v>131740334</v>
       </c>
       <c r="B43" t="n">
-        <v>93172</v>
+        <v>93160</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5137,21 +5128,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5161,10 +5152,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>614935</v>
+        <v>614945</v>
       </c>
       <c r="R43" t="n">
-        <v>6560472</v>
+        <v>6560495</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5227,10 +5218,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131738986</v>
+        <v>131737733</v>
       </c>
       <c r="B44" t="n">
-        <v>79893</v>
+        <v>93172</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5238,34 +5229,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>614832</v>
+        <v>614695</v>
       </c>
       <c r="R44" t="n">
-        <v>6560556</v>
+        <v>6560413</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5292,12 +5283,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5328,10 +5319,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131739037</v>
+        <v>131737764</v>
       </c>
       <c r="B45" t="n">
-        <v>79893</v>
+        <v>93172</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5339,34 +5330,38 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>615086</v>
+        <v>614836</v>
       </c>
       <c r="R45" t="n">
-        <v>6560375</v>
+        <v>6560376</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5393,12 +5388,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5429,10 +5429,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131739024</v>
+        <v>131737713</v>
       </c>
       <c r="B46" t="n">
-        <v>79893</v>
+        <v>93172</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5440,21 +5440,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5464,10 +5464,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>614774</v>
+        <v>614935</v>
       </c>
       <c r="R46" t="n">
-        <v>6560505</v>
+        <v>6560472</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5530,10 +5530,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131739023</v>
+        <v>131740368</v>
       </c>
       <c r="B47" t="n">
-        <v>79893</v>
+        <v>93163</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5541,34 +5541,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>614757</v>
+        <v>614772</v>
       </c>
       <c r="R47" t="n">
-        <v>6560461</v>
+        <v>6560415</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5603,12 +5603,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5631,10 +5637,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131740368</v>
+        <v>131740341</v>
       </c>
       <c r="B48" t="n">
-        <v>93163</v>
+        <v>93160</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5642,34 +5648,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>614772</v>
+        <v>614963</v>
       </c>
       <c r="R48" t="n">
-        <v>6560415</v>
+        <v>6560256</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5696,17 +5706,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8 st</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5715,7 +5725,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5738,10 +5747,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131740341</v>
+        <v>131737612</v>
       </c>
       <c r="B49" t="n">
-        <v>93160</v>
+        <v>93172</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5749,38 +5758,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>614963</v>
+        <v>614843</v>
       </c>
       <c r="R49" t="n">
-        <v>6560256</v>
+        <v>6560521</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5807,17 +5812,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>8 st</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5848,7 +5848,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737612</v>
+        <v>131737613</v>
       </c>
       <c r="B50" t="n">
         <v>93172</v>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>614843</v>
+        <v>614811</v>
       </c>
       <c r="R50" t="n">
-        <v>6560521</v>
+        <v>6560570</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5949,7 +5949,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737613</v>
+        <v>131737728</v>
       </c>
       <c r="B51" t="n">
         <v>93172</v>
@@ -5977,17 +5977,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>614811</v>
+        <v>614659</v>
       </c>
       <c r="R51" t="n">
-        <v>6560570</v>
+        <v>6560444</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6014,12 +6018,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6050,7 +6059,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131737728</v>
+        <v>131737608</v>
       </c>
       <c r="B52" t="n">
         <v>93172</v>
@@ -6078,21 +6087,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>614659</v>
+        <v>614654</v>
       </c>
       <c r="R52" t="n">
-        <v>6560444</v>
+        <v>6560489</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6119,17 +6124,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6160,7 +6160,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131737608</v>
+        <v>131737734</v>
       </c>
       <c r="B53" t="n">
         <v>93172</v>
@@ -6188,17 +6188,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>614654</v>
+        <v>614708</v>
       </c>
       <c r="R53" t="n">
-        <v>6560489</v>
+        <v>6560403</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6225,12 +6229,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6261,7 +6270,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131737734</v>
+        <v>131737760</v>
       </c>
       <c r="B54" t="n">
         <v>93172</v>
@@ -6291,7 +6300,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6300,10 +6309,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>614708</v>
+        <v>614880</v>
       </c>
       <c r="R54" t="n">
-        <v>6560403</v>
+        <v>6560400</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6340,7 +6349,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6371,10 +6380,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131737760</v>
+        <v>131739023</v>
       </c>
       <c r="B55" t="n">
-        <v>93172</v>
+        <v>79893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6382,38 +6391,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>614880</v>
+        <v>614757</v>
       </c>
       <c r="R55" t="n">
-        <v>6560400</v>
+        <v>6560461</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6446,11 +6451,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7969,37 +7969,37 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131736991</v>
+        <v>131737261</v>
       </c>
       <c r="B70" t="n">
-        <v>91331</v>
+        <v>93126</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2051</v>
+        <v>4361</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8008,10 +8008,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>614736</v>
+        <v>614895</v>
       </c>
       <c r="R70" t="n">
-        <v>6560397</v>
+        <v>6560392</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>3 st</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8079,45 +8079,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131740391</v>
+        <v>131739788</v>
       </c>
       <c r="B71" t="n">
-        <v>93163</v>
+        <v>92569</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5449</v>
+        <v>3298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>614945</v>
+        <v>615070</v>
       </c>
       <c r="R71" t="n">
-        <v>6560479</v>
+        <v>6560325</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8144,17 +8144,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>2 st</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8163,7 +8158,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8186,49 +8180,49 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131740335</v>
+        <v>131736991</v>
       </c>
       <c r="B72" t="n">
-        <v>93160</v>
+        <v>91331</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5448</v>
+        <v>2051</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>614815</v>
+        <v>614736</v>
       </c>
       <c r="R72" t="n">
-        <v>6560508</v>
+        <v>6560397</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8255,17 +8249,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8296,10 +8290,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131737261</v>
+        <v>131740391</v>
       </c>
       <c r="B73" t="n">
-        <v>93126</v>
+        <v>93163</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8307,38 +8301,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>614895</v>
+        <v>614945</v>
       </c>
       <c r="R73" t="n">
-        <v>6560392</v>
+        <v>6560479</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8375,7 +8365,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8384,6 +8374,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8406,45 +8397,49 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131739788</v>
+        <v>131740335</v>
       </c>
       <c r="B74" t="n">
-        <v>92569</v>
+        <v>93160</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3298</v>
+        <v>5448</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>615070</v>
+        <v>614815</v>
       </c>
       <c r="R74" t="n">
-        <v>6560325</v>
+        <v>6560508</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8471,12 +8466,17 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9913,10 +9913,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131737724</v>
+        <v>131739025</v>
       </c>
       <c r="B88" t="n">
-        <v>93172</v>
+        <v>79893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9924,38 +9924,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>614765</v>
+        <v>614887</v>
       </c>
       <c r="R88" t="n">
-        <v>6560506</v>
+        <v>6560423</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9988,11 +9984,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10023,49 +10014,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131737732</v>
+        <v>131733475</v>
       </c>
       <c r="B89" t="n">
-        <v>93172</v>
+        <v>8444</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5966</v>
+        <v>106554</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>614684</v>
+        <v>614840</v>
       </c>
       <c r="R89" t="n">
-        <v>6560422</v>
+        <v>6560403</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10092,17 +10079,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10133,10 +10115,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131737718</v>
+        <v>131737045</v>
       </c>
       <c r="B90" t="n">
-        <v>93172</v>
+        <v>92145</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10144,38 +10126,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5966</v>
+        <v>658</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>614844</v>
+        <v>614622</v>
       </c>
       <c r="R90" t="n">
-        <v>6560496</v>
+        <v>6560529</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10202,17 +10180,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10243,10 +10216,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131740366</v>
+        <v>131737724</v>
       </c>
       <c r="B91" t="n">
-        <v>93163</v>
+        <v>93172</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10254,22 +10227,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -10278,10 +10255,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>614682</v>
+        <v>614765</v>
       </c>
       <c r="R91" t="n">
-        <v>6560491</v>
+        <v>6560506</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10318,7 +10295,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10327,7 +10304,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10350,7 +10326,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131737745</v>
+        <v>131737732</v>
       </c>
       <c r="B92" t="n">
         <v>93172</v>
@@ -10380,19 +10356,19 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>614779</v>
+        <v>614684</v>
       </c>
       <c r="R92" t="n">
-        <v>6560385</v>
+        <v>6560422</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10429,7 +10405,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10460,10 +10436,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131740392</v>
+        <v>131737718</v>
       </c>
       <c r="B93" t="n">
-        <v>93163</v>
+        <v>93172</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10471,22 +10447,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10495,10 +10475,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>614832</v>
+        <v>614844</v>
       </c>
       <c r="R93" t="n">
-        <v>6560458</v>
+        <v>6560496</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10525,17 +10505,17 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>10 st</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10544,7 +10524,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10567,10 +10546,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131740342</v>
+        <v>131740366</v>
       </c>
       <c r="B94" t="n">
-        <v>93160</v>
+        <v>93163</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10578,38 +10557,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5448</v>
+        <v>5449</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>614971</v>
+        <v>614682</v>
       </c>
       <c r="R94" t="n">
-        <v>6560251</v>
+        <v>6560491</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10636,17 +10611,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>12 st</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10655,6 +10630,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10677,45 +10653,49 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131733475</v>
+        <v>131737745</v>
       </c>
       <c r="B95" t="n">
-        <v>8444</v>
+        <v>93172</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106554</v>
+        <v>5966</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>614840</v>
+        <v>614779</v>
       </c>
       <c r="R95" t="n">
-        <v>6560403</v>
+        <v>6560385</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10742,12 +10722,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10778,10 +10763,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131737045</v>
+        <v>131740392</v>
       </c>
       <c r="B96" t="n">
-        <v>92145</v>
+        <v>93163</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10789,34 +10774,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>5449</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>614622</v>
+        <v>614832</v>
       </c>
       <c r="R96" t="n">
-        <v>6560529</v>
+        <v>6560458</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10843,12 +10828,17 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>10 st</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10857,6 +10847,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10879,10 +10870,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131739025</v>
+        <v>131740342</v>
       </c>
       <c r="B97" t="n">
-        <v>79893</v>
+        <v>93160</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10890,34 +10881,38 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>5448</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>614887</v>
+        <v>614971</v>
       </c>
       <c r="R97" t="n">
-        <v>6560423</v>
+        <v>6560251</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10944,12 +10939,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>12 st</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -14996,10 +14996,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131739551</v>
+        <v>131740243</v>
       </c>
       <c r="B136" t="n">
-        <v>91846</v>
+        <v>92778</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15007,34 +15007,38 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>4745</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>614622</v>
+        <v>614829</v>
       </c>
       <c r="R136" t="n">
-        <v>6560528</v>
+        <v>6560371</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15061,12 +15065,17 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15097,10 +15106,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>131733304</v>
+        <v>131739551</v>
       </c>
       <c r="B137" t="n">
-        <v>93128</v>
+        <v>91846</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15108,38 +15117,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4362</v>
+        <v>1202</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>614759</v>
+        <v>614622</v>
       </c>
       <c r="R137" t="n">
-        <v>6560440</v>
+        <v>6560528</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15166,17 +15171,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>8 st</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15207,10 +15207,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>131737743</v>
+        <v>131733304</v>
       </c>
       <c r="B138" t="n">
-        <v>93172</v>
+        <v>93128</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15218,38 +15218,38 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>614731</v>
+        <v>614759</v>
       </c>
       <c r="R138" t="n">
-        <v>6560390</v>
+        <v>6560440</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15276,17 +15276,17 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8 st</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15317,10 +15317,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>131740394</v>
+        <v>131737743</v>
       </c>
       <c r="B139" t="n">
-        <v>93163</v>
+        <v>93172</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15328,34 +15328,38 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q139" t="n">
         <v>614731</v>
       </c>
       <c r="R139" t="n">
-        <v>6560512</v>
+        <v>6560390</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15382,17 +15386,17 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>1 st</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15401,7 +15405,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -15424,10 +15427,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>131737707</v>
+        <v>131740394</v>
       </c>
       <c r="B140" t="n">
-        <v>93172</v>
+        <v>93163</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15435,38 +15438,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>614934</v>
+        <v>614731</v>
       </c>
       <c r="R140" t="n">
-        <v>6560422</v>
+        <v>6560512</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15493,17 +15492,17 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1 st</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15512,6 +15511,7 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15534,7 +15534,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>131737748</v>
+        <v>131737707</v>
       </c>
       <c r="B141" t="n">
         <v>93172</v>
@@ -15564,19 +15564,19 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>614792</v>
+        <v>614934</v>
       </c>
       <c r="R141" t="n">
-        <v>6560431</v>
+        <v>6560422</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15613,7 +15613,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15644,10 +15644,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>131740402</v>
+        <v>131737748</v>
       </c>
       <c r="B142" t="n">
-        <v>93163</v>
+        <v>93172</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15655,34 +15655,38 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>615135</v>
+        <v>614792</v>
       </c>
       <c r="R142" t="n">
-        <v>6560485</v>
+        <v>6560431</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15709,17 +15713,17 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Ca 25st</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15728,7 +15732,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15751,10 +15754,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>131740243</v>
+        <v>131740402</v>
       </c>
       <c r="B143" t="n">
-        <v>92778</v>
+        <v>93163</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15762,38 +15765,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4745</v>
+        <v>5449</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Fr.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>614829</v>
+        <v>615135</v>
       </c>
       <c r="R143" t="n">
-        <v>6560371</v>
+        <v>6560485</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15820,17 +15819,17 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Ca 25st</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15839,6 +15838,7 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -16389,10 +16389,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>131737262</v>
+        <v>131737727</v>
       </c>
       <c r="B149" t="n">
-        <v>93126</v>
+        <v>93172</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16400,38 +16400,38 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>614741</v>
+        <v>614657</v>
       </c>
       <c r="R149" t="n">
-        <v>6560504</v>
+        <v>6560454</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16458,17 +16458,17 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>1 st</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16499,7 +16499,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>131737727</v>
+        <v>131737726</v>
       </c>
       <c r="B150" t="n">
         <v>93172</v>
@@ -16529,7 +16529,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -16538,10 +16538,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>614657</v>
+        <v>614639</v>
       </c>
       <c r="R150" t="n">
-        <v>6560454</v>
+        <v>6560514</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16609,7 +16609,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>131737726</v>
+        <v>131737706</v>
       </c>
       <c r="B151" t="n">
         <v>93172</v>
@@ -16639,19 +16639,19 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>614639</v>
+        <v>615019</v>
       </c>
       <c r="R151" t="n">
-        <v>6560514</v>
+        <v>6560434</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16719,10 +16719,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>131737706</v>
+        <v>131740400</v>
       </c>
       <c r="B152" t="n">
-        <v>93172</v>
+        <v>93163</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16730,38 +16730,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>615019</v>
+        <v>614952</v>
       </c>
       <c r="R152" t="n">
-        <v>6560434</v>
+        <v>6560279</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16788,17 +16784,17 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16807,6 +16803,7 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -16829,10 +16826,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>131740400</v>
+        <v>131737262</v>
       </c>
       <c r="B153" t="n">
-        <v>93163</v>
+        <v>93126</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16840,34 +16837,38 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr"/>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>614952</v>
+        <v>614741</v>
       </c>
       <c r="R153" t="n">
-        <v>6560279</v>
+        <v>6560504</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16904,7 +16905,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>2 st</t>
+          <t>1 st</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16913,7 +16914,6 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -19831,7 +19831,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>131734664</v>
+        <v>131734663</v>
       </c>
       <c r="B181" t="n">
         <v>79031</v>
@@ -19862,14 +19862,14 @@
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>615034</v>
+        <v>614679</v>
       </c>
       <c r="R181" t="n">
-        <v>6560418</v>
+        <v>6560422</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19896,12 +19896,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19932,7 +19932,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>131734663</v>
+        <v>131734664</v>
       </c>
       <c r="B182" t="n">
         <v>79031</v>
@@ -19963,14 +19963,14 @@
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>614679</v>
+        <v>615034</v>
       </c>
       <c r="R182" t="n">
-        <v>6560422</v>
+        <v>6560418</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19997,12 +19997,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD182" t="b">

--- a/artfynd/A 43282-2024 artfynd.xlsx
+++ b/artfynd/A 43282-2024 artfynd.xlsx
@@ -1745,7 +1745,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131737744</v>
+        <v>131737610</v>
       </c>
       <c r="B11" t="n">
         <v>93174</v>
@@ -1773,21 +1773,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>614738</v>
+        <v>614730</v>
       </c>
       <c r="R11" t="n">
-        <v>6560381</v>
+        <v>6560494</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1814,17 +1810,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,10 +1846,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131737716</v>
+        <v>131738982</v>
       </c>
       <c r="B12" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1866,38 +1857,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>614917</v>
+        <v>614776</v>
       </c>
       <c r="R12" t="n">
-        <v>6560491</v>
+        <v>6560497</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1924,17 +1911,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,10 +1947,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131740401</v>
+        <v>131739018</v>
       </c>
       <c r="B13" t="n">
-        <v>93165</v>
+        <v>79895</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1976,34 +1958,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nystugan Nord, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>614969</v>
+        <v>615028</v>
       </c>
       <c r="R13" t="n">
-        <v>6560271</v>
+        <v>6560422</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2030,17 +2012,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>22 st</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,7 +2026,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2072,7 +2048,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131737729</v>
+        <v>131737744</v>
       </c>
       <c r="B14" t="n">
         <v>93174</v>
@@ -2100,17 +2076,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>614639</v>
+        <v>614738</v>
       </c>
       <c r="R14" t="n">
-        <v>6560401</v>
+        <v>6560381</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2143,6 +2123,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,10 +2158,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131740363</v>
+        <v>131737716</v>
       </c>
       <c r="B15" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2184,22 +2169,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2208,10 +2197,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>614863</v>
+        <v>614917</v>
       </c>
       <c r="R15" t="n">
-        <v>6560516</v>
+        <v>6560491</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2248,7 +2237,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,7 +2246,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2280,10 +2268,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131737610</v>
+        <v>131740401</v>
       </c>
       <c r="B16" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2291,34 +2279,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nord, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>614730</v>
+        <v>614969</v>
       </c>
       <c r="R16" t="n">
-        <v>6560494</v>
+        <v>6560271</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2345,12 +2333,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>22 st</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2359,6 +2352,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2381,10 +2375,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131738982</v>
+        <v>131737729</v>
       </c>
       <c r="B17" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2392,34 +2386,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>614776</v>
+        <v>614639</v>
       </c>
       <c r="R17" t="n">
-        <v>6560497</v>
+        <v>6560401</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2446,12 +2440,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2482,10 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131739018</v>
+        <v>131740363</v>
       </c>
       <c r="B18" t="n">
-        <v>79895</v>
+        <v>93165</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2493,34 +2487,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615028</v>
+        <v>614863</v>
       </c>
       <c r="R18" t="n">
-        <v>6560422</v>
+        <v>6560516</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2555,12 +2549,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -3533,10 +3533,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131737762</v>
+        <v>131738985</v>
       </c>
       <c r="B28" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3544,38 +3544,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>614855</v>
+        <v>614827</v>
       </c>
       <c r="R28" t="n">
-        <v>6560397</v>
+        <v>6560518</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3602,17 +3598,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3643,7 +3634,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131737779</v>
+        <v>131737762</v>
       </c>
       <c r="B29" t="n">
         <v>93174</v>
@@ -3673,19 +3664,19 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>615173</v>
+        <v>614855</v>
       </c>
       <c r="R29" t="n">
-        <v>6560476</v>
+        <v>6560397</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3722,7 +3713,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3753,7 +3744,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131737781</v>
+        <v>131737779</v>
       </c>
       <c r="B30" t="n">
         <v>93174</v>
@@ -3783,7 +3774,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3792,10 +3783,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615158</v>
+        <v>615173</v>
       </c>
       <c r="R30" t="n">
-        <v>6560491</v>
+        <v>6560476</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3832,7 +3823,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4300,10 +4291,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131738985</v>
+        <v>131737781</v>
       </c>
       <c r="B35" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4311,34 +4302,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>614827</v>
+        <v>615158</v>
       </c>
       <c r="R35" t="n">
-        <v>6560518</v>
+        <v>6560491</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4365,12 +4360,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4502,10 +4502,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131736037</v>
+        <v>131740334</v>
       </c>
       <c r="B37" t="n">
-        <v>92086</v>
+        <v>93162</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4513,34 +4513,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1101</v>
+        <v>5448</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>614602</v>
+        <v>614945</v>
       </c>
       <c r="R37" t="n">
-        <v>6560488</v>
+        <v>6560495</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4603,10 +4603,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131740334</v>
+        <v>131737733</v>
       </c>
       <c r="B38" t="n">
-        <v>93162</v>
+        <v>93174</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4614,34 +4614,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>614945</v>
+        <v>614695</v>
       </c>
       <c r="R38" t="n">
-        <v>6560495</v>
+        <v>6560413</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4704,7 +4704,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131737733</v>
+        <v>131737764</v>
       </c>
       <c r="B39" t="n">
         <v>93174</v>
@@ -4732,17 +4732,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>614695</v>
+        <v>614836</v>
       </c>
       <c r="R39" t="n">
-        <v>6560413</v>
+        <v>6560376</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4775,6 +4779,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4805,7 +4814,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131737764</v>
+        <v>131737713</v>
       </c>
       <c r="B40" t="n">
         <v>93174</v>
@@ -4833,21 +4842,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>614836</v>
+        <v>614935</v>
       </c>
       <c r="R40" t="n">
-        <v>6560376</v>
+        <v>6560472</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4880,11 +4885,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4915,10 +4915,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131737713</v>
+        <v>131739037</v>
       </c>
       <c r="B41" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4926,34 +4926,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>614935</v>
+        <v>615086</v>
       </c>
       <c r="R41" t="n">
-        <v>6560472</v>
+        <v>6560375</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4980,12 +4980,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5016,7 +5016,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131739037</v>
+        <v>131739024</v>
       </c>
       <c r="B42" t="n">
         <v>79895</v>
@@ -5047,14 +5047,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>615086</v>
+        <v>614774</v>
       </c>
       <c r="R42" t="n">
-        <v>6560375</v>
+        <v>6560505</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5117,45 +5117,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131739024</v>
+        <v>131736787</v>
       </c>
       <c r="B43" t="n">
-        <v>79895</v>
+        <v>92220</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>2062</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>614774</v>
+        <v>614622</v>
       </c>
       <c r="R43" t="n">
-        <v>6560505</v>
+        <v>6560528</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5218,45 +5218,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131736787</v>
+        <v>131736576</v>
       </c>
       <c r="B44" t="n">
-        <v>92220</v>
+        <v>93152</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2062</v>
+        <v>2059</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>614622</v>
+        <v>614640</v>
       </c>
       <c r="R44" t="n">
-        <v>6560528</v>
+        <v>6560409</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5283,12 +5287,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>9 st</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5319,10 +5328,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131736576</v>
+        <v>131736037</v>
       </c>
       <c r="B45" t="n">
-        <v>93152</v>
+        <v>92086</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5330,38 +5339,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2059</v>
+        <v>1101</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>614640</v>
+        <v>614602</v>
       </c>
       <c r="R45" t="n">
-        <v>6560409</v>
+        <v>6560488</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5388,17 +5393,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>9 st</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5530,10 +5530,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131740368</v>
+        <v>131739023</v>
       </c>
       <c r="B47" t="n">
-        <v>93165</v>
+        <v>79895</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5541,34 +5541,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>614772</v>
+        <v>614757</v>
       </c>
       <c r="R47" t="n">
-        <v>6560415</v>
+        <v>6560461</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5603,18 +5603,12 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5637,10 +5631,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131740341</v>
+        <v>131740368</v>
       </c>
       <c r="B48" t="n">
-        <v>93162</v>
+        <v>93165</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5648,38 +5642,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5448</v>
+        <v>5449</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>614963</v>
+        <v>614772</v>
       </c>
       <c r="R48" t="n">
-        <v>6560256</v>
+        <v>6560415</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5706,17 +5696,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>8 st</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5725,6 +5715,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5747,10 +5738,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131737612</v>
+        <v>131740341</v>
       </c>
       <c r="B49" t="n">
-        <v>93174</v>
+        <v>93162</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5758,34 +5749,38 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>614843</v>
+        <v>614963</v>
       </c>
       <c r="R49" t="n">
-        <v>6560521</v>
+        <v>6560256</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5812,12 +5807,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>8 st</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5848,7 +5848,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737613</v>
+        <v>131737612</v>
       </c>
       <c r="B50" t="n">
         <v>93174</v>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>614811</v>
+        <v>614843</v>
       </c>
       <c r="R50" t="n">
-        <v>6560570</v>
+        <v>6560521</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5949,7 +5949,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737728</v>
+        <v>131737613</v>
       </c>
       <c r="B51" t="n">
         <v>93174</v>
@@ -5977,21 +5977,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>614659</v>
+        <v>614811</v>
       </c>
       <c r="R51" t="n">
-        <v>6560444</v>
+        <v>6560570</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6018,17 +6014,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6059,7 +6050,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131737608</v>
+        <v>131737728</v>
       </c>
       <c r="B52" t="n">
         <v>93174</v>
@@ -6087,17 +6078,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>614654</v>
+        <v>614659</v>
       </c>
       <c r="R52" t="n">
-        <v>6560489</v>
+        <v>6560444</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6124,12 +6119,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6160,7 +6160,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131737734</v>
+        <v>131737608</v>
       </c>
       <c r="B53" t="n">
         <v>93174</v>
@@ -6188,21 +6188,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>614708</v>
+        <v>614654</v>
       </c>
       <c r="R53" t="n">
-        <v>6560403</v>
+        <v>6560489</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6229,17 +6225,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6270,7 +6261,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131737760</v>
+        <v>131737734</v>
       </c>
       <c r="B54" t="n">
         <v>93174</v>
@@ -6300,7 +6291,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6309,10 +6300,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>614880</v>
+        <v>614708</v>
       </c>
       <c r="R54" t="n">
-        <v>6560400</v>
+        <v>6560403</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6349,7 +6340,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6380,10 +6371,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131739023</v>
+        <v>131737760</v>
       </c>
       <c r="B55" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6391,34 +6382,38 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>614757</v>
+        <v>614880</v>
       </c>
       <c r="R55" t="n">
-        <v>6560461</v>
+        <v>6560400</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6451,6 +6446,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6912,32 +6912,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131734662</v>
+        <v>131734255</v>
       </c>
       <c r="B60" t="n">
-        <v>79033</v>
+        <v>97385</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>990</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6947,10 +6947,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>614665</v>
+        <v>614670</v>
       </c>
       <c r="R60" t="n">
-        <v>6560415</v>
+        <v>6560435</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6977,12 +6977,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7013,10 +7013,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131739019</v>
+        <v>131737717</v>
       </c>
       <c r="B61" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7024,34 +7024,38 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>615022</v>
+        <v>614838</v>
       </c>
       <c r="R61" t="n">
-        <v>6560428</v>
+        <v>6560512</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7084,6 +7088,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7114,10 +7123,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131739038</v>
+        <v>131740397</v>
       </c>
       <c r="B62" t="n">
-        <v>79895</v>
+        <v>93165</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7125,34 +7134,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>614743</v>
+        <v>614907</v>
       </c>
       <c r="R62" t="n">
-        <v>6560468</v>
+        <v>6560338</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7179,12 +7188,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>5 st</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7193,6 +7207,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7215,45 +7230,49 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131736994</v>
+        <v>131737749</v>
       </c>
       <c r="B63" t="n">
-        <v>91333</v>
+        <v>93174</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2051</v>
+        <v>5966</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>615157</v>
+        <v>614849</v>
       </c>
       <c r="R63" t="n">
-        <v>6560412</v>
+        <v>6560446</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7280,17 +7299,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ramaria XXL</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7321,45 +7340,49 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131734255</v>
+        <v>131737714</v>
       </c>
       <c r="B64" t="n">
-        <v>97385</v>
+        <v>93174</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>990</v>
+        <v>5966</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>614670</v>
+        <v>614933</v>
       </c>
       <c r="R64" t="n">
-        <v>6560435</v>
+        <v>6560495</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7386,12 +7409,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>60+</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7422,10 +7450,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131737717</v>
+        <v>131734662</v>
       </c>
       <c r="B65" t="n">
-        <v>93174</v>
+        <v>79033</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7433,38 +7461,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>614838</v>
+        <v>614665</v>
       </c>
       <c r="R65" t="n">
-        <v>6560512</v>
+        <v>6560415</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7491,17 +7515,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7532,10 +7551,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131740397</v>
+        <v>131739019</v>
       </c>
       <c r="B66" t="n">
-        <v>93165</v>
+        <v>79895</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7543,34 +7562,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>614907</v>
+        <v>615022</v>
       </c>
       <c r="R66" t="n">
-        <v>6560338</v>
+        <v>6560428</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7597,17 +7616,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>5 st</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7616,7 +7630,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7639,10 +7652,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131737749</v>
+        <v>131739038</v>
       </c>
       <c r="B67" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7650,38 +7663,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>614849</v>
+        <v>614743</v>
       </c>
       <c r="R67" t="n">
-        <v>6560446</v>
+        <v>6560468</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7708,17 +7717,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>9</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7749,49 +7753,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131737714</v>
+        <v>131736994</v>
       </c>
       <c r="B68" t="n">
-        <v>93174</v>
+        <v>91333</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5966</v>
+        <v>2051</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>614933</v>
+        <v>615157</v>
       </c>
       <c r="R68" t="n">
-        <v>6560495</v>
+        <v>6560412</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7818,17 +7818,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Ramaria XXL</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8819,34 +8819,30 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131736990</v>
+        <v>131740369</v>
       </c>
       <c r="B78" t="n">
-        <v>91333</v>
+        <v>93165</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2051</v>
+        <v>5449</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>3</t>
@@ -8854,14 +8850,14 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>614738</v>
+        <v>615152</v>
       </c>
       <c r="R78" t="n">
-        <v>6560408</v>
+        <v>6560500</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8888,17 +8884,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>3 st</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8907,6 +8903,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8929,10 +8926,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131740369</v>
+        <v>131737723</v>
       </c>
       <c r="B79" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8940,34 +8937,38 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>615152</v>
+        <v>614756</v>
       </c>
       <c r="R79" t="n">
-        <v>6560500</v>
+        <v>6560527</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9004,7 +9005,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9013,7 +9014,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9036,7 +9036,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131737723</v>
+        <v>131737756</v>
       </c>
       <c r="B80" t="n">
         <v>93174</v>
@@ -9066,19 +9066,19 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>614756</v>
+        <v>614923</v>
       </c>
       <c r="R80" t="n">
-        <v>6560527</v>
+        <v>6560410</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9115,7 +9115,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9146,7 +9146,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131737756</v>
+        <v>131737725</v>
       </c>
       <c r="B81" t="n">
         <v>93174</v>
@@ -9176,19 +9176,19 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>614923</v>
+        <v>614660</v>
       </c>
       <c r="R81" t="n">
-        <v>6560410</v>
+        <v>6560511</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9256,7 +9256,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131737725</v>
+        <v>131737731</v>
       </c>
       <c r="B82" t="n">
         <v>93174</v>
@@ -9286,19 +9286,19 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>614660</v>
+        <v>614674</v>
       </c>
       <c r="R82" t="n">
-        <v>6560511</v>
+        <v>6560414</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9366,10 +9366,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131737731</v>
+        <v>131740396</v>
       </c>
       <c r="B83" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9377,23 +9377,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>4</t>
@@ -9401,14 +9397,14 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>614674</v>
+        <v>614785</v>
       </c>
       <c r="R83" t="n">
-        <v>6560414</v>
+        <v>6560564</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9435,17 +9431,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9454,6 +9450,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9476,10 +9473,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131740396</v>
+        <v>131737730</v>
       </c>
       <c r="B84" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9487,34 +9484,38 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>614785</v>
+        <v>614656</v>
       </c>
       <c r="R84" t="n">
-        <v>6560564</v>
+        <v>6560418</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9541,17 +9542,17 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9560,7 +9561,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9583,7 +9583,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131737730</v>
+        <v>131737754</v>
       </c>
       <c r="B85" t="n">
         <v>93174</v>
@@ -9613,19 +9613,19 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>614656</v>
+        <v>614888</v>
       </c>
       <c r="R85" t="n">
-        <v>6560418</v>
+        <v>6560440</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9693,49 +9693,49 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131737754</v>
+        <v>131736990</v>
       </c>
       <c r="B86" t="n">
-        <v>93174</v>
+        <v>91333</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5966</v>
+        <v>2051</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>614888</v>
+        <v>614738</v>
       </c>
       <c r="R86" t="n">
-        <v>6560440</v>
+        <v>6560408</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9762,17 +9762,17 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11086,10 +11086,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131737722</v>
+        <v>131739017</v>
       </c>
       <c r="B99" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11097,38 +11097,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>614773</v>
+        <v>615032</v>
       </c>
       <c r="R99" t="n">
-        <v>6560515</v>
+        <v>6560425</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11161,11 +11157,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>1o</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11196,10 +11187,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131740395</v>
+        <v>131737722</v>
       </c>
       <c r="B100" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11207,22 +11198,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11231,10 +11226,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>614715</v>
+        <v>614773</v>
       </c>
       <c r="R100" t="n">
-        <v>6560514</v>
+        <v>6560515</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11261,17 +11256,17 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>6 st</t>
+          <t>1o</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11280,7 +11275,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11303,7 +11297,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131740398</v>
+        <v>131740395</v>
       </c>
       <c r="B101" t="n">
         <v>93165</v>
@@ -11329,19 +11323,19 @@
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>614907</v>
+        <v>614715</v>
       </c>
       <c r="R101" t="n">
-        <v>6560326</v>
+        <v>6560514</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11378,7 +11372,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>6 st</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11410,10 +11404,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131737757</v>
+        <v>131740398</v>
       </c>
       <c r="B102" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11421,38 +11415,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>614887</v>
+        <v>614907</v>
       </c>
       <c r="R102" t="n">
-        <v>6560362</v>
+        <v>6560326</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11479,17 +11469,17 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11498,6 +11488,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11520,7 +11511,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737776</v>
+        <v>131737757</v>
       </c>
       <c r="B103" t="n">
         <v>93174</v>
@@ -11550,19 +11541,19 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Nystugan Nord, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>615009</v>
+        <v>614887</v>
       </c>
       <c r="R103" t="n">
-        <v>6560307</v>
+        <v>6560362</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11599,7 +11590,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11630,10 +11621,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131739017</v>
+        <v>131737776</v>
       </c>
       <c r="B104" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11641,34 +11632,38 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nystugan Nord, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>615032</v>
+        <v>615009</v>
       </c>
       <c r="R104" t="n">
-        <v>6560425</v>
+        <v>6560307</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11701,6 +11696,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12658,10 +12658,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131737739</v>
+        <v>131736464</v>
       </c>
       <c r="B114" t="n">
-        <v>93174</v>
+        <v>57911</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12669,38 +12669,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nord, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>614717</v>
+        <v>614934</v>
       </c>
       <c r="R114" t="n">
-        <v>6560453</v>
+        <v>6560353</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12727,17 +12723,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12768,7 +12759,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131737752</v>
+        <v>131737739</v>
       </c>
       <c r="B115" t="n">
         <v>93174</v>
@@ -12798,7 +12789,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -12807,10 +12798,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>614875</v>
+        <v>614717</v>
       </c>
       <c r="R115" t="n">
-        <v>6560431</v>
+        <v>6560453</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12847,7 +12838,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12878,7 +12869,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131737766</v>
+        <v>131737752</v>
       </c>
       <c r="B116" t="n">
         <v>93174</v>
@@ -12908,19 +12899,19 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>614826</v>
+        <v>614875</v>
       </c>
       <c r="R116" t="n">
-        <v>6560351</v>
+        <v>6560431</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12957,7 +12948,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12988,45 +12979,49 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131733366</v>
+        <v>131737766</v>
       </c>
       <c r="B117" t="n">
-        <v>92506</v>
+        <v>93174</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>615138</v>
+        <v>614826</v>
       </c>
       <c r="R117" t="n">
-        <v>6560392</v>
+        <v>6560351</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13059,6 +13054,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13089,49 +13089,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131737710</v>
+        <v>131733366</v>
       </c>
       <c r="B118" t="n">
-        <v>93174</v>
+        <v>92506</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>614961</v>
+        <v>615138</v>
       </c>
       <c r="R118" t="n">
-        <v>6560414</v>
+        <v>6560392</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13164,11 +13160,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13199,10 +13190,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131739022</v>
+        <v>131737710</v>
       </c>
       <c r="B119" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13210,34 +13201,38 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>614790</v>
+        <v>614961</v>
       </c>
       <c r="R119" t="n">
-        <v>6560493</v>
+        <v>6560414</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13270,6 +13265,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13300,10 +13300,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131736464</v>
+        <v>131739022</v>
       </c>
       <c r="B120" t="n">
-        <v>57911</v>
+        <v>79895</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13311,34 +13311,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Nystugan Nord, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>614934</v>
+        <v>614790</v>
       </c>
       <c r="R120" t="n">
-        <v>6560353</v>
+        <v>6560493</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13365,12 +13365,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13401,10 +13401,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131740365</v>
+        <v>131733306</v>
       </c>
       <c r="B121" t="n">
-        <v>93165</v>
+        <v>93130</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13412,22 +13412,26 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -13436,10 +13440,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>614741</v>
+        <v>614689</v>
       </c>
       <c r="R121" t="n">
-        <v>6560508</v>
+        <v>6560516</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13466,17 +13470,17 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1 St</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13485,7 +13489,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13508,45 +13511,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131737605</v>
+        <v>131732765</v>
       </c>
       <c r="B122" t="n">
-        <v>93174</v>
+        <v>93136</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>614921</v>
+        <v>614878</v>
       </c>
       <c r="R122" t="n">
-        <v>6560349</v>
+        <v>6560511</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13573,12 +13576,17 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Förekommer spritt rikligt</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13609,10 +13617,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131737753</v>
+        <v>131740365</v>
       </c>
       <c r="B123" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13620,26 +13628,22 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -13648,10 +13652,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>614883</v>
+        <v>614741</v>
       </c>
       <c r="R123" t="n">
-        <v>6560422</v>
+        <v>6560508</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13688,7 +13692,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13697,6 +13701,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13719,45 +13724,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131733367</v>
+        <v>131737605</v>
       </c>
       <c r="B124" t="n">
-        <v>92506</v>
+        <v>93174</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>614939</v>
+        <v>614921</v>
       </c>
       <c r="R124" t="n">
-        <v>6560438</v>
+        <v>6560349</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13784,12 +13789,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13820,7 +13825,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131737719</v>
+        <v>131737753</v>
       </c>
       <c r="B125" t="n">
         <v>93174</v>
@@ -13850,7 +13855,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -13859,10 +13864,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>614817</v>
+        <v>614883</v>
       </c>
       <c r="R125" t="n">
-        <v>6560509</v>
+        <v>6560422</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13899,7 +13904,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13930,49 +13935,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131737768</v>
+        <v>131733367</v>
       </c>
       <c r="B126" t="n">
-        <v>93174</v>
+        <v>92506</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>614843</v>
+        <v>614939</v>
       </c>
       <c r="R126" t="n">
-        <v>6560322</v>
+        <v>6560438</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14005,11 +14006,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14040,10 +14036,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131740367</v>
+        <v>131737719</v>
       </c>
       <c r="B127" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14051,22 +14047,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -14075,10 +14075,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>614742</v>
+        <v>614817</v>
       </c>
       <c r="R127" t="n">
-        <v>6560443</v>
+        <v>6560509</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14115,7 +14115,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14124,7 +14124,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -14147,7 +14146,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131737778</v>
+        <v>131737768</v>
       </c>
       <c r="B128" t="n">
         <v>93174</v>
@@ -14177,19 +14176,19 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>615115</v>
+        <v>614843</v>
       </c>
       <c r="R128" t="n">
-        <v>6560377</v>
+        <v>6560322</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14226,7 +14225,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14257,10 +14256,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131737741</v>
+        <v>131740367</v>
       </c>
       <c r="B129" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14268,26 +14267,22 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -14296,10 +14291,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>614754</v>
+        <v>614742</v>
       </c>
       <c r="R129" t="n">
-        <v>6560449</v>
+        <v>6560443</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14336,7 +14331,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14345,6 +14340,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -14367,7 +14363,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131737751</v>
+        <v>131737778</v>
       </c>
       <c r="B130" t="n">
         <v>93174</v>
@@ -14397,19 +14393,19 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>614860</v>
+        <v>615115</v>
       </c>
       <c r="R130" t="n">
-        <v>6560430</v>
+        <v>6560377</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14446,7 +14442,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14477,7 +14473,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131737604</v>
+        <v>131737741</v>
       </c>
       <c r="B131" t="n">
         <v>93174</v>
@@ -14505,17 +14501,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>615114</v>
+        <v>614754</v>
       </c>
       <c r="R131" t="n">
-        <v>6560473</v>
+        <v>6560449</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14542,12 +14542,17 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14578,45 +14583,49 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131733476</v>
+        <v>131737751</v>
       </c>
       <c r="B132" t="n">
-        <v>8444</v>
+        <v>93174</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106554</v>
+        <v>5966</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>614831</v>
+        <v>614860</v>
       </c>
       <c r="R132" t="n">
-        <v>6560599</v>
+        <v>6560430</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14643,12 +14652,17 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14679,10 +14693,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131733306</v>
+        <v>131737604</v>
       </c>
       <c r="B133" t="n">
-        <v>93130</v>
+        <v>93174</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14690,38 +14704,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>614689</v>
+        <v>615114</v>
       </c>
       <c r="R133" t="n">
-        <v>6560516</v>
+        <v>6560473</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14748,17 +14758,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>1 St</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14789,32 +14794,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131732765</v>
+        <v>131739040</v>
       </c>
       <c r="B134" t="n">
-        <v>93136</v>
+        <v>79895</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14824,10 +14829,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>614878</v>
+        <v>614705</v>
       </c>
       <c r="R134" t="n">
-        <v>6560511</v>
+        <v>6560468</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14854,17 +14859,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Förekommer spritt rikligt</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14895,32 +14895,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131739040</v>
+        <v>131733476</v>
       </c>
       <c r="B135" t="n">
-        <v>79895</v>
+        <v>8444</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>106554</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14930,10 +14930,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>614705</v>
+        <v>614831</v>
       </c>
       <c r="R135" t="n">
-        <v>6560468</v>
+        <v>6560599</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14960,12 +14960,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14996,10 +14996,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131739551</v>
+        <v>131737743</v>
       </c>
       <c r="B136" t="n">
-        <v>91848</v>
+        <v>93174</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15007,34 +15007,38 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>614622</v>
+        <v>614731</v>
       </c>
       <c r="R136" t="n">
-        <v>6560528</v>
+        <v>6560390</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15061,12 +15065,17 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15097,10 +15106,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>131737748</v>
+        <v>131740394</v>
       </c>
       <c r="B137" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15108,26 +15117,22 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -15136,10 +15141,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>614792</v>
+        <v>614731</v>
       </c>
       <c r="R137" t="n">
-        <v>6560431</v>
+        <v>6560512</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15166,17 +15171,17 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1 st</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15185,6 +15190,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -15207,10 +15213,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>131740402</v>
+        <v>131737707</v>
       </c>
       <c r="B138" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15218,22 +15224,26 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -15242,10 +15252,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>615135</v>
+        <v>614934</v>
       </c>
       <c r="R138" t="n">
-        <v>6560485</v>
+        <v>6560422</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15272,17 +15282,17 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>Ca 25st</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15291,7 +15301,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -15314,10 +15323,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>131740243</v>
+        <v>131737748</v>
       </c>
       <c r="B139" t="n">
-        <v>92780</v>
+        <v>93174</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15325,38 +15334,38 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>614829</v>
+        <v>614792</v>
       </c>
       <c r="R139" t="n">
-        <v>6560371</v>
+        <v>6560431</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15393,7 +15402,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15424,10 +15433,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>131733304</v>
+        <v>131740402</v>
       </c>
       <c r="B140" t="n">
-        <v>93130</v>
+        <v>93165</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15435,38 +15444,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>614759</v>
+        <v>615135</v>
       </c>
       <c r="R140" t="n">
-        <v>6560440</v>
+        <v>6560485</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15503,7 +15508,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>8 st</t>
+          <t>Ca 25st</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15512,6 +15517,7 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15534,45 +15540,49 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>131737932</v>
+        <v>131740243</v>
       </c>
       <c r="B141" t="n">
-        <v>8455</v>
+        <v>92780</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>106545</v>
+        <v>4745</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>615059</v>
+        <v>614829</v>
       </c>
       <c r="R141" t="n">
-        <v>6560324</v>
+        <v>6560371</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15599,17 +15609,17 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Förekommer spritt på tallågor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15640,10 +15650,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>131737743</v>
+        <v>131733304</v>
       </c>
       <c r="B142" t="n">
-        <v>93174</v>
+        <v>93130</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15651,38 +15661,38 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>614731</v>
+        <v>614759</v>
       </c>
       <c r="R142" t="n">
-        <v>6560390</v>
+        <v>6560440</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15709,17 +15719,17 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8 st</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15750,45 +15760,45 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>131740394</v>
+        <v>131737932</v>
       </c>
       <c r="B143" t="n">
-        <v>93165</v>
+        <v>8455</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5449</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>614731</v>
+        <v>615059</v>
       </c>
       <c r="R143" t="n">
-        <v>6560512</v>
+        <v>6560324</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15825,7 +15835,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>1 st</t>
+          <t>Förekommer spritt på tallågor</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15834,7 +15844,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -15857,49 +15866,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>131737707</v>
+        <v>131740304</v>
       </c>
       <c r="B144" t="n">
-        <v>93174</v>
+        <v>91341</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5966</v>
+        <v>256703</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>614934</v>
+        <v>615108</v>
       </c>
       <c r="R144" t="n">
-        <v>6560422</v>
+        <v>6560375</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15926,17 +15931,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15967,45 +15967,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>131740304</v>
+        <v>131739551</v>
       </c>
       <c r="B145" t="n">
-        <v>91341</v>
+        <v>91848</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>256703</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>615108</v>
+        <v>614622</v>
       </c>
       <c r="R145" t="n">
-        <v>6560375</v>
+        <v>6560528</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16032,12 +16032,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16936,45 +16936,45 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>131732764</v>
+        <v>131740364</v>
       </c>
       <c r="B154" t="n">
-        <v>93136</v>
+        <v>93165</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>614871</v>
+        <v>614841</v>
       </c>
       <c r="R154" t="n">
-        <v>6560446</v>
+        <v>6560503</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17001,12 +17001,17 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17015,6 +17020,7 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -17037,10 +17043,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>131740364</v>
+        <v>131737777</v>
       </c>
       <c r="B155" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17048,34 +17054,38 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>614841</v>
+        <v>615134</v>
       </c>
       <c r="R155" t="n">
-        <v>6560503</v>
+        <v>6560409</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17112,7 +17122,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17121,7 +17131,6 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
-      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
@@ -17144,7 +17153,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>131737777</v>
+        <v>131737772</v>
       </c>
       <c r="B156" t="n">
         <v>93174</v>
@@ -17174,19 +17183,19 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>615134</v>
+        <v>614898</v>
       </c>
       <c r="R156" t="n">
-        <v>6560409</v>
+        <v>6560304</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17223,7 +17232,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17254,7 +17263,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>131737772</v>
+        <v>131737606</v>
       </c>
       <c r="B157" t="n">
         <v>93174</v>
@@ -17282,21 +17291,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>614898</v>
+        <v>614656</v>
       </c>
       <c r="R157" t="n">
-        <v>6560304</v>
+        <v>6560442</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17323,17 +17328,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17364,7 +17364,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>131737606</v>
+        <v>131737709</v>
       </c>
       <c r="B158" t="n">
         <v>93174</v>
@@ -17392,17 +17392,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>614656</v>
+        <v>614958</v>
       </c>
       <c r="R158" t="n">
-        <v>6560442</v>
+        <v>6560433</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17429,12 +17433,17 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17465,7 +17474,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>131737709</v>
+        <v>131737759</v>
       </c>
       <c r="B159" t="n">
         <v>93174</v>
@@ -17495,19 +17504,19 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>614958</v>
+        <v>614874</v>
       </c>
       <c r="R159" t="n">
-        <v>6560433</v>
+        <v>6560379</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17544,7 +17553,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17575,7 +17584,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>131737759</v>
+        <v>131737761</v>
       </c>
       <c r="B160" t="n">
         <v>93174</v>
@@ -17605,7 +17614,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -17614,10 +17623,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>614874</v>
+        <v>614870</v>
       </c>
       <c r="R160" t="n">
-        <v>6560379</v>
+        <v>6560397</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17654,7 +17663,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17685,7 +17694,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>131737761</v>
+        <v>131737755</v>
       </c>
       <c r="B161" t="n">
         <v>93174</v>
@@ -17715,19 +17724,19 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>614870</v>
+        <v>614894</v>
       </c>
       <c r="R161" t="n">
-        <v>6560397</v>
+        <v>6560431</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17764,7 +17773,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17795,7 +17804,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>131737755</v>
+        <v>131737611</v>
       </c>
       <c r="B162" t="n">
         <v>93174</v>
@@ -17823,21 +17832,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>614894</v>
+        <v>614822</v>
       </c>
       <c r="R162" t="n">
-        <v>6560431</v>
+        <v>6560500</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17864,17 +17869,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17905,7 +17905,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>131737611</v>
+        <v>131737763</v>
       </c>
       <c r="B163" t="n">
         <v>93174</v>
@@ -17933,17 +17933,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>614822</v>
+        <v>614847</v>
       </c>
       <c r="R163" t="n">
-        <v>6560500</v>
+        <v>6560380</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17970,12 +17974,17 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18006,49 +18015,45 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>131737763</v>
+        <v>131732764</v>
       </c>
       <c r="B164" t="n">
-        <v>93174</v>
+        <v>93136</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>614847</v>
+        <v>614871</v>
       </c>
       <c r="R164" t="n">
-        <v>6560380</v>
+        <v>6560446</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18075,17 +18080,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18116,10 +18116,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>131737767</v>
+        <v>131738710</v>
       </c>
       <c r="B165" t="n">
-        <v>93174</v>
+        <v>97294</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18127,38 +18127,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>614840</v>
+        <v>614670</v>
       </c>
       <c r="R165" t="n">
-        <v>6560354</v>
+        <v>6560435</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18185,17 +18181,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18226,45 +18217,49 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>131737720</v>
+        <v>131740287</v>
       </c>
       <c r="B166" t="n">
-        <v>93174</v>
+        <v>93124</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5966</v>
+        <v>149</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
+          <t>(Peck) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>614767</v>
+        <v>614868</v>
       </c>
       <c r="R166" t="n">
-        <v>6560465</v>
+        <v>6560512</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18297,6 +18292,11 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18327,10 +18327,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>131740393</v>
+        <v>131737767</v>
       </c>
       <c r="B167" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18338,34 +18338,38 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>614703</v>
+        <v>614840</v>
       </c>
       <c r="R167" t="n">
-        <v>6560500</v>
+        <v>6560354</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18392,17 +18396,17 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>2 st</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18411,7 +18415,6 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -18434,7 +18437,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>131737735</v>
+        <v>131737720</v>
       </c>
       <c r="B168" t="n">
         <v>93174</v>
@@ -18462,21 +18465,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>614719</v>
+        <v>614767</v>
       </c>
       <c r="R168" t="n">
-        <v>6560410</v>
+        <v>6560465</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18509,11 +18508,6 @@
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18544,10 +18538,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>131737609</v>
+        <v>131740393</v>
       </c>
       <c r="B169" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18555,34 +18549,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>614698</v>
+        <v>614703</v>
       </c>
       <c r="R169" t="n">
-        <v>6560522</v>
+        <v>6560500</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18609,12 +18603,17 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18623,6 +18622,7 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -18645,10 +18645,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>131738710</v>
+        <v>131737735</v>
       </c>
       <c r="B170" t="n">
-        <v>97294</v>
+        <v>93174</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18656,34 +18656,38 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>614670</v>
+        <v>614719</v>
       </c>
       <c r="R170" t="n">
-        <v>6560435</v>
+        <v>6560410</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18710,12 +18714,17 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18746,49 +18755,45 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>131740287</v>
+        <v>131737609</v>
       </c>
       <c r="B171" t="n">
-        <v>93124</v>
+        <v>93174</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>149</v>
+        <v>5966</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>614868</v>
+        <v>614698</v>
       </c>
       <c r="R171" t="n">
-        <v>6560512</v>
+        <v>6560522</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18815,17 +18820,12 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18856,10 +18856,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>131735737</v>
+        <v>131740359</v>
       </c>
       <c r="B172" t="n">
-        <v>92638</v>
+        <v>93165</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18867,38 +18867,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>366</v>
+        <v>5449</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>615093</v>
+        <v>614877</v>
       </c>
       <c r="R172" t="n">
-        <v>6560461</v>
+        <v>6560513</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18925,17 +18921,17 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18944,6 +18940,7 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -18966,10 +18963,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>131732524</v>
+        <v>131737740</v>
       </c>
       <c r="B173" t="n">
-        <v>78942</v>
+        <v>93174</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18977,34 +18974,38 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>614915</v>
+        <v>614746</v>
       </c>
       <c r="R173" t="n">
-        <v>6560407</v>
+        <v>6560453</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19031,12 +19032,17 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19067,10 +19073,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>131740359</v>
+        <v>131737742</v>
       </c>
       <c r="B174" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19078,22 +19084,26 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
@@ -19102,10 +19112,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>614877</v>
+        <v>614738</v>
       </c>
       <c r="R174" t="n">
-        <v>6560513</v>
+        <v>6560442</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19132,17 +19142,17 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19151,7 +19161,6 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
-      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
@@ -19174,7 +19183,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>131737740</v>
+        <v>131737721</v>
       </c>
       <c r="B175" t="n">
         <v>93174</v>
@@ -19204,7 +19213,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -19213,10 +19222,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>614746</v>
+        <v>614776</v>
       </c>
       <c r="R175" t="n">
-        <v>6560453</v>
+        <v>6560488</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19253,7 +19262,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19284,7 +19293,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>131737742</v>
+        <v>131737775</v>
       </c>
       <c r="B176" t="n">
         <v>93174</v>
@@ -19314,19 +19323,19 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nord, Srm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>614738</v>
+        <v>614989</v>
       </c>
       <c r="R176" t="n">
-        <v>6560442</v>
+        <v>6560288</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19363,7 +19372,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19394,7 +19403,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>131737721</v>
+        <v>131737738</v>
       </c>
       <c r="B177" t="n">
         <v>93174</v>
@@ -19424,7 +19433,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -19433,10 +19442,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>614776</v>
+        <v>614711</v>
       </c>
       <c r="R177" t="n">
-        <v>6560488</v>
+        <v>6560481</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19473,7 +19482,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19504,10 +19513,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>131737775</v>
+        <v>131740399</v>
       </c>
       <c r="B178" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19515,38 +19524,34 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Nystugan Nord, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>614989</v>
+        <v>614904</v>
       </c>
       <c r="R178" t="n">
-        <v>6560288</v>
+        <v>6560330</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19573,17 +19578,17 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5 st</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19592,6 +19597,7 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -19614,10 +19620,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>131737738</v>
+        <v>131734664</v>
       </c>
       <c r="B179" t="n">
-        <v>93174</v>
+        <v>79033</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19625,38 +19631,34 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>614711</v>
+        <v>615034</v>
       </c>
       <c r="R179" t="n">
-        <v>6560481</v>
+        <v>6560418</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19689,11 +19691,6 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19724,10 +19721,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>131740399</v>
+        <v>131734663</v>
       </c>
       <c r="B180" t="n">
-        <v>93165</v>
+        <v>79033</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19735,34 +19732,34 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>614904</v>
+        <v>614679</v>
       </c>
       <c r="R180" t="n">
-        <v>6560330</v>
+        <v>6560422</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19789,17 +19786,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>5 st</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19808,7 +19800,6 @@
       <c r="AE180" t="b">
         <v>0</v>
       </c>
-      <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
       </c>
@@ -19831,10 +19822,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>131734664</v>
+        <v>131735737</v>
       </c>
       <c r="B181" t="n">
-        <v>79033</v>
+        <v>92638</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19842,34 +19833,38 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6446</v>
+        <v>366</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>615034</v>
+        <v>615093</v>
       </c>
       <c r="R181" t="n">
-        <v>6560418</v>
+        <v>6560461</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19896,12 +19891,17 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19932,10 +19932,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>131734663</v>
+        <v>131732524</v>
       </c>
       <c r="B182" t="n">
-        <v>79033</v>
+        <v>78942</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19943,34 +19943,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>614679</v>
+        <v>614915</v>
       </c>
       <c r="R182" t="n">
-        <v>6560422</v>
+        <v>6560407</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19997,12 +19997,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD182" t="b">

--- a/artfynd/A 43282-2024 artfynd.xlsx
+++ b/artfynd/A 43282-2024 artfynd.xlsx
@@ -4713,10 +4713,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131736037</v>
+        <v>131738986</v>
       </c>
       <c r="B39" t="n">
-        <v>92086</v>
+        <v>79895</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4724,34 +4724,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1101</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>614602</v>
+        <v>614832</v>
       </c>
       <c r="R39" t="n">
-        <v>6560488</v>
+        <v>6560556</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4778,12 +4778,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4814,7 +4814,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131738986</v>
+        <v>131739037</v>
       </c>
       <c r="B40" t="n">
         <v>79895</v>
@@ -4845,14 +4845,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>614832</v>
+        <v>615086</v>
       </c>
       <c r="R40" t="n">
-        <v>6560556</v>
+        <v>6560375</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4879,12 +4879,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4915,7 +4915,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131739037</v>
+        <v>131739024</v>
       </c>
       <c r="B41" t="n">
         <v>79895</v>
@@ -4946,14 +4946,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>615086</v>
+        <v>614774</v>
       </c>
       <c r="R41" t="n">
-        <v>6560375</v>
+        <v>6560505</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4980,12 +4980,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5016,10 +5016,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131739024</v>
+        <v>131740334</v>
       </c>
       <c r="B42" t="n">
-        <v>79895</v>
+        <v>93162</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5027,21 +5027,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>5448</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5051,10 +5051,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>614774</v>
+        <v>614945</v>
       </c>
       <c r="R42" t="n">
-        <v>6560505</v>
+        <v>6560495</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5117,10 +5117,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131740334</v>
+        <v>131737733</v>
       </c>
       <c r="B43" t="n">
-        <v>93162</v>
+        <v>93174</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5128,34 +5128,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>614945</v>
+        <v>614695</v>
       </c>
       <c r="R43" t="n">
-        <v>6560495</v>
+        <v>6560413</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131737733</v>
+        <v>131737764</v>
       </c>
       <c r="B44" t="n">
         <v>93174</v>
@@ -5246,17 +5246,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>614695</v>
+        <v>614836</v>
       </c>
       <c r="R44" t="n">
-        <v>6560413</v>
+        <v>6560376</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5289,6 +5293,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5319,7 +5328,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131737764</v>
+        <v>131737713</v>
       </c>
       <c r="B45" t="n">
         <v>93174</v>
@@ -5347,21 +5356,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>614836</v>
+        <v>614935</v>
       </c>
       <c r="R45" t="n">
-        <v>6560376</v>
+        <v>6560472</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5394,11 +5399,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5429,10 +5429,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131737713</v>
+        <v>131736037</v>
       </c>
       <c r="B46" t="n">
-        <v>93174</v>
+        <v>92086</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5440,34 +5440,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>1101</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>614935</v>
+        <v>614602</v>
       </c>
       <c r="R46" t="n">
-        <v>6560472</v>
+        <v>6560488</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5530,10 +5530,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131739023</v>
+        <v>131740368</v>
       </c>
       <c r="B47" t="n">
-        <v>79895</v>
+        <v>93165</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5541,34 +5541,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>614757</v>
+        <v>614772</v>
       </c>
       <c r="R47" t="n">
-        <v>6560461</v>
+        <v>6560415</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5603,12 +5603,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5631,10 +5637,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131740368</v>
+        <v>131740341</v>
       </c>
       <c r="B48" t="n">
-        <v>93165</v>
+        <v>93162</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5642,34 +5648,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>614772</v>
+        <v>614963</v>
       </c>
       <c r="R48" t="n">
-        <v>6560415</v>
+        <v>6560256</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5696,17 +5706,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8 st</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5715,7 +5725,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5738,10 +5747,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131740341</v>
+        <v>131737612</v>
       </c>
       <c r="B49" t="n">
-        <v>93162</v>
+        <v>93174</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5749,38 +5758,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>614963</v>
+        <v>614843</v>
       </c>
       <c r="R49" t="n">
-        <v>6560256</v>
+        <v>6560521</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5807,17 +5812,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>8 st</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5848,7 +5848,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737612</v>
+        <v>131737613</v>
       </c>
       <c r="B50" t="n">
         <v>93174</v>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>614843</v>
+        <v>614811</v>
       </c>
       <c r="R50" t="n">
-        <v>6560521</v>
+        <v>6560570</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5949,7 +5949,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737613</v>
+        <v>131737728</v>
       </c>
       <c r="B51" t="n">
         <v>93174</v>
@@ -5977,17 +5977,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>614811</v>
+        <v>614659</v>
       </c>
       <c r="R51" t="n">
-        <v>6560570</v>
+        <v>6560444</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6014,12 +6018,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6050,7 +6059,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131737728</v>
+        <v>131737608</v>
       </c>
       <c r="B52" t="n">
         <v>93174</v>
@@ -6078,21 +6087,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>614659</v>
+        <v>614654</v>
       </c>
       <c r="R52" t="n">
-        <v>6560444</v>
+        <v>6560489</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6119,17 +6124,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6160,7 +6160,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131737608</v>
+        <v>131737734</v>
       </c>
       <c r="B53" t="n">
         <v>93174</v>
@@ -6188,17 +6188,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>614654</v>
+        <v>614708</v>
       </c>
       <c r="R53" t="n">
-        <v>6560489</v>
+        <v>6560403</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6225,12 +6229,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6261,7 +6270,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131737734</v>
+        <v>131737760</v>
       </c>
       <c r="B54" t="n">
         <v>93174</v>
@@ -6291,7 +6300,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6300,10 +6309,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>614708</v>
+        <v>614880</v>
       </c>
       <c r="R54" t="n">
-        <v>6560403</v>
+        <v>6560400</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6340,7 +6349,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6371,10 +6380,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131737760</v>
+        <v>131739023</v>
       </c>
       <c r="B55" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6382,38 +6391,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>614880</v>
+        <v>614757</v>
       </c>
       <c r="R55" t="n">
-        <v>6560400</v>
+        <v>6560461</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6446,11 +6451,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7018,45 +7018,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131739019</v>
+        <v>131734255</v>
       </c>
       <c r="B61" t="n">
-        <v>79895</v>
+        <v>97385</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>990</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>615022</v>
+        <v>614670</v>
       </c>
       <c r="R61" t="n">
-        <v>6560428</v>
+        <v>6560435</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7083,12 +7083,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7119,7 +7119,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131739038</v>
+        <v>131739019</v>
       </c>
       <c r="B62" t="n">
         <v>79895</v>
@@ -7150,14 +7150,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>614743</v>
+        <v>615022</v>
       </c>
       <c r="R62" t="n">
-        <v>6560468</v>
+        <v>6560428</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7184,12 +7184,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7220,10 +7220,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131737717</v>
+        <v>131739038</v>
       </c>
       <c r="B63" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7231,38 +7231,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>614838</v>
+        <v>614743</v>
       </c>
       <c r="R63" t="n">
-        <v>6560512</v>
+        <v>6560468</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7289,17 +7285,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7330,10 +7321,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131740397</v>
+        <v>131737717</v>
       </c>
       <c r="B64" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7341,34 +7332,38 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>614907</v>
+        <v>614838</v>
       </c>
       <c r="R64" t="n">
-        <v>6560338</v>
+        <v>6560512</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7395,17 +7390,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>5 st</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7414,7 +7409,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7437,10 +7431,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131737749</v>
+        <v>131740397</v>
       </c>
       <c r="B65" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7448,38 +7442,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>614849</v>
+        <v>614907</v>
       </c>
       <c r="R65" t="n">
-        <v>6560446</v>
+        <v>6560338</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7506,17 +7496,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5 st</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7525,6 +7515,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7547,7 +7538,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131737714</v>
+        <v>131737749</v>
       </c>
       <c r="B66" t="n">
         <v>93174</v>
@@ -7577,7 +7568,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7586,10 +7577,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>614933</v>
+        <v>614849</v>
       </c>
       <c r="R66" t="n">
-        <v>6560495</v>
+        <v>6560446</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7626,7 +7617,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7657,45 +7648,49 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131734255</v>
+        <v>131737714</v>
       </c>
       <c r="B67" t="n">
-        <v>97385</v>
+        <v>93174</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>990</v>
+        <v>5966</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>614670</v>
+        <v>614933</v>
       </c>
       <c r="R67" t="n">
-        <v>6560435</v>
+        <v>6560495</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7722,12 +7717,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>60+</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8608,49 +8608,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131736990</v>
+        <v>131738984</v>
       </c>
       <c r="B76" t="n">
-        <v>91333</v>
+        <v>79895</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2051</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>614738</v>
+        <v>614801</v>
       </c>
       <c r="R76" t="n">
-        <v>6560408</v>
+        <v>6560517</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8677,17 +8673,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>3 st</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8718,10 +8709,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131738984</v>
+        <v>131740369</v>
       </c>
       <c r="B77" t="n">
-        <v>79895</v>
+        <v>93165</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8729,34 +8720,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>614801</v>
+        <v>615152</v>
       </c>
       <c r="R77" t="n">
-        <v>6560517</v>
+        <v>6560500</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8783,12 +8774,17 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8797,6 +8793,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8819,10 +8816,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131740369</v>
+        <v>131737723</v>
       </c>
       <c r="B78" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8830,34 +8827,38 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>615152</v>
+        <v>614756</v>
       </c>
       <c r="R78" t="n">
-        <v>6560500</v>
+        <v>6560527</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8894,7 +8895,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8903,7 +8904,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8926,7 +8926,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131737723</v>
+        <v>131737756</v>
       </c>
       <c r="B79" t="n">
         <v>93174</v>
@@ -8956,19 +8956,19 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>614756</v>
+        <v>614923</v>
       </c>
       <c r="R79" t="n">
-        <v>6560527</v>
+        <v>6560410</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9036,7 +9036,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131737756</v>
+        <v>131737725</v>
       </c>
       <c r="B80" t="n">
         <v>93174</v>
@@ -9066,19 +9066,19 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>614923</v>
+        <v>614660</v>
       </c>
       <c r="R80" t="n">
-        <v>6560410</v>
+        <v>6560511</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9115,7 +9115,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9146,10 +9146,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131737725</v>
+        <v>131740337</v>
       </c>
       <c r="B81" t="n">
-        <v>93174</v>
+        <v>93162</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9157,38 +9157,38 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>614660</v>
+        <v>614621</v>
       </c>
       <c r="R81" t="n">
-        <v>6560511</v>
+        <v>6560438</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15+</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9256,10 +9256,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131740337</v>
+        <v>131737731</v>
       </c>
       <c r="B82" t="n">
-        <v>93162</v>
+        <v>93174</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9267,38 +9267,38 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>614621</v>
+        <v>614674</v>
       </c>
       <c r="R82" t="n">
-        <v>6560438</v>
+        <v>6560414</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>15+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9366,10 +9366,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131737731</v>
+        <v>131740396</v>
       </c>
       <c r="B83" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9377,23 +9377,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>4</t>
@@ -9401,14 +9397,14 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>614674</v>
+        <v>614785</v>
       </c>
       <c r="R83" t="n">
-        <v>6560414</v>
+        <v>6560564</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9435,17 +9431,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9454,6 +9450,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9476,10 +9473,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131740396</v>
+        <v>131737730</v>
       </c>
       <c r="B84" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9487,34 +9484,38 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>614785</v>
+        <v>614656</v>
       </c>
       <c r="R84" t="n">
-        <v>6560564</v>
+        <v>6560418</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9541,17 +9542,17 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9560,7 +9561,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9583,7 +9583,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131737730</v>
+        <v>131737754</v>
       </c>
       <c r="B85" t="n">
         <v>93174</v>
@@ -9613,19 +9613,19 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>614656</v>
+        <v>614888</v>
       </c>
       <c r="R85" t="n">
-        <v>6560418</v>
+        <v>6560440</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9693,49 +9693,49 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131737754</v>
+        <v>131736990</v>
       </c>
       <c r="B86" t="n">
-        <v>93174</v>
+        <v>91333</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5966</v>
+        <v>2051</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>614888</v>
+        <v>614738</v>
       </c>
       <c r="R86" t="n">
-        <v>6560440</v>
+        <v>6560408</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9762,17 +9762,17 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -12658,10 +12658,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131736464</v>
+        <v>131739022</v>
       </c>
       <c r="B114" t="n">
-        <v>57911</v>
+        <v>79895</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12669,34 +12669,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Nystugan Nord, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>614934</v>
+        <v>614790</v>
       </c>
       <c r="R114" t="n">
-        <v>6560353</v>
+        <v>6560493</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12723,12 +12723,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12759,10 +12759,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131739022</v>
+        <v>131737739</v>
       </c>
       <c r="B115" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12770,34 +12770,38 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>614790</v>
+        <v>614717</v>
       </c>
       <c r="R115" t="n">
-        <v>6560493</v>
+        <v>6560453</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12830,6 +12834,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12860,7 +12869,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131737739</v>
+        <v>131737752</v>
       </c>
       <c r="B116" t="n">
         <v>93174</v>
@@ -12890,7 +12899,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -12899,10 +12908,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>614717</v>
+        <v>614875</v>
       </c>
       <c r="R116" t="n">
-        <v>6560453</v>
+        <v>6560431</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12939,7 +12948,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12970,7 +12979,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131737752</v>
+        <v>131737766</v>
       </c>
       <c r="B117" t="n">
         <v>93174</v>
@@ -13000,19 +13009,19 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>614875</v>
+        <v>614826</v>
       </c>
       <c r="R117" t="n">
-        <v>6560431</v>
+        <v>6560351</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13049,7 +13058,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13080,49 +13089,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131737766</v>
+        <v>131733366</v>
       </c>
       <c r="B118" t="n">
-        <v>93174</v>
+        <v>92506</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>614826</v>
+        <v>615138</v>
       </c>
       <c r="R118" t="n">
-        <v>6560351</v>
+        <v>6560392</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13155,11 +13160,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13190,45 +13190,49 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131733366</v>
+        <v>131737710</v>
       </c>
       <c r="B119" t="n">
-        <v>92506</v>
+        <v>93174</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>615138</v>
+        <v>614961</v>
       </c>
       <c r="R119" t="n">
-        <v>6560392</v>
+        <v>6560414</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13261,6 +13265,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13291,10 +13300,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131737710</v>
+        <v>131736464</v>
       </c>
       <c r="B120" t="n">
-        <v>93174</v>
+        <v>57911</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13302,38 +13311,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nystugan Nord, Srm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>614961</v>
+        <v>614934</v>
       </c>
       <c r="R120" t="n">
-        <v>6560414</v>
+        <v>6560353</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13360,17 +13365,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13401,10 +13401,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131733367</v>
+        <v>131733476</v>
       </c>
       <c r="B121" t="n">
-        <v>92506</v>
+        <v>8444</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13412,34 +13412,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6031</v>
+        <v>106554</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>614939</v>
+        <v>614831</v>
       </c>
       <c r="R121" t="n">
-        <v>6560438</v>
+        <v>6560599</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13466,12 +13466,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13502,10 +13502,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131737719</v>
+        <v>131733306</v>
       </c>
       <c r="B122" t="n">
-        <v>93174</v>
+        <v>93130</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13513,21 +13513,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -13541,10 +13541,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>614817</v>
+        <v>614689</v>
       </c>
       <c r="R122" t="n">
-        <v>6560509</v>
+        <v>6560516</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13571,17 +13571,17 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 St</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13612,45 +13612,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131737605</v>
+        <v>131732765</v>
       </c>
       <c r="B123" t="n">
-        <v>93174</v>
+        <v>93136</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>614921</v>
+        <v>614878</v>
       </c>
       <c r="R123" t="n">
-        <v>6560349</v>
+        <v>6560511</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13677,12 +13677,17 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Förekommer spritt rikligt</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13713,10 +13718,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131737753</v>
+        <v>131739040</v>
       </c>
       <c r="B124" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13724,38 +13729,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>614883</v>
+        <v>614705</v>
       </c>
       <c r="R124" t="n">
-        <v>6560422</v>
+        <v>6560468</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13782,17 +13783,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13823,10 +13819,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131737768</v>
+        <v>131740365</v>
       </c>
       <c r="B125" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13834,38 +13830,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>614843</v>
+        <v>614741</v>
       </c>
       <c r="R125" t="n">
-        <v>6560322</v>
+        <v>6560508</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13902,7 +13894,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13911,6 +13903,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13933,10 +13926,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131740367</v>
+        <v>131737605</v>
       </c>
       <c r="B126" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13944,34 +13937,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>614742</v>
+        <v>614921</v>
       </c>
       <c r="R126" t="n">
-        <v>6560443</v>
+        <v>6560349</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13998,17 +13991,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14017,7 +14005,6 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -14040,7 +14027,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131737778</v>
+        <v>131737753</v>
       </c>
       <c r="B127" t="n">
         <v>93174</v>
@@ -14070,19 +14057,19 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>615115</v>
+        <v>614883</v>
       </c>
       <c r="R127" t="n">
-        <v>6560377</v>
+        <v>6560422</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14119,7 +14106,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14150,49 +14137,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131737741</v>
+        <v>131733367</v>
       </c>
       <c r="B128" t="n">
-        <v>93174</v>
+        <v>92506</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>614754</v>
+        <v>614939</v>
       </c>
       <c r="R128" t="n">
-        <v>6560449</v>
+        <v>6560438</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14225,11 +14208,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14260,7 +14238,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131737751</v>
+        <v>131737719</v>
       </c>
       <c r="B129" t="n">
         <v>93174</v>
@@ -14290,7 +14268,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -14299,10 +14277,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>614860</v>
+        <v>614817</v>
       </c>
       <c r="R129" t="n">
-        <v>6560430</v>
+        <v>6560509</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14339,7 +14317,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14370,7 +14348,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131737604</v>
+        <v>131737768</v>
       </c>
       <c r="B130" t="n">
         <v>93174</v>
@@ -14398,17 +14376,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>615114</v>
+        <v>614843</v>
       </c>
       <c r="R130" t="n">
-        <v>6560473</v>
+        <v>6560322</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14435,12 +14417,17 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14471,45 +14458,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131733476</v>
+        <v>131740367</v>
       </c>
       <c r="B131" t="n">
-        <v>8444</v>
+        <v>93165</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106554</v>
+        <v>5449</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>614831</v>
+        <v>614742</v>
       </c>
       <c r="R131" t="n">
-        <v>6560599</v>
+        <v>6560443</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14536,12 +14523,17 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14550,6 +14542,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14572,10 +14565,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131733306</v>
+        <v>131737778</v>
       </c>
       <c r="B132" t="n">
-        <v>93130</v>
+        <v>93174</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14583,38 +14576,38 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>614689</v>
+        <v>615115</v>
       </c>
       <c r="R132" t="n">
-        <v>6560516</v>
+        <v>6560377</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14641,17 +14634,17 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>1 St</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14682,45 +14675,49 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131732765</v>
+        <v>131737741</v>
       </c>
       <c r="B133" t="n">
-        <v>93136</v>
+        <v>93174</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>614878</v>
+        <v>614754</v>
       </c>
       <c r="R133" t="n">
-        <v>6560511</v>
+        <v>6560449</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14747,17 +14744,17 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Förekommer spritt rikligt</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14788,10 +14785,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131739040</v>
+        <v>131737751</v>
       </c>
       <c r="B134" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14799,34 +14796,38 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>614705</v>
+        <v>614860</v>
       </c>
       <c r="R134" t="n">
-        <v>6560468</v>
+        <v>6560430</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14853,12 +14854,17 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14889,10 +14895,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131740365</v>
+        <v>131737604</v>
       </c>
       <c r="B135" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14900,34 +14906,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>614741</v>
+        <v>615114</v>
       </c>
       <c r="R135" t="n">
-        <v>6560508</v>
+        <v>6560473</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14954,17 +14960,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14973,7 +14974,6 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14996,45 +14996,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131739551</v>
+        <v>131737932</v>
       </c>
       <c r="B136" t="n">
-        <v>91848</v>
+        <v>8455</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>614622</v>
+        <v>615059</v>
       </c>
       <c r="R136" t="n">
-        <v>6560528</v>
+        <v>6560324</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15061,12 +15061,17 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Förekommer spritt på tallågor</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15097,10 +15102,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>131733304</v>
+        <v>131739551</v>
       </c>
       <c r="B137" t="n">
-        <v>93130</v>
+        <v>91848</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15108,38 +15113,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4362</v>
+        <v>1202</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>614759</v>
+        <v>614622</v>
       </c>
       <c r="R137" t="n">
-        <v>6560440</v>
+        <v>6560528</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15166,17 +15167,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>8 st</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15207,10 +15203,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>131740243</v>
+        <v>131733304</v>
       </c>
       <c r="B138" t="n">
-        <v>92780</v>
+        <v>93130</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15218,38 +15214,38 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>614829</v>
+        <v>614759</v>
       </c>
       <c r="R138" t="n">
-        <v>6560371</v>
+        <v>6560440</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15276,17 +15272,17 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8 st</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15317,10 +15313,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>131737743</v>
+        <v>131740243</v>
       </c>
       <c r="B139" t="n">
-        <v>93174</v>
+        <v>92780</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15328,26 +15324,26 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -15356,10 +15352,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>614731</v>
+        <v>614829</v>
       </c>
       <c r="R139" t="n">
-        <v>6560390</v>
+        <v>6560371</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15396,7 +15392,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15427,10 +15423,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>131740394</v>
+        <v>131737743</v>
       </c>
       <c r="B140" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15438,34 +15434,38 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q140" t="n">
         <v>614731</v>
       </c>
       <c r="R140" t="n">
-        <v>6560512</v>
+        <v>6560390</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15492,17 +15492,17 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>1 st</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15511,7 +15511,6 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15534,10 +15533,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>131737707</v>
+        <v>131740394</v>
       </c>
       <c r="B141" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15545,38 +15544,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>614934</v>
+        <v>614731</v>
       </c>
       <c r="R141" t="n">
-        <v>6560422</v>
+        <v>6560512</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15603,17 +15598,17 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1 st</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15622,6 +15617,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15644,7 +15640,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>131737748</v>
+        <v>131737707</v>
       </c>
       <c r="B142" t="n">
         <v>93174</v>
@@ -15674,19 +15670,19 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>614792</v>
+        <v>614934</v>
       </c>
       <c r="R142" t="n">
-        <v>6560431</v>
+        <v>6560422</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15723,7 +15719,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15754,10 +15750,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>131740402</v>
+        <v>131737748</v>
       </c>
       <c r="B143" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15765,34 +15761,38 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>615135</v>
+        <v>614792</v>
       </c>
       <c r="R143" t="n">
-        <v>6560485</v>
+        <v>6560431</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15819,17 +15819,17 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ca 25st</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15838,7 +15838,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -15861,45 +15860,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>131740304</v>
+        <v>131740402</v>
       </c>
       <c r="B144" t="n">
-        <v>91341</v>
+        <v>93165</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>256703</v>
+        <v>5449</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>615108</v>
+        <v>615135</v>
       </c>
       <c r="R144" t="n">
-        <v>6560375</v>
+        <v>6560485</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15934,12 +15933,18 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Ca 25st</t>
+        </is>
+      </c>
       <c r="AD144" t="b">
         <v>0</v>
       </c>
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -15962,10 +15967,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>131737932</v>
+        <v>131740304</v>
       </c>
       <c r="B145" t="n">
-        <v>8455</v>
+        <v>91341</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15973,21 +15978,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>106545</v>
+        <v>256703</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15997,10 +16002,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>615059</v>
+        <v>615108</v>
       </c>
       <c r="R145" t="n">
-        <v>6560324</v>
+        <v>6560375</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16033,11 +16038,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Förekommer spritt på tallågor</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16068,10 +16068,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>131737727</v>
+        <v>131732523</v>
       </c>
       <c r="B146" t="n">
-        <v>93174</v>
+        <v>78942</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16079,38 +16079,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>614657</v>
+        <v>614818</v>
       </c>
       <c r="R146" t="n">
-        <v>6560454</v>
+        <v>6560356</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16137,17 +16133,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16178,7 +16169,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>131737726</v>
+        <v>131737727</v>
       </c>
       <c r="B147" t="n">
         <v>93174</v>
@@ -16208,7 +16199,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -16217,10 +16208,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>614639</v>
+        <v>614657</v>
       </c>
       <c r="R147" t="n">
-        <v>6560514</v>
+        <v>6560454</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16257,7 +16248,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16288,7 +16279,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>131737706</v>
+        <v>131737726</v>
       </c>
       <c r="B148" t="n">
         <v>93174</v>
@@ -16318,19 +16309,19 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>615019</v>
+        <v>614639</v>
       </c>
       <c r="R148" t="n">
-        <v>6560434</v>
+        <v>6560514</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16367,7 +16358,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16398,10 +16389,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>131740400</v>
+        <v>131737706</v>
       </c>
       <c r="B149" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16409,34 +16400,38 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>614952</v>
+        <v>615019</v>
       </c>
       <c r="R149" t="n">
-        <v>6560279</v>
+        <v>6560434</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16463,17 +16458,17 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>2 st</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16482,7 +16477,6 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -16505,10 +16499,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>131732523</v>
+        <v>131740400</v>
       </c>
       <c r="B150" t="n">
-        <v>78942</v>
+        <v>93165</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16516,34 +16510,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>353</v>
+        <v>5449</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>614818</v>
+        <v>614952</v>
       </c>
       <c r="R150" t="n">
-        <v>6560356</v>
+        <v>6560279</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16570,12 +16564,17 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16584,6 +16583,7 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43282-2024 artfynd.xlsx
+++ b/artfynd/A 43282-2024 artfynd.xlsx
@@ -2891,45 +2891,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131736022</v>
+        <v>131737737</v>
       </c>
       <c r="B22" t="n">
-        <v>92287</v>
+        <v>93174</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5420</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>614774</v>
+        <v>614697</v>
       </c>
       <c r="R22" t="n">
-        <v>6560503</v>
+        <v>6560445</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2962,6 +2966,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2992,10 +3001,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131740241</v>
+        <v>131737603</v>
       </c>
       <c r="B23" t="n">
-        <v>92780</v>
+        <v>93174</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3003,38 +3012,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>614922</v>
+        <v>615176</v>
       </c>
       <c r="R23" t="n">
-        <v>6560422</v>
+        <v>6560478</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3061,17 +3066,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3102,7 +3102,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131737737</v>
+        <v>131737708</v>
       </c>
       <c r="B24" t="n">
         <v>93174</v>
@@ -3132,19 +3132,19 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>614697</v>
+        <v>614945</v>
       </c>
       <c r="R24" t="n">
-        <v>6560445</v>
+        <v>6560420</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3212,7 +3212,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131737603</v>
+        <v>131737704</v>
       </c>
       <c r="B25" t="n">
         <v>93174</v>
@@ -3240,17 +3240,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615176</v>
+        <v>615034</v>
       </c>
       <c r="R25" t="n">
-        <v>6560478</v>
+        <v>6560411</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3277,12 +3281,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3313,49 +3322,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131737708</v>
+        <v>131736022</v>
       </c>
       <c r="B26" t="n">
-        <v>93174</v>
+        <v>92287</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>614945</v>
+        <v>614774</v>
       </c>
       <c r="R26" t="n">
-        <v>6560420</v>
+        <v>6560503</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3388,11 +3393,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3423,10 +3423,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131737704</v>
+        <v>131740241</v>
       </c>
       <c r="B27" t="n">
-        <v>93174</v>
+        <v>92780</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3434,26 +3434,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>615034</v>
+        <v>614922</v>
       </c>
       <c r="R27" t="n">
-        <v>6560411</v>
+        <v>6560422</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -5530,10 +5530,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131740368</v>
+        <v>131739023</v>
       </c>
       <c r="B47" t="n">
-        <v>93165</v>
+        <v>79895</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5541,34 +5541,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>614772</v>
+        <v>614757</v>
       </c>
       <c r="R47" t="n">
-        <v>6560415</v>
+        <v>6560461</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5603,18 +5603,12 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5637,10 +5631,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131740341</v>
+        <v>131740368</v>
       </c>
       <c r="B48" t="n">
-        <v>93162</v>
+        <v>93165</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5648,38 +5642,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5448</v>
+        <v>5449</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>614963</v>
+        <v>614772</v>
       </c>
       <c r="R48" t="n">
-        <v>6560256</v>
+        <v>6560415</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5706,17 +5696,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>8 st</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5725,6 +5715,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5747,10 +5738,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131737612</v>
+        <v>131740341</v>
       </c>
       <c r="B49" t="n">
-        <v>93174</v>
+        <v>93162</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5758,34 +5749,38 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>614843</v>
+        <v>614963</v>
       </c>
       <c r="R49" t="n">
-        <v>6560521</v>
+        <v>6560256</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5812,12 +5807,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>8 st</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5848,7 +5848,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737613</v>
+        <v>131737612</v>
       </c>
       <c r="B50" t="n">
         <v>93174</v>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>614811</v>
+        <v>614843</v>
       </c>
       <c r="R50" t="n">
-        <v>6560570</v>
+        <v>6560521</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5949,7 +5949,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737728</v>
+        <v>131737613</v>
       </c>
       <c r="B51" t="n">
         <v>93174</v>
@@ -5977,21 +5977,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>614659</v>
+        <v>614811</v>
       </c>
       <c r="R51" t="n">
-        <v>6560444</v>
+        <v>6560570</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6018,17 +6014,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6059,7 +6050,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131737608</v>
+        <v>131737728</v>
       </c>
       <c r="B52" t="n">
         <v>93174</v>
@@ -6087,17 +6078,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>614654</v>
+        <v>614659</v>
       </c>
       <c r="R52" t="n">
-        <v>6560489</v>
+        <v>6560444</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6124,12 +6119,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6160,7 +6160,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131737734</v>
+        <v>131737608</v>
       </c>
       <c r="B53" t="n">
         <v>93174</v>
@@ -6188,21 +6188,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>614708</v>
+        <v>614654</v>
       </c>
       <c r="R53" t="n">
-        <v>6560403</v>
+        <v>6560489</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6229,17 +6225,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6270,7 +6261,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131737760</v>
+        <v>131737734</v>
       </c>
       <c r="B54" t="n">
         <v>93174</v>
@@ -6300,7 +6291,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6309,10 +6300,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>614880</v>
+        <v>614708</v>
       </c>
       <c r="R54" t="n">
-        <v>6560400</v>
+        <v>6560403</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6349,7 +6340,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6380,10 +6371,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131739023</v>
+        <v>131737760</v>
       </c>
       <c r="B55" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6391,34 +6382,38 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>614757</v>
+        <v>614880</v>
       </c>
       <c r="R55" t="n">
-        <v>6560461</v>
+        <v>6560400</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6451,6 +6446,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7018,45 +7018,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131734255</v>
+        <v>131739019</v>
       </c>
       <c r="B61" t="n">
-        <v>97385</v>
+        <v>79895</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>990</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>614670</v>
+        <v>615022</v>
       </c>
       <c r="R61" t="n">
-        <v>6560435</v>
+        <v>6560428</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7083,12 +7083,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7119,7 +7119,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131739019</v>
+        <v>131739038</v>
       </c>
       <c r="B62" t="n">
         <v>79895</v>
@@ -7150,14 +7150,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>615022</v>
+        <v>614743</v>
       </c>
       <c r="R62" t="n">
-        <v>6560428</v>
+        <v>6560468</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7184,12 +7184,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7220,10 +7220,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131739038</v>
+        <v>131737717</v>
       </c>
       <c r="B63" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7231,34 +7231,38 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>614743</v>
+        <v>614838</v>
       </c>
       <c r="R63" t="n">
-        <v>6560468</v>
+        <v>6560512</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7285,12 +7289,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7321,10 +7330,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131737717</v>
+        <v>131740397</v>
       </c>
       <c r="B64" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7332,38 +7341,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>614838</v>
+        <v>614907</v>
       </c>
       <c r="R64" t="n">
-        <v>6560512</v>
+        <v>6560338</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7390,17 +7395,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5 st</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7409,6 +7414,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7431,10 +7437,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131740397</v>
+        <v>131737749</v>
       </c>
       <c r="B65" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7442,34 +7448,38 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>614907</v>
+        <v>614849</v>
       </c>
       <c r="R65" t="n">
-        <v>6560338</v>
+        <v>6560446</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7496,17 +7506,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>5 st</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7515,7 +7525,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7538,7 +7547,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131737749</v>
+        <v>131737714</v>
       </c>
       <c r="B66" t="n">
         <v>93174</v>
@@ -7568,7 +7577,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7577,10 +7586,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>614849</v>
+        <v>614933</v>
       </c>
       <c r="R66" t="n">
-        <v>6560446</v>
+        <v>6560495</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7617,7 +7626,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7648,49 +7657,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131737714</v>
+        <v>131734255</v>
       </c>
       <c r="B67" t="n">
-        <v>93174</v>
+        <v>97385</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5966</v>
+        <v>990</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Warnst.) R.M.Schust.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>614933</v>
+        <v>614670</v>
       </c>
       <c r="R67" t="n">
-        <v>6560495</v>
+        <v>6560435</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7717,17 +7722,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>60+</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7859,49 +7859,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131740288</v>
+        <v>131739788</v>
       </c>
       <c r="B69" t="n">
-        <v>93124</v>
+        <v>92571</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>149</v>
+        <v>3298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>614871</v>
+        <v>615070</v>
       </c>
       <c r="R69" t="n">
-        <v>6560514</v>
+        <v>6560325</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7928,17 +7924,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7969,33 +7960,37 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131740391</v>
+        <v>131740288</v>
       </c>
       <c r="B70" t="n">
-        <v>93165</v>
+        <v>93124</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5449</v>
+        <v>149</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>Boletopsis grisea</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Peck) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8004,10 +7999,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>614945</v>
+        <v>614871</v>
       </c>
       <c r="R70" t="n">
-        <v>6560479</v>
+        <v>6560514</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8034,17 +8029,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>2 st</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8053,7 +8048,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8076,10 +8070,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131740335</v>
+        <v>131737261</v>
       </c>
       <c r="B71" t="n">
-        <v>93162</v>
+        <v>93128</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8087,38 +8081,38 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>614815</v>
+        <v>614895</v>
       </c>
       <c r="R71" t="n">
-        <v>6560508</v>
+        <v>6560392</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8145,17 +8139,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8186,45 +8180,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131737931</v>
+        <v>131740391</v>
       </c>
       <c r="B72" t="n">
-        <v>8455</v>
+        <v>93165</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>5449</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>614669</v>
+        <v>614945</v>
       </c>
       <c r="R72" t="n">
-        <v>6560513</v>
+        <v>6560479</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8251,12 +8245,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8265,6 +8264,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8287,49 +8287,49 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131736991</v>
+        <v>131740335</v>
       </c>
       <c r="B73" t="n">
-        <v>91333</v>
+        <v>93162</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2051</v>
+        <v>5448</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>614736</v>
+        <v>614815</v>
       </c>
       <c r="R73" t="n">
-        <v>6560397</v>
+        <v>6560508</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8356,17 +8356,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>3 st</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8397,45 +8397,49 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131739788</v>
+        <v>131736991</v>
       </c>
       <c r="B74" t="n">
-        <v>92571</v>
+        <v>91333</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3298</v>
+        <v>2051</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>615070</v>
+        <v>614736</v>
       </c>
       <c r="R74" t="n">
-        <v>6560325</v>
+        <v>6560397</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8462,12 +8466,17 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8498,49 +8507,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131737261</v>
+        <v>131737931</v>
       </c>
       <c r="B75" t="n">
-        <v>93128</v>
+        <v>8455</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4361</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>614895</v>
+        <v>614669</v>
       </c>
       <c r="R75" t="n">
-        <v>6560392</v>
+        <v>6560513</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8567,17 +8572,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>4 st</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8608,45 +8608,49 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131738984</v>
+        <v>131736990</v>
       </c>
       <c r="B76" t="n">
-        <v>79895</v>
+        <v>91333</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>2051</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>614801</v>
+        <v>614738</v>
       </c>
       <c r="R76" t="n">
-        <v>6560517</v>
+        <v>6560408</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8673,12 +8677,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8709,10 +8718,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131740369</v>
+        <v>131738984</v>
       </c>
       <c r="B77" t="n">
-        <v>93165</v>
+        <v>79895</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8720,34 +8729,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>615152</v>
+        <v>614801</v>
       </c>
       <c r="R77" t="n">
-        <v>6560500</v>
+        <v>6560517</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8774,17 +8783,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8793,7 +8797,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8816,10 +8819,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131737723</v>
+        <v>131740369</v>
       </c>
       <c r="B78" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8827,38 +8830,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>614756</v>
+        <v>615152</v>
       </c>
       <c r="R78" t="n">
-        <v>6560527</v>
+        <v>6560500</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8895,7 +8894,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8904,6 +8903,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8926,7 +8926,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131737756</v>
+        <v>131737723</v>
       </c>
       <c r="B79" t="n">
         <v>93174</v>
@@ -8956,19 +8956,19 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>614923</v>
+        <v>614756</v>
       </c>
       <c r="R79" t="n">
-        <v>6560410</v>
+        <v>6560527</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9036,7 +9036,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131737725</v>
+        <v>131737756</v>
       </c>
       <c r="B80" t="n">
         <v>93174</v>
@@ -9066,19 +9066,19 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>614660</v>
+        <v>614923</v>
       </c>
       <c r="R80" t="n">
-        <v>6560511</v>
+        <v>6560410</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9115,7 +9115,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9146,10 +9146,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131740337</v>
+        <v>131737725</v>
       </c>
       <c r="B81" t="n">
-        <v>93162</v>
+        <v>93174</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9157,38 +9157,38 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>614621</v>
+        <v>614660</v>
       </c>
       <c r="R81" t="n">
-        <v>6560438</v>
+        <v>6560511</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>15+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9256,10 +9256,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131737731</v>
+        <v>131740337</v>
       </c>
       <c r="B82" t="n">
-        <v>93174</v>
+        <v>93162</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9267,38 +9267,38 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>614674</v>
+        <v>614621</v>
       </c>
       <c r="R82" t="n">
-        <v>6560414</v>
+        <v>6560438</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15+</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9366,10 +9366,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131740396</v>
+        <v>131737731</v>
       </c>
       <c r="B83" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9377,19 +9377,23 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
           <t>4</t>
@@ -9397,14 +9401,14 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>614785</v>
+        <v>614674</v>
       </c>
       <c r="R83" t="n">
-        <v>6560564</v>
+        <v>6560414</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9431,17 +9435,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9450,7 +9454,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9473,10 +9476,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131737730</v>
+        <v>131740396</v>
       </c>
       <c r="B84" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9484,38 +9487,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>614656</v>
+        <v>614785</v>
       </c>
       <c r="R84" t="n">
-        <v>6560418</v>
+        <v>6560564</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9542,17 +9541,17 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9561,6 +9560,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9583,7 +9583,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131737754</v>
+        <v>131737730</v>
       </c>
       <c r="B85" t="n">
         <v>93174</v>
@@ -9613,19 +9613,19 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>614888</v>
+        <v>614656</v>
       </c>
       <c r="R85" t="n">
-        <v>6560440</v>
+        <v>6560418</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9693,49 +9693,49 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131736990</v>
+        <v>131737754</v>
       </c>
       <c r="B86" t="n">
-        <v>91333</v>
+        <v>93174</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2051</v>
+        <v>5966</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>614738</v>
+        <v>614888</v>
       </c>
       <c r="R86" t="n">
-        <v>6560408</v>
+        <v>6560440</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9762,17 +9762,17 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>3 st</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -14996,45 +14996,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131737932</v>
+        <v>131739551</v>
       </c>
       <c r="B136" t="n">
-        <v>8455</v>
+        <v>91848</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>615059</v>
+        <v>614622</v>
       </c>
       <c r="R136" t="n">
-        <v>6560324</v>
+        <v>6560528</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15061,17 +15061,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Förekommer spritt på tallågor</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15102,10 +15097,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>131739551</v>
+        <v>131733304</v>
       </c>
       <c r="B137" t="n">
-        <v>91848</v>
+        <v>93130</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15113,34 +15108,38 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1202</v>
+        <v>4362</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>614622</v>
+        <v>614759</v>
       </c>
       <c r="R137" t="n">
-        <v>6560528</v>
+        <v>6560440</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15167,12 +15166,17 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>8 st</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15203,10 +15207,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>131733304</v>
+        <v>131740243</v>
       </c>
       <c r="B138" t="n">
-        <v>93130</v>
+        <v>92780</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15214,38 +15218,38 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>614759</v>
+        <v>614829</v>
       </c>
       <c r="R138" t="n">
-        <v>6560440</v>
+        <v>6560371</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15272,17 +15276,17 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>8 st</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15313,10 +15317,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>131740243</v>
+        <v>131737743</v>
       </c>
       <c r="B139" t="n">
-        <v>92780</v>
+        <v>93174</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15324,26 +15328,26 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -15352,10 +15356,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>614829</v>
+        <v>614731</v>
       </c>
       <c r="R139" t="n">
-        <v>6560371</v>
+        <v>6560390</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15392,7 +15396,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15423,10 +15427,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>131737743</v>
+        <v>131740394</v>
       </c>
       <c r="B140" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15434,38 +15438,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q140" t="n">
         <v>614731</v>
       </c>
       <c r="R140" t="n">
-        <v>6560390</v>
+        <v>6560512</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15492,17 +15492,17 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 st</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15511,6 +15511,7 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15533,10 +15534,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>131740394</v>
+        <v>131737707</v>
       </c>
       <c r="B141" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15544,34 +15545,38 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>614731</v>
+        <v>614934</v>
       </c>
       <c r="R141" t="n">
-        <v>6560512</v>
+        <v>6560422</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15598,17 +15603,17 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>1 st</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15617,7 +15622,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15640,7 +15644,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>131737707</v>
+        <v>131737748</v>
       </c>
       <c r="B142" t="n">
         <v>93174</v>
@@ -15670,19 +15674,19 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>614934</v>
+        <v>614792</v>
       </c>
       <c r="R142" t="n">
-        <v>6560422</v>
+        <v>6560431</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15719,7 +15723,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15750,10 +15754,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>131737748</v>
+        <v>131740402</v>
       </c>
       <c r="B143" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15761,38 +15765,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>614792</v>
+        <v>615135</v>
       </c>
       <c r="R143" t="n">
-        <v>6560431</v>
+        <v>6560485</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15819,17 +15819,17 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>Ca 25st</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15838,6 +15838,7 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -15860,45 +15861,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>131740402</v>
+        <v>131737932</v>
       </c>
       <c r="B144" t="n">
-        <v>93165</v>
+        <v>8455</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5449</v>
+        <v>106545</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>615135</v>
+        <v>615059</v>
       </c>
       <c r="R144" t="n">
-        <v>6560485</v>
+        <v>6560324</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15935,7 +15936,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ca 25st</t>
+          <t>Förekommer spritt på tallågor</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15944,7 +15945,6 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -16936,45 +16936,45 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>131740364</v>
+        <v>131732764</v>
       </c>
       <c r="B154" t="n">
-        <v>93165</v>
+        <v>93136</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>614841</v>
+        <v>614871</v>
       </c>
       <c r="R154" t="n">
-        <v>6560503</v>
+        <v>6560446</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17001,17 +17001,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17020,7 +17015,6 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -17043,10 +17037,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>131737777</v>
+        <v>131740364</v>
       </c>
       <c r="B155" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17054,38 +17048,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>615134</v>
+        <v>614841</v>
       </c>
       <c r="R155" t="n">
-        <v>6560409</v>
+        <v>6560503</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17122,7 +17112,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17131,6 +17121,7 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
+      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
@@ -17153,7 +17144,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>131737772</v>
+        <v>131737777</v>
       </c>
       <c r="B156" t="n">
         <v>93174</v>
@@ -17183,19 +17174,19 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>614898</v>
+        <v>615134</v>
       </c>
       <c r="R156" t="n">
-        <v>6560304</v>
+        <v>6560409</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17232,7 +17223,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17263,7 +17254,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>131737606</v>
+        <v>131737772</v>
       </c>
       <c r="B157" t="n">
         <v>93174</v>
@@ -17291,17 +17282,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>614656</v>
+        <v>614898</v>
       </c>
       <c r="R157" t="n">
-        <v>6560442</v>
+        <v>6560304</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17328,12 +17323,17 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17364,7 +17364,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>131737709</v>
+        <v>131737606</v>
       </c>
       <c r="B158" t="n">
         <v>93174</v>
@@ -17392,21 +17392,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>614958</v>
+        <v>614656</v>
       </c>
       <c r="R158" t="n">
-        <v>6560433</v>
+        <v>6560442</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17433,17 +17429,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17474,7 +17465,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>131737759</v>
+        <v>131737709</v>
       </c>
       <c r="B159" t="n">
         <v>93174</v>
@@ -17504,19 +17495,19 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>614874</v>
+        <v>614958</v>
       </c>
       <c r="R159" t="n">
-        <v>6560379</v>
+        <v>6560433</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17553,7 +17544,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17584,7 +17575,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>131737761</v>
+        <v>131737759</v>
       </c>
       <c r="B160" t="n">
         <v>93174</v>
@@ -17614,7 +17605,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -17623,10 +17614,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>614870</v>
+        <v>614874</v>
       </c>
       <c r="R160" t="n">
-        <v>6560397</v>
+        <v>6560379</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17663,7 +17654,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17694,7 +17685,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>131737755</v>
+        <v>131737761</v>
       </c>
       <c r="B161" t="n">
         <v>93174</v>
@@ -17724,19 +17715,19 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>614894</v>
+        <v>614870</v>
       </c>
       <c r="R161" t="n">
-        <v>6560431</v>
+        <v>6560397</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17773,7 +17764,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17804,7 +17795,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>131737611</v>
+        <v>131737755</v>
       </c>
       <c r="B162" t="n">
         <v>93174</v>
@@ -17832,17 +17823,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>614822</v>
+        <v>614894</v>
       </c>
       <c r="R162" t="n">
-        <v>6560500</v>
+        <v>6560431</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17869,12 +17864,17 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17905,7 +17905,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>131737763</v>
+        <v>131737611</v>
       </c>
       <c r="B163" t="n">
         <v>93174</v>
@@ -17933,21 +17933,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>614847</v>
+        <v>614822</v>
       </c>
       <c r="R163" t="n">
-        <v>6560380</v>
+        <v>6560500</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17974,17 +17970,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18015,45 +18006,49 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>131732764</v>
+        <v>131737763</v>
       </c>
       <c r="B164" t="n">
-        <v>93136</v>
+        <v>93174</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>614871</v>
+        <v>614847</v>
       </c>
       <c r="R164" t="n">
-        <v>6560446</v>
+        <v>6560380</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18080,12 +18075,17 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD164" t="b">

--- a/artfynd/A 43282-2024 artfynd.xlsx
+++ b/artfynd/A 43282-2024 artfynd.xlsx
@@ -2583,45 +2583,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131732769</v>
+        <v>131737607</v>
       </c>
       <c r="B19" t="n">
-        <v>93136</v>
+        <v>93174</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615104</v>
+        <v>614643</v>
       </c>
       <c r="R19" t="n">
-        <v>6560485</v>
+        <v>6560479</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2648,17 +2648,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Återkommer spritt</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2790,45 +2785,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131737607</v>
+        <v>131732769</v>
       </c>
       <c r="B21" t="n">
-        <v>93174</v>
+        <v>93136</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>614643</v>
+        <v>615104</v>
       </c>
       <c r="R21" t="n">
-        <v>6560479</v>
+        <v>6560485</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2855,12 +2850,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Återkommer spritt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3533,10 +3533,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131737762</v>
+        <v>131738985</v>
       </c>
       <c r="B28" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3544,38 +3544,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>614855</v>
+        <v>614827</v>
       </c>
       <c r="R28" t="n">
-        <v>6560397</v>
+        <v>6560518</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3602,17 +3598,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3643,10 +3634,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131737779</v>
+        <v>131739020</v>
       </c>
       <c r="B29" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3654,38 +3645,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>615173</v>
+        <v>614839</v>
       </c>
       <c r="R29" t="n">
-        <v>6560476</v>
+        <v>6560502</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3718,11 +3705,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3753,7 +3735,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131737781</v>
+        <v>131737762</v>
       </c>
       <c r="B30" t="n">
         <v>93174</v>
@@ -3783,19 +3765,19 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615158</v>
+        <v>614855</v>
       </c>
       <c r="R30" t="n">
-        <v>6560491</v>
+        <v>6560397</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3832,7 +3814,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3863,7 +3845,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131737746</v>
+        <v>131737779</v>
       </c>
       <c r="B31" t="n">
         <v>93174</v>
@@ -3893,19 +3875,19 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>614777</v>
+        <v>615173</v>
       </c>
       <c r="R31" t="n">
-        <v>6560432</v>
+        <v>6560476</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3942,7 +3924,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3973,10 +3955,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131740362</v>
+        <v>131737781</v>
       </c>
       <c r="B32" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3984,19 +3966,23 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>1</t>
@@ -4008,10 +3994,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>614974</v>
+        <v>615158</v>
       </c>
       <c r="R32" t="n">
-        <v>6560411</v>
+        <v>6560491</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4057,7 +4043,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4080,7 +4065,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737750</v>
+        <v>131737746</v>
       </c>
       <c r="B33" t="n">
         <v>93174</v>
@@ -4110,7 +4095,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4119,10 +4104,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>614846</v>
+        <v>614777</v>
       </c>
       <c r="R33" t="n">
-        <v>6560435</v>
+        <v>6560432</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4159,7 +4144,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4190,10 +4175,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131737765</v>
+        <v>131740362</v>
       </c>
       <c r="B34" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4201,38 +4186,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>614814</v>
+        <v>614974</v>
       </c>
       <c r="R34" t="n">
-        <v>6560371</v>
+        <v>6560411</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4269,7 +4250,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4278,6 +4259,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4300,10 +4282,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131738985</v>
+        <v>131737750</v>
       </c>
       <c r="B35" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4311,34 +4293,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>614827</v>
+        <v>614846</v>
       </c>
       <c r="R35" t="n">
-        <v>6560518</v>
+        <v>6560435</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4365,12 +4351,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4401,10 +4392,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131739020</v>
+        <v>131737765</v>
       </c>
       <c r="B36" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4412,34 +4403,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>614839</v>
+        <v>614814</v>
       </c>
       <c r="R36" t="n">
-        <v>6560502</v>
+        <v>6560371</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4472,6 +4467,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4502,45 +4502,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131736787</v>
+        <v>131740334</v>
       </c>
       <c r="B37" t="n">
-        <v>92220</v>
+        <v>93162</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2062</v>
+        <v>5448</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>614622</v>
+        <v>614945</v>
       </c>
       <c r="R37" t="n">
-        <v>6560528</v>
+        <v>6560495</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4567,12 +4567,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4603,10 +4603,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131736576</v>
+        <v>131737733</v>
       </c>
       <c r="B38" t="n">
-        <v>93152</v>
+        <v>93174</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4614,38 +4614,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>614640</v>
+        <v>614695</v>
       </c>
       <c r="R38" t="n">
-        <v>6560409</v>
+        <v>6560413</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4672,17 +4668,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>9 st</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4713,10 +4704,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131738986</v>
+        <v>131737764</v>
       </c>
       <c r="B39" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4724,34 +4715,38 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>614832</v>
+        <v>614836</v>
       </c>
       <c r="R39" t="n">
-        <v>6560556</v>
+        <v>6560376</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4778,12 +4773,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4814,10 +4814,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131739037</v>
+        <v>131737713</v>
       </c>
       <c r="B40" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4825,34 +4825,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>615086</v>
+        <v>614935</v>
       </c>
       <c r="R40" t="n">
-        <v>6560375</v>
+        <v>6560472</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4879,12 +4879,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4915,10 +4915,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131739024</v>
+        <v>131736037</v>
       </c>
       <c r="B41" t="n">
-        <v>79895</v>
+        <v>92086</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4926,34 +4926,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>1101</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>614774</v>
+        <v>614602</v>
       </c>
       <c r="R41" t="n">
-        <v>6560505</v>
+        <v>6560488</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5016,10 +5016,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131740334</v>
+        <v>131738986</v>
       </c>
       <c r="B42" t="n">
-        <v>93162</v>
+        <v>79895</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5027,21 +5027,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5448</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5051,10 +5051,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>614945</v>
+        <v>614832</v>
       </c>
       <c r="R42" t="n">
-        <v>6560495</v>
+        <v>6560556</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5117,10 +5117,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131737733</v>
+        <v>131739037</v>
       </c>
       <c r="B43" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5128,34 +5128,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>614695</v>
+        <v>615086</v>
       </c>
       <c r="R43" t="n">
-        <v>6560413</v>
+        <v>6560375</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5218,10 +5218,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131737764</v>
+        <v>131739024</v>
       </c>
       <c r="B44" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5229,38 +5229,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>614836</v>
+        <v>614774</v>
       </c>
       <c r="R44" t="n">
-        <v>6560376</v>
+        <v>6560505</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5293,11 +5289,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5328,45 +5319,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131737713</v>
+        <v>131736787</v>
       </c>
       <c r="B45" t="n">
-        <v>93174</v>
+        <v>92220</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>2062</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>614935</v>
+        <v>614622</v>
       </c>
       <c r="R45" t="n">
-        <v>6560472</v>
+        <v>6560528</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5393,12 +5384,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5429,10 +5420,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131736037</v>
+        <v>131736576</v>
       </c>
       <c r="B46" t="n">
-        <v>92086</v>
+        <v>93152</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5440,34 +5431,38 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1101</v>
+        <v>2059</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>614602</v>
+        <v>614640</v>
       </c>
       <c r="R46" t="n">
-        <v>6560488</v>
+        <v>6560409</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5494,12 +5489,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>9 st</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5530,10 +5530,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131739023</v>
+        <v>131740368</v>
       </c>
       <c r="B47" t="n">
-        <v>79895</v>
+        <v>93165</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5541,34 +5541,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>614757</v>
+        <v>614772</v>
       </c>
       <c r="R47" t="n">
-        <v>6560461</v>
+        <v>6560415</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5603,12 +5603,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5631,10 +5637,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131740368</v>
+        <v>131740341</v>
       </c>
       <c r="B48" t="n">
-        <v>93165</v>
+        <v>93162</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5642,34 +5648,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>614772</v>
+        <v>614963</v>
       </c>
       <c r="R48" t="n">
-        <v>6560415</v>
+        <v>6560256</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5696,17 +5706,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8 st</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5715,7 +5725,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5738,10 +5747,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131740341</v>
+        <v>131737612</v>
       </c>
       <c r="B49" t="n">
-        <v>93162</v>
+        <v>93174</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5749,38 +5758,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>614963</v>
+        <v>614843</v>
       </c>
       <c r="R49" t="n">
-        <v>6560256</v>
+        <v>6560521</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5807,17 +5812,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>8 st</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5848,7 +5848,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737612</v>
+        <v>131737613</v>
       </c>
       <c r="B50" t="n">
         <v>93174</v>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>614843</v>
+        <v>614811</v>
       </c>
       <c r="R50" t="n">
-        <v>6560521</v>
+        <v>6560570</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5949,7 +5949,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737613</v>
+        <v>131737728</v>
       </c>
       <c r="B51" t="n">
         <v>93174</v>
@@ -5977,17 +5977,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>614811</v>
+        <v>614659</v>
       </c>
       <c r="R51" t="n">
-        <v>6560570</v>
+        <v>6560444</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6014,12 +6018,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6050,7 +6059,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131737728</v>
+        <v>131737608</v>
       </c>
       <c r="B52" t="n">
         <v>93174</v>
@@ -6078,21 +6087,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>614659</v>
+        <v>614654</v>
       </c>
       <c r="R52" t="n">
-        <v>6560444</v>
+        <v>6560489</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6119,17 +6124,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6160,7 +6160,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131737608</v>
+        <v>131737734</v>
       </c>
       <c r="B53" t="n">
         <v>93174</v>
@@ -6188,17 +6188,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>614654</v>
+        <v>614708</v>
       </c>
       <c r="R53" t="n">
-        <v>6560489</v>
+        <v>6560403</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6225,12 +6229,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6261,7 +6270,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131737734</v>
+        <v>131737760</v>
       </c>
       <c r="B54" t="n">
         <v>93174</v>
@@ -6291,7 +6300,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6300,10 +6309,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>614708</v>
+        <v>614880</v>
       </c>
       <c r="R54" t="n">
-        <v>6560403</v>
+        <v>6560400</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6340,7 +6349,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6371,10 +6380,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131737760</v>
+        <v>131739023</v>
       </c>
       <c r="B55" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6382,38 +6391,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>614880</v>
+        <v>614757</v>
       </c>
       <c r="R55" t="n">
-        <v>6560400</v>
+        <v>6560461</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6446,11 +6451,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6481,10 +6481,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131735736</v>
+        <v>131737712</v>
       </c>
       <c r="B56" t="n">
-        <v>92638</v>
+        <v>93174</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6492,38 +6492,38 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>366</v>
+        <v>5966</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>614666</v>
+        <v>614922</v>
       </c>
       <c r="R56" t="n">
-        <v>6560445</v>
+        <v>6560461</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6550,17 +6550,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>3 st</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6591,10 +6591,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131737712</v>
+        <v>131735736</v>
       </c>
       <c r="B57" t="n">
-        <v>93174</v>
+        <v>92638</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6602,38 +6602,38 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5966</v>
+        <v>366</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>614922</v>
+        <v>614666</v>
       </c>
       <c r="R57" t="n">
-        <v>6560461</v>
+        <v>6560445</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6660,17 +6660,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6912,45 +6912,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131736994</v>
+        <v>131734662</v>
       </c>
       <c r="B60" t="n">
-        <v>91333</v>
+        <v>79033</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2051</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>615157</v>
+        <v>614665</v>
       </c>
       <c r="R60" t="n">
-        <v>6560412</v>
+        <v>6560415</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6977,17 +6977,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ramaria XXL</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7657,10 +7652,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131734255</v>
+        <v>131736994</v>
       </c>
       <c r="B67" t="n">
-        <v>97385</v>
+        <v>91333</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7668,34 +7663,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>990</v>
+        <v>2051</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>614670</v>
+        <v>615157</v>
       </c>
       <c r="R67" t="n">
-        <v>6560435</v>
+        <v>6560412</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7722,12 +7717,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ramaria XXL</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7758,32 +7758,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131734662</v>
+        <v>131734255</v>
       </c>
       <c r="B68" t="n">
-        <v>79033</v>
+        <v>97385</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>990</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7793,10 +7793,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>614665</v>
+        <v>614670</v>
       </c>
       <c r="R68" t="n">
-        <v>6560415</v>
+        <v>6560435</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7823,12 +7823,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7859,45 +7859,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131739788</v>
+        <v>131740391</v>
       </c>
       <c r="B69" t="n">
-        <v>92571</v>
+        <v>93165</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3298</v>
+        <v>5449</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>615070</v>
+        <v>614945</v>
       </c>
       <c r="R69" t="n">
-        <v>6560325</v>
+        <v>6560479</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7924,12 +7924,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7938,6 +7943,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7960,37 +7966,37 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131740288</v>
+        <v>131740335</v>
       </c>
       <c r="B70" t="n">
-        <v>93124</v>
+        <v>93162</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>149</v>
+        <v>5448</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -7999,10 +8005,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>614871</v>
+        <v>614815</v>
       </c>
       <c r="R70" t="n">
-        <v>6560514</v>
+        <v>6560508</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8039,7 +8045,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8070,49 +8076,49 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131737261</v>
+        <v>131740288</v>
       </c>
       <c r="B71" t="n">
-        <v>93128</v>
+        <v>93124</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4361</v>
+        <v>149</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>614895</v>
+        <v>614871</v>
       </c>
       <c r="R71" t="n">
-        <v>6560392</v>
+        <v>6560514</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8139,17 +8145,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8180,10 +8186,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131740391</v>
+        <v>131737261</v>
       </c>
       <c r="B72" t="n">
-        <v>93165</v>
+        <v>93128</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8191,34 +8197,38 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>614945</v>
+        <v>614895</v>
       </c>
       <c r="R72" t="n">
-        <v>6560479</v>
+        <v>6560392</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8255,7 +8265,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>2 st</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8264,7 +8274,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8287,49 +8296,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131740335</v>
+        <v>131739788</v>
       </c>
       <c r="B73" t="n">
-        <v>93162</v>
+        <v>92571</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5448</v>
+        <v>3298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>614815</v>
+        <v>615070</v>
       </c>
       <c r="R73" t="n">
-        <v>6560508</v>
+        <v>6560325</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8356,17 +8361,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8397,49 +8397,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131736991</v>
+        <v>131737931</v>
       </c>
       <c r="B74" t="n">
-        <v>91333</v>
+        <v>8455</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2051</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>614736</v>
+        <v>614669</v>
       </c>
       <c r="R74" t="n">
-        <v>6560397</v>
+        <v>6560513</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8466,17 +8462,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>3 st</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8507,45 +8498,49 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131737931</v>
+        <v>131736991</v>
       </c>
       <c r="B75" t="n">
-        <v>8455</v>
+        <v>91333</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>2051</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>614669</v>
+        <v>614736</v>
       </c>
       <c r="R75" t="n">
-        <v>6560513</v>
+        <v>6560397</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8572,12 +8567,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9803,10 +9803,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131732767</v>
+        <v>131733475</v>
       </c>
       <c r="B87" t="n">
-        <v>93136</v>
+        <v>8444</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9814,34 +9814,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>106554</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>615105</v>
+        <v>614840</v>
       </c>
       <c r="R87" t="n">
-        <v>6560378</v>
+        <v>6560403</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9868,17 +9868,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Spritt i området</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10019,10 +10014,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131739025</v>
+        <v>131737724</v>
       </c>
       <c r="B89" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10030,34 +10025,38 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>614887</v>
+        <v>614765</v>
       </c>
       <c r="R89" t="n">
-        <v>6560423</v>
+        <v>6560506</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10090,6 +10089,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10120,7 +10124,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131737724</v>
+        <v>131737732</v>
       </c>
       <c r="B90" t="n">
         <v>93174</v>
@@ -10155,14 +10159,14 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>614765</v>
+        <v>614684</v>
       </c>
       <c r="R90" t="n">
-        <v>6560506</v>
+        <v>6560422</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10230,7 +10234,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131737732</v>
+        <v>131737718</v>
       </c>
       <c r="B91" t="n">
         <v>93174</v>
@@ -10265,14 +10269,14 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>614684</v>
+        <v>614844</v>
       </c>
       <c r="R91" t="n">
-        <v>6560422</v>
+        <v>6560496</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10340,10 +10344,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131737718</v>
+        <v>131740366</v>
       </c>
       <c r="B92" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10351,26 +10355,22 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -10379,10 +10379,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>614844</v>
+        <v>614682</v>
       </c>
       <c r="R92" t="n">
-        <v>6560496</v>
+        <v>6560491</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10428,6 +10428,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10450,10 +10451,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131740366</v>
+        <v>131737745</v>
       </c>
       <c r="B93" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10461,34 +10462,38 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>48</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>614682</v>
+        <v>614779</v>
       </c>
       <c r="R93" t="n">
-        <v>6560491</v>
+        <v>6560385</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10525,7 +10530,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10534,7 +10539,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10557,10 +10561,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131737745</v>
+        <v>131740392</v>
       </c>
       <c r="B94" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10568,38 +10572,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>614779</v>
+        <v>614832</v>
       </c>
       <c r="R94" t="n">
-        <v>6560385</v>
+        <v>6560458</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10626,17 +10626,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>10 st</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10645,6 +10645,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10667,10 +10668,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131740392</v>
+        <v>131740342</v>
       </c>
       <c r="B95" t="n">
-        <v>93165</v>
+        <v>93162</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10678,34 +10679,38 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>614832</v>
+        <v>614971</v>
       </c>
       <c r="R95" t="n">
-        <v>6560458</v>
+        <v>6560251</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10732,17 +10737,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>10 st</t>
+          <t>12 st</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10751,7 +10756,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10774,10 +10778,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131740342</v>
+        <v>131737045</v>
       </c>
       <c r="B96" t="n">
-        <v>93162</v>
+        <v>92147</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10785,38 +10789,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5448</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>614971</v>
+        <v>614622</v>
       </c>
       <c r="R96" t="n">
-        <v>6560251</v>
+        <v>6560529</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10849,11 +10849,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>12 st</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10884,10 +10879,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131733475</v>
+        <v>131732767</v>
       </c>
       <c r="B97" t="n">
-        <v>8444</v>
+        <v>93136</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10895,34 +10890,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106554</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>614840</v>
+        <v>615105</v>
       </c>
       <c r="R97" t="n">
-        <v>6560403</v>
+        <v>6560378</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10949,12 +10944,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Spritt i området</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10985,10 +10985,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131737045</v>
+        <v>131739025</v>
       </c>
       <c r="B98" t="n">
-        <v>92147</v>
+        <v>79895</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10996,34 +10996,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>614622</v>
+        <v>614887</v>
       </c>
       <c r="R98" t="n">
-        <v>6560529</v>
+        <v>6560423</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11050,12 +11050,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11086,45 +11086,49 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131736992</v>
+        <v>131737722</v>
       </c>
       <c r="B99" t="n">
-        <v>91333</v>
+        <v>93174</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2051</v>
+        <v>5966</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>614848</v>
+        <v>614773</v>
       </c>
       <c r="R99" t="n">
-        <v>6560378</v>
+        <v>6560515</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11151,12 +11155,17 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>1o</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11187,10 +11196,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131739042</v>
+        <v>131740395</v>
       </c>
       <c r="B100" t="n">
-        <v>79895</v>
+        <v>93165</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11198,34 +11207,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>614859</v>
+        <v>614715</v>
       </c>
       <c r="R100" t="n">
-        <v>6560517</v>
+        <v>6560514</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11260,12 +11269,18 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>6 st</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11288,10 +11303,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131739016</v>
+        <v>131740398</v>
       </c>
       <c r="B101" t="n">
-        <v>79895</v>
+        <v>93165</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11299,34 +11314,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>615035</v>
+        <v>614907</v>
       </c>
       <c r="R101" t="n">
-        <v>6560425</v>
+        <v>6560326</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11353,12 +11368,17 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11367,6 +11387,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11389,10 +11410,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131739017</v>
+        <v>131737757</v>
       </c>
       <c r="B102" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11400,34 +11421,38 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>615032</v>
+        <v>614887</v>
       </c>
       <c r="R102" t="n">
-        <v>6560425</v>
+        <v>6560362</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11460,6 +11485,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11490,7 +11520,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737722</v>
+        <v>131737776</v>
       </c>
       <c r="B103" t="n">
         <v>93174</v>
@@ -11520,19 +11550,19 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nord, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>614773</v>
+        <v>615009</v>
       </c>
       <c r="R103" t="n">
-        <v>6560515</v>
+        <v>6560307</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11569,7 +11599,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>1o</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11600,45 +11630,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131740395</v>
+        <v>131736992</v>
       </c>
       <c r="B104" t="n">
-        <v>93165</v>
+        <v>91333</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5449</v>
+        <v>2051</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Ramaria boreimaxima</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>614715</v>
+        <v>614848</v>
       </c>
       <c r="R104" t="n">
-        <v>6560514</v>
+        <v>6560378</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11665,17 +11695,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>6 st</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11684,7 +11709,6 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11707,10 +11731,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131740398</v>
+        <v>131739016</v>
       </c>
       <c r="B105" t="n">
-        <v>93165</v>
+        <v>79895</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11718,34 +11742,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>614907</v>
+        <v>615035</v>
       </c>
       <c r="R105" t="n">
-        <v>6560326</v>
+        <v>6560425</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11772,17 +11796,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>4 st</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11791,7 +11810,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11814,10 +11832,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131737757</v>
+        <v>131739042</v>
       </c>
       <c r="B106" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11825,38 +11843,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>614887</v>
+        <v>614859</v>
       </c>
       <c r="R106" t="n">
-        <v>6560362</v>
+        <v>6560517</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11883,17 +11897,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11924,10 +11933,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131737776</v>
+        <v>131739017</v>
       </c>
       <c r="B107" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11935,38 +11944,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nystugan Nord, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>615009</v>
+        <v>615032</v>
       </c>
       <c r="R107" t="n">
-        <v>6560307</v>
+        <v>6560425</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11999,11 +12004,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12034,10 +12034,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131732521</v>
+        <v>131737715</v>
       </c>
       <c r="B108" t="n">
-        <v>78942</v>
+        <v>93174</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12045,34 +12045,38 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>614661</v>
+        <v>614932</v>
       </c>
       <c r="R108" t="n">
-        <v>6560444</v>
+        <v>6560487</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12105,6 +12109,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12135,10 +12144,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131739021</v>
+        <v>131737780</v>
       </c>
       <c r="B109" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12146,34 +12155,38 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>614820</v>
+        <v>615164</v>
       </c>
       <c r="R109" t="n">
-        <v>6560501</v>
+        <v>6560465</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12206,6 +12219,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12438,10 +12456,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131737715</v>
+        <v>131732521</v>
       </c>
       <c r="B112" t="n">
-        <v>93174</v>
+        <v>78942</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12449,38 +12467,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>614932</v>
+        <v>614661</v>
       </c>
       <c r="R112" t="n">
-        <v>6560487</v>
+        <v>6560444</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12513,11 +12527,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12548,10 +12557,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131737780</v>
+        <v>131739021</v>
       </c>
       <c r="B113" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12559,38 +12568,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>615164</v>
+        <v>614820</v>
       </c>
       <c r="R113" t="n">
-        <v>6560465</v>
+        <v>6560501</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12623,11 +12628,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12658,10 +12658,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131739022</v>
+        <v>131737739</v>
       </c>
       <c r="B114" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12669,34 +12669,38 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>614790</v>
+        <v>614717</v>
       </c>
       <c r="R114" t="n">
-        <v>6560493</v>
+        <v>6560453</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12729,6 +12733,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12759,7 +12768,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131737739</v>
+        <v>131737752</v>
       </c>
       <c r="B115" t="n">
         <v>93174</v>
@@ -12789,7 +12798,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -12798,10 +12807,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>614717</v>
+        <v>614875</v>
       </c>
       <c r="R115" t="n">
-        <v>6560453</v>
+        <v>6560431</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12838,7 +12847,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12869,7 +12878,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131737752</v>
+        <v>131737766</v>
       </c>
       <c r="B116" t="n">
         <v>93174</v>
@@ -12899,19 +12908,19 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>614875</v>
+        <v>614826</v>
       </c>
       <c r="R116" t="n">
-        <v>6560431</v>
+        <v>6560351</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12948,7 +12957,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12979,49 +12988,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131737766</v>
+        <v>131733366</v>
       </c>
       <c r="B117" t="n">
-        <v>93174</v>
+        <v>92506</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>614826</v>
+        <v>615138</v>
       </c>
       <c r="R117" t="n">
-        <v>6560351</v>
+        <v>6560392</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13054,11 +13059,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13089,45 +13089,49 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131733366</v>
+        <v>131737710</v>
       </c>
       <c r="B118" t="n">
-        <v>92506</v>
+        <v>93174</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>615138</v>
+        <v>614961</v>
       </c>
       <c r="R118" t="n">
-        <v>6560392</v>
+        <v>6560414</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13160,6 +13164,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13190,10 +13199,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131737710</v>
+        <v>131739022</v>
       </c>
       <c r="B119" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13201,38 +13210,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>614961</v>
+        <v>614790</v>
       </c>
       <c r="R119" t="n">
-        <v>6560414</v>
+        <v>6560493</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13265,11 +13270,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13401,45 +13401,49 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131733476</v>
+        <v>131733306</v>
       </c>
       <c r="B121" t="n">
-        <v>8444</v>
+        <v>93130</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106554</v>
+        <v>4362</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>614831</v>
+        <v>614689</v>
       </c>
       <c r="R121" t="n">
-        <v>6560599</v>
+        <v>6560516</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13472,6 +13476,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>1 St</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13502,49 +13511,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131733306</v>
+        <v>131732765</v>
       </c>
       <c r="B122" t="n">
-        <v>93130</v>
+        <v>93136</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>614689</v>
+        <v>614878</v>
       </c>
       <c r="R122" t="n">
-        <v>6560516</v>
+        <v>6560511</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13581,7 +13586,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>1 St</t>
+          <t>Förekommer spritt rikligt</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13612,45 +13617,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131732765</v>
+        <v>131740365</v>
       </c>
       <c r="B123" t="n">
-        <v>93136</v>
+        <v>93165</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>614878</v>
+        <v>614741</v>
       </c>
       <c r="R123" t="n">
-        <v>6560511</v>
+        <v>6560508</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13677,17 +13682,17 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Förekommer spritt rikligt</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13696,6 +13701,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13718,10 +13724,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131739040</v>
+        <v>131737605</v>
       </c>
       <c r="B124" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13729,34 +13735,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>614705</v>
+        <v>614921</v>
       </c>
       <c r="R124" t="n">
-        <v>6560468</v>
+        <v>6560349</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13783,12 +13789,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13819,10 +13825,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131740365</v>
+        <v>131737753</v>
       </c>
       <c r="B125" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13830,22 +13836,26 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -13854,10 +13864,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>614741</v>
+        <v>614883</v>
       </c>
       <c r="R125" t="n">
-        <v>6560508</v>
+        <v>6560422</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13894,7 +13904,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13903,7 +13913,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13926,45 +13935,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131737605</v>
+        <v>131733367</v>
       </c>
       <c r="B126" t="n">
-        <v>93174</v>
+        <v>92506</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>614921</v>
+        <v>614939</v>
       </c>
       <c r="R126" t="n">
-        <v>6560349</v>
+        <v>6560438</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13991,12 +14000,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14027,7 +14036,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131737753</v>
+        <v>131737719</v>
       </c>
       <c r="B127" t="n">
         <v>93174</v>
@@ -14057,7 +14066,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -14066,10 +14075,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>614883</v>
+        <v>614817</v>
       </c>
       <c r="R127" t="n">
-        <v>6560422</v>
+        <v>6560509</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14106,7 +14115,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14137,45 +14146,49 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131733367</v>
+        <v>131737768</v>
       </c>
       <c r="B128" t="n">
-        <v>92506</v>
+        <v>93174</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>614939</v>
+        <v>614843</v>
       </c>
       <c r="R128" t="n">
-        <v>6560438</v>
+        <v>6560322</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14208,6 +14221,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14238,10 +14256,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131737719</v>
+        <v>131740367</v>
       </c>
       <c r="B129" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14249,26 +14267,22 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -14277,10 +14291,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>614817</v>
+        <v>614742</v>
       </c>
       <c r="R129" t="n">
-        <v>6560509</v>
+        <v>6560443</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14317,7 +14331,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14326,6 +14340,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -14348,7 +14363,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131737768</v>
+        <v>131737778</v>
       </c>
       <c r="B130" t="n">
         <v>93174</v>
@@ -14378,19 +14393,19 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>614843</v>
+        <v>615115</v>
       </c>
       <c r="R130" t="n">
-        <v>6560322</v>
+        <v>6560377</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14427,7 +14442,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14458,10 +14473,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131740367</v>
+        <v>131737741</v>
       </c>
       <c r="B131" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14469,22 +14484,26 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -14493,10 +14512,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>614742</v>
+        <v>614754</v>
       </c>
       <c r="R131" t="n">
-        <v>6560443</v>
+        <v>6560449</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14533,7 +14552,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14542,7 +14561,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14565,7 +14583,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131737778</v>
+        <v>131737751</v>
       </c>
       <c r="B132" t="n">
         <v>93174</v>
@@ -14595,19 +14613,19 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>615115</v>
+        <v>614860</v>
       </c>
       <c r="R132" t="n">
-        <v>6560377</v>
+        <v>6560430</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14644,7 +14662,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14675,7 +14693,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131737741</v>
+        <v>131737604</v>
       </c>
       <c r="B133" t="n">
         <v>93174</v>
@@ -14703,21 +14721,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>614754</v>
+        <v>615114</v>
       </c>
       <c r="R133" t="n">
-        <v>6560449</v>
+        <v>6560473</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14744,17 +14758,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14785,10 +14794,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131737751</v>
+        <v>131739040</v>
       </c>
       <c r="B134" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14796,38 +14805,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>614860</v>
+        <v>614705</v>
       </c>
       <c r="R134" t="n">
-        <v>6560430</v>
+        <v>6560468</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14854,17 +14859,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14895,45 +14895,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131737604</v>
+        <v>131733476</v>
       </c>
       <c r="B135" t="n">
-        <v>93174</v>
+        <v>8444</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5966</v>
+        <v>106554</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>615114</v>
+        <v>614831</v>
       </c>
       <c r="R135" t="n">
-        <v>6560473</v>
+        <v>6560599</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14960,12 +14960,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14996,45 +14996,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131739551</v>
+        <v>131737932</v>
       </c>
       <c r="B136" t="n">
-        <v>91848</v>
+        <v>8455</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>614622</v>
+        <v>615059</v>
       </c>
       <c r="R136" t="n">
-        <v>6560528</v>
+        <v>6560324</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15061,12 +15061,17 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Förekommer spritt på tallågor</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15097,49 +15102,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>131733304</v>
+        <v>131740304</v>
       </c>
       <c r="B137" t="n">
-        <v>93130</v>
+        <v>91341</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4362</v>
+        <v>256703</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>614759</v>
+        <v>615108</v>
       </c>
       <c r="R137" t="n">
-        <v>6560440</v>
+        <v>6560375</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15172,11 +15173,6 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>8 st</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15207,10 +15203,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>131740243</v>
+        <v>131737743</v>
       </c>
       <c r="B138" t="n">
-        <v>92780</v>
+        <v>93174</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15218,26 +15214,26 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -15246,10 +15242,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>614829</v>
+        <v>614731</v>
       </c>
       <c r="R138" t="n">
-        <v>6560371</v>
+        <v>6560390</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15286,7 +15282,7 @@
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15317,10 +15313,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>131737743</v>
+        <v>131740394</v>
       </c>
       <c r="B139" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15328,38 +15324,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q139" t="n">
         <v>614731</v>
       </c>
       <c r="R139" t="n">
-        <v>6560390</v>
+        <v>6560512</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15386,17 +15378,17 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 st</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15405,6 +15397,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -15427,10 +15420,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>131740394</v>
+        <v>131737707</v>
       </c>
       <c r="B140" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15438,34 +15431,38 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>614731</v>
+        <v>614934</v>
       </c>
       <c r="R140" t="n">
-        <v>6560512</v>
+        <v>6560422</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15492,17 +15489,17 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>1 st</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15511,7 +15508,6 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15534,7 +15530,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>131737707</v>
+        <v>131737748</v>
       </c>
       <c r="B141" t="n">
         <v>93174</v>
@@ -15564,19 +15560,19 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>614934</v>
+        <v>614792</v>
       </c>
       <c r="R141" t="n">
-        <v>6560422</v>
+        <v>6560431</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15613,7 +15609,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15644,10 +15640,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>131737748</v>
+        <v>131740402</v>
       </c>
       <c r="B142" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15655,38 +15651,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>614792</v>
+        <v>615135</v>
       </c>
       <c r="R142" t="n">
-        <v>6560431</v>
+        <v>6560485</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15713,17 +15705,17 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>Ca 25st</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15732,6 +15724,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15754,10 +15747,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>131740402</v>
+        <v>131740243</v>
       </c>
       <c r="B143" t="n">
-        <v>93165</v>
+        <v>92780</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15765,34 +15758,38 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5449</v>
+        <v>4745</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr"/>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>615135</v>
+        <v>614829</v>
       </c>
       <c r="R143" t="n">
-        <v>6560485</v>
+        <v>6560371</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15819,17 +15816,17 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ca 25st</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15838,7 +15835,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -15861,45 +15857,49 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>131737932</v>
+        <v>131733304</v>
       </c>
       <c r="B144" t="n">
-        <v>8455</v>
+        <v>93130</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106545</v>
+        <v>4362</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>615059</v>
+        <v>614759</v>
       </c>
       <c r="R144" t="n">
-        <v>6560324</v>
+        <v>6560440</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Förekommer spritt på tallågor</t>
+          <t>8 st</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15967,45 +15967,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>131740304</v>
+        <v>131739551</v>
       </c>
       <c r="B145" t="n">
-        <v>91341</v>
+        <v>91848</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>256703</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>615108</v>
+        <v>614622</v>
       </c>
       <c r="R145" t="n">
-        <v>6560375</v>
+        <v>6560528</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16032,12 +16032,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16068,10 +16068,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>131732523</v>
+        <v>131737727</v>
       </c>
       <c r="B146" t="n">
-        <v>78942</v>
+        <v>93174</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16079,34 +16079,38 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>614818</v>
+        <v>614657</v>
       </c>
       <c r="R146" t="n">
-        <v>6560356</v>
+        <v>6560454</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16133,12 +16137,17 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16169,7 +16178,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>131737727</v>
+        <v>131737726</v>
       </c>
       <c r="B147" t="n">
         <v>93174</v>
@@ -16199,7 +16208,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -16208,10 +16217,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>614657</v>
+        <v>614639</v>
       </c>
       <c r="R147" t="n">
-        <v>6560454</v>
+        <v>6560514</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16248,7 +16257,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16279,7 +16288,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>131737726</v>
+        <v>131737706</v>
       </c>
       <c r="B148" t="n">
         <v>93174</v>
@@ -16309,19 +16318,19 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>614639</v>
+        <v>615019</v>
       </c>
       <c r="R148" t="n">
-        <v>6560514</v>
+        <v>6560434</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16358,7 +16367,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16389,10 +16398,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>131737706</v>
+        <v>131740400</v>
       </c>
       <c r="B149" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16400,38 +16409,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>615019</v>
+        <v>614952</v>
       </c>
       <c r="R149" t="n">
-        <v>6560434</v>
+        <v>6560279</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16458,17 +16463,17 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16477,6 +16482,7 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -16499,10 +16505,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>131740400</v>
+        <v>131737264</v>
       </c>
       <c r="B150" t="n">
-        <v>93165</v>
+        <v>93128</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16510,34 +16516,38 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr"/>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>614952</v>
+        <v>615062</v>
       </c>
       <c r="R150" t="n">
-        <v>6560279</v>
+        <v>6560402</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16574,7 +16584,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>2 st</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16583,7 +16593,6 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16606,7 +16615,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>131737262</v>
+        <v>131737266</v>
       </c>
       <c r="B151" t="n">
         <v>93128</v>
@@ -16636,19 +16645,19 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>614741</v>
+        <v>615141</v>
       </c>
       <c r="R151" t="n">
-        <v>6560504</v>
+        <v>6560479</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16685,7 +16694,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>1 st</t>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16716,7 +16725,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>131737266</v>
+        <v>131737262</v>
       </c>
       <c r="B152" t="n">
         <v>93128</v>
@@ -16746,19 +16755,19 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>615141</v>
+        <v>614741</v>
       </c>
       <c r="R152" t="n">
-        <v>6560479</v>
+        <v>6560504</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16795,7 +16804,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>2 st</t>
+          <t>1 st</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16826,10 +16835,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>131737264</v>
+        <v>131732523</v>
       </c>
       <c r="B153" t="n">
-        <v>93128</v>
+        <v>78942</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16837,38 +16846,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>615062</v>
+        <v>614818</v>
       </c>
       <c r="R153" t="n">
-        <v>6560402</v>
+        <v>6560356</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16895,17 +16900,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>4 st</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16936,45 +16936,45 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>131732764</v>
+        <v>131740364</v>
       </c>
       <c r="B154" t="n">
-        <v>93136</v>
+        <v>93165</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>614871</v>
+        <v>614841</v>
       </c>
       <c r="R154" t="n">
-        <v>6560446</v>
+        <v>6560503</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17001,12 +17001,17 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17015,6 +17020,7 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -17037,10 +17043,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>131740364</v>
+        <v>131737777</v>
       </c>
       <c r="B155" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17048,34 +17054,38 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>614841</v>
+        <v>615134</v>
       </c>
       <c r="R155" t="n">
-        <v>6560503</v>
+        <v>6560409</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17112,7 +17122,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17121,7 +17131,6 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
-      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
@@ -17144,7 +17153,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>131737777</v>
+        <v>131737772</v>
       </c>
       <c r="B156" t="n">
         <v>93174</v>
@@ -17174,19 +17183,19 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>615134</v>
+        <v>614898</v>
       </c>
       <c r="R156" t="n">
-        <v>6560409</v>
+        <v>6560304</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17223,7 +17232,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17254,7 +17263,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>131737772</v>
+        <v>131737606</v>
       </c>
       <c r="B157" t="n">
         <v>93174</v>
@@ -17282,21 +17291,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>614898</v>
+        <v>614656</v>
       </c>
       <c r="R157" t="n">
-        <v>6560304</v>
+        <v>6560442</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17323,17 +17328,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17364,7 +17364,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>131737606</v>
+        <v>131737709</v>
       </c>
       <c r="B158" t="n">
         <v>93174</v>
@@ -17392,17 +17392,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>614656</v>
+        <v>614958</v>
       </c>
       <c r="R158" t="n">
-        <v>6560442</v>
+        <v>6560433</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17429,12 +17433,17 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17465,7 +17474,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>131737709</v>
+        <v>131737759</v>
       </c>
       <c r="B159" t="n">
         <v>93174</v>
@@ -17495,19 +17504,19 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>614958</v>
+        <v>614874</v>
       </c>
       <c r="R159" t="n">
-        <v>6560433</v>
+        <v>6560379</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17544,7 +17553,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17575,7 +17584,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>131737759</v>
+        <v>131737761</v>
       </c>
       <c r="B160" t="n">
         <v>93174</v>
@@ -17605,7 +17614,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -17614,10 +17623,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>614874</v>
+        <v>614870</v>
       </c>
       <c r="R160" t="n">
-        <v>6560379</v>
+        <v>6560397</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17654,7 +17663,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17685,7 +17694,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>131737761</v>
+        <v>131737755</v>
       </c>
       <c r="B161" t="n">
         <v>93174</v>
@@ -17715,19 +17724,19 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>614870</v>
+        <v>614894</v>
       </c>
       <c r="R161" t="n">
-        <v>6560397</v>
+        <v>6560431</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17764,7 +17773,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17795,7 +17804,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>131737755</v>
+        <v>131737611</v>
       </c>
       <c r="B162" t="n">
         <v>93174</v>
@@ -17823,21 +17832,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>614894</v>
+        <v>614822</v>
       </c>
       <c r="R162" t="n">
-        <v>6560431</v>
+        <v>6560500</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17864,17 +17869,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17905,7 +17905,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>131737611</v>
+        <v>131737763</v>
       </c>
       <c r="B163" t="n">
         <v>93174</v>
@@ -17933,17 +17933,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>614822</v>
+        <v>614847</v>
       </c>
       <c r="R163" t="n">
-        <v>6560500</v>
+        <v>6560380</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17970,12 +17974,17 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18006,49 +18015,45 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>131737763</v>
+        <v>131732764</v>
       </c>
       <c r="B164" t="n">
-        <v>93174</v>
+        <v>93136</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>614847</v>
+        <v>614871</v>
       </c>
       <c r="R164" t="n">
-        <v>6560380</v>
+        <v>6560446</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18075,17 +18080,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18116,10 +18116,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>131738710</v>
+        <v>131737767</v>
       </c>
       <c r="B165" t="n">
-        <v>97294</v>
+        <v>93174</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18127,34 +18127,38 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>614670</v>
+        <v>614840</v>
       </c>
       <c r="R165" t="n">
-        <v>6560435</v>
+        <v>6560354</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18181,12 +18185,17 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18217,49 +18226,45 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>131740287</v>
+        <v>131737720</v>
       </c>
       <c r="B166" t="n">
-        <v>93124</v>
+        <v>93174</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>149</v>
+        <v>5966</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>614868</v>
+        <v>614767</v>
       </c>
       <c r="R166" t="n">
-        <v>6560512</v>
+        <v>6560465</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18292,11 +18297,6 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18327,10 +18327,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>131737767</v>
+        <v>131740393</v>
       </c>
       <c r="B167" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18338,38 +18338,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>614840</v>
+        <v>614703</v>
       </c>
       <c r="R167" t="n">
-        <v>6560354</v>
+        <v>6560500</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18396,17 +18392,17 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18415,6 +18411,7 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -18437,7 +18434,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>131737720</v>
+        <v>131737735</v>
       </c>
       <c r="B168" t="n">
         <v>93174</v>
@@ -18465,17 +18462,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr"/>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>614767</v>
+        <v>614719</v>
       </c>
       <c r="R168" t="n">
-        <v>6560465</v>
+        <v>6560410</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18508,6 +18509,11 @@
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18538,10 +18544,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>131740393</v>
+        <v>131737609</v>
       </c>
       <c r="B169" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18549,34 +18555,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>614703</v>
+        <v>614698</v>
       </c>
       <c r="R169" t="n">
-        <v>6560500</v>
+        <v>6560522</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18603,17 +18609,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>2 st</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18622,7 +18623,6 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -18645,10 +18645,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>131737735</v>
+        <v>131738710</v>
       </c>
       <c r="B170" t="n">
-        <v>93174</v>
+        <v>97294</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18656,38 +18656,34 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>614719</v>
+        <v>614670</v>
       </c>
       <c r="R170" t="n">
-        <v>6560410</v>
+        <v>6560435</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18714,17 +18710,12 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18755,45 +18746,49 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>131737609</v>
+        <v>131740287</v>
       </c>
       <c r="B171" t="n">
-        <v>93174</v>
+        <v>93124</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5966</v>
+        <v>149</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
+          <t>(Peck) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>614698</v>
+        <v>614868</v>
       </c>
       <c r="R171" t="n">
-        <v>6560522</v>
+        <v>6560512</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18820,12 +18815,17 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD171" t="b">

--- a/artfynd/A 43282-2024 artfynd.xlsx
+++ b/artfynd/A 43282-2024 artfynd.xlsx
@@ -1745,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131737744</v>
+        <v>131740401</v>
       </c>
       <c r="B11" t="n">
-        <v>93215</v>
+        <v>93209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,38 +1756,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nord, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>614738</v>
+        <v>614969</v>
       </c>
       <c r="R11" t="n">
-        <v>6560381</v>
+        <v>6560271</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1814,17 +1810,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>22 st</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,6 +1829,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1855,10 +1852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131737716</v>
+        <v>131737729</v>
       </c>
       <c r="B12" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1883,21 +1880,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>614917</v>
+        <v>614639</v>
       </c>
       <c r="R12" t="n">
-        <v>6560491</v>
+        <v>6560401</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1930,11 +1923,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,10 +1953,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131740401</v>
+        <v>131740363</v>
       </c>
       <c r="B13" t="n">
-        <v>93206</v>
+        <v>93209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1991,19 +1979,19 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nystugan Nord, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>614969</v>
+        <v>614863</v>
       </c>
       <c r="R13" t="n">
-        <v>6560271</v>
+        <v>6560516</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2030,17 +2018,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>22 st</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,10 +2060,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131737729</v>
+        <v>131737744</v>
       </c>
       <c r="B14" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2100,17 +2088,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>614639</v>
+        <v>614738</v>
       </c>
       <c r="R14" t="n">
-        <v>6560401</v>
+        <v>6560381</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2143,6 +2135,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131740363</v>
+        <v>131737716</v>
       </c>
       <c r="B15" t="n">
-        <v>93206</v>
+        <v>93218</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2184,22 +2181,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2208,10 +2209,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>614863</v>
+        <v>614917</v>
       </c>
       <c r="R15" t="n">
-        <v>6560516</v>
+        <v>6560491</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2248,7 +2249,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,7 +2258,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>131737610</v>
       </c>
       <c r="B16" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>131738982</v>
       </c>
       <c r="B17" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>131739018</v>
       </c>
       <c r="B18" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131737607</v>
+        <v>131740240</v>
       </c>
       <c r="B19" t="n">
-        <v>93215</v>
+        <v>92824</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,34 +2594,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>614643</v>
+        <v>615041</v>
       </c>
       <c r="R19" t="n">
-        <v>6560479</v>
+        <v>6560443</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2684,10 +2684,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131740240</v>
+        <v>131737607</v>
       </c>
       <c r="B20" t="n">
-        <v>92821</v>
+        <v>93218</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,34 +2695,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615041</v>
+        <v>614643</v>
       </c>
       <c r="R20" t="n">
-        <v>6560443</v>
+        <v>6560479</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2788,7 +2788,7 @@
         <v>131732769</v>
       </c>
       <c r="B21" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>131736022</v>
       </c>
       <c r="B22" t="n">
-        <v>92328</v>
+        <v>92331</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>131740241</v>
       </c>
       <c r="B23" t="n">
-        <v>92821</v>
+        <v>92824</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>131737737</v>
       </c>
       <c r="B24" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>131737603</v>
       </c>
       <c r="B25" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>131737708</v>
       </c>
       <c r="B26" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>131737704</v>
       </c>
       <c r="B27" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3533,10 +3533,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131739020</v>
+        <v>131740362</v>
       </c>
       <c r="B28" t="n">
-        <v>79934</v>
+        <v>93209</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3544,34 +3544,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>614839</v>
+        <v>614974</v>
       </c>
       <c r="R28" t="n">
-        <v>6560502</v>
+        <v>6560411</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3606,12 +3606,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3634,10 +3640,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131738985</v>
+        <v>131737762</v>
       </c>
       <c r="B29" t="n">
-        <v>79934</v>
+        <v>93218</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3645,34 +3651,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>614827</v>
+        <v>614855</v>
       </c>
       <c r="R29" t="n">
-        <v>6560518</v>
+        <v>6560397</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3699,12 +3709,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3735,10 +3750,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131737762</v>
+        <v>131737779</v>
       </c>
       <c r="B30" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3765,19 +3780,19 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>614855</v>
+        <v>615173</v>
       </c>
       <c r="R30" t="n">
-        <v>6560397</v>
+        <v>6560476</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3814,7 +3829,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3845,10 +3860,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131737779</v>
+        <v>131737781</v>
       </c>
       <c r="B31" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3875,7 +3890,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3884,10 +3899,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615173</v>
+        <v>615158</v>
       </c>
       <c r="R31" t="n">
-        <v>6560476</v>
+        <v>6560491</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3924,7 +3939,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3955,10 +3970,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131737781</v>
+        <v>131737746</v>
       </c>
       <c r="B32" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3985,19 +4000,19 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615158</v>
+        <v>614777</v>
       </c>
       <c r="R32" t="n">
-        <v>6560491</v>
+        <v>6560432</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4034,7 +4049,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4065,10 +4080,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737746</v>
+        <v>131737750</v>
       </c>
       <c r="B33" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4095,7 +4110,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4104,10 +4119,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>614777</v>
+        <v>614846</v>
       </c>
       <c r="R33" t="n">
-        <v>6560432</v>
+        <v>6560435</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4144,7 +4159,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4175,10 +4190,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131740362</v>
+        <v>131737765</v>
       </c>
       <c r="B34" t="n">
-        <v>93206</v>
+        <v>93218</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4186,34 +4201,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>614974</v>
+        <v>614814</v>
       </c>
       <c r="R34" t="n">
-        <v>6560411</v>
+        <v>6560371</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4250,7 +4269,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4259,7 +4278,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4282,10 +4300,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131737750</v>
+        <v>131739020</v>
       </c>
       <c r="B35" t="n">
-        <v>93215</v>
+        <v>79936</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4293,38 +4311,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>614846</v>
+        <v>614839</v>
       </c>
       <c r="R35" t="n">
-        <v>6560435</v>
+        <v>6560502</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4357,11 +4371,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4392,10 +4401,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131737765</v>
+        <v>131738985</v>
       </c>
       <c r="B36" t="n">
-        <v>93215</v>
+        <v>79936</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4403,38 +4412,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>614814</v>
+        <v>614827</v>
       </c>
       <c r="R36" t="n">
-        <v>6560371</v>
+        <v>6560518</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4461,17 +4466,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4502,45 +4502,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131736787</v>
+        <v>131737733</v>
       </c>
       <c r="B37" t="n">
-        <v>92261</v>
+        <v>93218</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2062</v>
+        <v>5966</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>614622</v>
+        <v>614695</v>
       </c>
       <c r="R37" t="n">
-        <v>6560528</v>
+        <v>6560413</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4567,12 +4567,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4603,10 +4603,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131736576</v>
+        <v>131737764</v>
       </c>
       <c r="B38" t="n">
-        <v>93193</v>
+        <v>93218</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4614,21 +4614,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4638,14 +4638,14 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>614640</v>
+        <v>614836</v>
       </c>
       <c r="R38" t="n">
-        <v>6560409</v>
+        <v>6560376</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4672,17 +4672,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>9 st</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4713,32 +4713,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131736037</v>
+        <v>131736787</v>
       </c>
       <c r="B39" t="n">
-        <v>92127</v>
+        <v>92264</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1101</v>
+        <v>2062</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4748,10 +4748,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>614602</v>
+        <v>614622</v>
       </c>
       <c r="R39" t="n">
-        <v>6560488</v>
+        <v>6560528</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4778,12 +4778,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4814,10 +4814,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131740334</v>
+        <v>131736576</v>
       </c>
       <c r="B40" t="n">
-        <v>93203</v>
+        <v>93196</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4825,34 +4825,38 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5448</v>
+        <v>2059</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>614945</v>
+        <v>614640</v>
       </c>
       <c r="R40" t="n">
-        <v>6560495</v>
+        <v>6560409</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4879,12 +4883,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>9 st</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4915,10 +4924,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131737733</v>
+        <v>131740334</v>
       </c>
       <c r="B41" t="n">
-        <v>93215</v>
+        <v>93206</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4926,34 +4935,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>614695</v>
+        <v>614945</v>
       </c>
       <c r="R41" t="n">
-        <v>6560413</v>
+        <v>6560495</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5016,10 +5025,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131737764</v>
+        <v>131737713</v>
       </c>
       <c r="B42" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5044,21 +5053,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>614836</v>
+        <v>614935</v>
       </c>
       <c r="R42" t="n">
-        <v>6560376</v>
+        <v>6560472</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5091,11 +5096,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5126,10 +5126,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131737713</v>
+        <v>131736037</v>
       </c>
       <c r="B43" t="n">
-        <v>93215</v>
+        <v>92130</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5137,34 +5137,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5966</v>
+        <v>1101</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>614935</v>
+        <v>614602</v>
       </c>
       <c r="R43" t="n">
-        <v>6560472</v>
+        <v>6560488</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5230,7 +5230,7 @@
         <v>131738986</v>
       </c>
       <c r="B44" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>131739037</v>
       </c>
       <c r="B45" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>131739024</v>
       </c>
       <c r="B46" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5530,10 +5530,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131739023</v>
+        <v>131740368</v>
       </c>
       <c r="B47" t="n">
-        <v>79934</v>
+        <v>93209</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5541,34 +5541,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>614757</v>
+        <v>614772</v>
       </c>
       <c r="R47" t="n">
-        <v>6560461</v>
+        <v>6560415</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5603,12 +5603,18 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5631,7 +5637,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131740368</v>
+        <v>131740341</v>
       </c>
       <c r="B48" t="n">
         <v>93206</v>
@@ -5642,34 +5648,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>614772</v>
+        <v>614963</v>
       </c>
       <c r="R48" t="n">
-        <v>6560415</v>
+        <v>6560256</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5696,17 +5706,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8 st</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5715,7 +5725,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5738,10 +5747,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131740341</v>
+        <v>131737612</v>
       </c>
       <c r="B49" t="n">
-        <v>93203</v>
+        <v>93218</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5749,38 +5758,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>614963</v>
+        <v>614843</v>
       </c>
       <c r="R49" t="n">
-        <v>6560256</v>
+        <v>6560521</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5807,17 +5812,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>8 st</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5848,10 +5848,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737612</v>
+        <v>131737613</v>
       </c>
       <c r="B50" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>614843</v>
+        <v>614811</v>
       </c>
       <c r="R50" t="n">
-        <v>6560521</v>
+        <v>6560570</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5949,10 +5949,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737613</v>
+        <v>131737728</v>
       </c>
       <c r="B51" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5977,17 +5977,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>614811</v>
+        <v>614659</v>
       </c>
       <c r="R51" t="n">
-        <v>6560570</v>
+        <v>6560444</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6014,12 +6018,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6050,10 +6059,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131737728</v>
+        <v>131737608</v>
       </c>
       <c r="B52" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6078,21 +6087,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>614659</v>
+        <v>614654</v>
       </c>
       <c r="R52" t="n">
-        <v>6560444</v>
+        <v>6560489</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6119,17 +6124,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6160,10 +6160,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131737608</v>
+        <v>131737734</v>
       </c>
       <c r="B53" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6188,17 +6188,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>614654</v>
+        <v>614708</v>
       </c>
       <c r="R53" t="n">
-        <v>6560489</v>
+        <v>6560403</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6225,12 +6229,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6261,10 +6270,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131737734</v>
+        <v>131737760</v>
       </c>
       <c r="B54" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6291,7 +6300,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6300,10 +6309,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>614708</v>
+        <v>614880</v>
       </c>
       <c r="R54" t="n">
-        <v>6560403</v>
+        <v>6560400</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6340,7 +6349,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6371,10 +6380,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131737760</v>
+        <v>131739023</v>
       </c>
       <c r="B55" t="n">
-        <v>93215</v>
+        <v>79936</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6382,38 +6391,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>614880</v>
+        <v>614757</v>
       </c>
       <c r="R55" t="n">
-        <v>6560400</v>
+        <v>6560461</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6446,11 +6451,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6481,10 +6481,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131735736</v>
+        <v>131737712</v>
       </c>
       <c r="B56" t="n">
-        <v>92679</v>
+        <v>93218</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6492,38 +6492,38 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>366</v>
+        <v>5966</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>614666</v>
+        <v>614922</v>
       </c>
       <c r="R56" t="n">
-        <v>6560445</v>
+        <v>6560461</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6550,17 +6550,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>3 st</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6591,45 +6591,49 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131736812</v>
+        <v>131740242</v>
       </c>
       <c r="B57" t="n">
-        <v>93189</v>
+        <v>92824</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4366</v>
+        <v>4745</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>614856</v>
+        <v>614849</v>
       </c>
       <c r="R57" t="n">
-        <v>6560514</v>
+        <v>6560382</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6656,12 +6660,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6692,10 +6701,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131740242</v>
+        <v>131735736</v>
       </c>
       <c r="B58" t="n">
-        <v>92821</v>
+        <v>92682</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6703,38 +6712,38 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4745</v>
+        <v>366</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>614849</v>
+        <v>614666</v>
       </c>
       <c r="R58" t="n">
-        <v>6560382</v>
+        <v>6560445</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6761,17 +6770,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6802,49 +6811,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131737712</v>
+        <v>131736812</v>
       </c>
       <c r="B59" t="n">
-        <v>93215</v>
+        <v>93192</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>614922</v>
+        <v>614856</v>
       </c>
       <c r="R59" t="n">
-        <v>6560461</v>
+        <v>6560514</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6871,17 +6876,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6912,45 +6912,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131736994</v>
+        <v>131740397</v>
       </c>
       <c r="B60" t="n">
-        <v>91374</v>
+        <v>93209</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2051</v>
+        <v>5449</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>615157</v>
+        <v>614907</v>
       </c>
       <c r="R60" t="n">
-        <v>6560412</v>
+        <v>6560338</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6987,7 +6987,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ramaria XXL</t>
+          <t>5 st</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6996,6 +6996,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7018,10 +7019,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131740397</v>
+        <v>131737714</v>
       </c>
       <c r="B61" t="n">
-        <v>93206</v>
+        <v>93218</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7029,34 +7030,38 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>614907</v>
+        <v>614933</v>
       </c>
       <c r="R61" t="n">
-        <v>6560338</v>
+        <v>6560495</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7083,17 +7088,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>5 st</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7102,7 +7107,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7125,45 +7129,49 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131734255</v>
+        <v>131737717</v>
       </c>
       <c r="B62" t="n">
-        <v>97426</v>
+        <v>93218</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>990</v>
+        <v>5966</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>614670</v>
+        <v>614838</v>
       </c>
       <c r="R62" t="n">
-        <v>6560435</v>
+        <v>6560512</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7190,12 +7198,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7226,10 +7239,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131737717</v>
+        <v>131737749</v>
       </c>
       <c r="B63" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7256,7 +7269,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7265,10 +7278,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>614838</v>
+        <v>614849</v>
       </c>
       <c r="R63" t="n">
-        <v>6560512</v>
+        <v>6560446</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7305,7 +7318,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7336,45 +7349,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131734662</v>
+        <v>131736994</v>
       </c>
       <c r="B64" t="n">
-        <v>79072</v>
+        <v>91377</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>2051</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>614665</v>
+        <v>615157</v>
       </c>
       <c r="R64" t="n">
-        <v>6560415</v>
+        <v>6560412</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7401,12 +7414,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ramaria XXL</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7437,49 +7455,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131737749</v>
+        <v>131734255</v>
       </c>
       <c r="B65" t="n">
-        <v>93215</v>
+        <v>97429</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5966</v>
+        <v>990</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Warnst.) R.M.Schust.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>614849</v>
+        <v>614670</v>
       </c>
       <c r="R65" t="n">
-        <v>6560446</v>
+        <v>6560435</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7506,17 +7520,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>9</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7547,10 +7556,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131737714</v>
+        <v>131734662</v>
       </c>
       <c r="B66" t="n">
-        <v>93215</v>
+        <v>79074</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7558,38 +7567,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>614933</v>
+        <v>614665</v>
       </c>
       <c r="R66" t="n">
-        <v>6560495</v>
+        <v>6560415</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7616,17 +7621,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>60+</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7660,7 +7660,7 @@
         <v>131739019</v>
       </c>
       <c r="B67" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>131739038</v>
       </c>
       <c r="B68" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7859,10 +7859,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131737931</v>
+        <v>131739788</v>
       </c>
       <c r="B69" t="n">
-        <v>8455</v>
+        <v>92615</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7870,34 +7870,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>3298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>614669</v>
+        <v>615070</v>
       </c>
       <c r="R69" t="n">
-        <v>6560513</v>
+        <v>6560325</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7963,7 +7963,7 @@
         <v>131740288</v>
       </c>
       <c r="B70" t="n">
-        <v>93165</v>
+        <v>93168</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>131736991</v>
       </c>
       <c r="B71" t="n">
-        <v>91374</v>
+        <v>91377</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8180,10 +8180,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131737261</v>
+        <v>131740391</v>
       </c>
       <c r="B72" t="n">
-        <v>93169</v>
+        <v>93209</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8191,38 +8191,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>614895</v>
+        <v>614945</v>
       </c>
       <c r="R72" t="n">
-        <v>6560392</v>
+        <v>6560479</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8259,7 +8255,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8268,6 +8264,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8290,45 +8287,49 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131739788</v>
+        <v>131740335</v>
       </c>
       <c r="B73" t="n">
-        <v>92612</v>
+        <v>93206</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3298</v>
+        <v>5448</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>615070</v>
+        <v>614815</v>
       </c>
       <c r="R73" t="n">
-        <v>6560325</v>
+        <v>6560508</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8355,12 +8356,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8391,10 +8397,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131740391</v>
+        <v>131737261</v>
       </c>
       <c r="B74" t="n">
-        <v>93206</v>
+        <v>93172</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8402,34 +8408,38 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>614945</v>
+        <v>614895</v>
       </c>
       <c r="R74" t="n">
-        <v>6560479</v>
+        <v>6560392</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8466,7 +8476,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>2 st</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8475,7 +8485,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8498,49 +8507,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131740335</v>
+        <v>131737931</v>
       </c>
       <c r="B75" t="n">
-        <v>93203</v>
+        <v>8455</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5448</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>614815</v>
+        <v>614669</v>
       </c>
       <c r="R75" t="n">
-        <v>6560508</v>
+        <v>6560513</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8567,17 +8572,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8608,34 +8608,30 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131736990</v>
+        <v>131740369</v>
       </c>
       <c r="B76" t="n">
-        <v>91374</v>
+        <v>93209</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2051</v>
+        <v>5449</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>3</t>
@@ -8643,14 +8639,14 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>614738</v>
+        <v>615152</v>
       </c>
       <c r="R76" t="n">
-        <v>6560408</v>
+        <v>6560500</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8677,17 +8673,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>3 st</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8696,6 +8692,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8718,10 +8715,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131740369</v>
+        <v>131737725</v>
       </c>
       <c r="B77" t="n">
-        <v>93206</v>
+        <v>93218</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8729,19 +8726,23 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
           <t>3</t>
@@ -8749,14 +8750,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>615152</v>
+        <v>614660</v>
       </c>
       <c r="R77" t="n">
-        <v>6560500</v>
+        <v>6560511</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8802,7 +8803,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8825,10 +8825,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131737723</v>
+        <v>131740337</v>
       </c>
       <c r="B78" t="n">
-        <v>93215</v>
+        <v>93206</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8836,38 +8836,38 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>614756</v>
+        <v>614621</v>
       </c>
       <c r="R78" t="n">
-        <v>6560527</v>
+        <v>6560438</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8904,7 +8904,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15+</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8935,10 +8935,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131737756</v>
+        <v>131740396</v>
       </c>
       <c r="B79" t="n">
-        <v>93215</v>
+        <v>93209</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8946,38 +8946,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>614923</v>
+        <v>614785</v>
       </c>
       <c r="R79" t="n">
-        <v>6560410</v>
+        <v>6560564</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9004,17 +9000,17 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9023,6 +9019,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9045,10 +9042,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131737725</v>
+        <v>131737754</v>
       </c>
       <c r="B80" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9075,7 +9072,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9084,10 +9081,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>614660</v>
+        <v>614888</v>
       </c>
       <c r="R80" t="n">
-        <v>6560511</v>
+        <v>6560440</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9124,7 +9121,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9155,10 +9152,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131740337</v>
+        <v>131737723</v>
       </c>
       <c r="B81" t="n">
-        <v>93203</v>
+        <v>93218</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9166,38 +9163,38 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>614621</v>
+        <v>614756</v>
       </c>
       <c r="R81" t="n">
-        <v>6560438</v>
+        <v>6560527</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9234,7 +9231,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>15+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9265,10 +9262,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131737731</v>
+        <v>131737756</v>
       </c>
       <c r="B82" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9295,19 +9292,19 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>614674</v>
+        <v>614923</v>
       </c>
       <c r="R82" t="n">
-        <v>6560414</v>
+        <v>6560410</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9344,7 +9341,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9375,10 +9372,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131740396</v>
+        <v>131737731</v>
       </c>
       <c r="B83" t="n">
-        <v>93206</v>
+        <v>93218</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9386,19 +9383,23 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
           <t>4</t>
@@ -9406,14 +9407,14 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>614785</v>
+        <v>614674</v>
       </c>
       <c r="R83" t="n">
-        <v>6560564</v>
+        <v>6560414</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9440,17 +9441,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9459,7 +9460,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9485,7 +9485,7 @@
         <v>131737730</v>
       </c>
       <c r="B84" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9592,10 +9592,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131737754</v>
+        <v>131738984</v>
       </c>
       <c r="B85" t="n">
-        <v>93215</v>
+        <v>79936</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9603,38 +9603,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>614888</v>
+        <v>614801</v>
       </c>
       <c r="R85" t="n">
-        <v>6560440</v>
+        <v>6560517</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9661,17 +9657,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9702,45 +9693,49 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131738984</v>
+        <v>131736990</v>
       </c>
       <c r="B86" t="n">
-        <v>79934</v>
+        <v>91377</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>2051</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>614801</v>
+        <v>614738</v>
       </c>
       <c r="R86" t="n">
-        <v>6560517</v>
+        <v>6560408</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9767,12 +9762,17 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9803,10 +9803,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131740366</v>
+        <v>131737265</v>
       </c>
       <c r="B87" t="n">
-        <v>93206</v>
+        <v>93172</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9814,34 +9814,38 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>614682</v>
+        <v>615132</v>
       </c>
       <c r="R87" t="n">
-        <v>6560491</v>
+        <v>6560489</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9868,17 +9872,17 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9887,7 +9891,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9910,45 +9913,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131740392</v>
+        <v>131732767</v>
       </c>
       <c r="B88" t="n">
-        <v>93206</v>
+        <v>93180</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>614832</v>
+        <v>615105</v>
       </c>
       <c r="R88" t="n">
-        <v>6560458</v>
+        <v>6560378</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9975,17 +9978,17 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>10 st</t>
+          <t>Spritt i området</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9994,7 +9997,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -10017,10 +10019,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131740342</v>
+        <v>131737045</v>
       </c>
       <c r="B89" t="n">
-        <v>93203</v>
+        <v>92191</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10028,38 +10030,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5448</v>
+        <v>658</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>614971</v>
+        <v>614622</v>
       </c>
       <c r="R89" t="n">
-        <v>6560251</v>
+        <v>6560529</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10092,11 +10090,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>12 st</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10127,45 +10120,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131733475</v>
+        <v>131739025</v>
       </c>
       <c r="B90" t="n">
-        <v>8444</v>
+        <v>79936</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106554</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>614840</v>
+        <v>614887</v>
       </c>
       <c r="R90" t="n">
-        <v>6560403</v>
+        <v>6560423</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10192,12 +10185,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10228,10 +10221,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131737045</v>
+        <v>131740366</v>
       </c>
       <c r="B91" t="n">
-        <v>92188</v>
+        <v>93209</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10239,34 +10232,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>5449</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>614622</v>
+        <v>614682</v>
       </c>
       <c r="R91" t="n">
-        <v>6560529</v>
+        <v>6560491</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10293,12 +10286,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10307,6 +10305,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10329,10 +10328,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131737265</v>
+        <v>131740392</v>
       </c>
       <c r="B92" t="n">
-        <v>93169</v>
+        <v>93209</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10340,38 +10339,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>615132</v>
+        <v>614832</v>
       </c>
       <c r="R92" t="n">
-        <v>6560489</v>
+        <v>6560458</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10398,17 +10393,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>10 st</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10417,6 +10412,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10439,45 +10435,49 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131732767</v>
+        <v>131740342</v>
       </c>
       <c r="B93" t="n">
-        <v>93177</v>
+        <v>93206</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>615105</v>
+        <v>614971</v>
       </c>
       <c r="R93" t="n">
-        <v>6560378</v>
+        <v>6560251</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Spritt i området</t>
+          <t>12 st</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10548,7 +10548,7 @@
         <v>131737724</v>
       </c>
       <c r="B94" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>131737732</v>
       </c>
       <c r="B95" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>131737718</v>
       </c>
       <c r="B96" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>131737745</v>
       </c>
       <c r="B97" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10985,45 +10985,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131739025</v>
+        <v>131733475</v>
       </c>
       <c r="B98" t="n">
-        <v>79934</v>
+        <v>8444</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>106554</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>614887</v>
+        <v>614840</v>
       </c>
       <c r="R98" t="n">
-        <v>6560423</v>
+        <v>6560403</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11050,12 +11050,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11089,7 +11089,7 @@
         <v>131736992</v>
       </c>
       <c r="B99" t="n">
-        <v>91374</v>
+        <v>91377</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11187,10 +11187,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131737722</v>
+        <v>131740395</v>
       </c>
       <c r="B100" t="n">
-        <v>93215</v>
+        <v>93209</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11198,26 +11198,22 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11226,10 +11222,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>614773</v>
+        <v>614715</v>
       </c>
       <c r="R100" t="n">
-        <v>6560515</v>
+        <v>6560514</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11256,17 +11252,17 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>1o</t>
+          <t>6 st</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11275,6 +11271,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11297,10 +11294,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131740395</v>
+        <v>131740398</v>
       </c>
       <c r="B101" t="n">
-        <v>93206</v>
+        <v>93209</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11323,19 +11320,19 @@
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>614715</v>
+        <v>614907</v>
       </c>
       <c r="R101" t="n">
-        <v>6560514</v>
+        <v>6560326</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11372,7 +11369,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>6 st</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11404,10 +11401,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131740398</v>
+        <v>131737722</v>
       </c>
       <c r="B102" t="n">
-        <v>93206</v>
+        <v>93218</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11415,34 +11412,38 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>614907</v>
+        <v>614773</v>
       </c>
       <c r="R102" t="n">
-        <v>6560326</v>
+        <v>6560515</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11469,17 +11470,17 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>1o</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11488,7 +11489,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11514,7 +11514,7 @@
         <v>131737757</v>
       </c>
       <c r="B103" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         <v>131737776</v>
       </c>
       <c r="B104" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>131739042</v>
       </c>
       <c r="B105" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>131739016</v>
       </c>
       <c r="B106" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>131739017</v>
       </c>
       <c r="B107" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12037,7 +12037,7 @@
         <v>131736993</v>
       </c>
       <c r="B108" t="n">
-        <v>91374</v>
+        <v>91377</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>131740080</v>
       </c>
       <c r="B109" t="n">
-        <v>91910</v>
+        <v>91913</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12236,10 +12236,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131737715</v>
+        <v>131732521</v>
       </c>
       <c r="B110" t="n">
-        <v>93215</v>
+        <v>78983</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12247,38 +12247,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>614932</v>
+        <v>614661</v>
       </c>
       <c r="R110" t="n">
-        <v>6560487</v>
+        <v>6560444</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12311,11 +12307,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12346,10 +12337,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131737780</v>
+        <v>131739021</v>
       </c>
       <c r="B111" t="n">
-        <v>93215</v>
+        <v>79936</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12357,38 +12348,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>615164</v>
+        <v>614820</v>
       </c>
       <c r="R111" t="n">
-        <v>6560465</v>
+        <v>6560501</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12421,11 +12408,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12456,10 +12438,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131732521</v>
+        <v>131737715</v>
       </c>
       <c r="B112" t="n">
-        <v>78981</v>
+        <v>93218</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12467,34 +12449,38 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>614661</v>
+        <v>614932</v>
       </c>
       <c r="R112" t="n">
-        <v>6560444</v>
+        <v>6560487</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12527,6 +12513,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12557,10 +12548,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131739021</v>
+        <v>131737780</v>
       </c>
       <c r="B113" t="n">
-        <v>79934</v>
+        <v>93218</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12568,34 +12559,38 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>614820</v>
+        <v>615164</v>
       </c>
       <c r="R113" t="n">
-        <v>6560501</v>
+        <v>6560465</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12628,6 +12623,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12658,10 +12658,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131736464</v>
+        <v>131737752</v>
       </c>
       <c r="B114" t="n">
-        <v>57945</v>
+        <v>93218</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12669,34 +12669,38 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Nystugan Nord, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>614934</v>
+        <v>614875</v>
       </c>
       <c r="R114" t="n">
-        <v>6560353</v>
+        <v>6560431</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12723,12 +12727,17 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>29</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12762,7 +12771,7 @@
         <v>131737739</v>
       </c>
       <c r="B115" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12869,10 +12878,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131737752</v>
+        <v>131737766</v>
       </c>
       <c r="B116" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12899,19 +12908,19 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>614875</v>
+        <v>614826</v>
       </c>
       <c r="R116" t="n">
-        <v>6560431</v>
+        <v>6560351</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12948,7 +12957,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12979,49 +12988,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131737766</v>
+        <v>131733366</v>
       </c>
       <c r="B117" t="n">
-        <v>93215</v>
+        <v>92550</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>614826</v>
+        <v>615138</v>
       </c>
       <c r="R117" t="n">
-        <v>6560351</v>
+        <v>6560392</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13054,11 +13059,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13089,45 +13089,49 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131733366</v>
+        <v>131737710</v>
       </c>
       <c r="B118" t="n">
-        <v>92547</v>
+        <v>93218</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>615138</v>
+        <v>614961</v>
       </c>
       <c r="R118" t="n">
-        <v>6560392</v>
+        <v>6560414</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13160,6 +13164,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13190,10 +13199,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131737710</v>
+        <v>131739022</v>
       </c>
       <c r="B119" t="n">
-        <v>93215</v>
+        <v>79936</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13201,38 +13210,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>614961</v>
+        <v>614790</v>
       </c>
       <c r="R119" t="n">
-        <v>6560414</v>
+        <v>6560493</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13265,11 +13270,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13300,10 +13300,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131739022</v>
+        <v>131736464</v>
       </c>
       <c r="B120" t="n">
-        <v>79934</v>
+        <v>57945</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13311,34 +13311,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nord, Srm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>614790</v>
+        <v>614934</v>
       </c>
       <c r="R120" t="n">
-        <v>6560493</v>
+        <v>6560353</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13365,12 +13365,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13401,49 +13401,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131733306</v>
+        <v>131733476</v>
       </c>
       <c r="B121" t="n">
-        <v>93171</v>
+        <v>8444</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4362</v>
+        <v>106554</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>614689</v>
+        <v>614831</v>
       </c>
       <c r="R121" t="n">
-        <v>6560516</v>
+        <v>6560599</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13476,11 +13472,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>1 St</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13511,45 +13502,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131732765</v>
+        <v>131740365</v>
       </c>
       <c r="B122" t="n">
-        <v>93177</v>
+        <v>93209</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>614878</v>
+        <v>614741</v>
       </c>
       <c r="R122" t="n">
-        <v>6560511</v>
+        <v>6560508</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13576,17 +13567,17 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Förekommer spritt rikligt</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13595,6 +13586,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13617,10 +13609,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131739040</v>
+        <v>131737753</v>
       </c>
       <c r="B123" t="n">
-        <v>79934</v>
+        <v>93218</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13628,34 +13620,38 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>614705</v>
+        <v>614883</v>
       </c>
       <c r="R123" t="n">
-        <v>6560468</v>
+        <v>6560422</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13682,12 +13678,17 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13718,10 +13719,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131740365</v>
+        <v>131740367</v>
       </c>
       <c r="B124" t="n">
-        <v>93206</v>
+        <v>93209</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13744,7 +13745,7 @@
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -13753,10 +13754,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>614741</v>
+        <v>614742</v>
       </c>
       <c r="R124" t="n">
-        <v>6560508</v>
+        <v>6560443</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13793,7 +13794,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13825,10 +13826,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131737605</v>
+        <v>131737741</v>
       </c>
       <c r="B125" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13853,17 +13854,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>614921</v>
+        <v>614754</v>
       </c>
       <c r="R125" t="n">
-        <v>6560349</v>
+        <v>6560449</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13890,12 +13895,17 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13926,10 +13936,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131737753</v>
+        <v>131737751</v>
       </c>
       <c r="B126" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13956,7 +13966,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -13965,10 +13975,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>614883</v>
+        <v>614860</v>
       </c>
       <c r="R126" t="n">
-        <v>6560422</v>
+        <v>6560430</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14005,7 +14015,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14036,45 +14046,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131733367</v>
+        <v>131737605</v>
       </c>
       <c r="B127" t="n">
-        <v>92547</v>
+        <v>93218</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>614939</v>
+        <v>614921</v>
       </c>
       <c r="R127" t="n">
-        <v>6560438</v>
+        <v>6560349</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14101,12 +14111,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14137,49 +14147,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131737719</v>
+        <v>131733367</v>
       </c>
       <c r="B128" t="n">
-        <v>93215</v>
+        <v>92550</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>614817</v>
+        <v>614939</v>
       </c>
       <c r="R128" t="n">
-        <v>6560509</v>
+        <v>6560438</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14212,11 +14218,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14247,10 +14248,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131737768</v>
+        <v>131737719</v>
       </c>
       <c r="B129" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14277,19 +14278,19 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>614843</v>
+        <v>614817</v>
       </c>
       <c r="R129" t="n">
-        <v>6560322</v>
+        <v>6560509</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14326,7 +14327,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14357,10 +14358,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131740367</v>
+        <v>131737768</v>
       </c>
       <c r="B130" t="n">
-        <v>93206</v>
+        <v>93218</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14368,34 +14369,38 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>614742</v>
+        <v>614843</v>
       </c>
       <c r="R130" t="n">
-        <v>6560443</v>
+        <v>6560322</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14432,7 +14437,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14441,7 +14446,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -14467,7 +14471,7 @@
         <v>131737778</v>
       </c>
       <c r="B131" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14574,10 +14578,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131737741</v>
+        <v>131737604</v>
       </c>
       <c r="B132" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14602,21 +14606,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>614754</v>
+        <v>615114</v>
       </c>
       <c r="R132" t="n">
-        <v>6560449</v>
+        <v>6560473</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14643,17 +14643,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14684,10 +14679,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131737751</v>
+        <v>131733306</v>
       </c>
       <c r="B133" t="n">
-        <v>93215</v>
+        <v>93174</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14695,26 +14690,26 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -14723,10 +14718,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>614860</v>
+        <v>614689</v>
       </c>
       <c r="R133" t="n">
-        <v>6560430</v>
+        <v>6560516</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14753,17 +14748,17 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1 St</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14794,45 +14789,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131737604</v>
+        <v>131732765</v>
       </c>
       <c r="B134" t="n">
-        <v>93215</v>
+        <v>93180</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>615114</v>
+        <v>614878</v>
       </c>
       <c r="R134" t="n">
-        <v>6560473</v>
+        <v>6560511</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14859,12 +14854,17 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Förekommer spritt rikligt</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14895,32 +14895,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131733476</v>
+        <v>131739040</v>
       </c>
       <c r="B135" t="n">
-        <v>8444</v>
+        <v>79936</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106554</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14930,10 +14930,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>614831</v>
+        <v>614705</v>
       </c>
       <c r="R135" t="n">
-        <v>6560599</v>
+        <v>6560468</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14960,12 +14960,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14996,10 +14996,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131733304</v>
+        <v>131740243</v>
       </c>
       <c r="B136" t="n">
-        <v>93171</v>
+        <v>92824</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15007,38 +15007,38 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>614759</v>
+        <v>614829</v>
       </c>
       <c r="R136" t="n">
-        <v>6560440</v>
+        <v>6560371</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15065,17 +15065,17 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>8 st</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15106,10 +15106,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>131740243</v>
+        <v>131740394</v>
       </c>
       <c r="B137" t="n">
-        <v>92821</v>
+        <v>93209</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15117,23 +15117,19 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4745</v>
+        <v>5449</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Fr.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>1</t>
@@ -15141,14 +15137,14 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>614829</v>
+        <v>614731</v>
       </c>
       <c r="R137" t="n">
-        <v>6560371</v>
+        <v>6560512</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15175,17 +15171,17 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 st</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15194,6 +15190,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -15216,10 +15213,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>131739551</v>
+        <v>131737707</v>
       </c>
       <c r="B138" t="n">
-        <v>91889</v>
+        <v>93218</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15227,34 +15224,38 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>614622</v>
+        <v>614934</v>
       </c>
       <c r="R138" t="n">
-        <v>6560528</v>
+        <v>6560422</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15281,12 +15282,17 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15317,10 +15323,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>131737743</v>
+        <v>131737748</v>
       </c>
       <c r="B139" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15347,19 +15353,19 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>614731</v>
+        <v>614792</v>
       </c>
       <c r="R139" t="n">
-        <v>6560390</v>
+        <v>6560431</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15396,7 +15402,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15427,10 +15433,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>131740394</v>
+        <v>131740402</v>
       </c>
       <c r="B140" t="n">
-        <v>93206</v>
+        <v>93209</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15453,19 +15459,19 @@
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>614731</v>
+        <v>615135</v>
       </c>
       <c r="R140" t="n">
-        <v>6560512</v>
+        <v>6560485</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15502,7 +15508,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>1 st</t>
+          <t>Ca 25st</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15534,10 +15540,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>131737707</v>
+        <v>131737743</v>
       </c>
       <c r="B141" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15564,19 +15570,19 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>614934</v>
+        <v>614731</v>
       </c>
       <c r="R141" t="n">
-        <v>6560422</v>
+        <v>6560390</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15613,7 +15619,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15644,10 +15650,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>131737748</v>
+        <v>131733304</v>
       </c>
       <c r="B142" t="n">
-        <v>93215</v>
+        <v>93174</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15655,26 +15661,26 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -15683,10 +15689,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>614792</v>
+        <v>614759</v>
       </c>
       <c r="R142" t="n">
-        <v>6560431</v>
+        <v>6560440</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15713,17 +15719,17 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8 st</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15754,10 +15760,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>131740402</v>
+        <v>131739551</v>
       </c>
       <c r="B143" t="n">
-        <v>93206</v>
+        <v>91892</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15765,34 +15771,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5449</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>615135</v>
+        <v>614622</v>
       </c>
       <c r="R143" t="n">
-        <v>6560485</v>
+        <v>6560528</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15819,17 +15825,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Ca 25st</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15838,7 +15839,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -15970,7 +15970,7 @@
         <v>131740304</v>
       </c>
       <c r="B145" t="n">
-        <v>91382</v>
+        <v>91385</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16068,10 +16068,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>131732523</v>
+        <v>131737726</v>
       </c>
       <c r="B146" t="n">
-        <v>78981</v>
+        <v>93218</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16079,34 +16079,38 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>614818</v>
+        <v>614639</v>
       </c>
       <c r="R146" t="n">
-        <v>6560356</v>
+        <v>6560514</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16133,12 +16137,17 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16169,10 +16178,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>131737264</v>
+        <v>131737706</v>
       </c>
       <c r="B147" t="n">
-        <v>93169</v>
+        <v>93218</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16180,21 +16189,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -16208,10 +16217,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>615062</v>
+        <v>615019</v>
       </c>
       <c r="R147" t="n">
-        <v>6560402</v>
+        <v>6560434</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16238,17 +16247,17 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16279,10 +16288,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>131737266</v>
+        <v>131740400</v>
       </c>
       <c r="B148" t="n">
-        <v>93169</v>
+        <v>93209</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16290,23 +16299,19 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
           <t>2</t>
@@ -16314,14 +16319,14 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>615141</v>
+        <v>614952</v>
       </c>
       <c r="R148" t="n">
-        <v>6560479</v>
+        <v>6560279</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16367,6 +16372,7 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -16389,10 +16395,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>131737262</v>
+        <v>131732523</v>
       </c>
       <c r="B149" t="n">
-        <v>93169</v>
+        <v>78983</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16400,38 +16406,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>614741</v>
+        <v>614818</v>
       </c>
       <c r="R149" t="n">
-        <v>6560504</v>
+        <v>6560356</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16458,17 +16460,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>1 st</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16499,10 +16496,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>131737727</v>
+        <v>131737264</v>
       </c>
       <c r="B150" t="n">
-        <v>93215</v>
+        <v>93172</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16510,21 +16507,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -16534,14 +16531,14 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>614657</v>
+        <v>615062</v>
       </c>
       <c r="R150" t="n">
-        <v>6560454</v>
+        <v>6560402</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16568,17 +16565,17 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16609,10 +16606,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>131737726</v>
+        <v>131737266</v>
       </c>
       <c r="B151" t="n">
-        <v>93215</v>
+        <v>93172</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16620,38 +16617,38 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>614639</v>
+        <v>615141</v>
       </c>
       <c r="R151" t="n">
-        <v>6560514</v>
+        <v>6560479</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16678,17 +16675,17 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16719,10 +16716,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>131737706</v>
+        <v>131737262</v>
       </c>
       <c r="B152" t="n">
-        <v>93215</v>
+        <v>93172</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16730,38 +16727,38 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>615019</v>
+        <v>614741</v>
       </c>
       <c r="R152" t="n">
-        <v>6560434</v>
+        <v>6560504</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16788,17 +16785,17 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1 st</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16829,10 +16826,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>131740400</v>
+        <v>131737727</v>
       </c>
       <c r="B153" t="n">
-        <v>93206</v>
+        <v>93218</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16840,34 +16837,38 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>614952</v>
+        <v>614657</v>
       </c>
       <c r="R153" t="n">
-        <v>6560279</v>
+        <v>6560454</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16894,17 +16895,17 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>2 st</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16913,7 +16914,6 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -16939,7 +16939,7 @@
         <v>131740364</v>
       </c>
       <c r="B154" t="n">
-        <v>93206</v>
+        <v>93209</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17043,10 +17043,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>131737777</v>
+        <v>131737709</v>
       </c>
       <c r="B155" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -17082,10 +17082,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>615134</v>
+        <v>614958</v>
       </c>
       <c r="R155" t="n">
-        <v>6560409</v>
+        <v>6560433</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17153,49 +17153,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>131737772</v>
+        <v>131732764</v>
       </c>
       <c r="B156" t="n">
-        <v>93215</v>
+        <v>93180</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>614898</v>
+        <v>614871</v>
       </c>
       <c r="R156" t="n">
-        <v>6560304</v>
+        <v>6560446</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17222,17 +17218,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17263,10 +17254,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>131737606</v>
+        <v>131737777</v>
       </c>
       <c r="B157" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17291,17 +17282,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>614656</v>
+        <v>615134</v>
       </c>
       <c r="R157" t="n">
-        <v>6560442</v>
+        <v>6560409</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17328,12 +17323,17 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17364,10 +17364,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>131737709</v>
+        <v>131737772</v>
       </c>
       <c r="B158" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17394,19 +17394,19 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>614958</v>
+        <v>614898</v>
       </c>
       <c r="R158" t="n">
-        <v>6560433</v>
+        <v>6560304</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17443,7 +17443,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17474,10 +17474,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>131737759</v>
+        <v>131737606</v>
       </c>
       <c r="B159" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17502,21 +17502,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>614874</v>
+        <v>614656</v>
       </c>
       <c r="R159" t="n">
-        <v>6560379</v>
+        <v>6560442</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17543,17 +17539,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17584,10 +17575,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>131737761</v>
+        <v>131737759</v>
       </c>
       <c r="B160" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17614,7 +17605,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -17623,10 +17614,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>614870</v>
+        <v>614874</v>
       </c>
       <c r="R160" t="n">
-        <v>6560397</v>
+        <v>6560379</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17663,7 +17654,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17694,10 +17685,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>131737755</v>
+        <v>131737761</v>
       </c>
       <c r="B161" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17724,19 +17715,19 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>614894</v>
+        <v>614870</v>
       </c>
       <c r="R161" t="n">
-        <v>6560431</v>
+        <v>6560397</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17773,7 +17764,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17804,10 +17795,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>131737611</v>
+        <v>131737755</v>
       </c>
       <c r="B162" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17832,17 +17823,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>614822</v>
+        <v>614894</v>
       </c>
       <c r="R162" t="n">
-        <v>6560500</v>
+        <v>6560431</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17869,12 +17864,17 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17905,10 +17905,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>131737763</v>
+        <v>131737611</v>
       </c>
       <c r="B163" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17933,21 +17933,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>614847</v>
+        <v>614822</v>
       </c>
       <c r="R163" t="n">
-        <v>6560380</v>
+        <v>6560500</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17974,17 +17970,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18015,45 +18006,49 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>131732764</v>
+        <v>131737763</v>
       </c>
       <c r="B164" t="n">
-        <v>93177</v>
+        <v>93218</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>614871</v>
+        <v>614847</v>
       </c>
       <c r="R164" t="n">
-        <v>6560446</v>
+        <v>6560380</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18080,12 +18075,17 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18119,7 +18119,7 @@
         <v>131738710</v>
       </c>
       <c r="B165" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>131740287</v>
       </c>
       <c r="B166" t="n">
-        <v>93165</v>
+        <v>93168</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18327,10 +18327,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>131737767</v>
+        <v>131737720</v>
       </c>
       <c r="B167" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18355,21 +18355,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>614840</v>
+        <v>614767</v>
       </c>
       <c r="R167" t="n">
-        <v>6560354</v>
+        <v>6560465</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18402,11 +18398,6 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18437,10 +18428,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>131737720</v>
+        <v>131740393</v>
       </c>
       <c r="B168" t="n">
-        <v>93215</v>
+        <v>93209</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18448,34 +18439,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>614767</v>
+        <v>614703</v>
       </c>
       <c r="R168" t="n">
-        <v>6560465</v>
+        <v>6560500</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18502,12 +18493,17 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18516,6 +18512,7 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -18538,10 +18535,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>131740393</v>
+        <v>131737767</v>
       </c>
       <c r="B169" t="n">
-        <v>93206</v>
+        <v>93218</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18549,34 +18546,38 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>614703</v>
+        <v>614840</v>
       </c>
       <c r="R169" t="n">
-        <v>6560500</v>
+        <v>6560354</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18603,17 +18604,17 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>2 st</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18622,7 +18623,6 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -18648,7 +18648,7 @@
         <v>131737735</v>
       </c>
       <c r="B170" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>131737609</v>
       </c>
       <c r="B171" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18856,10 +18856,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>131737740</v>
+        <v>131732524</v>
       </c>
       <c r="B172" t="n">
-        <v>93215</v>
+        <v>78983</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18867,38 +18867,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>614746</v>
+        <v>614915</v>
       </c>
       <c r="R172" t="n">
-        <v>6560453</v>
+        <v>6560407</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18925,17 +18921,12 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18966,10 +18957,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>131737721</v>
+        <v>131737742</v>
       </c>
       <c r="B173" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18996,7 +18987,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -19005,10 +18996,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>614776</v>
+        <v>614738</v>
       </c>
       <c r="R173" t="n">
-        <v>6560488</v>
+        <v>6560442</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19045,7 +19036,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19076,10 +19067,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>131737775</v>
+        <v>131737721</v>
       </c>
       <c r="B174" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19106,19 +19097,19 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Nystugan Nord, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>614989</v>
+        <v>614776</v>
       </c>
       <c r="R174" t="n">
-        <v>6560288</v>
+        <v>6560488</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19155,7 +19146,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19186,10 +19177,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>131735737</v>
+        <v>131737775</v>
       </c>
       <c r="B175" t="n">
-        <v>92679</v>
+        <v>93218</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19197,38 +19188,38 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>366</v>
+        <v>5966</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nystugan Nord, Srm</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>615093</v>
+        <v>614989</v>
       </c>
       <c r="R175" t="n">
-        <v>6560461</v>
+        <v>6560288</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19255,17 +19246,17 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19296,10 +19287,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>131732524</v>
+        <v>131737738</v>
       </c>
       <c r="B176" t="n">
-        <v>78981</v>
+        <v>93218</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19307,34 +19298,38 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>614915</v>
+        <v>614711</v>
       </c>
       <c r="R176" t="n">
-        <v>6560407</v>
+        <v>6560481</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19361,12 +19356,17 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19397,10 +19397,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>131740359</v>
+        <v>131734664</v>
       </c>
       <c r="B177" t="n">
-        <v>93206</v>
+        <v>79074</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19408,34 +19408,34 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>614877</v>
+        <v>615034</v>
       </c>
       <c r="R177" t="n">
-        <v>6560513</v>
+        <v>6560418</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19462,17 +19462,12 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19481,7 +19476,6 @@
       <c r="AE177" t="b">
         <v>0</v>
       </c>
-      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
@@ -19504,10 +19498,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>131734664</v>
+        <v>131734663</v>
       </c>
       <c r="B178" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19535,14 +19529,14 @@
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>615034</v>
+        <v>614679</v>
       </c>
       <c r="R178" t="n">
-        <v>6560418</v>
+        <v>6560422</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19569,12 +19563,12 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19605,10 +19599,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>131737742</v>
+        <v>131740359</v>
       </c>
       <c r="B179" t="n">
-        <v>93215</v>
+        <v>93209</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19616,26 +19610,22 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -19644,10 +19634,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>614738</v>
+        <v>614877</v>
       </c>
       <c r="R179" t="n">
-        <v>6560442</v>
+        <v>6560513</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19674,17 +19664,17 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19693,6 +19683,7 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
+      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>
@@ -19715,10 +19706,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>131734663</v>
+        <v>131737740</v>
       </c>
       <c r="B180" t="n">
-        <v>79072</v>
+        <v>93218</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19726,34 +19717,38 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>614679</v>
+        <v>614746</v>
       </c>
       <c r="R180" t="n">
-        <v>6560422</v>
+        <v>6560453</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19780,12 +19775,17 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19816,10 +19816,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>131737738</v>
+        <v>131740399</v>
       </c>
       <c r="B181" t="n">
-        <v>93215</v>
+        <v>93209</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19827,38 +19827,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>614711</v>
+        <v>614904</v>
       </c>
       <c r="R181" t="n">
-        <v>6560481</v>
+        <v>6560330</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19885,17 +19881,17 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5 st</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19904,6 +19900,7 @@
       <c r="AE181" t="b">
         <v>0</v>
       </c>
+      <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="b">
         <v>0</v>
       </c>
@@ -19926,10 +19923,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>131740399</v>
+        <v>131735737</v>
       </c>
       <c r="B182" t="n">
-        <v>93206</v>
+        <v>92682</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19937,34 +19934,38 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>5449</v>
+        <v>366</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr"/>
+          <t>Artomyces pyxidatus</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>614904</v>
+        <v>615093</v>
       </c>
       <c r="R182" t="n">
-        <v>6560330</v>
+        <v>6560461</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19991,17 +19992,17 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>5 st</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20010,7 +20011,6 @@
       <c r="AE182" t="b">
         <v>0</v>
       </c>
-      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43282-2024 artfynd.xlsx
+++ b/artfynd/A 43282-2024 artfynd.xlsx
@@ -4502,10 +4502,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131737733</v>
+        <v>131740334</v>
       </c>
       <c r="B37" t="n">
-        <v>93218</v>
+        <v>93206</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4513,34 +4513,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>614695</v>
+        <v>614945</v>
       </c>
       <c r="R37" t="n">
-        <v>6560413</v>
+        <v>6560495</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4603,7 +4603,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131737764</v>
+        <v>131737713</v>
       </c>
       <c r="B38" t="n">
         <v>93218</v>
@@ -4631,21 +4631,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>614836</v>
+        <v>614935</v>
       </c>
       <c r="R38" t="n">
-        <v>6560376</v>
+        <v>6560472</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4678,11 +4674,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4713,45 +4704,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131736787</v>
+        <v>131737733</v>
       </c>
       <c r="B39" t="n">
-        <v>92264</v>
+        <v>93218</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2062</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>614622</v>
+        <v>614695</v>
       </c>
       <c r="R39" t="n">
-        <v>6560528</v>
+        <v>6560413</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4778,12 +4769,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4814,10 +4805,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131736576</v>
+        <v>131737764</v>
       </c>
       <c r="B40" t="n">
-        <v>93196</v>
+        <v>93218</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4825,21 +4816,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4849,14 +4840,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Toren Sydost, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>614640</v>
+        <v>614836</v>
       </c>
       <c r="R40" t="n">
-        <v>6560409</v>
+        <v>6560376</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4883,17 +4874,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>9 st</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4924,45 +4915,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131740334</v>
+        <v>131736787</v>
       </c>
       <c r="B41" t="n">
-        <v>93206</v>
+        <v>92264</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5448</v>
+        <v>2062</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>614945</v>
+        <v>614622</v>
       </c>
       <c r="R41" t="n">
-        <v>6560495</v>
+        <v>6560528</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4989,12 +4980,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5025,10 +5016,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131737713</v>
+        <v>131736576</v>
       </c>
       <c r="B42" t="n">
-        <v>93218</v>
+        <v>93196</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5036,34 +5027,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Toren Sydost, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>614935</v>
+        <v>614640</v>
       </c>
       <c r="R42" t="n">
-        <v>6560472</v>
+        <v>6560409</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5090,12 +5085,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>9 st</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -11086,45 +11086,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131736992</v>
+        <v>131740395</v>
       </c>
       <c r="B99" t="n">
-        <v>91377</v>
+        <v>93209</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2051</v>
+        <v>5449</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>614848</v>
+        <v>614715</v>
       </c>
       <c r="R99" t="n">
-        <v>6560378</v>
+        <v>6560514</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11151,12 +11151,17 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>6 st</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11165,6 +11170,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11187,7 +11193,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131740395</v>
+        <v>131740398</v>
       </c>
       <c r="B100" t="n">
         <v>93209</v>
@@ -11213,19 +11219,19 @@
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Pipmossen Sydväst, Srm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>614715</v>
+        <v>614907</v>
       </c>
       <c r="R100" t="n">
-        <v>6560514</v>
+        <v>6560326</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11262,7 +11268,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>6 st</t>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11294,45 +11300,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131740398</v>
+        <v>131736992</v>
       </c>
       <c r="B101" t="n">
-        <v>93209</v>
+        <v>91377</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5449</v>
+        <v>2051</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Ramaria boreimaxima</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Pipmossen Sydväst, Srm</t>
+          <t>Pipmossen Väst, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>614907</v>
+        <v>614848</v>
       </c>
       <c r="R101" t="n">
-        <v>6560326</v>
+        <v>6560378</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11359,17 +11365,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>4 st</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11378,7 +11379,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -12658,10 +12658,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131737752</v>
+        <v>131739022</v>
       </c>
       <c r="B114" t="n">
-        <v>93218</v>
+        <v>79936</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12669,38 +12669,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>614875</v>
+        <v>614790</v>
       </c>
       <c r="R114" t="n">
-        <v>6560431</v>
+        <v>6560493</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12733,11 +12729,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12768,10 +12759,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131737739</v>
+        <v>131736464</v>
       </c>
       <c r="B115" t="n">
-        <v>93218</v>
+        <v>57945</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12779,38 +12770,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nord, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>614717</v>
+        <v>614934</v>
       </c>
       <c r="R115" t="n">
-        <v>6560453</v>
+        <v>6560353</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12837,17 +12824,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12878,7 +12860,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131737766</v>
+        <v>131737752</v>
       </c>
       <c r="B116" t="n">
         <v>93218</v>
@@ -12908,19 +12890,19 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Pipmossen Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>614826</v>
+        <v>614875</v>
       </c>
       <c r="R116" t="n">
-        <v>6560351</v>
+        <v>6560431</